--- a/data/PA_Journal_Digest_Archive.xlsx
+++ b/data/PA_Journal_Digest_Archive.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J219"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -510,43 +510,5882 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Justin P. Johnson; Greg Lockhart; Erick Yokomizo; Matthew W. Hurtienne</t>
+        </is>
+      </c>
       <c r="B2" s="2" t="n">
         <v>2026</v>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>A Pending Research Article</t>
+          <t>Organizational Resilience in Public Workforce Transitions: A Case Study of Continuity and Change under the DOGE Reforms</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Governance</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>서베이</t>
-        </is>
-      </c>
+          <t>Review of Public Personnel Administration</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>초록을 기반으로 생성한 테스트 요약</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>This abstract is now available and contains sufficient detail for the digest.</t>
-        </is>
-      </c>
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Tae Hyun Lim; Yu Jeong Hwang</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Does Office Type Determine Gendered Campaign Messages?</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Political Communication</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr"/>
+      <c r="F3" s="2" t="inlineStr"/>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr"/>
+      <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Guillermo M. Cejudo; Fernando Nieto-Morales</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Unpacking local government responsiveness to social media: evidence from Mexico</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Public Management Review</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr"/>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Na Tang; Wenjia Huang; Nana Huang; Mengyao Zhang</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>The Right Key for the Right Lock: How Government Response Methods and Demand Types Affect Citizen Satisfaction</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Public Administration</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr"/>
+      <c r="F5" s="2" t="inlineStr"/>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Matthew T. Pietryka; Amber E. Boydstun; Taylor N. Carlson</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Do Political Discussion Partners Share Policy Priorities and Policy Frames?</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Political Behavior</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="inlineStr"/>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Ali Karčić</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Credible Prejudice? When and Why Mainstream Party Adoption of Far-Right Rhetoric Weakens Anti-Prejudice Norms</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Political Behavior</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr"/>
+      <c r="F7" s="2" t="inlineStr"/>
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Ben Suykens; Johan Hvenmark; ChiaKo Hung; Aaron Van Steenlandt; Bram Verschuere</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Welfare State Convergence or Robustness? Comparing Nonprofit Marketization Patterns Across Belgium, Sweden and the United States</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Public Management Review</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr"/>
+      <c r="F8" s="2" t="inlineStr"/>
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Julie Beasley</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>The promises and pitfalls of AI in public service: a review of AI snake oil,</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>International Public Management Journal</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr"/>
+      <c r="F9" s="2" t="inlineStr"/>
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>André K. Rodarte</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>The Democratic Cost of Pursuing Virality: A Study into Parliamentary Communications</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Political Communication</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr"/>
+      <c r="F10" s="2" t="inlineStr"/>
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Austin M. McCrea; Nathan Favero</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Preferences for symbolic representation: identity, context, and selection of mental health providers</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>International Public Management Journal</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr"/>
+      <c r="F11" s="2" t="inlineStr"/>
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Jinah Yoo</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>How Citizens Perceive Public Service Performance: Do Reference Points Really Matter?</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Public Performance &amp; Management Review</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr"/>
+      <c r="F12" s="2" t="inlineStr"/>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Jingjing Cai; Kaisar Kaher</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>From co-production to value co-creation: NGOs as catalysts of cyclical public value in rural China</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Public Management Review</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr"/>
+      <c r="F13" s="2" t="inlineStr"/>
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Maria Gintova</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Fairness and equity in hybrid work: insights from the Ontario Public Service</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>International Public Management Journal</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr"/>
+      <c r="F14" s="2" t="inlineStr"/>
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>David Melamed; Jack G. R. Wippell; Eric W. Schoon; Ronald L. Breiger</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Turning Hazard Models Inside Out</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Political Analysis</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr"/>
+      <c r="F15" s="2" t="inlineStr"/>
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Zeki Sarigil; Ayşenur Dal</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>The Limits of Incumbent Blame Games in Times of Crisis: Experimental Evidence from Electoral Autocracy</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Political Behavior</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr"/>
+      <c r="F16" s="2" t="inlineStr"/>
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Ana Luiza Terra Costa Mathias; Rosa Maria Fischer</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Revisiting the political-social dimension of public value</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Public Management Review</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr"/>
+      <c r="F17" s="2" t="inlineStr"/>
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Siqi Chen; Jiaheng Ling</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Insider or outsider: negative performance feedback and top manager succession in the public sector</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Public Management Review</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr"/>
+      <c r="F18" s="2" t="inlineStr"/>
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Donald Moynihan</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>From Civic Tech to DOGE : The Role of Tech Movements in the American Administrative State</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Public Administration</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr"/>
+      <c r="F19" s="2" t="inlineStr"/>
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr"/>
+      <c r="J19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Maryam Zahmatkesh; Ian Kirkpatrick</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Brake or bridge? The dual impact of clientelism on hospital corporatization in Iran</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Public Management Review</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr"/>
+      <c r="F20" s="2" t="inlineStr"/>
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr"/>
+      <c r="J20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Olle Folke; Johanna Rickne</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>The seniority ceiling: Why some immigrants struggle to rise in political office</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>The Journal of Politics</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr"/>
+      <c r="F21" s="2" t="inlineStr"/>
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr"/>
+      <c r="I21" s="2" t="inlineStr"/>
+      <c r="J21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Edgar Mathevet; Lauriane Cailleux</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Evaluating the Effectiveness of Open‐Source LLMs for Automated Analysis of Multilingual Consultation Feedback: A Swiss Case Study</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Policy Studies Journal</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr"/>
+      <c r="F22" s="2" t="inlineStr"/>
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr"/>
+      <c r="I22" s="2" t="inlineStr"/>
+      <c r="J22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Ariel Hasell; Sedona Chinn</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Do Your Own Research: What Skepticism of Expertise Means for the News Media in the U.S.</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Political Communication</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr"/>
+      <c r="F23" s="2" t="inlineStr"/>
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr"/>
+      <c r="I23" s="2" t="inlineStr"/>
+      <c r="J23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Trystan Loustau; Ashley Fabrizio; Liane Young; Jordan Wylie; Stylianos Syropoulos</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Partisans misperceive and are influenced by dynamic norms</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Political Psychology</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr"/>
+      <c r="F24" s="2" t="inlineStr"/>
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr"/>
+      <c r="I24" s="2" t="inlineStr"/>
+      <c r="J24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Alex G. Gillett; Kevin D. Tennent; Michael Macaulay</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Introducing public management and global sporting mega-events: public value, ecosystems, learning and temporality</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Public Management Review</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr"/>
+      <c r="F25" s="2" t="inlineStr"/>
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr"/>
+      <c r="I25" s="2" t="inlineStr"/>
+      <c r="J25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Lingwei Cheng; Saerim Kim; Andrew Sullivan</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Data-Driven Collaboration in Mandated Networks: US Homelessness Services</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>International Journal of Public Administration</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr"/>
+      <c r="F26" s="2" t="inlineStr"/>
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr"/>
+      <c r="I26" s="2" t="inlineStr"/>
+      <c r="J26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Mathieu Molines; Martin Storme; Cathy Y. Guo</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>When police officers surrender: the effect of citizen incivility on withdrawal and turnover</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>International Public Management Journal</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr"/>
+      <c r="F27" s="2" t="inlineStr"/>
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr"/>
+      <c r="I27" s="2" t="inlineStr"/>
+      <c r="J27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Christopher Claassen</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Voting for Democracy? Testing Political-Cultural Constraints on Democratic Backsliding</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Public Opinion Quarterly</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr"/>
+      <c r="F28" s="2" t="inlineStr"/>
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr"/>
+      <c r="I28" s="2" t="inlineStr"/>
+      <c r="J28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Ben Merriman</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>The “Professional Mortality” Problem in Early City Management: A Study of Organized Denial</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Public Administration Review</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr"/>
+      <c r="F29" s="2" t="inlineStr"/>
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr"/>
+      <c r="I29" s="2" t="inlineStr"/>
+      <c r="J29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Xénia Farkas; Simon Lindgren</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>The Language of Democratic Resilience and Decline: A Comparative Study of Politicians’ Communication on Facebook in Sweden and Hungary</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Political Communication</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr"/>
+      <c r="F30" s="2" t="inlineStr"/>
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr"/>
+      <c r="I30" s="2" t="inlineStr"/>
+      <c r="J30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Albert Meijer; Lukas Lorenz; Isabelle Donatz‐Fest; Jan‐Luuk Hoff</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>Responsible Algorithmization in the Public Sector: A “Natural Perspective” Based on Ethnographic Research in Regulation, Policing, and Healthcare</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Public Administration</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr"/>
+      <c r="F31" s="2" t="inlineStr"/>
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr"/>
+      <c r="I31" s="2" t="inlineStr"/>
+      <c r="J31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Seung-Ho An; Suyeon Jo; Kenneth J Meier</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Public service equity and stakeholder satisfaction: evidence from 56 countries on how parents, teachers, and students respond to gender gaps in education</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>International Public Management Journal</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr"/>
+      <c r="F32" s="2" t="inlineStr"/>
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr"/>
+      <c r="I32" s="2" t="inlineStr"/>
+      <c r="J32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Tianyi Gao; Yixue Yao</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>Performance Feedback and Strategic Reporting—Evidence from China’s Government Work Report</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Public Performance &amp; Management Review</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr"/>
+      <c r="F33" s="2" t="inlineStr"/>
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr"/>
+      <c r="I33" s="2" t="inlineStr"/>
+      <c r="J33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Xiaoyu Wang; James L. Perry; Yuming Wang; Dingxiang Chen; Bangcheng Liu</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>Inspired to Serve: Exposure to Moral Models to Enhance Public Service Motivation</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Public Administration</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr"/>
+      <c r="F34" s="2" t="inlineStr"/>
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr"/>
+      <c r="I34" s="2" t="inlineStr"/>
+      <c r="J34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Rowie Huijbregts; Ellen van Bueren; Wouter Jan Verheul; Bert George</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>How context and tensions shape public values assessment: findings from a case study of a Dutch agency</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>International Public Management Journal</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr"/>
+      <c r="F35" s="2" t="inlineStr"/>
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr"/>
+      <c r="I35" s="2" t="inlineStr"/>
+      <c r="J35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Ahmed Mohammed Sayed Mostafa</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>How and When Does Negative Beneficiary Contact Relate to Service Behaviors? Unpacking the Roles of Prosocial Impact and Service-Oriented High-Performance Work Systems in Public Healthcare</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>International Public Management Journal</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr"/>
+      <c r="F36" s="2" t="inlineStr"/>
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr"/>
+      <c r="I36" s="2" t="inlineStr"/>
+      <c r="J36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Mike Farjam; Hendrik Meyer</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>From Antagonistic Talk to Cooperative Acts: The Effect of Polarization Cues on Newspaper Audiences</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Political Behavior</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr"/>
+      <c r="F37" s="2" t="inlineStr"/>
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr"/>
+      <c r="I37" s="2" t="inlineStr"/>
+      <c r="J37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Barbara Zyzak</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>Collaborative platforms in digital government: structural and cultural barriers to coordination</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>International Public Management Journal</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr"/>
+      <c r="F38" s="2" t="inlineStr"/>
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr"/>
+      <c r="I38" s="2" t="inlineStr"/>
+      <c r="J38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Ogadinma Enwereazu; Kaylyn Jackson Schiff; Tyler Girard; Alexander Wilhelm; Daniel S. Schiff</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>A Public Values Framework for AI Governance: Evidence From US Federal AI Policymaking</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Public Administration</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr"/>
+      <c r="F39" s="2" t="inlineStr"/>
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr"/>
+      <c r="I39" s="2" t="inlineStr"/>
+      <c r="J39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Nathan K. Chan; Jin X. Goh</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>Working hard to belong: Meritocratic ideology and deportation sentiments among Latino and Asian Americans</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Political Psychology</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr"/>
+      <c r="F40" s="2" t="inlineStr"/>
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr"/>
+      <c r="I40" s="2" t="inlineStr"/>
+      <c r="J40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Junqi Zhang</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>Still Women Help Women? Gender Congruence, Social Stereotypes, and Street-Level Discretionary Decision-Making</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>International Journal of Public Administration</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr"/>
+      <c r="F41" s="2" t="inlineStr"/>
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr"/>
+      <c r="I41" s="2" t="inlineStr"/>
+      <c r="J41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Michael W. Bauer; Daniel Kovarek; Bárbara Motta; Andrzej Schultz</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>Restoring the Deformed Administrative State? Bureaucratic Repair After Illiberal Rule</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Public Administration Review</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr"/>
+      <c r="F42" s="2" t="inlineStr"/>
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr"/>
+      <c r="I42" s="2" t="inlineStr"/>
+      <c r="J42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Fernando D. Domingos; Antonio D. R. E. Caluz; Michael Gibson; Vinícius M. Magnani</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>Investor Orientation and Commitment in Outcomes‐Based Public Service Contracts</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Public Administration Review</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr"/>
+      <c r="F43" s="2" t="inlineStr"/>
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr"/>
+      <c r="I43" s="2" t="inlineStr"/>
+      <c r="J43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Ann-Kristina Løkke; Daniel Skov Gregersen; Lotte Bøgh Andersen</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>Absenteeism and Presenteeism in Times of Change: The Role of Stress and Job Satisfaction</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Review of Public Personnel Administration</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr"/>
+      <c r="F44" s="2" t="inlineStr"/>
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr"/>
+      <c r="I44" s="2" t="inlineStr"/>
+      <c r="J44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Geert Brinkman; Arwin van Buuren; Suzan Christiaanse; Irene Fierloos; Wiesje Korf</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>Unlocking the transformative potential of design: reflections from practice on navigating barriers to designing for societal transformation</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Public Management Review</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr"/>
+      <c r="F45" s="2" t="inlineStr"/>
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr"/>
+      <c r="I45" s="2" t="inlineStr"/>
+      <c r="J45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Adalmir de Oliveira Gomes</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>Institutional Conversion and Digital Transformation in Local Governments: A Longitudinal Analysis of Trajectories</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Journal of Public Administration Research and Theory</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr"/>
+      <c r="F46" s="2" t="inlineStr"/>
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr"/>
+      <c r="I46" s="2" t="inlineStr"/>
+      <c r="J46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>Huanming Wang; Bing Ran</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>How Were Governance Pathways Formed for Public Service Co‐Production? A Contingency Perspective</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Public Administration</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr"/>
+      <c r="F47" s="2" t="inlineStr"/>
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr"/>
+      <c r="I47" s="2" t="inlineStr"/>
+      <c r="J47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Jonne Kamphorst; Horacio Larreguy</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>Get Out the Volunteer: Encouraging Diverse Political Party Activism</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Political Analysis</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr"/>
+      <c r="F48" s="2" t="inlineStr"/>
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr"/>
+      <c r="I48" s="2" t="inlineStr"/>
+      <c r="J48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>John Murphy; Alexander Coppock; Seth J. Hill; Lynn Vavreck</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>Do Emotional Ads Persuade? Evidence from Real-Time Campaign Advertising Experiments</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Political Communication</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr"/>
+      <c r="F49" s="2" t="inlineStr"/>
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr"/>
+      <c r="I49" s="2" t="inlineStr"/>
+      <c r="J49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Liu Chen; Tom Christensen; Xufeng Zhu</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>Balancing Particularism and Universalism in Welfare Policy: Insights From China's Hukou Reform</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Policy Studies Journal</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr"/>
+      <c r="F50" s="2" t="inlineStr"/>
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr"/>
+      <c r="I50" s="2" t="inlineStr"/>
+      <c r="J50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>Xue‐Fei Yan; Zhihao Ma</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>Revisiting the SciPop Scale: Measurement alignment, scoring rules, and cross‐context comparability</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Political Psychology</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr"/>
+      <c r="F51" s="2" t="inlineStr"/>
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr"/>
+      <c r="I51" s="2" t="inlineStr"/>
+      <c r="J51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>Sebastian Hemesath; Markus Tepe; Saja Aljuneidi-Dückino; Susanne Boll</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>Let the Machine Impose the Fine! Algorithmic Discretion with Negative Outcomes. Experimental Evidence from Germany</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>International Journal of Public Administration</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr"/>
+      <c r="F52" s="2" t="inlineStr"/>
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr"/>
+      <c r="I52" s="2" t="inlineStr"/>
+      <c r="J52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>Cheng Chen; Shuwei Zhang; Peng Wen; Yiting Zhang</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>A fish rots from the head down: unpacking the trickle-down effect of leaders’ unethical pro-organizational behaviour (UPB) in the Chinese public sector</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>Public Management Review</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr"/>
+      <c r="F53" s="2" t="inlineStr"/>
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr"/>
+      <c r="I53" s="2" t="inlineStr"/>
+      <c r="J53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>Seunghyun Kim</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>A Model of Agency Behavior in Participatory Budgeting: A Resource Dependence Perspective</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Journal of Public Administration Research and Theory</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr"/>
+      <c r="F54" s="2" t="inlineStr"/>
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr"/>
+      <c r="I54" s="2" t="inlineStr"/>
+      <c r="J54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>Nhung Nguyen; Luu Trong Tuan; Diep Nguyen; Dinh Cong Khai; Tuyen Nguyen</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>When tasks feel unjustified: effects of illegitimate tasks on public servants’ citizen-oriented boundary-spanning behaviours</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>Public Management Review</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr"/>
+      <c r="F55" s="2" t="inlineStr"/>
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr"/>
+      <c r="I55" s="2" t="inlineStr"/>
+      <c r="J55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>Akhil Jain; Nidhi Mishra; Rajalaxmi Kamath; Vinita S. Sahay; Teena Bharti</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>Understanding Meritocracy: From an Imagination of ‘Ideal’ to Producing ‘Myth’ and Beyond</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Administration &amp; Society</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr"/>
+      <c r="F56" s="2" t="inlineStr"/>
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr"/>
+      <c r="I56" s="2" t="inlineStr"/>
+      <c r="J56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>Ruth Dixon; Rozana Himaz; Maia King; Barbara Maria Piotrowska</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>Strategies for Public Administration Research: Insights From the Scholarship of Christopher Hood</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Public Administration</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr"/>
+      <c r="F57" s="2" t="inlineStr"/>
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr"/>
+      <c r="I57" s="2" t="inlineStr"/>
+      <c r="J57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Noel Hyndman; Mariannunziata Liguori</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>Performance-measurement systems as actors and boundary objects: a sociomaterial perspective to the provision of prison services</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Public Management Review</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr"/>
+      <c r="F58" s="2" t="inlineStr"/>
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr"/>
+      <c r="I58" s="2" t="inlineStr"/>
+      <c r="J58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>Daniel Zorrilla-Velazquez</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>NGO Selection in a Marketized Foreign Aid System: Evidence from USAID Contracts</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>International Journal of Public Administration</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr"/>
+      <c r="F59" s="2" t="inlineStr"/>
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr"/>
+      <c r="I59" s="2" t="inlineStr"/>
+      <c r="J59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>Zhuocheng Lu; Fei Fan; Zhennan Yang; Song Wang</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>How Artificial Intelligence Facilitates Collaborative Governance? Research on Mechanisms and Multi‐Dimensional Effects Based on Triple Entities</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Public Administration</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr"/>
+      <c r="F60" s="2" t="inlineStr"/>
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr"/>
+      <c r="I60" s="2" t="inlineStr"/>
+      <c r="J60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>Jopang Jopang; Syamsul Alam; Rahman Tandi; La Ode Muhammad Elwan</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>Functionalization Without Instruments: How Local Bureaucrats Make Sense of Unfinished Reform While Managing Public Services</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>International Journal of Public Administration</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr"/>
+      <c r="F61" s="2" t="inlineStr"/>
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr"/>
+      <c r="I61" s="2" t="inlineStr"/>
+      <c r="J61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>Chongmyoung Lee</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>Exploring the Associations Between Performance Information Use and Nonprofit Performance: The Mediating Role of Goal Clarity, Developmental Culture, and Organizational Capacity</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>International Journal of Public Administration</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr"/>
+      <c r="F62" s="2" t="inlineStr"/>
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr"/>
+      <c r="I62" s="2" t="inlineStr"/>
+      <c r="J62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>Ping Xu; Ling Zhu; Sebastian Ege</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>Evolving Contexts and Diverging Strategies: Federalism and the Politics of Immigrant Welfare Exclusion in the US</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>Policy Studies Journal</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr"/>
+      <c r="F63" s="2" t="inlineStr"/>
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr"/>
+      <c r="I63" s="2" t="inlineStr"/>
+      <c r="J63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Arturo Luna Cancino; Javier Reyes‐Martínez</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>Ethnoracial Characteristics and Police Abuse Within Mexico's Criminal Justice System</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Policy Studies Journal</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr"/>
+      <c r="F64" s="2" t="inlineStr"/>
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr"/>
+      <c r="I64" s="2" t="inlineStr"/>
+      <c r="J64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>Naoki Egami; Diana Da In Lee</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>Designing multi‐site studies for external validity: Site selection via synthetic purposive sampling</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>American Journal of Political Science</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr"/>
+      <c r="F65" s="2" t="inlineStr"/>
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr"/>
+      <c r="I65" s="2" t="inlineStr"/>
+      <c r="J65" s="2" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>Vedant Kaul; Ujwal Shankar</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>Accountability in Public Administration: A Review and Conceptual Integration</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>International Journal of Public Administration</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr"/>
+      <c r="F66" s="2" t="inlineStr"/>
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr"/>
+      <c r="I66" s="2" t="inlineStr"/>
+      <c r="J66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>Manon Koopman; Koen Migchelbrink; Leonie Heres</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>Why Politicians Misbehave: A Systematic Review of How Attributes of Political Office Affect Moral Decision‐Making and Behavior</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>Public Administration Review</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr"/>
+      <c r="F67" s="2" t="inlineStr"/>
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr"/>
+      <c r="I67" s="2" t="inlineStr"/>
+      <c r="J67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Ben Kizel; Nissim Cohen</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>Policy Entrepreneurs and Policy Change When Politicians Are Absent: The Inclusion of Autistic Individuals in Armed Forces</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Public Administration</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr"/>
+      <c r="F68" s="2" t="inlineStr"/>
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr"/>
+      <c r="I68" s="2" t="inlineStr"/>
+      <c r="J68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>Santhosh Juvvaka; Rupak Biswas</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>Connecting Philosophy and Public Administration: Directions of Inquiry—A Review</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>International Journal of Public Administration</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr"/>
+      <c r="F69" s="2" t="inlineStr"/>
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr"/>
+      <c r="I69" s="2" t="inlineStr"/>
+      <c r="J69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>Waldemiro Francisco Sorte Junior</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>Bounded Rationality and Public Policy: From Target Groups’ Behavior to Policymakers’ Constraints</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>International Journal of Public Administration</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr"/>
+      <c r="F70" s="2" t="inlineStr"/>
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr"/>
+      <c r="I70" s="2" t="inlineStr"/>
+      <c r="J70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>Daniel Large; Steven Wolf</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>Systemic Political Capacity and Regulatory Failure: Evidence From Proactive Conservation Under the Endangered Species Act</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Administration &amp; Society</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr"/>
+      <c r="F71" s="2" t="inlineStr"/>
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr"/>
+      <c r="I71" s="2" t="inlineStr"/>
+      <c r="J71" s="2" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>Ahmad Nur Hidayat; Nina Karlina; Ramadhan Pancasilawan; R. Widya Setiabudi Sumadinata</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>Digital Election Platforms, Administrative Performance, and the Accountability Squeeze: Recentralization by Design in Indonesia’s Regional Elections</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Public Performance &amp; Management Review</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr"/>
+      <c r="F72" s="2" t="inlineStr"/>
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr"/>
+      <c r="I72" s="2" t="inlineStr"/>
+      <c r="J72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>Vincent Brussee</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>Dead Ends and Policy Change in Chinese Experimental Governance</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr"/>
+      <c r="F73" s="2" t="inlineStr"/>
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr"/>
+      <c r="I73" s="2" t="inlineStr"/>
+      <c r="J73" s="2" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>Lukáš Lafférs; Jozef Michal Mintal; Ivan Sutóris</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>Correcting for Nonignorable Nonresponse Bias in Ordinal Observational Survey Data</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Political Analysis</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr"/>
+      <c r="F74" s="2" t="inlineStr"/>
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr"/>
+      <c r="I74" s="2" t="inlineStr"/>
+      <c r="J74" s="2" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>Louise Halberg Nielsen</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>Women Politicians’ Role Model Effects: The Influence of Shared Identities Beyond Gender</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>Political Behavior</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr"/>
+      <c r="F75" s="2" t="inlineStr"/>
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr"/>
+      <c r="I75" s="2" t="inlineStr"/>
+      <c r="J75" s="2" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>Joyce Kasing Tagal; Derek Ouyang; Daniel E. Ho</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>The Practice and Origins of Performance Measurement: Assessing the Sunnyvale Model, 1984–2023</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>Public Administration Review</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr"/>
+      <c r="F76" s="2" t="inlineStr"/>
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr"/>
+      <c r="I76" s="2" t="inlineStr"/>
+      <c r="J76" s="2" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>Olivier Rubin; Olov Hemmingsson; Evangelia Petridou; Jörgen Sparf</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>From Policy Legitimization to Blame Avoidance—Discursive Strategies During Denmark's Mink Culling Crisis</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>Policy Studies Journal</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr"/>
+      <c r="F77" s="2" t="inlineStr"/>
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr"/>
+      <c r="I77" s="2" t="inlineStr"/>
+      <c r="J77" s="2" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>Elizabeth Bell; Sebastian Jilke</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>Administrative Burden and the Access–Fraud Trade‐Off</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Journal of Policy Analysis and Management</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr"/>
+      <c r="F78" s="2" t="inlineStr"/>
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr"/>
+      <c r="I78" s="2" t="inlineStr"/>
+      <c r="J78" s="2" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>Pascal D. Koenig</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>Why Government Turns to AI – What Citizens Believe and How it Matters. Survey Evidence from Germany and the Netherlands</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>The American Review of Public Administration</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr"/>
+      <c r="F79" s="2" t="inlineStr"/>
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr"/>
+      <c r="I79" s="2" t="inlineStr"/>
+      <c r="J79" s="2" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>Kounghun Nam; Daniel Rudy</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>Managing Through Crisis: Understanding Personnel Stability in the States During Economic Downturns</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Public Performance &amp; Management Review</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr"/>
+      <c r="F80" s="2" t="inlineStr"/>
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr"/>
+      <c r="I80" s="2" t="inlineStr"/>
+      <c r="J80" s="2" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>Qing Li; Mengjie Yan; Yu Shi</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>Fiscal Competition, Intergovernmental Transfer, and Local Debt Management</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Public Performance &amp; Management Review</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr"/>
+      <c r="F81" s="2" t="inlineStr"/>
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr"/>
+      <c r="I81" s="2" t="inlineStr"/>
+      <c r="J81" s="2" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>Lauren Azevedo; Ratna B. Dougherty; Kaila Witkowski; Christa L. Remington</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>Culture as Administrative Infrastructure: Crisis Governance and Community Recovery After the Maui Wildfires</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>The American Review of Public Administration</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr"/>
+      <c r="F82" s="2" t="inlineStr"/>
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr"/>
+      <c r="I82" s="2" t="inlineStr"/>
+      <c r="J82" s="2" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>Johan Sandén</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>Autonomy in Prison: Street-Level Bureaucrats Re-Connecting with Their Purpose</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>International Journal of Public Administration</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr"/>
+      <c r="F83" s="2" t="inlineStr"/>
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr"/>
+      <c r="I83" s="2" t="inlineStr"/>
+      <c r="J83" s="2" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>Jonny Holmström</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t>Working with semantic machines: The role of semantic reconciliation in public sector data governance</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Government Information Quarterly</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr"/>
+      <c r="F84" s="2" t="inlineStr"/>
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr"/>
+      <c r="I84" s="2" t="inlineStr"/>
+      <c r="J84" s="2" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>Igor Garcia Ballhausen Sampaio; Eduardo de Oliveira Andrade; Sérgio de Souza Barbosa Fontes; Flávia Cristina Bernardini; José Viterbo</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t>Trustworthy AI in public administration: The PRO-Trust pipeline for ethical fraud detection in public procurement</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Government Information Quarterly</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr"/>
+      <c r="F85" s="2" t="inlineStr"/>
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr"/>
+      <c r="I85" s="2" t="inlineStr"/>
+      <c r="J85" s="2" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>Eva Sørensen; Jacob Torfing</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C86" s="3" t="inlineStr">
+        <is>
+          <t>The Role of Public Administrators in Building a Robust Liberal Democracy</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Public Administration Review</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr"/>
+      <c r="F86" s="2" t="inlineStr"/>
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr"/>
+      <c r="I86" s="2" t="inlineStr"/>
+      <c r="J86" s="2" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>Eliane Bucher; Itziar Castelló; Christian Fieseler</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C87" s="3" t="inlineStr">
+        <is>
+          <t>Normative entrainment through affect in national artificial intelligence strategies</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Government Information Quarterly</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr"/>
+      <c r="F87" s="2" t="inlineStr"/>
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr"/>
+      <c r="I87" s="2" t="inlineStr"/>
+      <c r="J87" s="2" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>Anne Goldmann; Sandra Plümer</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C88" s="3" t="inlineStr">
+        <is>
+          <t>Narrating the AI Act: Policy narratives on artificial intelligence, their construction, and evolution within the European Parliament</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Government Information Quarterly</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr"/>
+      <c r="F88" s="2" t="inlineStr"/>
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr"/>
+      <c r="I88" s="2" t="inlineStr"/>
+      <c r="J88" s="2" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>MICHAEL KISTNER; MICHAEL HESELTINE; ROBERT ALVAREZ; MAYA FITCH; LUCAS LOTHAMER; ELIZABETH SIMAS</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C89" s="3" t="inlineStr">
+        <is>
+          <t>Measuring Partisanship and Representation in Online Congressional Communications</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>American Political Science Review</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr"/>
+      <c r="F89" s="2" t="inlineStr"/>
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr"/>
+      <c r="I89" s="2" t="inlineStr"/>
+      <c r="J89" s="2" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>Oliver George Kayas; Efpraxia D. Zamani</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C90" s="3" t="inlineStr">
+        <is>
+          <t>Managerial resistance to digital workplace surveillance in a local government authority</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>Government Information Quarterly</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr"/>
+      <c r="F90" s="2" t="inlineStr"/>
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr"/>
+      <c r="I90" s="2" t="inlineStr"/>
+      <c r="J90" s="2" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>Michelle Allgood</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C91" s="3" t="inlineStr">
+        <is>
+          <t>Increasing Equitable Access in Public Service: A Descriptive Study About Accessible Materials</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Public Administration Review</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr"/>
+      <c r="F91" s="2" t="inlineStr"/>
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr"/>
+      <c r="I91" s="2" t="inlineStr"/>
+      <c r="J91" s="2" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>Christian Østergaard Madsen; Ulf Melin; Karl Kristian Larsson</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C92" s="3" t="inlineStr">
+        <is>
+          <t>Hybrid bureaucracy: The relationship between digital technologies and institutional arrangements in public welfare agencies</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Government Information Quarterly</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr"/>
+      <c r="F92" s="2" t="inlineStr"/>
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr"/>
+      <c r="I92" s="2" t="inlineStr"/>
+      <c r="J92" s="2" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>Jung Eun Kim; Kwan Nok Chan; Wai Fung Lam; Edward Kei Fung Chan</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C93" s="3" t="inlineStr">
+        <is>
+          <t>Government institutions and data custodianship over personal information: Comparing citizen preferences in Hong Kong and South Korea</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>Government Information Quarterly</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr"/>
+      <c r="F93" s="2" t="inlineStr"/>
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr"/>
+      <c r="I93" s="2" t="inlineStr"/>
+      <c r="J93" s="2" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>Jonathan Crusoe; Johan Magnusson; Johan Eklund</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C94" s="3" t="inlineStr">
+        <is>
+          <t>Digital maturity: Testing an existing framework through scale development</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>Government Information Quarterly</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr"/>
+      <c r="F94" s="2" t="inlineStr"/>
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr"/>
+      <c r="I94" s="2" t="inlineStr"/>
+      <c r="J94" s="2" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>Sara Thabit; Till Degkwitz; Mahardika Fadmastuti; Luca Mora</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C95" s="3" t="inlineStr">
+        <is>
+          <t>Decentralisation in public sector data platforms: A pathway to enhancing public value?</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Government Information Quarterly</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr"/>
+      <c r="F95" s="2" t="inlineStr"/>
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr"/>
+      <c r="I95" s="2" t="inlineStr"/>
+      <c r="J95" s="2" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>Battulga Buyannemekh; Dolores E. Luna; Sergio Picazo-Vela; Luis F. Luna-Reyes</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C96" s="3" t="inlineStr">
+        <is>
+          <t>Citizens' perspectives on administrative burden in digital government services</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>Government Information Quarterly</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr"/>
+      <c r="F96" s="2" t="inlineStr"/>
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr"/>
+      <c r="I96" s="2" t="inlineStr"/>
+      <c r="J96" s="2" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>MARKUS PRIOR; TALBOT M. ANDREWS</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C97" s="3" t="inlineStr">
+        <is>
+          <t>Are Voters Myopic or Looking for Improvement?</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>American Political Science Review</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr"/>
+      <c r="F97" s="2" t="inlineStr"/>
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr"/>
+      <c r="I97" s="2" t="inlineStr"/>
+      <c r="J97" s="2" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>Moritz Schmid; Jurgen Willems</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C98" s="3" t="inlineStr">
+        <is>
+          <t>AI for integrity: Predicting public servants' susceptibility to corruption via supervised machine learning</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Government Information Quarterly</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr"/>
+      <c r="F98" s="2" t="inlineStr"/>
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr"/>
+      <c r="I98" s="2" t="inlineStr"/>
+      <c r="J98" s="2" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>Sudong Kim</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C99" s="3" t="inlineStr">
+        <is>
+          <t>AI ambivalence and digital civic engagement: Dual pathways of hindrance and capability development</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Government Information Quarterly</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr"/>
+      <c r="F99" s="2" t="inlineStr"/>
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr"/>
+      <c r="I99" s="2" t="inlineStr"/>
+      <c r="J99" s="2" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>Katrine Skagen</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C100" s="3" t="inlineStr">
+        <is>
+          <t>Why Some Critical Junctures Lead Nowhere: Exploring Dynamic and Static Policy Paths</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr"/>
+      <c r="F100" s="2" t="inlineStr"/>
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr"/>
+      <c r="I100" s="2" t="inlineStr"/>
+      <c r="J100" s="2" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>Pablo P. Castello</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C101" s="3" t="inlineStr">
+        <is>
+          <t>The territorial rights of wild animals: Justification</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>American Journal of Political Science</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr"/>
+      <c r="F101" s="2" t="inlineStr"/>
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr"/>
+      <c r="I101" s="2" t="inlineStr"/>
+      <c r="J101" s="2" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>Tipeng Chen</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C102" s="3" t="inlineStr">
+        <is>
+          <t>Serving the Public as Civil Servants or Citizens? Public Employees’ Exposure to Public Participation, Job Satisfaction, and Volunteering</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>Review of Public Personnel Administration</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr"/>
+      <c r="F102" s="2" t="inlineStr"/>
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr"/>
+      <c r="I102" s="2" t="inlineStr"/>
+      <c r="J102" s="2" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>Sara Holland Levin; Rui Wang; Junwan Seo; Yi Yin Leong; Emma Bennett; Dongdong Yang; Zhuohui Yang; Matt Chen; Yini Zhang; Jiyoun Suk</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C103" s="3" t="inlineStr">
+        <is>
+          <t>From #StayWoke to “Culture Wars”: How Social Justice Discourse is Separately and Synergistically Politicized on Twitter and YouTube</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Political Communication</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr"/>
+      <c r="F103" s="2" t="inlineStr"/>
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr"/>
+      <c r="I103" s="2" t="inlineStr"/>
+      <c r="J103" s="2" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>Woo Chang Kang; Sunkyoung Park; Osbern Huang; Koh Iwabuchi; Tetsuro Kobayashi</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C104" s="3" t="inlineStr">
+        <is>
+          <t>Democratic Accountability in East Asia: A Comparative Experimental Study of Voter Responses to Norm Violations</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>Political Communication</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr"/>
+      <c r="F104" s="2" t="inlineStr"/>
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr"/>
+      <c r="I104" s="2" t="inlineStr"/>
+      <c r="J104" s="2" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>Imane Hijal-Moghrabi</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C105" s="3" t="inlineStr">
+        <is>
+          <t>Advancing the Sustainability Development Goals Through Workforce Professionalization in Public Procurement: The Case of Lebanon</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>Review of Public Personnel Administration</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr"/>
+      <c r="F105" s="2" t="inlineStr"/>
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr"/>
+      <c r="I105" s="2" t="inlineStr"/>
+      <c r="J105" s="2" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>Feng Yang; Lin Zhu</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C106" s="3" t="inlineStr">
+        <is>
+          <t>Social Norms, State Punishment, and Motivation Crowding in Anti‐Corruption Messaging: Experimental Evidence From China</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr"/>
+      <c r="F106" s="2" t="inlineStr"/>
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr"/>
+      <c r="I106" s="2" t="inlineStr"/>
+      <c r="J106" s="2" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>Suzanne Leland; Jaclyn Piatak; Zachary Mohr</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C107" s="3" t="inlineStr">
+        <is>
+          <t>Credit Attribution for Public Service Providers and Their Employees: Implications from Contracting Out</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>The American Review of Public Administration</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr"/>
+      <c r="F107" s="2" t="inlineStr"/>
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr"/>
+      <c r="I107" s="2" t="inlineStr"/>
+      <c r="J107" s="2" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>Karina Arias‐Yurisch; Karina Retamal‐Soto; Alejandro Espinosa‐Rada</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C108" s="3" t="inlineStr">
+        <is>
+          <t>Disclosing Power Dynamics in Metropolitan Governance: An Analysis of Network Micro‐Mechanisms of Change in an Evolving Inter‐Municipal Network</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>Policy Studies Journal</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr"/>
+      <c r="F108" s="2" t="inlineStr"/>
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr"/>
+      <c r="I108" s="2" t="inlineStr"/>
+      <c r="J108" s="2" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>Peter Luca Versteegen; Joseph B. Phillips; Lilliana Mason</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C109" s="3" t="inlineStr">
+        <is>
+          <t>Cool Citizens? How Affectively Unpolarized Citizens View and Participate in Democracy</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>Political Behavior</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr"/>
+      <c r="F109" s="2" t="inlineStr"/>
+      <c r="G109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="inlineStr"/>
+      <c r="I109" s="2" t="inlineStr"/>
+      <c r="J109" s="2" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>Ruben B. Mathisen</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C110" s="3" t="inlineStr">
+        <is>
+          <t>Coincidental Representation: How Congruence and Influence shape Public Satisfaction with Government</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>Political Behavior</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr"/>
+      <c r="F110" s="2" t="inlineStr"/>
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr"/>
+      <c r="I110" s="2" t="inlineStr"/>
+      <c r="J110" s="2" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>Sulikah Asmorowati; Violeta Schubert; Mary S. Mangai; Jusuf Irianto; Tri Yuniningsih; Saskia Intandivanty Kamalia Anggika; Wilujeng Dwi Windhiari</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C111" s="3" t="inlineStr">
+        <is>
+          <t>Toward a Gender Sensitive and Locally Rooted co‐Production Approach: Insights From Implementing Child Stunting Eradication Program in Indonesia</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>Public Administration Review</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr"/>
+      <c r="F111" s="2" t="inlineStr"/>
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr"/>
+      <c r="I111" s="2" t="inlineStr"/>
+      <c r="J111" s="2" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>Edmund Poku Adu; Julius A. Nukpezah</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C112" s="3" t="inlineStr">
+        <is>
+          <t>Coordination Costs and Homelessness Housing Form Choice</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>Public Administration Review</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr"/>
+      <c r="F112" s="2" t="inlineStr"/>
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr"/>
+      <c r="I112" s="2" t="inlineStr"/>
+      <c r="J112" s="2" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>Michal Plaček; Juraj Nemec; David Špaček; Eduard Bakoš</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C113" s="3" t="inlineStr">
+        <is>
+          <t>Can cooperation between a city and a region lead to a robust solution during a polycrisis? – the case of Czechia</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>Public Management Review</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr"/>
+      <c r="F113" s="2" t="inlineStr"/>
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr"/>
+      <c r="I113" s="2" t="inlineStr"/>
+      <c r="J113" s="2" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr"/>
+      <c r="B114" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C114" s="3" t="inlineStr">
+        <is>
+          <t>Issue Information</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>Public Administration Review</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr"/>
+      <c r="F114" s="2" t="inlineStr"/>
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr"/>
+      <c r="I114" s="2" t="inlineStr"/>
+      <c r="J114" s="2" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>Tor Erik Nyberg; Trond Løyning; Annett Arntzen</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C115" s="3" t="inlineStr">
+        <is>
+          <t>Cross-Sectoral Collaboration for Work Inclusion and the Governance Perspective: A Systematic Literature Review and Research Directions</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>International Journal of Public Administration</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr"/>
+      <c r="F115" s="2" t="inlineStr"/>
+      <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr"/>
+      <c r="I115" s="2" t="inlineStr"/>
+      <c r="J115" s="2" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>Mads Pieter van Luttervelt; Mathias Rask Østergaard-Nielsen; Martin Bækgaard; Zuzana Murdoch; Benny Geys</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C116" s="3" t="inlineStr">
+        <is>
+          <t>Civil Servants and Democratic Backsliding: The Role of Managerial Signals</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>Journal of Public Administration Research and Theory</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr"/>
+      <c r="F116" s="2" t="inlineStr"/>
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr"/>
+      <c r="I116" s="2" t="inlineStr"/>
+      <c r="J116" s="2" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>Jae-Moo Lee; Kyung-Seu Cho</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C117" s="3" t="inlineStr">
+        <is>
+          <t>South Korea’s Three Kindergarten Laws: A Revision Process Analysis Using a Complex Policy Change Analytical Model</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>Administration &amp; Society</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr"/>
+      <c r="F117" s="2" t="inlineStr"/>
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr"/>
+      <c r="I117" s="2" t="inlineStr"/>
+      <c r="J117" s="2" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>Christoph Ivanusch; Simon M. Luebke; Anna-Katharina Wurst; Jörg Haßler</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C118" s="3" t="inlineStr">
+        <is>
+          <t>Social Media Savvy? The Use and Effectiveness of Political Parties’ Issue Strategies Across Platforms in the German Federal Election Campaign 2025</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>Political Communication</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr"/>
+      <c r="F118" s="2" t="inlineStr"/>
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr"/>
+      <c r="I118" s="2" t="inlineStr"/>
+      <c r="J118" s="2" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>Justin Pottle</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C119" s="3" t="inlineStr">
+        <is>
+          <t>Partisan bias in a sorted party system: A problem of epistemic inequality</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>American Journal of Political Science</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr"/>
+      <c r="F119" s="2" t="inlineStr"/>
+      <c r="G119" s="2" t="inlineStr"/>
+      <c r="H119" s="2" t="inlineStr"/>
+      <c r="I119" s="2" t="inlineStr"/>
+      <c r="J119" s="2" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>Cigdem V. Sirin; Nicholas A. Valentino; José D. Villalobos</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C120" s="3" t="inlineStr">
+        <is>
+          <t>Outgroup Empathy and Opposition to Restrictive Voting Laws</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>Political Behavior</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr"/>
+      <c r="F120" s="2" t="inlineStr"/>
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr"/>
+      <c r="I120" s="2" t="inlineStr"/>
+      <c r="J120" s="2" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>Jill Nicholson-Crotty; Courtney Hahm; Sean Nicholson-Crotty</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C121" s="3" t="inlineStr">
+        <is>
+          <t>Disparity in Police Disciplinary Outcomes: The Mediating Effect of Complaint Disposition for Organizational Outgroups</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>The American Review of Public Administration</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr"/>
+      <c r="F121" s="2" t="inlineStr"/>
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr"/>
+      <c r="I121" s="2" t="inlineStr"/>
+      <c r="J121" s="2" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>Mirae Kim; Alisa Moldavanova</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C122" s="3" t="inlineStr">
+        <is>
+          <t>Connected for Survival: How Organizational Networks with Government Strengthen Nonprofit Resilience in Delivering Public Services</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>International Journal of Public Administration</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr"/>
+      <c r="F122" s="2" t="inlineStr"/>
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr"/>
+      <c r="I122" s="2" t="inlineStr"/>
+      <c r="J122" s="2" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>W. G. Will Zhao</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C123" s="3" t="inlineStr">
+        <is>
+          <t>Beyond monolithic state logic: how top-down accountability shapes policy implementation</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>Public Management Review</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr"/>
+      <c r="F123" s="2" t="inlineStr"/>
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr"/>
+      <c r="I123" s="2" t="inlineStr"/>
+      <c r="J123" s="2" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr"/>
+      <c r="B124" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C124" s="3" t="inlineStr">
+        <is>
+          <t>Referee Acknowledgments</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>Journal of Policy Analysis and Management</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr"/>
+      <c r="F124" s="2" t="inlineStr"/>
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr"/>
+      <c r="I124" s="2" t="inlineStr"/>
+      <c r="J124" s="2" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>Maayan Davidovitz; Rachel Gali Cinamon</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C125" s="3" t="inlineStr">
+        <is>
+          <t>Negotiating Presence: The Dynamics of Passive Representation Among Ultra‐Orthodox Women in Public Organizations</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>Public Administration</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr"/>
+      <c r="F125" s="2" t="inlineStr"/>
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="inlineStr"/>
+      <c r="I125" s="2" t="inlineStr"/>
+      <c r="J125" s="2" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>Xuede Gao; Haoyun Ma; Xu Zou</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C126" s="3" t="inlineStr">
+        <is>
+          <t>Implicit-Explicit Incongruence: The Dual Structure of Public Value Preferences in Civil Servants</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>International Journal of Public Administration</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr"/>
+      <c r="F126" s="2" t="inlineStr"/>
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr"/>
+      <c r="I126" s="2" t="inlineStr"/>
+      <c r="J126" s="2" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>Ofri Shalev Greenman; Einat Lavee</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C127" s="3" t="inlineStr">
+        <is>
+          <t>Gender inequality at the street level explained: redoing gender through informal practices</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>Public Management Review</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr"/>
+      <c r="F127" s="2" t="inlineStr"/>
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr"/>
+      <c r="I127" s="2" t="inlineStr"/>
+      <c r="J127" s="2" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>Negin Salimi; Stijn van Hiele</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C128" s="3" t="inlineStr">
+        <is>
+          <t>Contingent capacity: navigating organizational dependency in Dutch municipal energy transitions</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>Public Management Review</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr"/>
+      <c r="F128" s="2" t="inlineStr"/>
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr"/>
+      <c r="I128" s="2" t="inlineStr"/>
+      <c r="J128" s="2" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>Thomas Rabovsky; Matthew C. Nowlin; Emily Mee</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C129" s="3" t="inlineStr">
+        <is>
+          <t>Cultural Theory, Political Ideology, and Burden Tolerance: The Role of Core Beliefs in Shaping Support for Administrative Burdens</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>The American Review of Public Administration</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr"/>
+      <c r="F129" s="2" t="inlineStr"/>
+      <c r="G129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="inlineStr"/>
+      <c r="I129" s="2" t="inlineStr"/>
+      <c r="J129" s="2" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>Ximena Pizarro‐Bore; Javier Fuenzalida; Norma M. Riccucci; Constanza Faune</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C130" s="3" t="inlineStr">
+        <is>
+          <t>Rethinking Top Public Management Through Relational Dynamics: A Systems‐Informed Study of Senior Executives</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>Public Administration</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr"/>
+      <c r="F130" s="2" t="inlineStr"/>
+      <c r="G130" s="2" t="inlineStr"/>
+      <c r="H130" s="2" t="inlineStr"/>
+      <c r="I130" s="2" t="inlineStr"/>
+      <c r="J130" s="2" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>Marjorie De la Cruz; Milena I. Neshkova; Yoon‐Jung Choi</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C131" s="3" t="inlineStr">
+        <is>
+          <t>Does Gender Budgeting Improve Women's Well‐Being, Equality, and Empowerment?</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>Public Administration</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr"/>
+      <c r="F131" s="2" t="inlineStr"/>
+      <c r="G131" s="2" t="inlineStr"/>
+      <c r="H131" s="2" t="inlineStr"/>
+      <c r="I131" s="2" t="inlineStr"/>
+      <c r="J131" s="2" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>Mhamed Biygautane; Stewart Clegg</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C132" s="3" t="inlineStr">
+        <is>
+          <t>Power circuit alignment and reform trajectories: a dynamic framework for public management research</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>Perspectives on Public Management and Governance</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr"/>
+      <c r="F132" s="2" t="inlineStr"/>
+      <c r="G132" s="2" t="inlineStr"/>
+      <c r="H132" s="2" t="inlineStr"/>
+      <c r="I132" s="2" t="inlineStr"/>
+      <c r="J132" s="2" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>Sun Gue (Susan) Yang; Chan Hyeon Hur; Carla Flink</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C133" s="3" t="inlineStr">
+        <is>
+          <t>Gender-Responsive Budgeting in Higher Education: An Examination of Collegiate Athletics Student Aid</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>Public Performance &amp; Management Review</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr"/>
+      <c r="F133" s="2" t="inlineStr"/>
+      <c r="G133" s="2" t="inlineStr"/>
+      <c r="H133" s="2" t="inlineStr"/>
+      <c r="I133" s="2" t="inlineStr"/>
+      <c r="J133" s="2" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>Tingzhong Huang; Wenyan Tu</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C134" s="3" t="inlineStr">
+        <is>
+          <t>Why Street-Level Bureaucrats Leave: The Effects of Organizational Transparency and Role Conflict</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>The American Review of Public Administration</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr"/>
+      <c r="F134" s="2" t="inlineStr"/>
+      <c r="G134" s="2" t="inlineStr"/>
+      <c r="H134" s="2" t="inlineStr"/>
+      <c r="I134" s="2" t="inlineStr"/>
+      <c r="J134" s="2" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>Irene Henriques; Rick Colbourne; Christian Eva; Jesse Pirini; Barbara Allen; Ana Maria Peredo</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C135" s="3" t="inlineStr">
+        <is>
+          <t>Towards inclusive prosperity: comparative analysis of Indigenous procurement policies in Canada, Australia, and New Zealand</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>Public Management Review</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr"/>
+      <c r="F135" s="2" t="inlineStr"/>
+      <c r="G135" s="2" t="inlineStr"/>
+      <c r="H135" s="2" t="inlineStr"/>
+      <c r="I135" s="2" t="inlineStr"/>
+      <c r="J135" s="2" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>Gaston Brice Nkoumou Ngoa; Donald Ferdinand Okere Atanga; Marie Laure Belomo Onguene</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C136" s="3" t="inlineStr">
+        <is>
+          <t>Tax Mobilization in Africa: Is the Secret Hidden in Women's Political Empowerment?</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>Public Administration Review</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr"/>
+      <c r="F136" s="2" t="inlineStr"/>
+      <c r="G136" s="2" t="inlineStr"/>
+      <c r="H136" s="2" t="inlineStr"/>
+      <c r="I136" s="2" t="inlineStr"/>
+      <c r="J136" s="2" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>M. Blake Emidy; Anmol Soni; Evan Mistur</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C137" s="3" t="inlineStr">
+        <is>
+          <t>Sifting Through: Federal Separations in 2025 and Their Implications for Knowledge Loss and Agency Capacity</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>Public Administration Review</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr"/>
+      <c r="F137" s="2" t="inlineStr"/>
+      <c r="G137" s="2" t="inlineStr"/>
+      <c r="H137" s="2" t="inlineStr"/>
+      <c r="I137" s="2" t="inlineStr"/>
+      <c r="J137" s="2" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>Isabella Rebasso; Yanna Krupnikov</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C138" s="3" t="inlineStr">
+        <is>
+          <t>Rethinking Assumptions About Moral Content Selection: Moral-Emotional Content May Be Less Appealing Than Assumed</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>Political Communication</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr"/>
+      <c r="F138" s="2" t="inlineStr"/>
+      <c r="G138" s="2" t="inlineStr"/>
+      <c r="H138" s="2" t="inlineStr"/>
+      <c r="I138" s="2" t="inlineStr"/>
+      <c r="J138" s="2" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>Smadar Cohen‐Chen; Garrett L. Brady; Gerben A. van Kleef; Eran Halperin</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C139" s="3" t="inlineStr">
+        <is>
+          <t>Not‐so‐great expectations: Outgroup indifference facilitates conflict resolution in negatively interdependent contexts</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>Political Psychology</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr"/>
+      <c r="F139" s="2" t="inlineStr"/>
+      <c r="G139" s="2" t="inlineStr"/>
+      <c r="H139" s="2" t="inlineStr"/>
+      <c r="I139" s="2" t="inlineStr"/>
+      <c r="J139" s="2" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>Byunggeor Moon</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C140" s="3" t="inlineStr">
+        <is>
+          <t>Informal Authority, Legitimacy Transition, and Institutional Change: A Theory of Advisory Capture</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>Public Administration Review</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr"/>
+      <c r="F140" s="2" t="inlineStr"/>
+      <c r="G140" s="2" t="inlineStr"/>
+      <c r="H140" s="2" t="inlineStr"/>
+      <c r="I140" s="2" t="inlineStr"/>
+      <c r="J140" s="2" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>Je Hoon Chae; Tim Groeling; Hyunjin (Jin) Song</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C141" s="3" t="inlineStr">
+        <is>
+          <t>Hold That Thought: Enhancing the Durability of Fact-Checking Effects Through Low-Cost Accuracy Reminders</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>Political Communication</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr"/>
+      <c r="F141" s="2" t="inlineStr"/>
+      <c r="G141" s="2" t="inlineStr"/>
+      <c r="H141" s="2" t="inlineStr"/>
+      <c r="I141" s="2" t="inlineStr"/>
+      <c r="J141" s="2" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>Björn Boman; Jonas Hultin Rosenberg; Johan Wejryd</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C142" s="3" t="inlineStr">
+        <is>
+          <t>Does disability trump family background? Determinants of electoral participation among young individuals with intellectual disability</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>Political Psychology</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr"/>
+      <c r="F142" s="2" t="inlineStr"/>
+      <c r="G142" s="2" t="inlineStr"/>
+      <c r="H142" s="2" t="inlineStr"/>
+      <c r="I142" s="2" t="inlineStr"/>
+      <c r="J142" s="2" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>Sean Safford</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C143" s="3" t="inlineStr">
+        <is>
+          <t>Three Configurations of In‐House Government Consulting: Public‐Value Purpose and Organizational Viability</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr"/>
+      <c r="F143" s="2" t="inlineStr"/>
+      <c r="G143" s="2" t="inlineStr"/>
+      <c r="H143" s="2" t="inlineStr"/>
+      <c r="I143" s="2" t="inlineStr"/>
+      <c r="J143" s="2" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>Eric S. Zeemering</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C144" s="3" t="inlineStr">
+        <is>
+          <t>Partisanship, Public Service Values, and Public Service Recognition Week Proclamations</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>The American Review of Public Administration</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr"/>
+      <c r="F144" s="2" t="inlineStr"/>
+      <c r="G144" s="2" t="inlineStr"/>
+      <c r="H144" s="2" t="inlineStr"/>
+      <c r="I144" s="2" t="inlineStr"/>
+      <c r="J144" s="2" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>Fabian Hattke; Judith Hattke; David Hensel; Pamela Herd; Janne Kalucza; Donald Moynihan; Rick Vogel</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C145" s="3" t="inlineStr">
+        <is>
+          <t>Face‐to‐Face With Administrative Burdens: Design Simplification, Emotional Costs, and Procedural Outcomes in Digital Welfare Applications</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>Public Administration</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr"/>
+      <c r="F145" s="2" t="inlineStr"/>
+      <c r="G145" s="2" t="inlineStr"/>
+      <c r="H145" s="2" t="inlineStr"/>
+      <c r="I145" s="2" t="inlineStr"/>
+      <c r="J145" s="2" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>Mary K. Feeney; Julie Langer; Justin M. Stritch</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C146" s="3" t="inlineStr">
+        <is>
+          <t>Expansive Public Service Delivery: Advancing Public Value Governance</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>Public Administration Review</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr"/>
+      <c r="F146" s="2" t="inlineStr"/>
+      <c r="G146" s="2" t="inlineStr"/>
+      <c r="H146" s="2" t="inlineStr"/>
+      <c r="I146" s="2" t="inlineStr"/>
+      <c r="J146" s="2" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>Clair Yang</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C147" s="3" t="inlineStr">
+        <is>
+          <t>A theory of political divergence and gradual institutional change</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>American Journal of Political Science</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr"/>
+      <c r="F147" s="2" t="inlineStr"/>
+      <c r="G147" s="2" t="inlineStr"/>
+      <c r="H147" s="2" t="inlineStr"/>
+      <c r="I147" s="2" t="inlineStr"/>
+      <c r="J147" s="2" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>Yongzheng Yang; Qingqing Zhang; Peng Liu</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C148" s="3" t="inlineStr">
+        <is>
+          <t>To Add Insult to Injury: Exploring the Impact of Policy Inequity on Administrative Burden</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>Public Administration Review</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr"/>
+      <c r="F148" s="2" t="inlineStr"/>
+      <c r="G148" s="2" t="inlineStr"/>
+      <c r="H148" s="2" t="inlineStr"/>
+      <c r="I148" s="2" t="inlineStr"/>
+      <c r="J148" s="2" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>Marina Carelli Reis; Ana Paula Franco Paes Leme Barbosa; Jacob Brix; Mario Sergio Salerno</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C149" s="3" t="inlineStr">
+        <is>
+          <t>Public sector innovation management in the shadow: why the overlooked sibling still matters</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>Public Management Review</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr"/>
+      <c r="F149" s="2" t="inlineStr"/>
+      <c r="G149" s="2" t="inlineStr"/>
+      <c r="H149" s="2" t="inlineStr"/>
+      <c r="I149" s="2" t="inlineStr"/>
+      <c r="J149" s="2" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>Whitney Afonso; Zachary Mohr</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C150" s="3" t="inlineStr">
+        <is>
+          <t>Managers as message makers: a conjoint experiment on information framing and citizen support for local sales tax referenda</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>International Public Management Journal</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr"/>
+      <c r="F150" s="2" t="inlineStr"/>
+      <c r="G150" s="2" t="inlineStr"/>
+      <c r="H150" s="2" t="inlineStr"/>
+      <c r="I150" s="2" t="inlineStr"/>
+      <c r="J150" s="2" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>David Ibañez; Ricardo A. Bello‐Gómez</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C151" s="3" t="inlineStr">
+        <is>
+          <t>Democratic Backsliding and Governance Outcomes: Measuring Administrative and Political Channels of Decline</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>Public Administration Review</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr"/>
+      <c r="F151" s="2" t="inlineStr"/>
+      <c r="G151" s="2" t="inlineStr"/>
+      <c r="H151" s="2" t="inlineStr"/>
+      <c r="I151" s="2" t="inlineStr"/>
+      <c r="J151" s="2" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>Jaeyeong Nam; Daniel L Fay; Emily Boykin; Elizabeth Bell</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C152" s="3" t="inlineStr">
+        <is>
+          <t>Conditional Compliance: The Role of Sector and Policy Design in State Sexual Misconduct Policy</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>Journal of Public Administration Research and Theory</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr"/>
+      <c r="F152" s="2" t="inlineStr"/>
+      <c r="G152" s="2" t="inlineStr"/>
+      <c r="H152" s="2" t="inlineStr"/>
+      <c r="I152" s="2" t="inlineStr"/>
+      <c r="J152" s="2" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>Dede Setiono</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C153" s="3" t="inlineStr">
+        <is>
+          <t>Governing Before the State: Indigenous Javanese Administrative Theory</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>Public Administration Review</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr"/>
+      <c r="F153" s="2" t="inlineStr"/>
+      <c r="G153" s="2" t="inlineStr"/>
+      <c r="H153" s="2" t="inlineStr"/>
+      <c r="I153" s="2" t="inlineStr"/>
+      <c r="J153" s="2" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>Jared Abbott; Jose Morales‐Arilla</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C154" s="3" t="inlineStr">
+        <is>
+          <t>Captured participatory institutions: Theory and evidence from Venezuela's Consejos Comunales</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>American Journal of Political Science</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr"/>
+      <c r="F154" s="2" t="inlineStr"/>
+      <c r="G154" s="2" t="inlineStr"/>
+      <c r="H154" s="2" t="inlineStr"/>
+      <c r="I154" s="2" t="inlineStr"/>
+      <c r="J154" s="2" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>Joshua P. Darr; Susan Robinson</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C155" s="3" t="inlineStr">
+        <is>
+          <t>Assessing Civic Journalism Training: A Mixed-Method Applied Research Study</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>Political Communication</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr"/>
+      <c r="F155" s="2" t="inlineStr"/>
+      <c r="G155" s="2" t="inlineStr"/>
+      <c r="H155" s="2" t="inlineStr"/>
+      <c r="I155" s="2" t="inlineStr"/>
+      <c r="J155" s="2" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>Jessica L. Berrett; Amanda J. Stewart; Kerry Kuenzi</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C156" s="3" t="inlineStr">
+        <is>
+          <t>More Than the Sum of Its Parts? Bridging Research-to-Practice Gaps to Explain Local Nonprofit Sector Health</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>Administration &amp; Society</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr"/>
+      <c r="F156" s="2" t="inlineStr"/>
+      <c r="G156" s="2" t="inlineStr"/>
+      <c r="H156" s="2" t="inlineStr"/>
+      <c r="I156" s="2" t="inlineStr"/>
+      <c r="J156" s="2" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>Amanda Austin; Edward Hohe; Ryan Kennedy; Leib Litman; William Minozzi; Laura Moses</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C157" s="3" t="inlineStr">
+        <is>
+          <t>An Experimental Comparison of AI-Enabled Semi-Structured Interviews and Fixed Surveys: Respondent Satisfaction, Response Patterns, Quality, and Representation</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>Public Opinion Quarterly</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr"/>
+      <c r="F157" s="2" t="inlineStr"/>
+      <c r="G157" s="2" t="inlineStr"/>
+      <c r="H157" s="2" t="inlineStr"/>
+      <c r="I157" s="2" t="inlineStr"/>
+      <c r="J157" s="2" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>Shirley Kempeneer</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C158" s="3" t="inlineStr">
+        <is>
+          <t>Agile Digital Transformation and the Rule of Law: Perks and Perils in a Belgian and a Dutch Public Sector Organization</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>Public Administration</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr"/>
+      <c r="F158" s="2" t="inlineStr"/>
+      <c r="G158" s="2" t="inlineStr"/>
+      <c r="H158" s="2" t="inlineStr"/>
+      <c r="I158" s="2" t="inlineStr"/>
+      <c r="J158" s="2" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>Gary Johnson; Spencer Cragun; Jake Yoder</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C159" s="3" t="inlineStr">
+        <is>
+          <t>Under Pressure: Analyzing LEO Turnover in America's Swing and Pivot Counties for 2016, 2020, 2024</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>Public Administration Review</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr"/>
+      <c r="F159" s="2" t="inlineStr"/>
+      <c r="G159" s="2" t="inlineStr"/>
+      <c r="H159" s="2" t="inlineStr"/>
+      <c r="I159" s="2" t="inlineStr"/>
+      <c r="J159" s="2" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>Insyirah Mujtahid; Nurul Huda Rashid; Kokil Jaidka</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C160" s="3" t="inlineStr">
+        <is>
+          <t>Reclaiming Place Through Symbolic Geographies: Visual Resistance on Palestinian Instagram</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>Political Communication</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr"/>
+      <c r="F160" s="2" t="inlineStr"/>
+      <c r="G160" s="2" t="inlineStr"/>
+      <c r="H160" s="2" t="inlineStr"/>
+      <c r="I160" s="2" t="inlineStr"/>
+      <c r="J160" s="2" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>Jason D. Rivera; Claire Connolly Knox; Clinton McNair; Joseph T. Ripberger</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C161" s="3" t="inlineStr">
+        <is>
+          <t>Organizational Capacity to Implement Social Equity in Emergency Management: A Local Government Perspective</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>Public Administration</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr"/>
+      <c r="F161" s="2" t="inlineStr"/>
+      <c r="G161" s="2" t="inlineStr"/>
+      <c r="H161" s="2" t="inlineStr"/>
+      <c r="I161" s="2" t="inlineStr"/>
+      <c r="J161" s="2" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>Tingzhong Huang; Rui Wang; Can Chen; Herong Gao</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C162" s="3" t="inlineStr">
+        <is>
+          <t>From Social Equity Budgeting to Revenue Equity: Minority Leadership and Local Governments' Exploitative Revenues</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>Public Administration</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr"/>
+      <c r="F162" s="2" t="inlineStr"/>
+      <c r="G162" s="2" t="inlineStr"/>
+      <c r="H162" s="2" t="inlineStr"/>
+      <c r="I162" s="2" t="inlineStr"/>
+      <c r="J162" s="2" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>Siyu Liang</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C163" s="3" t="inlineStr">
+        <is>
+          <t>Enemies Abroad, Animosity at Home: Media Influence on U.S.-China Policy and Anti-Asian Sentiment</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>Political Communication</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr"/>
+      <c r="F163" s="2" t="inlineStr"/>
+      <c r="G163" s="2" t="inlineStr"/>
+      <c r="H163" s="2" t="inlineStr"/>
+      <c r="I163" s="2" t="inlineStr"/>
+      <c r="J163" s="2" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>Piotr Jabkowski; Mariusz Baranowski; Piotr Cichocki</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C164" s="3" t="inlineStr">
+        <is>
+          <t>Attitudes Toward Energy Across European Union Member States (2006–2024)</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>Public Opinion Quarterly</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr"/>
+      <c r="F164" s="2" t="inlineStr"/>
+      <c r="G164" s="2" t="inlineStr"/>
+      <c r="H164" s="2" t="inlineStr"/>
+      <c r="I164" s="2" t="inlineStr"/>
+      <c r="J164" s="2" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>Tiana Marrese; Ying Liu; Femida Handy</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C165" s="3" t="inlineStr">
+        <is>
+          <t>The Gendered Path of Least Resistance: First Entry and Exit Behaviors of Public and Nonprofit Employees</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>Public Administration Review</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr"/>
+      <c r="F165" s="2" t="inlineStr"/>
+      <c r="G165" s="2" t="inlineStr"/>
+      <c r="H165" s="2" t="inlineStr"/>
+      <c r="I165" s="2" t="inlineStr"/>
+      <c r="J165" s="2" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>David Lee; ChiaKo Hung</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C166" s="3" t="inlineStr">
+        <is>
+          <t>The Cost Savings in Inter-Organizational Cooperation: A Meta-Analytic Review and Extension</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>Public Performance &amp; Management Review</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr"/>
+      <c r="F166" s="2" t="inlineStr"/>
+      <c r="G166" s="2" t="inlineStr"/>
+      <c r="H166" s="2" t="inlineStr"/>
+      <c r="I166" s="2" t="inlineStr"/>
+      <c r="J166" s="2" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>Silvia Pianta; Paula Rettl</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C167" s="3" t="inlineStr">
+        <is>
+          <t>Global harms, local profits: How the uneven costs of natural disasters affect support for green political platforms</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>American Journal of Political Science</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr"/>
+      <c r="F167" s="2" t="inlineStr"/>
+      <c r="G167" s="2" t="inlineStr"/>
+      <c r="H167" s="2" t="inlineStr"/>
+      <c r="I167" s="2" t="inlineStr"/>
+      <c r="J167" s="2" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>Hanzhang Liu; Linan Yao</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C168" s="3" t="inlineStr">
+        <is>
+          <t>Entertainment as Trojan Horse: Voluntary Consumption of Propaganda in China</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>Political Communication</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr"/>
+      <c r="F168" s="2" t="inlineStr"/>
+      <c r="G168" s="2" t="inlineStr"/>
+      <c r="H168" s="2" t="inlineStr"/>
+      <c r="I168" s="2" t="inlineStr"/>
+      <c r="J168" s="2" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>Antonio Amuza; Vasile Dîncu</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C169" s="3" t="inlineStr">
+        <is>
+          <t>Affective Legitimacy and Digital Populism: Evidence from Romania’s Annulled Presidential Elections</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>Political Communication</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr"/>
+      <c r="F169" s="2" t="inlineStr"/>
+      <c r="G169" s="2" t="inlineStr"/>
+      <c r="H169" s="2" t="inlineStr"/>
+      <c r="I169" s="2" t="inlineStr"/>
+      <c r="J169" s="2" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>Yuna Blajer de la Garza</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C170" s="3" t="inlineStr">
+        <is>
+          <t>(Non)belonging and (un)freedom</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>American Journal of Political Science</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr"/>
+      <c r="F170" s="2" t="inlineStr"/>
+      <c r="G170" s="2" t="inlineStr"/>
+      <c r="H170" s="2" t="inlineStr"/>
+      <c r="I170" s="2" t="inlineStr"/>
+      <c r="J170" s="2" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>Gianluca Maistri; Chiara Leardini; Gianluca Veronesi; Enrico Zaninotto</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C171" s="3" t="inlineStr">
+        <is>
+          <t>“Old Habits Die Hard”: Formal Politicization and the Turnover of Public Hospital CEOs</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>Administration &amp; Society</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr"/>
+      <c r="F171" s="2" t="inlineStr"/>
+      <c r="G171" s="2" t="inlineStr"/>
+      <c r="H171" s="2" t="inlineStr"/>
+      <c r="I171" s="2" t="inlineStr"/>
+      <c r="J171" s="2" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>Warda Belabas; Koen Migchelbrink</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C172" s="3" t="inlineStr">
+        <is>
+          <t>Should we stay or should we go? Implications of trust in the municipality for second-generation migrants’ behavioural intentions towards the municipality</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>Public Management Review</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr"/>
+      <c r="F172" s="2" t="inlineStr"/>
+      <c r="G172" s="2" t="inlineStr"/>
+      <c r="H172" s="2" t="inlineStr"/>
+      <c r="I172" s="2" t="inlineStr"/>
+      <c r="J172" s="2" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>Elliott Edsall</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C173" s="3" t="inlineStr">
+        <is>
+          <t>Policing the Political Boundary: How the r/BarstoolSports Audience Confronts Politicization</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>Political Communication</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr"/>
+      <c r="F173" s="2" t="inlineStr"/>
+      <c r="G173" s="2" t="inlineStr"/>
+      <c r="H173" s="2" t="inlineStr"/>
+      <c r="I173" s="2" t="inlineStr"/>
+      <c r="J173" s="2" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>Laura Cervi; Sarah J. Jackson</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C174" s="3" t="inlineStr">
+        <is>
+          <t>Kamala is Brat: TikTok and the Affective Politics of Memes</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>Political Communication</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr"/>
+      <c r="F174" s="2" t="inlineStr"/>
+      <c r="G174" s="2" t="inlineStr"/>
+      <c r="H174" s="2" t="inlineStr"/>
+      <c r="I174" s="2" t="inlineStr"/>
+      <c r="J174" s="2" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>James E Wright II; Brittany Houston</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C175" s="3" t="inlineStr">
+        <is>
+          <t>Beyond neutrality: QuantCrit as a methodological corrective in quantitative public administration research</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>Perspectives on Public Management and Governance</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr"/>
+      <c r="F175" s="2" t="inlineStr"/>
+      <c r="G175" s="2" t="inlineStr"/>
+      <c r="H175" s="2" t="inlineStr"/>
+      <c r="I175" s="2" t="inlineStr"/>
+      <c r="J175" s="2" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>Melody Huang; Erin Hartman</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C176" s="3" t="inlineStr">
+        <is>
+          <t>Assessing Nonignorable Response: Sensitivity Analysis for Survey Weighting, with Applications to Survey Estimates of COVID-19 Vaccination Uptake</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>Public Opinion Quarterly</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr"/>
+      <c r="F176" s="2" t="inlineStr"/>
+      <c r="G176" s="2" t="inlineStr"/>
+      <c r="H176" s="2" t="inlineStr"/>
+      <c r="I176" s="2" t="inlineStr"/>
+      <c r="J176" s="2" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>Alastair Stark; Hridesh Gajural; Jack Corbett; Dennis C Grube; Heather Lovell; Rodney Scott</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C177" s="3" t="inlineStr">
+        <is>
+          <t>Institutional Amnesia and Public Administration: Does History Repeat?</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>Journal of Public Administration Research and Theory</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr"/>
+      <c r="F177" s="2" t="inlineStr"/>
+      <c r="G177" s="2" t="inlineStr"/>
+      <c r="H177" s="2" t="inlineStr"/>
+      <c r="I177" s="2" t="inlineStr"/>
+      <c r="J177" s="2" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>Petter Gullmark</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C178" s="3" t="inlineStr">
+        <is>
+          <t>How Front-Line Public Managers Become Institutional Entrepreneurs</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>The American Review of Public Administration</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr"/>
+      <c r="F178" s="2" t="inlineStr"/>
+      <c r="G178" s="2" t="inlineStr"/>
+      <c r="H178" s="2" t="inlineStr"/>
+      <c r="I178" s="2" t="inlineStr"/>
+      <c r="J178" s="2" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>Craig R. Smith</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C179" s="3" t="inlineStr">
+        <is>
+          <t>Civic Embeddedness and Public Employment: How Institutional Proximity Structures Civic Participation</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>The American Review of Public Administration</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr"/>
+      <c r="F179" s="2" t="inlineStr"/>
+      <c r="G179" s="2" t="inlineStr"/>
+      <c r="H179" s="2" t="inlineStr"/>
+      <c r="I179" s="2" t="inlineStr"/>
+      <c r="J179" s="2" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>Paolo Belardinelli; Martin Lodge</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C180" s="3" t="inlineStr">
+        <is>
+          <t>Citizens’ support for behavioural public policy and trust in government: evidence from two online experiments</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>Public Management Review</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr"/>
+      <c r="F180" s="2" t="inlineStr"/>
+      <c r="G180" s="2" t="inlineStr"/>
+      <c r="H180" s="2" t="inlineStr"/>
+      <c r="I180" s="2" t="inlineStr"/>
+      <c r="J180" s="2" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>Margot Lissens; Cato Waeterloos; Laura Vandenbosch; Desirée Schmuck</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C181" s="3" t="inlineStr">
+        <is>
+          <t>Trending Topics, Growing Knowledge? How Curating Actors’ Political Social Media Content Affects Youth’s Political Knowledge</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>Political Communication</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr"/>
+      <c r="F181" s="2" t="inlineStr"/>
+      <c r="G181" s="2" t="inlineStr"/>
+      <c r="H181" s="2" t="inlineStr"/>
+      <c r="I181" s="2" t="inlineStr"/>
+      <c r="J181" s="2" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>Alexander L. Q. Chen‐Florea</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C182" s="3" t="inlineStr">
+        <is>
+          <t>Putting Democratic Theory and Principles of Justice in the Right Place: Ethical Pluralism in Collaborative and Participatory Governance</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>Public Administration Review</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr"/>
+      <c r="F182" s="2" t="inlineStr"/>
+      <c r="G182" s="2" t="inlineStr"/>
+      <c r="H182" s="2" t="inlineStr"/>
+      <c r="I182" s="2" t="inlineStr"/>
+      <c r="J182" s="2" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>Oscar Nowlan</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C183" s="3" t="inlineStr">
+        <is>
+          <t>Public Service Delegation and the Mechanisms of Blame Attribution: Evidence From a Survey Experiment on Public Service Failure</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>Public Administration Review</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr"/>
+      <c r="F183" s="2" t="inlineStr"/>
+      <c r="G183" s="2" t="inlineStr"/>
+      <c r="H183" s="2" t="inlineStr"/>
+      <c r="I183" s="2" t="inlineStr"/>
+      <c r="J183" s="2" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>Niva Golan-Nadir</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C184" s="3" t="inlineStr">
+        <is>
+          <t>Navigating Ambiguity: Street-Level Managers Discretion in the Implementation of Religious Policy in Divided Societies</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
+        <is>
+          <t>The American Review of Public Administration</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="inlineStr"/>
+      <c r="F184" s="2" t="inlineStr"/>
+      <c r="G184" s="2" t="inlineStr"/>
+      <c r="H184" s="2" t="inlineStr"/>
+      <c r="I184" s="2" t="inlineStr"/>
+      <c r="J184" s="2" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>STUART J. TURNBULL-DUGARTE; ALBERTO LÓPEZ ORTEGA</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C185" s="3" t="inlineStr">
+        <is>
+          <t>Instrumentally Inclusive: The Political Psychology of Homonationalism – CORRIGENDUM</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
+        <is>
+          <t>American Political Science Review</t>
+        </is>
+      </c>
+      <c r="E185" s="2" t="inlineStr"/>
+      <c r="F185" s="2" t="inlineStr"/>
+      <c r="G185" s="2" t="inlineStr"/>
+      <c r="H185" s="2" t="inlineStr"/>
+      <c r="I185" s="2" t="inlineStr"/>
+      <c r="J185" s="2" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>Marcy Shieh</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C186" s="3" t="inlineStr">
+        <is>
+          <t>Examining the Influence of Media Coverage on Information-Seeking of Judicial Candidates</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
+        <is>
+          <t>Political Communication</t>
+        </is>
+      </c>
+      <c r="E186" s="2" t="inlineStr"/>
+      <c r="F186" s="2" t="inlineStr"/>
+      <c r="G186" s="2" t="inlineStr"/>
+      <c r="H186" s="2" t="inlineStr"/>
+      <c r="I186" s="2" t="inlineStr"/>
+      <c r="J186" s="2" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>Philip Leifeld; Laurence Brandenberger</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C187" s="3" t="inlineStr">
+        <is>
+          <t>Endogenous coalition formation in policy debates</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="inlineStr">
+        <is>
+          <t>American Journal of Political Science</t>
+        </is>
+      </c>
+      <c r="E187" s="2" t="inlineStr"/>
+      <c r="F187" s="2" t="inlineStr"/>
+      <c r="G187" s="2" t="inlineStr"/>
+      <c r="H187" s="2" t="inlineStr"/>
+      <c r="I187" s="2" t="inlineStr"/>
+      <c r="J187" s="2" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>Maxwell Palmer; Benjamin Schneer</t>
+        </is>
+      </c>
+      <c r="B188" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C188" s="3" t="inlineStr">
+        <is>
+          <t>Durable majority gerrymanders: Where partisan gerrymandering can displace democracy</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
+        <is>
+          <t>American Journal of Political Science</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="inlineStr"/>
+      <c r="F188" s="2" t="inlineStr"/>
+      <c r="G188" s="2" t="inlineStr"/>
+      <c r="H188" s="2" t="inlineStr"/>
+      <c r="I188" s="2" t="inlineStr"/>
+      <c r="J188" s="2" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>Huanming Wang; Xiaoyun Sun; Bing Ran</t>
+        </is>
+      </c>
+      <c r="B189" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C189" s="3" t="inlineStr">
+        <is>
+          <t>The Bureaucratic Paradox of Citizen Agency: Institutional Crowding‐Out in Government‐Catalyzed Co‐Production in Shanghai, China</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="E189" s="2" t="inlineStr"/>
+      <c r="F189" s="2" t="inlineStr"/>
+      <c r="G189" s="2" t="inlineStr"/>
+      <c r="H189" s="2" t="inlineStr"/>
+      <c r="I189" s="2" t="inlineStr"/>
+      <c r="J189" s="2" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>Jinke M. Oostvogel; Matthew M. Young; Bram Klievink</t>
+        </is>
+      </c>
+      <c r="B190" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C190" s="3" t="inlineStr">
+        <is>
+          <t>Getting the Priorities Straight: Public Values in AI Adoption</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
+        <is>
+          <t>Public Administration</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="inlineStr"/>
+      <c r="F190" s="2" t="inlineStr"/>
+      <c r="G190" s="2" t="inlineStr"/>
+      <c r="H190" s="2" t="inlineStr"/>
+      <c r="I190" s="2" t="inlineStr"/>
+      <c r="J190" s="2" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>Marco Mattei; John Michael</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C191" s="3" t="inlineStr">
+        <is>
+          <t>Consistency, not waste aversion, explains apparent sunk‐cost effects in politics</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="inlineStr">
+        <is>
+          <t>Political Psychology</t>
+        </is>
+      </c>
+      <c r="E191" s="2" t="inlineStr"/>
+      <c r="F191" s="2" t="inlineStr"/>
+      <c r="G191" s="2" t="inlineStr"/>
+      <c r="H191" s="2" t="inlineStr"/>
+      <c r="I191" s="2" t="inlineStr"/>
+      <c r="J191" s="2" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>Richard M. Walker; Jiasheng Zhang; Bert George</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C192" s="3" t="inlineStr">
+        <is>
+          <t>Reference points, negativity bias and citizens’ performance evaluations: a replication and extension</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
+        <is>
+          <t>Public Management Review</t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="inlineStr"/>
+      <c r="F192" s="2" t="inlineStr"/>
+      <c r="G192" s="2" t="inlineStr"/>
+      <c r="H192" s="2" t="inlineStr"/>
+      <c r="I192" s="2" t="inlineStr"/>
+      <c r="J192" s="2" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>Guangdong Wu; Jiawen Li; Yanlu Zha</t>
+        </is>
+      </c>
+      <c r="B193" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C193" s="3" t="inlineStr">
+        <is>
+          <t>Navigating the digital transformation: unravelling the dynamic evolution of smart city collaborative governance networks</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="inlineStr">
+        <is>
+          <t>Public Management Review</t>
+        </is>
+      </c>
+      <c r="E193" s="2" t="inlineStr"/>
+      <c r="F193" s="2" t="inlineStr"/>
+      <c r="G193" s="2" t="inlineStr"/>
+      <c r="H193" s="2" t="inlineStr"/>
+      <c r="I193" s="2" t="inlineStr"/>
+      <c r="J193" s="2" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>Ole Helby Petersen; Matthew Potoski; Lena Brogaard</t>
+        </is>
+      </c>
+      <c r="B194" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C194" s="3" t="inlineStr">
+        <is>
+          <t>Improving Cooperation in Government Purchasing Through Formal‐Relational Contracting</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
+        <is>
+          <t>Public Administration Review</t>
+        </is>
+      </c>
+      <c r="E194" s="2" t="inlineStr"/>
+      <c r="F194" s="2" t="inlineStr"/>
+      <c r="G194" s="2" t="inlineStr"/>
+      <c r="H194" s="2" t="inlineStr"/>
+      <c r="I194" s="2" t="inlineStr"/>
+      <c r="J194" s="2" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>Lie Philip Santoso</t>
+        </is>
+      </c>
+      <c r="B195" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C195" s="3" t="inlineStr">
+        <is>
+          <t>Elite Interactions and Social Bonds: How Partisan Cooperation Shapes Perceptions of Cross-Party Friendships</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="inlineStr">
+        <is>
+          <t>Political Behavior</t>
+        </is>
+      </c>
+      <c r="E195" s="2" t="inlineStr"/>
+      <c r="F195" s="2" t="inlineStr"/>
+      <c r="G195" s="2" t="inlineStr"/>
+      <c r="H195" s="2" t="inlineStr"/>
+      <c r="I195" s="2" t="inlineStr"/>
+      <c r="J195" s="2" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>Jordon Peugh</t>
+        </is>
+      </c>
+      <c r="B196" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C196" s="3" t="inlineStr">
+        <is>
+          <t>AAPOR Presidential Address AAPOR Presidential Address 2026: Bearing Witness to This Moment</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
+        <is>
+          <t>Public Opinion Quarterly</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="inlineStr"/>
+      <c r="F196" s="2" t="inlineStr"/>
+      <c r="G196" s="2" t="inlineStr"/>
+      <c r="H196" s="2" t="inlineStr"/>
+      <c r="I196" s="2" t="inlineStr"/>
+      <c r="J196" s="2" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>Bill Schultz; Eric A. Coleman; Rani Parker; Jacob Manyindo; Emmanuel Mukuru</t>
+        </is>
+      </c>
+      <c r="B197" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C197" s="3" t="inlineStr">
+        <is>
+          <t>Transparency and Responsibility Attribution: A Field Experiment in Western Uganda</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="inlineStr">
+        <is>
+          <t>Policy Studies Journal</t>
+        </is>
+      </c>
+      <c r="E197" s="2" t="inlineStr"/>
+      <c r="F197" s="2" t="inlineStr"/>
+      <c r="G197" s="2" t="inlineStr"/>
+      <c r="H197" s="2" t="inlineStr"/>
+      <c r="I197" s="2" t="inlineStr"/>
+      <c r="J197" s="2" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>Roberto Ulloa; Leonard Tiedemann; Peter Selb; Celina Kacperski</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C198" s="3" t="inlineStr">
+        <is>
+          <t>The Knowledge Gap in a High-Choice Media Environment: Experimental Evidence from Online Search</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
+        <is>
+          <t>Political Communication</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="inlineStr"/>
+      <c r="F198" s="2" t="inlineStr"/>
+      <c r="G198" s="2" t="inlineStr"/>
+      <c r="H198" s="2" t="inlineStr"/>
+      <c r="I198" s="2" t="inlineStr"/>
+      <c r="J198" s="2" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>Sarah Van Impe; Lieselot Danneels; Ben Suykens</t>
+        </is>
+      </c>
+      <c r="B199" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C199" s="3" t="inlineStr">
+        <is>
+          <t>Institutional Pressures or Organizational Capacity? Antecedents of Digital Maturity in Local Governments</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="inlineStr">
+        <is>
+          <t>Public Administration</t>
+        </is>
+      </c>
+      <c r="E199" s="2" t="inlineStr"/>
+      <c r="F199" s="2" t="inlineStr"/>
+      <c r="G199" s="2" t="inlineStr"/>
+      <c r="H199" s="2" t="inlineStr"/>
+      <c r="I199" s="2" t="inlineStr"/>
+      <c r="J199" s="2" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>Felicia Pratto</t>
+        </is>
+      </c>
+      <c r="B200" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C200" s="3" t="inlineStr">
+        <is>
+          <t>Social dominance orientation</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="inlineStr">
+        <is>
+          <t>Political Psychology</t>
+        </is>
+      </c>
+      <c r="E200" s="2" t="inlineStr"/>
+      <c r="F200" s="2" t="inlineStr"/>
+      <c r="G200" s="2" t="inlineStr"/>
+      <c r="H200" s="2" t="inlineStr"/>
+      <c r="I200" s="2" t="inlineStr"/>
+      <c r="J200" s="2" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>John D Marvel; Sheeling Neo; Rachel Cho; Sangwon Ju</t>
+        </is>
+      </c>
+      <c r="B201" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C201" s="3" t="inlineStr">
+        <is>
+          <t>Large Language Models and Conversational Counter-Arguments to Anti-Public Sector Bias</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="inlineStr">
+        <is>
+          <t>Journal of Public Administration Research and Theory</t>
+        </is>
+      </c>
+      <c r="E201" s="2" t="inlineStr"/>
+      <c r="F201" s="2" t="inlineStr"/>
+      <c r="G201" s="2" t="inlineStr"/>
+      <c r="H201" s="2" t="inlineStr"/>
+      <c r="I201" s="2" t="inlineStr"/>
+      <c r="J201" s="2" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>Mario Kieft</t>
+        </is>
+      </c>
+      <c r="B202" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C202" s="3" t="inlineStr">
+        <is>
+          <t>Knowledge Logics and Epistemic Tension in Public Decision Making: An Analytical Perspective for Public Administration and Governance</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="inlineStr">
+        <is>
+          <t>Administration &amp; Society</t>
+        </is>
+      </c>
+      <c r="E202" s="2" t="inlineStr"/>
+      <c r="F202" s="2" t="inlineStr"/>
+      <c r="G202" s="2" t="inlineStr"/>
+      <c r="H202" s="2" t="inlineStr"/>
+      <c r="I202" s="2" t="inlineStr"/>
+      <c r="J202" s="2" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>Noam Brenner</t>
+        </is>
+      </c>
+      <c r="B203" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C203" s="3" t="inlineStr">
+        <is>
+          <t>Beyond Contact: Social Cohesion and Municipal Legitimacy in Times of Crisis</t>
+        </is>
+      </c>
+      <c r="D203" s="2" t="inlineStr">
+        <is>
+          <t>Administration &amp; Society</t>
+        </is>
+      </c>
+      <c r="E203" s="2" t="inlineStr"/>
+      <c r="F203" s="2" t="inlineStr"/>
+      <c r="G203" s="2" t="inlineStr"/>
+      <c r="H203" s="2" t="inlineStr"/>
+      <c r="I203" s="2" t="inlineStr"/>
+      <c r="J203" s="2" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>Sarah Pralle; Emily Thorson</t>
+        </is>
+      </c>
+      <c r="B204" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C204" s="3" t="inlineStr">
+        <is>
+          <t>The Effects of Policy Success Versus Failure Narratives</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="inlineStr">
+        <is>
+          <t>Policy Studies Journal</t>
+        </is>
+      </c>
+      <c r="E204" s="2" t="inlineStr"/>
+      <c r="F204" s="2" t="inlineStr"/>
+      <c r="G204" s="2" t="inlineStr"/>
+      <c r="H204" s="2" t="inlineStr"/>
+      <c r="I204" s="2" t="inlineStr"/>
+      <c r="J204" s="2" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>Naomi Head</t>
+        </is>
+      </c>
+      <c r="B205" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C205" s="3" t="inlineStr">
+        <is>
+          <t>Affective regimes and ontological security: When empathy threatens the state</t>
+        </is>
+      </c>
+      <c r="D205" s="2" t="inlineStr">
+        <is>
+          <t>Political Psychology</t>
+        </is>
+      </c>
+      <c r="E205" s="2" t="inlineStr"/>
+      <c r="F205" s="2" t="inlineStr"/>
+      <c r="G205" s="2" t="inlineStr"/>
+      <c r="H205" s="2" t="inlineStr"/>
+      <c r="I205" s="2" t="inlineStr"/>
+      <c r="J205" s="2" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>Justice Nyigmah Bawole; Kelvin Omari Mintah; Zechariah Langnel</t>
+        </is>
+      </c>
+      <c r="B206" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C206" s="3" t="inlineStr">
+        <is>
+          <t>Youth and Corruption in Ghana: Perspectives from University Student Leaders</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="inlineStr">
+        <is>
+          <t>International Journal of Public Administration</t>
+        </is>
+      </c>
+      <c r="E206" s="2" t="inlineStr"/>
+      <c r="F206" s="2" t="inlineStr"/>
+      <c r="G206" s="2" t="inlineStr"/>
+      <c r="H206" s="2" t="inlineStr"/>
+      <c r="I206" s="2" t="inlineStr"/>
+      <c r="J206" s="2" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>Rocco Caferra; Giuseppe Di Liddo; Andrea Morone; Fabrizio Striani</t>
+        </is>
+      </c>
+      <c r="B207" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C207" s="3" t="inlineStr">
+        <is>
+          <t>Telemedicine Use in a Fragmented Federal System: State Policy Variation and Access to Digital Health Services in the United States</t>
+        </is>
+      </c>
+      <c r="D207" s="2" t="inlineStr">
+        <is>
+          <t>Administration &amp; Society</t>
+        </is>
+      </c>
+      <c r="E207" s="2" t="inlineStr"/>
+      <c r="F207" s="2" t="inlineStr"/>
+      <c r="G207" s="2" t="inlineStr"/>
+      <c r="H207" s="2" t="inlineStr"/>
+      <c r="I207" s="2" t="inlineStr"/>
+      <c r="J207" s="2" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>Naomi Rommens</t>
+        </is>
+      </c>
+      <c r="B208" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C208" s="3" t="inlineStr">
+        <is>
+          <t>Perspectives on Placemaking: Affective Practices and the Lived Dimensions of Space</t>
+        </is>
+      </c>
+      <c r="D208" s="2" t="inlineStr">
+        <is>
+          <t>Administration &amp; Society</t>
+        </is>
+      </c>
+      <c r="E208" s="2" t="inlineStr"/>
+      <c r="F208" s="2" t="inlineStr"/>
+      <c r="G208" s="2" t="inlineStr"/>
+      <c r="H208" s="2" t="inlineStr"/>
+      <c r="I208" s="2" t="inlineStr"/>
+      <c r="J208" s="2" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
+        <is>
+          <t>Tianyu Chen; William G. Prince; Lewis Faulk; Mirae Kim</t>
+        </is>
+      </c>
+      <c r="B209" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C209" s="3" t="inlineStr">
+        <is>
+          <t>Personnel Stability During Environmental Turbulence: Testing Performance Disruption Buffering in Service Providing Nonprofits</t>
+        </is>
+      </c>
+      <c r="D209" s="2" t="inlineStr">
+        <is>
+          <t>Public Performance &amp; Management Review</t>
+        </is>
+      </c>
+      <c r="E209" s="2" t="inlineStr"/>
+      <c r="F209" s="2" t="inlineStr"/>
+      <c r="G209" s="2" t="inlineStr"/>
+      <c r="H209" s="2" t="inlineStr"/>
+      <c r="I209" s="2" t="inlineStr"/>
+      <c r="J209" s="2" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>Pirmin Bundi; Valérie Pattyn</t>
+        </is>
+      </c>
+      <c r="B210" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C210" s="3" t="inlineStr">
+        <is>
+          <t>It Does Matter. A New Framework on the Influence of Policy Evaluation</t>
+        </is>
+      </c>
+      <c r="D210" s="2" t="inlineStr">
+        <is>
+          <t>Policy Studies Journal</t>
+        </is>
+      </c>
+      <c r="E210" s="2" t="inlineStr"/>
+      <c r="F210" s="2" t="inlineStr"/>
+      <c r="G210" s="2" t="inlineStr"/>
+      <c r="H210" s="2" t="inlineStr"/>
+      <c r="I210" s="2" t="inlineStr"/>
+      <c r="J210" s="2" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t>Iseul Choi; Minjung Kim</t>
+        </is>
+      </c>
+      <c r="B211" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C211" s="3" t="inlineStr">
+        <is>
+          <t>How Do Clear Equity Goals Affect Citizens’ Assessment of Agency Performance? Evidence from a Survey Experiment</t>
+        </is>
+      </c>
+      <c r="D211" s="2" t="inlineStr">
+        <is>
+          <t>Public Performance &amp; Management Review</t>
+        </is>
+      </c>
+      <c r="E211" s="2" t="inlineStr"/>
+      <c r="F211" s="2" t="inlineStr"/>
+      <c r="G211" s="2" t="inlineStr"/>
+      <c r="H211" s="2" t="inlineStr"/>
+      <c r="I211" s="2" t="inlineStr"/>
+      <c r="J211" s="2" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t>Gianmarco Daniele; Gemma Dipoppa; Massimo Pulejo</t>
+        </is>
+      </c>
+      <c r="B212" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C212" s="3" t="inlineStr">
+        <is>
+          <t>Attacking Women or their Policies? Understanding Violence against Women in Politics</t>
+        </is>
+      </c>
+      <c r="D212" s="2" t="inlineStr">
+        <is>
+          <t>The Journal of Politics</t>
+        </is>
+      </c>
+      <c r="E212" s="2" t="inlineStr"/>
+      <c r="F212" s="2" t="inlineStr"/>
+      <c r="G212" s="2" t="inlineStr"/>
+      <c r="H212" s="2" t="inlineStr"/>
+      <c r="I212" s="2" t="inlineStr"/>
+      <c r="J212" s="2" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="inlineStr">
+        <is>
+          <t>Xiaoxiao Shen</t>
+        </is>
+      </c>
+      <c r="B213" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C213" s="3" t="inlineStr">
+        <is>
+          <t>When propaganda resonates</t>
+        </is>
+      </c>
+      <c r="D213" s="2" t="inlineStr">
+        <is>
+          <t>Political Psychology</t>
+        </is>
+      </c>
+      <c r="E213" s="2" t="inlineStr"/>
+      <c r="F213" s="2" t="inlineStr"/>
+      <c r="G213" s="2" t="inlineStr"/>
+      <c r="H213" s="2" t="inlineStr"/>
+      <c r="I213" s="2" t="inlineStr"/>
+      <c r="J213" s="2" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="inlineStr"/>
+      <c r="B214" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C214" s="3" t="inlineStr">
+        <is>
+          <t>Issue Information</t>
+        </is>
+      </c>
+      <c r="D214" s="2" t="inlineStr">
+        <is>
+          <t>Political Psychology</t>
+        </is>
+      </c>
+      <c r="E214" s="2" t="inlineStr"/>
+      <c r="F214" s="2" t="inlineStr"/>
+      <c r="G214" s="2" t="inlineStr"/>
+      <c r="H214" s="2" t="inlineStr"/>
+      <c r="I214" s="2" t="inlineStr"/>
+      <c r="J214" s="2" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="inlineStr">
+        <is>
+          <t>Ida Bruun Nørregaard</t>
+        </is>
+      </c>
+      <c r="B215" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C215" s="3" t="inlineStr">
+        <is>
+          <t>How moral values underpin and affect attitudes on ethnic discrimination</t>
+        </is>
+      </c>
+      <c r="D215" s="2" t="inlineStr">
+        <is>
+          <t>Political Psychology</t>
+        </is>
+      </c>
+      <c r="E215" s="2" t="inlineStr"/>
+      <c r="F215" s="2" t="inlineStr"/>
+      <c r="G215" s="2" t="inlineStr"/>
+      <c r="H215" s="2" t="inlineStr"/>
+      <c r="I215" s="2" t="inlineStr"/>
+      <c r="J215" s="2" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="inlineStr">
+        <is>
+          <t>Jesse L. Barnes; Michael A. Powell</t>
+        </is>
+      </c>
+      <c r="B216" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C216" s="3" t="inlineStr">
+        <is>
+          <t>Does Political Decoupling Through Fair Market Privatization Improve Managerial and Political Outcomes? Insights From Water Utility Sales</t>
+        </is>
+      </c>
+      <c r="D216" s="2" t="inlineStr">
+        <is>
+          <t>Public Administration Review</t>
+        </is>
+      </c>
+      <c r="E216" s="2" t="inlineStr"/>
+      <c r="F216" s="2" t="inlineStr"/>
+      <c r="G216" s="2" t="inlineStr"/>
+      <c r="H216" s="2" t="inlineStr"/>
+      <c r="I216" s="2" t="inlineStr"/>
+      <c r="J216" s="2" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="inlineStr">
+        <is>
+          <t>Mingrui Chen; Zhirong Jerry Zhao</t>
+        </is>
+      </c>
+      <c r="B217" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C217" s="3" t="inlineStr">
+        <is>
+          <t>A Race to the Top: The Adoption of Net‐Zero City Pledges in Large US Cities</t>
+        </is>
+      </c>
+      <c r="D217" s="2" t="inlineStr">
+        <is>
+          <t>Public Administration Review</t>
+        </is>
+      </c>
+      <c r="E217" s="2" t="inlineStr"/>
+      <c r="F217" s="2" t="inlineStr"/>
+      <c r="G217" s="2" t="inlineStr"/>
+      <c r="H217" s="2" t="inlineStr"/>
+      <c r="I217" s="2" t="inlineStr"/>
+      <c r="J217" s="2" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="inlineStr">
+        <is>
+          <t>André Borges; Arnaldo Mauerberg</t>
+        </is>
+      </c>
+      <c r="B218" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C218" s="3" t="inlineStr">
+        <is>
+          <t>Senior Bureaucrats, Coalitions and the Quality of Government: Accounting for Effective Governance in Fragmented Settings</t>
+        </is>
+      </c>
+      <c r="D218" s="2" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="E218" s="2" t="inlineStr"/>
+      <c r="F218" s="2" t="inlineStr"/>
+      <c r="G218" s="2" t="inlineStr"/>
+      <c r="H218" s="2" t="inlineStr"/>
+      <c r="I218" s="2" t="inlineStr"/>
+      <c r="J218" s="2" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="inlineStr">
+        <is>
+          <t>Christine H. Roch; Ellen V. Rubin</t>
+        </is>
+      </c>
+      <c r="B219" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C219" s="3" t="inlineStr">
+        <is>
+          <t>Accountability systems and coping in the bureaucratic environment</t>
+        </is>
+      </c>
+      <c r="D219" s="2" t="inlineStr">
+        <is>
+          <t>Public Management Review</t>
+        </is>
+      </c>
+      <c r="E219" s="2" t="inlineStr"/>
+      <c r="F219" s="2" t="inlineStr"/>
+      <c r="G219" s="2" t="inlineStr"/>
+      <c r="H219" s="2" t="inlineStr"/>
+      <c r="I219" s="2" t="inlineStr"/>
+      <c r="J219" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:J1"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C215" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C216" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C217" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C218" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C219" r:id="rId218"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/PA_Journal_Digest_Archive.xlsx
+++ b/data/PA_Journal_Digest_Archive.xlsx
@@ -528,12 +528,36 @@
           <t>Review of Public Personnel Administration</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr"/>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr"/>
-      <c r="J2" s="2" t="inlineStr"/>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>질적연구</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>사례연구</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Organizational Resilience</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Operational Continuity</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>이 질적 사례연구는 DOGE 인력개혁 초기 시행에서 연방 현장 파견조직이 보안인가가 필요한 보안담당자 공석에도 업무 연속성을 어떻게 유지했는지, 면담·설문·조직자료를 통해 분석했다. 업무 재분배, 지식 포착, 리더십, 비공식 조정으로 핵심 운영은 지속됐지만, 업무 집중과 문서화되지 않은 지식 의존 및 개인 노력에 대한 의존이 커져 운영 연속성이 조직 회복탄력성의 약화를 가릴 수 있음을 보였다.</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>This qualitative case study examines how a federal field detachment sustained operational continuity during the initial implementation of the Department of Government Efficiency (DOGE) workforce reforms. Centered on the loss of a clearance-restricted Security Officer, the study draws on interviews, surveys, and organizational artifacts to examine how responsibilities were redistributed under constrained staffing conditions. Findings indicate that mission-essential operations were maintained through task redistribution, knowledge capture, leadership, and informal coordination; however, these adaptive responses also increased workload concentration, exposed dependence on undocumented institutional knowledge, and heightened reliance on individual effort. The study distinguishes operational continuity from organizational resilience by demonstrating that sustained mission performance can mask underlying degradation in organizational capacity. The findings extend beyond the DOGE reforms and offer practical lessons for workforce restructuring, continuity planning, succession management, and organizational resilience across public and private organizations.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -554,12 +578,36 @@
           <t>Political Communication</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="2" t="inlineStr"/>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>혼합방법론</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>텍스트 내용분석</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Strategic Stereotype Theory</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Gendered Messaging</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>정치적 직위의 유형과 수준에 따라 후보자의 성별이 선거 메시지에 미치는 영향이 어떻게 달라지는지를, 한국의 2000~2022년 전국·지방선거에서 지역구 행정부·입법부 후보자가 배포한 공식 선거공보 46,966건의 관계적 언어와 여성 관련 정책 용어로 분석했다. 여성 후보자는 남성 후보자보다 관계적 정체성과 여성 정책을 더 강조했으며, 이러한 성별 격차는 행정부보다 입법부 선거에서, 전국보다 지방 수준에서 더 크게 나타났다.</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>This study examines how candidates’ gender shapes campaign messaging across different branches and levels of political office. Prior research offers mixed evidence on whether women are more likely than men to emphasize communal traits and women-related policies, often because gender effects are examined without fully accounting for institutional context. We address this inconsistency by foregrounding the role of electoral institutions. Building on strategic stereotype theory, we argue that gendered campaign messaging is a strategic response to office-specific incentives and expectations. In particular, we expect gendered appeals to be more prevalent at lower levels of government than at higher levels, and more pronounced in legislative than in executive races. We test these expectations using an original dataset of 46,966 official campaign booklets issued by all candidates competing for district-based executive and legislative offices in seventeen national and local elections in South Korea from 2000 to 2022. These booklets are legally standardized, page-limited documents distributed to voters and provide a rare opportunity to compare campaign messages across offices while holding the communication medium constant. We measure gendered messaging through candidates’ use of relational language and women-related policy terms. The results show that female candidates emphasize relational identities and women’s policy concerns more than male candidates. Crucially, the magnitude of this gender gap varies across institutional contexts. Gender differences are larger in legislative contests than in executive races and increase as elections move from national to subnational levels.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -580,12 +628,36 @@
           <t>Public Management Review</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="2" t="inlineStr"/>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>혼합방법론</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>크리스프셋 비교</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Government Responsiveness</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Citizen Engagement</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>멕시코 635개 지방자치단체의 페이스북 활용을 대상으로, 지방정부가 시민에게 반응할 가능성을 어떻게 좌우하는지 혼합방법과 크리스프셋 질적비교분석으로 분석했다. 소규모 지방정부는 적응 잠재력과 공식 참여정책이 있을 때, 대도시는 자원·확립된 참여 규칙과 정책·우호적 환경이 있을 때 시민 참여와 상호작용에 더 반응적이었다.</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Local governments worldwide increasingly adopt social media to engage citizens. What factors make governments more likely to respond to citizens on social media? We explore how Mexican municipal governments use Facebook to interact with citizens, with a mixed-methods approach analysing data from 635 municipalities. Using a crisp-set qualitative comparative analysis, we distinguish between general responsiveness (channel setup) and interactive responsiveness (substantive engagement). Small municipalities are more likely to engage citizens when adaptive potential and formal participation policies are present. In contrast, larger cities show responsiveness when they have available resources, established participation rules and policies, and a propitious environment.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -606,12 +678,36 @@
           <t>Public Administration</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="2" t="inlineStr"/>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>실험</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>설문 실험</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Government Responsiveness</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Perceived Fairness</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>정부의 전통적·AI 기반 응답 방식과 시민 요구 유형이 시민 만족도에 미치는 영향을 2×3 집단 간 설문 실험으로 분석했다. AI 기반 응답은 전통적 응답보다 만족도를 높였고, 상담 요구의 만족도가 가장 높고 제안 요구가 가장 낮았으며, 응답 방식과 요구 유형의 상호작용이 유의했고 지각된 공정성이 매개하고 참여 경험이 조절했다.</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>ABSTRACT Faced with diverse and complex demands from citizens, the government has consistently sought ways to enhance its ability to respond. Metaphorically, citizens' needs can be viewed as locks, and the government requires keys to unlock them. Artificial intelligence (AI) is an innovative new key offering a fresh paradigm for unlocking the door to high citizen satisfaction. Drawing on government responsiveness theory, this study applies a 2 × 3 between‐subjects survey experiment to explore the impact of government response methods (traditional responses, AI‐enabled responses) and citizen demand types (consultation, complaint/help‐seeking, suggestions) on citizen satisfaction. Findings show that AI‐enabled government responses significantly increase citizen satisfaction compared to traditional approaches. Among demand types, consultation yields the highest satisfaction, while suggestion results in the lowest. Further, the satisfaction level is significantly influenced by the interaction effect between response method and demand type. Perceived fairness mediates the relationship between government responses and citizen satisfaction, with citizen participation experience having a moderating effect. This study offers new insights into increasing citizen satisfaction from the perspective of government responses. It reveals the content‐dependent nature of AI‐enabled government responses, helping the government create unique AI response strategies and enhance digital interaction with citizens.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -632,12 +728,36 @@
           <t>Political Behavior</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="2" t="inlineStr"/>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr"/>
-      <c r="I6" s="2" t="inlineStr"/>
-      <c r="J6" s="2" t="inlineStr"/>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>질적연구</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>자료 재분석</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Political Discussion Networks</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Policy Framing</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>정치적 토론 네트워크에서 사람들이 토론 상대와 정책 우선순위 및 정책 프레임을 공유하는지 검토하기 위해 1996년 인디애나폴리스–세인트루이스 연구 자료를 재분석했다. 사람들은 대체로 상대와 우선순위와 프레임이 모두 달랐지만, 정책 우선순위는 상대와 불균형적으로 공유되었고 우선순위가 일치할 때 동일한 프레임을 채택하는 경향도 나타났다.</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>Abstract To understand politics, people often rely on political discussion. Among the many ways that discussion may shape political perceptions, one possible mechanism is by promoting a shared sense of priorities— which issues are important. A second mechanism is by framing how people think about important issues. We examine these potential mechanisms by answering the descriptive question: Do policy priorities and policy frames tend to co-occur within political discussion networks? We answer this question by reanalyzing the 1996 Indianapolis-St. Louis Study in which participants—and their discussion partners—described the most important problem facing the United States in their own words. We show that the modal outcome is for people to hold both different priorities and different frames than their discussion partners. This finding stands in contrast to network scholarship suggesting that homophily is so often the norm. Yet we also show that people disproportionately share the same policy priorities as their discussion partners, and adopt the same frames in thinking about policy topics, especially when their policy priorities match. This finding suggests that some policy priorities are so embedded in certain frames of thinking that the topic and frame stay linked even as the topic may diffuse through a social network.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -658,12 +778,36 @@
           <t>Political Behavior</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr"/>
-      <c r="F7" s="2" t="inlineStr"/>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr"/>
-      <c r="I7" s="2" t="inlineStr"/>
-      <c r="J7" s="2" t="inlineStr"/>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>혼합방법론</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>비교분석·설문실험</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Anti-Prejudice Norms</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Normative Credibility</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>주류 정당이 극우 정당의 반무슬림 수사를 채택할 때 반편견 규범이 약화되는지, 그리고 그 효과가 언제 나타나는지를 분석했다. 6개 유럽 국가의 의회 연설에 대한 비교 관찰분석과 독일·덴마크의 사전등록 설문실험을 결합한 결과, 독일에서는 주류 정당의 수사가 극우 정당의 수사보다 반편견 규범을 더 약화시켰지만 덴마크에서는 유사한 효과가 나타나지 않았으며, 무슬림 대상 수사의 효과는 다른 외집단에 대한 태도에도 파급되었다.</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>Abstract This article examines whether mainstream political parties adopt prejudiced rhetoric from the far right and how such shifts shape anti-prejudice norms. Building on existing work, I argue that mainstream parties are particularly influential in weakening anti-prejudice norms because they possess greater normative credibility and legitimacy than far-right parties. Empirically, the article combines cross-national observational evidence with two preregistered survey experiments in Germany and Denmark. Using parliamentary speeches from six European countries between 1994 and 2022, I document rising mainstream party anti-Muslim rhetoric and its association with weaker norms against holding far-right views. The experiments provide causal evidence for the argument. In Germany, exposure to prejudiced rhetoric weakens anti-prejudice norms, but only when voiced by mainstream parties, rather than far right parties, likely due to their normative credibility and legitimacy. In Denmark, comparable effects are absent, consistent with decades of mainstream accommodation having already normalized such rhetoric. The experimental results also show that rhetoric targeting Muslims weakens anti-prejudice norms toward out-groups more broadly, suggesting spillover effects. These findings have important implications for future scholarship: when mainstream parties adopt prejudiced rhetoric from the far right, they affect not only electoral politics, but also the broader social norm environment.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -684,12 +828,36 @@
           <t>Public Management Review</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr"/>
-      <c r="F8" s="2" t="inlineStr"/>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr"/>
-      <c r="I8" s="2" t="inlineStr"/>
-      <c r="J8" s="2" t="inlineStr"/>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>서베이</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>국가 간 비교 설문</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>New Public Management</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Welfare State Robustness</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>이 연구는 벨기에·스웨덴·미국 비영리조직의 설문자료를 비교해 비영리 시장화 패턴의 차이와 맥락적 설명 여부를 검토했다. 조직 수준에서는 복지국가 수렴보다 복지국가의 견고성이 시장화 양상을 설명하는 데 더 적절한 틀이라는 결과를 제시한다.</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>New Public Management (NPM) reforms are argued to have induced welfare state convergence in public sector organizing. However, this argument has been examined mainly at the discourse and decision-making level, leaving the adoption of NPM reforms at the organizational level underexplored. Taking non-profit marketization as a case, this study draws on survey data from non-profits across three welfare states to examine the extent to which (a) different marketization patterns appear and (b) these patterns are explained by contextual differences. Findings suggest that welfare state robustness, not convergence, is the superior frame of reference at the organizational level.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -710,12 +878,36 @@
           <t>International Public Management Journal</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr"/>
-      <c r="F9" s="2" t="inlineStr"/>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr"/>
-      <c r="I9" s="2" t="inlineStr"/>
-      <c r="J9" s="2" t="inlineStr"/>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>이론/개념</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>문헌 검토</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>AI Snake Oil</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>이 글은 Narayanan과 Kapoor의 저서를 바탕으로 공공서비스에서 AI의 약속과 위험, 특히 ‘AI snake oil’에 관한 논의를 검토한다. AI의 발전이 제시하는 기대와 한계를 함께 조명하지만, 제공된 초록만으로는 별도의 연구질문이나 경험적 분석, 구체적 결론을 확인할 수 없다.</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>In their recent and first coauthored book, computer science scholars, Arvind Narayanan and Sayash Kapoor address promises and pitfalls with the “dawn of AI” (Narayanan and Kapoor 2024:3) amid the e...</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -736,12 +928,36 @@
           <t>Political Communication</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr"/>
-      <c r="F10" s="2" t="inlineStr"/>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr"/>
-      <c r="I10" s="2" t="inlineStr"/>
-      <c r="J10" s="2" t="inlineStr"/>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>혼합방법론</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>순차 혼합</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Mediatization</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Platform Incentives</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>브라질 정치인들이 소셜미디어에서 의회 활동과 지역구 서비스를 알리는 대신 가시성을 높이기 위해 대립적 콘텐츠와 뉴스 주기 연계를 활용하는 이유와 효과를, 심층 인터뷰와 페이스북·인스타그램·트위터 게시물 450만 건의 계산적 분석으로 검토했다. 의회 관련 게시물은 참여도가 낮고 대립적 언어는 참여도를 높이는 것으로 나타나, 플랫폼 유인이 정치인들로 하여금 의정활동을 축소하고 대립을 우선시하게 해 책무성을 약화시킬 수 있음을 보였다.</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>The transformation of parliamentarians into media producers has heightened concerns about emerging forms of political communication. This mixed-methods paper examines the strategies they employ to enhance their digital presence. Based on in-depth interviews, it shows that Brazilian parliamentarians believe that social media penalize them for posting about congressional matters, reporting that content about legislative work and constituency services receives little engagement online. Conversely, they view the production of antagonistic content and alignment with news cycles as essential to maintaining an engaging social media presence. A computational analysis of 4,5 million posts on Facebook, Instagram, and Twitter supports these evaluations: posts about congressional matters are associated with lower engagement metrics, while the use of antagonistic language increases them. The analysis further discusses pathways through which visibility is sustained at the intersection of platform incentives and communicative practices. In sum, this mixed-methods study demonstrates that the mediatization of politics has created perverse incentives for parliamentarians to downplay congressional activity and prioritize confrontations on social media, weakening accountability in ways that may resonate far beyond Brazil.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -762,12 +978,36 @@
           <t>International Public Management Journal</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr"/>
-      <c r="F11" s="2" t="inlineStr"/>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr"/>
-      <c r="I11" s="2" t="inlineStr"/>
-      <c r="J11" s="2" t="inlineStr"/>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>실험</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>컨조인트 실험</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Symbolic Representation</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Marginalization</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>이 연구는 시민이 어떤 맥락에서 자신과 인구학적으로 유사한 정신건강 서비스 제공자를 선호하는지 알아보기 위해, 실제 서비스 목록을 반영한 제공자 정보를 활용한 컨조인트 실험을 실시했다. 상징적 대표성 선호는 여성·논바이너리 응답자·유색인종처럼 상당한 주변화를 경험한 집단에서 가장 뚜렷했으며, 대기시간과 서비스 제공 방식은 이를 일관되게 조절하지 않았다.</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>Citizens often favor public servants who resemble them demographically, but studies also indicate that this preference for symbolic representation may be unevenly distributed, shaped by individuals’ own lived experiences. Against this backdrop, we ask: in what contexts do citizens express a preference for symbolic representation? Focusing on publicly-supported mental health services as an empirical case, we field a conjoint experiment depicting provider information in a format informed by real-world listings. We find that preferences for symbolic representation are most apparent for social groups that have experienced significant marginalization—women, non-binary respondents, and people of color. Meanwhile, factors describing the organizational context in which services are provided—wait times and modality of service provision—do not appear to consistently moderate the preference for symbolic representation. These results underscore the importance of macro factors, such as systemic racism and sexism, in shaping individual preferences for bureaucratic representation.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -788,12 +1028,36 @@
           <t>Public Performance &amp; Management Review</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr"/>
-      <c r="F12" s="2" t="inlineStr"/>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr"/>
-      <c r="I12" s="2" t="inlineStr"/>
-      <c r="J12" s="2" t="inlineStr"/>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>실험</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>설문 실험</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Social Reference Points</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Historical Reference Points</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>이 연구는 과거 실적과 동료 집단 실적 같은 기준점의 유형·조합이 시민의 공공서비스 성과 인식과 태도에 어떤 영향을 미치는지 세 차례 사전등록 무작위 설문실험으로 검토했다. 사회적 기준점은 단독으로 제시될 때보다 역사적 기준점과 함께 제시될 때 더 두드러졌으며, 서비스 변화 지지는 기준점보다 절대적 성과 수준의 영향을 받았다.</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>Performance metrics are often reported alongside benchmarks, such as past performance (historical reference point) or peer group performance (social reference point), often as part of a performance report or dashboard to inform the public and hold agencies accountable. Prior research has found that social reference points are more salient than historical ones in shaping citizens’ perceived performance. However, additional empirical evidence is crucial to enhance the generalizability of these findings and deepen our understanding of how citizens process different benchmarks. This study conceptually replicates and extends earlier work to further investigate how different types and combinations of benchmarks influence citizens’ perceptions and attitudes through three pre-registered randomized survey experiments. The findings reveal that reference points interact in complex ways: social reference points are less influential when presented alone but become more salient when paired with historical benchmarks. Moreover, while absolute performance levels affect citizens’ support for changes in public services, benchmarks alone do not. These results suggest that social reference points, historical reference points, and absolute performance metrics can all have meaning to citizens when forming judgments about public performance and making decisions. This study contributes to the literature by offering a more comprehensive understanding of how citizens interpret complex performance information.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -814,12 +1078,36 @@
           <t>Public Management Review</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr"/>
-      <c r="F13" s="2" t="inlineStr"/>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr"/>
-      <c r="I13" s="2" t="inlineStr"/>
-      <c r="J13" s="2" t="inlineStr"/>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>질적연구</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>사례연구·연결망 분석</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Value Co-Creation</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Institutional Intermediaries</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>중국 농촌 생태 거버넌스 사례를 통해, NGO가 문제 규정·계획·규칙 형성에 초기부터 참여함으로써 공동생산이 지역적으로 지속되는 가치 공동창출로 전환되는 과정을 분석한다. 질적 자료와 사회연결망 분석 결과, NGO는 경계 연결자를 넘어 제도적 중개자로서 거버넌스 arrangements와 지역 역량을 재구성하며 제도적 내재성, 행위자 흡수, 적응적 거버넌스를 통해 순환적 공공가치를 촉진하는 것으로 나타났다.</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>This study explores how NGOs facilitate the transition from co-production to value co-creation in rural ecological governance through a case study of the Guanba River Basin, China. Drawing on qualitative evidence and social network analysis, it reveals that NGOs’ front-loaded participation in problem framing, planning, and rule formation creates institutional and relational foundations for collaborative governance. Beyond boundary-spanning roles, NGOs function as institutional intermediaries that reshape governance arrangements and enhance local capacity. Value co-creation emerges through institutional embeddedness, actor absorption, and adaptive governance within a recursive ecosystem. This study provides an institutionally grounded explanation of how externally facilitated co-production evolves into locally sustained value co-creation.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -840,12 +1128,36 @@
           <t>International Public Management Journal</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr"/>
-      <c r="F14" s="2" t="inlineStr"/>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr"/>
-      <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" s="2" t="inlineStr"/>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>질적연구</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>질적 내용분석·면담</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Organizational Justice</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>온타리오 공공서비스의 하이브리드 근무에 대한 공정성과 형평성 인식을 레딧 자료의 질적 내용분석과 원주민·흑인 공무원 대상 반구조화 면담으로 분석했다. 분석 결과 하이브리드 근무 접근성의 불평등, 시행·집행의 불일치, 인종화된 공무원에게 집중되는 부담이 나타났으며, 이는 다양한 인력의 채용과 유지에 영향을 줄 수 있는 것으로 제시됐다.</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>Hybrid work—alternating between office and remote locations—has become the norm across Canadian public services, yet questions remain about whether it is implemented fairly. In 2022, the Ontario Public Service (OPS) mandated three in-office days per week, then announced in August 2025 that all employees must return to the office full-time. Based on qualitative content analysis of OPS subreddit data and semi-structured interviews with Indigenous and Black public servants, this paper explores perspectives on hybrid work, focusing on fairness and equity. It examines access to hybrid arrangements, consistency in implementation and enforcement, and impacts on recruitment and retention. Findings reveal concerns about unequal access, inconsistent enforcement, and disproportionate burdens on racialized public servants, along with implications for recruiting and retaining talent. Fairness and equity should therefore be central considerations in public sector hybrid work and return-to-office policies, given their impacts on recruiting and retaining a diverse government workforce.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -866,12 +1178,36 @@
           <t>Political Analysis</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr"/>
-      <c r="F15" s="2" t="inlineStr"/>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr"/>
-      <c r="I15" s="2" t="inlineStr"/>
-      <c r="J15" s="2" t="inlineStr"/>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>방법 미상</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Cox 위험모형</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Regression Inside Out</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Democratic Durability</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>이 연구는 회귀계수의 사례별 기여를 분해하는 RIO를 선형 예측자를 추정하는 모든 모형으로 확장하고, 사례별 기여가 평균 기준과 다른지를 검정하는 부트스트랩과 모형 진단, 특히 DFBETA와의 관계를 제시한다. 이를 민주주의 지속성을 분석한 Cox 비례위험모형에 적용해 이러한 확장의 유용성을 보인다.</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>Abstract Regression Inside Out (RIO) describes a set of related methods based on a decomposition of regression coefficients by individual cases. In this article, we offer three important extensions of RIO: 1) we generalize RIO to any model for which linear predictors are estimated; 2) we introduce an adapted bootstrap approach for determining whether case-level contributions differ from the baseline average contribution for cases; and 3) we describe how RIO is related to model diagnostics, particularly DFBETA. To illustrate the value added of these extensions, we apply RIO to a published example of the Cox proportional hazard model exploring factors associated with democratic durability.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -892,12 +1228,36 @@
           <t>Political Behavior</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr"/>
-      <c r="F16" s="2" t="inlineStr"/>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr"/>
-      <c r="I16" s="2" t="inlineStr"/>
-      <c r="J16" s="2" t="inlineStr"/>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>실험</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>설문 실험</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Crisis Framing</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Political Accountability</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>이 연구는 튀르키예의 선거권위주의 맥락에서 지구온난화·지진·경제붕괴·팬데믹 위기에 종교적·음모론적·과학적 책임 귀속 프레임이 집권자에 대한 태도에 미치는 영향과 조건을 전국 대면 설문실험으로 분석했다. 책임 귀속 프레임의 독립적 효과는 대체로 제한적이었지만, 종교 기반 프레임은 위기의 성격에 따라 달라져 정부 책임 인식이 낮고 불확실성이 큰 지진·팬데믹에서 기후·경제 위기보다 더 유리한 효과를 보였다.</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>Abstract This study investigates how blame-attributing crisis frames influence support for incumbents in an electoral authoritarian context, focusing on Türkiye. It asks how, to what extent, and under what conditions incumbents’ blame frames shape public attitudes toward the government. The study examines four crisis types (i.e., global warming , earthquake , economic collapse , and pandemic ) and compares the effects of religious , conspiratorial , and scientific framing across these contexts. Drawing on original data from seven pre-survey focus groups and a nationwide face-to-face survey experiment with 3,562 respondents, the findings indicate that the independent effects of blame frames are generally limited. However, the effectiveness of religion-based blame framing is highly context dependent. Compared with climate and economic crises, its estimated effects are more favorable in crises characterized by high uncertainty and relatively low perceived governmental responsibility, such as earthquake and pandemic. These findings suggest that the effectiveness of blame attribution is conditioned by the nature of the crisis itself. The study contributes to research on crisis framing, political accountability, and authoritarian durability.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -918,12 +1278,36 @@
           <t>Public Management Review</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr"/>
-      <c r="F17" s="2" t="inlineStr"/>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr"/>
-      <c r="I17" s="2" t="inlineStr"/>
-      <c r="J17" s="2" t="inlineStr"/>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>질적연구</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>다중 사례연구</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Public Value</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Social Enterprise</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>본 연구는 국가를 넘어 공공가치를 식별하기 위해 공공가치의 정치·사회적 차원을 어떻게 조작화할 수 있는지 탐구한다. 브라질 사회적기업 3곳을 대상으로 문서분석, 현장방문, 반구조화 인터뷰를 실시한 결과, 해당 차원을 구성하는 8개 요소를 정의하고 조직의 실천과 관계에서 이를 식별할 수 있음을 보였다.</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>Public value research increasingly recognizes that societal value is generated by public, private, philanthropic, and hybrid actors. However, empirical tools for identifying public value beyond the state remain underdeveloped, particularly regarding its political-social dimension. This study operationalizes this dimension by identifying and analytically defining eight constituent elements. It draws on a multiple case study of three Brazilian social enterprises, combining document analysis, field visits, and semi-structured interviews. Findings clarify the dimension’s components and demonstrate how they can be identified in organizational practices and relationships. The study advances empirical approaches to public value and extends research to non-state actors in a non-European context.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -944,12 +1328,36 @@
           <t>Public Management Review</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr"/>
-      <c r="F18" s="2" t="inlineStr"/>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr"/>
-      <c r="I18" s="2" t="inlineStr"/>
-      <c r="J18" s="2" t="inlineStr"/>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>실험</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>교체자료 분석</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Negative Performance Feedback</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Succession Origin</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>공공조직의 부정적 성과 피드백이 최고관리자 후계자의 내부·외부 출신 선택에 어떤 영향을 미치는지 2,045건의 최고관리자 교체 자료로 분석했다. 부정적 성과 피드백은 내부 승계 가능성을 41.7% 낮췄으며, 내부 승진 이력과 탐색적 학습 강조는 외부 후계자 선택을 강화했다.</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>Facing performance pressure, public organizations frequently experience top manager turnover, yet how they select successors is understudied. This study argues negative performance feedback (NPF) critically influences successor origin. Based on 2,045 TM turnovers , we find that NPF reduces the odds of internal succession by 41.7%. Internal promotion history strengthens external successor selection by signalling a break from discredited routines, while exploratory learning emphasis reinforces external selection as strategic identity. This research advances public management by offering a dynamic, antecedent-based explanation for TM selection, challenging monolithic views of organizational history, and highlighting successor origin as a strategic governance tool.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -970,12 +1378,36 @@
           <t>Public Administration</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr"/>
-      <c r="F19" s="2" t="inlineStr"/>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr"/>
-      <c r="I19" s="2" t="inlineStr"/>
-      <c r="J19" s="2" t="inlineStr"/>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>이론/개념</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>개념적 비교</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Civic Tech</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>State Capacity</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>이 글은 미국에서 정부를 위한 시민기술 운동의 기원·핵심 가치·발전을 설명하고, 시민기술과 DOGE가 기술을 통해 미국 행정국가를 재편하는 상반된 비전을 제시한다고 분석한다. 시민기술은 공공서비스 이용자를 중심에 두고 국가역량을 높이려 했으나 2014~2024년 정부 내 영향력을 확대하는 데 그쳤고, 근본적 변화를 실행할 충분한 권력을 확보하지 못했다고 주장한다.</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>ABSTRACT The second Trump administration saw the Department of Government Efficiency (DOGE), a group of outsider technologists given extraordinary power to pursue a massive downsizing of the federal government. They also displaced an alternative approach: the civic tech movement. Civic tech for government applies technology, data, and human‐centered design to improve policy implementation, fueled by prosocial motivation, promising to increase state capacity in a way that centers attention on public service clients. This article explains the origins of civic tech for government in the US setting, its core values, and evolution. The movement grew in prominence and influence from 2014 to 2024, making steady inroads into government but never gaining sufficient power to implement profound change. The conflicting origins, philosophy, and power between civic tech and DOGE offer contrasting visions for how tech can reshape the American administrative state.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -996,12 +1428,36 @@
           <t>Public Management Review</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr"/>
-      <c r="F20" s="2" t="inlineStr"/>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr"/>
-      <c r="I20" s="2" t="inlineStr"/>
-      <c r="J20" s="2" t="inlineStr"/>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>질적연구</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>사례연구</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>Clientelism</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Corporatization</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>이 연구는 이란 보건의료 부문 사례를 통해 고객주의적 사회관계가 병원 법인화 개혁을 필연적으로 저해하는지, 아니면 관리자가 조직 목표를 달성하도록 돕는 문화적 가교로 작용하는지를 탐구한다. 세계적 개혁 모형과 국가의 문화적 생태계 간 부적합성 속에서 고객주의는 법인화를 좌절시키는 제동장치이면서도 개혁 실행을 위해 관리자가 조정해야 하는 내재적 요소로 나타난다.</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>Public management reforms like corporatization often fail due to a lack of cultural and institutional compatibility, leading to divergence from globally prescribed reform models rather than convergence towards their intended managerial and organizational outcomes. While global templates prioritize managerial autonomy and efficiency, national ‘cultural ecologies’ filter these changes, sometimes creating deceptive window dressing to secure external legitimacy. This paper addresses a significant gap in current research by exploring how social relationships governed by clientelism – integral to the cultural ecologies of many countries – also impact on reform implementation. Using the Iranian healthcare sector as a case study, the paper investigates whether clientelism inevitably derails corporatization (the brake) or serves as an inherent cultural component that managers must navigate to achieve organizational goals (the bridge).</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1022,12 +1478,36 @@
           <t>The Journal of Politics</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr"/>
-      <c r="F21" s="2" t="inlineStr"/>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr"/>
-      <c r="I21" s="2" t="inlineStr"/>
-      <c r="J21" s="2" t="inlineStr"/>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>준실험</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>비교 식별전략</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>Political Incorporation</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>Seniority Ceiling</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>스웨덴의 선거투표용지와 행정자료를 연계하고, 지방자치단체 간 이동을 한 내국인과 비교하는 식별전략을 통해 이민자의 정치직 진출을 제한하는 연공서열 장벽을 분석한다. 연공서열 장벽은 이민자와 내국인의 정치직 보유 격차의 약 절반, 상위 직급에서의 통합 악화 경향의 거의 전부를 설명하며, 자격 축적 기회가 적은 최근 이주자와 고령 이주자에게 특히 크게 작용한다.</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>First-generation immigrants face a seniority ceiling that limits their political incorporation as candidates and officeholders. Career ladders that require qualification time in lower positions create structural barriers for this group. We use linked data from Swedish electoral ballots andadministrative records to examine this idea. A novel identification strategy isolates the effect of seniority-based promotion structures from immigrant-specific disadvantages by comparing immigrants’ incorporation patterns to those of internal movers—native-born Swedes whorelocate between municipalities. The seniority ceiling explains about half of the immigrant-native gap in holding political positions and almost the entire gradient of worsening incorporation at higher levels. We find strong selection effects at both the individual and group level. The seniority ceiling restricts incorporation at higher career steps for those with fewer opportunities to accumulate qualification time: those who arrived more recently or at older ages.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1048,12 +1528,36 @@
           <t>Policy Studies Journal</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr"/>
-      <c r="F22" s="2" t="inlineStr"/>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr"/>
-      <c r="I22" s="2" t="inlineStr"/>
-      <c r="J22" s="2" t="inlineStr"/>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>준실험</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>사례 기반 벤치마크</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Large Language Models</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Participatory Governance</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>이 연구노트는 스위스의 3개 의회 전 단계 공론협의 자료를 대상으로 오픈소스 LLM(Gemma3:27b)과 독점 LLM(GPT-5-mini)이 다언어·기술적 이질성이 높은 의견을 공식 행정 보고서와 비교해 얼마나 정확하고 완전하게 분석하는지 사례 기반으로 평가한다. 오픈소스 모델은 단순한 협의에서 평균 정확도 90%를 보였지만 내용 검색의 완전성은 70%였고, 두 비교 상황에서는 독점 모델이 더 우수했으며, LLM은 인간 전문성을 대체하기보다 보완하는 데 유용한 것으로 나타났다.</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>ABSTRACT Public consultations are a cornerstone of democratic policymaking, yet the sheer volume and heterogeneity of submissions often overwhelm traditional analysis. Emerging large language models (LLMs) offer new opportunities for making sense of such data, but their performance in contexts with high linguistic and technical diversity remains underexplored. In this research note, we present a case‐based demonstration rather than a generalizable evaluation, assessing an open‐source LLM (Gemma3:27b) and a proprietary LLM (GPT‐5‐mini) for analyzing stakeholder inputs from three Swiss pre‐parliamentary consultations. The coexistence of multiple languages and varying technical complexity in submissions creates uniquely challenging datasets, providing a rigorous test for automated tools. We benchmark the model against official administrative reports, assessing accuracy and completeness. Results show the open‐source model performs excellently in straightforward consultations, achieving a mean accuracy of 90%, but encounters difficulties in retrieving the substantive content (overall completeness: 70%). Comparatively, the proprietary model obtains better results than the open‐source one in these two settings. Overall, LLMs can streamline analysis and enhance interpretive capacity, complementing (but not replacing) human expertise. The study highlights both the potential and limits of algorithmic support for participatory governance in linguistically and technically diverse environments.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1074,12 +1578,36 @@
           <t>Political Communication</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr"/>
-      <c r="F23" s="2" t="inlineStr"/>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr"/>
-      <c r="I23" s="2" t="inlineStr"/>
-      <c r="J23" s="2" t="inlineStr"/>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>서베이</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>패널 설문</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>Skepticism of Expertise</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>Media Trust</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>2020년 미국 대선 맥락에서 패널 설문으로 ‘스스로 조사하기(DYOR)’ 인식이 뉴스 이용과 주류 언론 태도에 미치는 관련성을 분석했다. DYOR 인식은 초당파적 뉴스 이용과 믿음의 정확성 저하, 언론에 대한 부정적 태도와 연관되어 주류 언론 및 전문성에 대한 불신을 강화할 가능성을 보였다.</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>In the U.S. the availability of news information has grown exponentially while trust in traditional sources of news and information has declined. Amid this high-information, low-trust environment, many now advocate for doing your own research (DYOR) to discern accurate claims from false, misleading, or biased information. The perception that it is better to do one’s own research has important implications for information seeking and attitudes toward mainstream news and journalism. In this study, we use a panel survey to investigate DYOR perceptions in the context of the 2020 U.S. election. We find that DYOR perceptions are associated with decreased nonpartisan news use, decreased belief accuracy, and more negative attitudes toward media, highlighting how information skepticism may be contributing to adversarial views toward mainstream media and expertise. Results suggest that such perceptions encourage negative views of news media and may contribute to distrust of public institutions.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1100,12 +1628,36 @@
           <t>Political Psychology</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr"/>
-      <c r="F24" s="2" t="inlineStr"/>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr"/>
-      <c r="I24" s="2" t="inlineStr"/>
-      <c r="J24" s="2" t="inlineStr"/>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>혼합방법론</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>설문 실험</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Dynamic Norms</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>Outparty Attitudes</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>미국 맥락에서 정당 간 태도 변화에 대한 동적 규범 인식의 오류와 이를 교정하는 메시지가 상대 정당에 대한 인식과 감정에 미치는 영향을 설문 연구와 개입 실험으로 검토했다. 사람들은 다양한 사회 이슈에서 양당의 공통 지지가 증가한 정도를 체계적으로 오인했으며, 현재의 정당 간 격차를 강조하지 않고 태도 변화의 추세만 제시한 메시지는 공통 기반과 소속감에 대한 기대를 높이고 상대 정당에 대한 호감과 긍정적 인상을 소폭 증가시켰다.</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>Abstract Perceptions of social norms, and how those norms change over time, play a central role in shaping how people understand and respond to political divides. We developed and iteratively refined dynamic‐norm messages about bipartisan attitude change to reduce divisive outparty perceptions and attitudes in a US context. We first identified real‐world issues that gained support over time among both Democrats and Republicans and were judged as believable. Study 1 documented systematic misperceptions of attitude change across a range of social issues and linked these misperceptions to colder outparty feelings. We then tested intervention messages that adapted standard static‐norm templates with the addition of information about change over time (dynamic norm; Study 2). This intervention increased expectations of future common ground but did not reliably improve downstream outparty attitudes. Next, we tested a refined intervention message that isolated dynamic norm information (Study 3). The refined dynamic norm message increased expected common ground and expected future feelings of belonging among the outparty and was associated with small but reliable increases in outparty warmth and positive outparty impressions relative to control. These results suggest that emphasizing trajectories of public opinion without highlighting current partisan gaps may be a useful strategy for reducing polarization.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1126,12 +1678,36 @@
           <t>Public Management Review</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr"/>
-      <c r="F25" s="2" t="inlineStr"/>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr"/>
-      <c r="I25" s="2" t="inlineStr"/>
-      <c r="J25" s="2" t="inlineStr"/>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>방법 미상</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>다양한 연구</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>Public Value</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>Policy Learning</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>이 특집호는 공공관리와 글로벌 스포츠 메가이벤트의 관계를 공공가치, 생태계, 학습, 시간성의 관점에서 다룬 세계 각지의 질적·양적, 현재·역사적·종단 연구들을 소개한다. 초록은 개별 연구의 구체적 연구질문이나 종합적 주요 발견을 제시하지 않는다.</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>We are delighted to introduce this Special Issue which collects authors and studies from around the world; qualitative and quantitative, current, historic, and longitudinal. Each paper contributes ...</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1152,12 +1728,36 @@
           <t>International Journal of Public Administration</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr"/>
-      <c r="F26" s="2" t="inlineStr"/>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr"/>
-      <c r="I26" s="2" t="inlineStr"/>
-      <c r="J26" s="2" t="inlineStr"/>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>질적연구</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>반구조화 인터뷰</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Data Value Chain</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>Shared Governance</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>이 연구는 미국 노숙인 서비스 네트워크에서 의무화된 노숙인정보관리시스템(HMIS)의 데이터 인프라가 제공기관 간 협력과 권력관계에 어떻게 영향을 미치는지, 중앙플로리다 CoC 지도자와 서비스 제공자 12명의 반구조화 인터뷰를 주제분석해 검토했다. 표준화된 데이터는 조정·책무성과 집단학습을 높일 수 있지만, 자원·분석역량·의사결정 권한의 격차로 참여의 형평성이 제약되고 데이터 공유가 순응을 강제하는 권력 비대칭을 강화할 수 있는 것으로 나타났다.</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>When governments mandate collaboration, data often becomes the currency for coordination and control. This study examines how data infrastructures shape collaboration and power dynamics within US homelessness service networks, where Continuums of Care (CoCs) coordinate providers through the mandated Homeless Management Information System (HMIS). This study analyzes data from 12 semi-structured interviews of CoC leaders and service providers in Central Florida using thematic analysis informed by the data value chain framework. The findings show that data sharing can enhance coordination and accountability but also reinforce power asymmetries between mandators and collaborators. While standardized data enable collaboration among providers, disparities in resources, analytical capacity, and decision authority constrain equitable participation. The study extends the data value chain model and shows that data-driven collaboration in mandated networks can promote collective learning while also enforcing compliance. These findings suggest that investments in analytical capacity and shared governance can strengthen collaboration in mandated networks.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -1178,12 +1778,36 @@
           <t>International Public Management Journal</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr"/>
-      <c r="F27" s="2" t="inlineStr"/>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr"/>
-      <c r="I27" s="2" t="inlineStr"/>
-      <c r="J27" s="2" t="inlineStr"/>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>서베이</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>종단 설문</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>Conservation of Resources</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>Perceived Organizational Support</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>시민의 무례가 경찰관의 업무 이탈과 이직 의향에 미치는 종단적 영향을 검토하고, 조직지원인식이 이를 완화하는지 1,397명을 대상으로 한 3시점 설문으로 분석했다. 시민의 무례는 업무 이탈을 매개로 이직 의향을 높였으며, 조직지원인식은 이 경로를 약화시켰다.</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>Why do seemingly minor acts of citizen disrespect matter for police retention? Drawing on Conservation of Resources (COR) theory and sociometer theory, this study examines how citizen incivility shapes officers’ withdrawal processes over time. Using a three-wave longitudinal survey of 1,397 police officers, we test whether baseline exposure to citizen incivility predicts subsequent trajectories of work disengagement and turnover intention. We argue that citizen incivility functions as a low intensity but psychologically consequential interpersonal cue that subtly threatens officers’ perceived social standing, depleting psychological resources, fostering disengagement, and ultimately increasing turnover intention. We further propose that perceived organizational support (POS), as a valued resource and a signal of institutional recognition, buffers these adverse effects. Results confirm that citizen incivility indirectly predicts turnover intention through disengagement, and that POS attenuates this pathway. These findings advance understanding of resource-loss dynamics in public service contexts and highlight the protective role of organizational support in sustaining frontline engagement and retention.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -1204,12 +1828,36 @@
           <t>Public Opinion Quarterly</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr"/>
-      <c r="F28" s="2" t="inlineStr"/>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr"/>
-      <c r="I28" s="2" t="inlineStr"/>
-      <c r="J28" s="2" t="inlineStr"/>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>실험</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>후보 컨조인트</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>Political Culture</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>Democratic Backsliding</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>정치문화가 민주주의 후퇴를 초래하는 반민주적 후보에 대한 유권자의 선거 저항을 완화하는지, 미국·폴란드·한국에서 후보 선택 컨조인트 실험으로 비교 분석했다. 자유민주주의의 핵심 제도와 절차에 대한 지지가 정당·이념적 유인이 상충하는 선택에서도 반민주적 후보에 대한 저항을 가장 일관되게 예측했으며, 다른 민주적 지향의 효과는 상대적으로 덜 일관됐다.</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>Abstract Democratic backsliding continues to pose a clear danger to contemporary democracies. While a growing literature shows that voters often tolerate antidemocratic candidates when partisan or ideological incentives pull in that direction, we know less about whether support for democracy, institutional trust, political tolerance, and other democratic orientations ameliorate such temptations. We address this question with a systematic comparison of six measures of political culture as predictors of electoral resistance to antidemocratic candidates. Using candidate-choice conjoint experiments fielded in three democracies facing backsliding pressures—the United States, Poland, and South Korea—we find that several democratic orientations are associated with greater resistance to antidemocratic candidates. Among them, support for the core institutions and processes of liberal democracy stands out as the most consistent predictor. Its relationship with prodemocratic choice remains meaningful even in “cross-pressured” choices where partisan or ideological incentives pull voters away from the prodemocratic option. These findings suggest that political culture matters for democratic resilience, though some components of it matter much more consistently than others.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -1230,12 +1878,36 @@
           <t>Public Administration Review</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr"/>
-      <c r="F29" s="2" t="inlineStr"/>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr"/>
-      <c r="I29" s="2" t="inlineStr"/>
-      <c r="J29" s="2" t="inlineStr"/>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>질적연구</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>역사적 문헌분석</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>Professional Mortality</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>Organized Denial</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>이 연구는 초기 도시관리 전문직에서 높은 이직률인 ‘전문직 사망’의 원인과 이를 둘러싼 조직적 침묵을 분석한다. 역사적 자료에 따르면 폭력과 위협, 정치적 개입, 대인관계상의 실수가 이직을 초래했지만, 전문직 조직과 옹호자들은 1920년대 선거 반대에 대응해 도시관리자제도의 생존을 우선하며 이러한 문제를 공개적으로 인정하거나 집단적으로 대응하지 않았다.</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>ABSTRACT The early city management profession experienced appalling rates of attrition. This problem of “professional mortality” had been clearly recognized by the end of World War I: causes of attrition included threats and violence against managers, intense political interference in managers' work, and interpersonal missteps. Yet the organized management profession and advocates of the manager plan actively ignored threats and were unwilling to respond collectively or officially to political interference; leading scholars recognized but did not publicly discuss common interpersonal problems faced by managers. This silence on the underlying causes of turnover marked an effort to protect the manager plan's viability in the face of growing electoral opposition during the 1920s, placing the interests of the profession above its practicing members. The optimistic, rationalist discourses of advocates, scholars, and professional leaders rested on self‐conscious denial of uncomfortable realities; a full historical accounting may help avoid repeating these mistakes.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -1256,12 +1928,36 @@
           <t>Political Communication</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr"/>
-      <c r="F30" s="2" t="inlineStr"/>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr"/>
-      <c r="I30" s="2" t="inlineStr"/>
-      <c r="J30" s="2" t="inlineStr"/>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>질적연구</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>계산적 텍스트 분석</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>Democratic Resilience</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>Populism</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>스웨덴과 헝가리 정당 지도자들의 2022~2024년 페이스북 게시물 9,737건을 계산적 텍스트 분석으로 비교해, 정치인들이 민주주의의 어떤 차원을 강조하고 그 담론이 포퓰리즘·집권/야당 지위·정치적 사건에 따라 어떻게 달라지는지 분석했다. 헝가리 집권 세력은 민주주의를 포퓰리즘적·성과 중심적으로 구성한 반면, 스웨덴에서는 포퓰리스트와 비포퓰리스트 모두 숙의적 레퍼토리를 공유했으며, 헝가리의 담론은 사건 주도적이고 스웨덴의 담론은 지속적·비판적으로 성찰적이었다.</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>While most research on democratic resilience and decline focuses on institutional erosion, less is known about how these shifts manifest in elite political communication. We examine how democratic resilience and decline are articulated on Facebook by political leaders, comparing Hungary, an archetype of informational autocracy, and Sweden, a case of resilient democracy. Drawing on 9,737 Facebook posts from 10 Swedish and 9 Hungarian party leaders between 2022 and 2024, we use computational text analysis to identify linguistic, rhetorical, and emotional patterns. We address three research questions: (1) What dimensions of democracy do politicians emphasize, and how do these emphases differ between resilient and backsliding contexts? (2) How do populism and government/opposition dynamics shape these patterns? (3) How do patterns vary across campaigns, crises, and routine communication? Our results show that democracy is not only institutional but also communicatively produced through distinct discursive logics. Disaggregating by actor affiliation and populist orientation reveals that actors in the Hungarian government frame democracy in populist, performance-based terms. In contrast, in Sweden, both populists and non-populists communicate within a shared, deliberative repertoire. Temporal analysis highlights that Hungary’s discourse on democracy is event-driven and affirmatively neutral, while Sweden’s is sustained and critically self-reflective. We advance the concept of elite communicative resilience, finding that patterns of democratic discourse differ markedly between resilient and backsliding contexts in ways that parallel institutional differences.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -1282,12 +1978,36 @@
           <t>Public Administration</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr"/>
-      <c r="F31" s="2" t="inlineStr"/>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr"/>
-      <c r="I31" s="2" t="inlineStr"/>
-      <c r="J31" s="2" t="inlineStr"/>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>질적연구</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>민족지 연구</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>Responsible Algorithmization</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>Sense-Making</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>이 논문은 공공부문에서 공공가치를 보호하는 책임 있는 알고리즘화를 어떻게 이해할 수 있는지 묻고, 네덜란드의 규제·경찰·보건의료 분야를 대상으로 민족지 연구를 수행했다. 분석 결과 알고리즘화는 사전에 구조화되고 중립적이며 폐쇄적인 과정이 아니라 emergent하고 정치적이며 개방적이고 파편적인 과정이므로, 형식적 구조와 절차에 초점을 둔 합리적 접근만으로는 충분하지 않으며 수동적 책임뿐 아니라 능동적 책임도 다뤄야 한다.</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>ABSTRACT Responsible algorithmization refers to the use of algorithms in the public sector while safeguarding public values. Approaches to responsible algorithmization suggested by the EU, OECD, and others depart from a rational perspective and highlight formal structures and procedures. This paper complements this perspective by adding a “natural perspective,” which emphasizes sense‐making and actual practices. This natural perspective is used for a set of ethnographic studies of algorithmization in three domains in the Netherlands: regulation, policing, and healthcare. Our findings show that algorithmization of government organizations is an emergent, political, open, and fragmented process, rather than, as assumed by rational approaches to responsible algorithmization, pre‐structured, neutral, closed, and simple. This means that rational approaches fall short of providing a comprehensive basis for establishing responsible algorithmization. We conclude that not only passive responsibility but also active responsibility for algorithmization in the public sector needs to be addressed to safeguard public values.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -1308,12 +2028,36 @@
           <t>International Public Management Journal</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr"/>
-      <c r="F32" s="2" t="inlineStr"/>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr"/>
-      <c r="I32" s="2" t="inlineStr"/>
-      <c r="J32" s="2" t="inlineStr"/>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>혼합방법론</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>국가 패널 분석</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Gender Equity</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>Stakeholder Satisfaction</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>56개국 TIMSS 2011~2019 국가 간 패널 자료를 활용해 교육 성취도의 성별 격차와 학생·학부모의 학교 만족도 및 교사의 직무 만족도 간 관계를 분석했다. 성별 불평등은 낮은 만족도와 관련되며, 여학생 학부모와 사회경제적 지위가 높은 학부모가 성별 격차에 가장 크게 반응했다.</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>This study examines how gender equity in educational achievement relates to the satisfaction of three key stakeholders: students, parents, and teachers. Using cross-national panel data from the Trends in International Mathematics and Science Study (TIMSS), covering 56 countries from 2011 to 2019, we link gender gaps in student math and science performance to student and parent satisfaction with schooling, as well as teacher satisfaction with their jobs. We find that gender inequity is associated with lower satisfaction, but parents with a female student and higher SES respond to the gender inequity the most. These findings extend the citizen satisfaction and public service equity literatures by showing that different stakeholders in the same public service system can respond quite differently to inequities, with implications for how governments communicate about and address performance gaps and equity concerns.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -1334,12 +2078,36 @@
           <t>Public Performance &amp; Management Review</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr"/>
-      <c r="F33" s="2" t="inlineStr"/>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr"/>
-      <c r="I33" s="2" t="inlineStr"/>
-      <c r="J33" s="2" t="inlineStr"/>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>실험</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>지방정부 패널</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>Bounded Rationality</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>Blame Avoidance</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>중국 지방정부의 정부업무보고(2013~2019년) 자료를 활용해, 제한된 합리성과 책임회피 이론에 기반하여 긍정·부정 성과 피드백이 네 가지 전략적 보고 방식에 미치는 영향을 로짓모형으로 분석했다. 네 가지 전략 모두 부정적 성과 피드백과 정(+)의 관련성을 보였으며, 역사적 비교 기준 이동을 제외한 세 전략은 긍정적 성과 피드백과 부(-)의 관련성을 보였다.</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>Previous research on performance gaming behavior has primarily focused on data manipulation and effort manipulation. This article examines strategic reporting, a broad form of performance gaming in public organizations, by identifying four strategies: text-only reporting, social comparison benchmark shifting, historical comparison benchmark shifting, and absolute level absence. Drawing on theories of bounded rationality and blame avoidance, it investigates how positive and negative performance feedback shape strategic reporting behavior. Using data from Chinese municipal governments (2013–2019), logit model results suggest systematic variation across four strategic reporting strategies. All four strategies are positively associated with negative performance feedback, while all strategies but historical benchmark shifting are negatively associated with positive performance feedback. These findings contribute to the literature on performance gaming and performance feedback, while offering practical implications for strengthening governmental transparency and accountability.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -1360,12 +2128,36 @@
           <t>Public Administration</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr"/>
-      <c r="F34" s="2" t="inlineStr"/>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr"/>
-      <c r="I34" s="2" t="inlineStr"/>
-      <c r="J34" s="2" t="inlineStr"/>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>혼합방법론</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>회상 실험·현장 설문</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>Public Service Motivation</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>Moral Elevation</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>공공부문 교육에서 도덕적 모범 인물에 노출되는 것이 공공서비스동기(PSM)를 어떻게 강화하는지, 회상 실험과 현장 설문을 결합해 분석했다. 드문 도덕적 모범 인물에 대한 노출은 도덕적 고양을 유발하고, 이것이 심리적 자원 보충을 통해 PSM을 높였으며, 인지적 부담이 클수록 그 동기 효과가 강했다.</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>ABSTRACT Public service motivation (PSM) is widely recognized as a predictor of positive outcomes, yet relatively little is known about how it can be deliberately cultivated. Drawing on conservation of resources (COR) theory, the present research investigates whether and how exposure to moral exemplars embedded in public‐sector training enhances PSM. Employing a multi‐method design that combines a recall experiment with a field survey, we find that exposure to uncommon moral exemplars elicits moral elevation, which functions as a replenishment of psychological resources and, in turn, strengthens public employees' PSM. Moreover, this mediating mechanism is moderated by cognitive load, such that public employees experiencing greater cognitive demands derive stronger motivational benefits from moral elevation. By identifying moral elevation as a psychological resource mechanism and cognitive load as a boundary condition, this research opens the “black box” of PSM development. It highlights how training can serve as an institutional platform for delivering specific moral content that cultivates and sustains public employees' motivation to serve.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -1386,12 +2178,36 @@
           <t>International Public Management Journal</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr"/>
-      <c r="F35" s="2" t="inlineStr"/>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr"/>
-      <c r="I35" s="2" t="inlineStr"/>
-      <c r="J35" s="2" t="inlineStr"/>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>질적연구</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>사례연구·인터뷰</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>Public Value</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>이 연구는 네덜란드 정부기관에서 맥락이 공공가치 평가(PVA)의 실제 수행에 어떤 영향을 미치는지 질적 사례연구로 분석했다. 인터뷰와 문헌 검토, 기관 내 검증 세션을 통해 PVA가 독립적 분석이 아니라 행위자의 역할, 거버넌스 arrangements, 상호작용에 의해 형성되는 지속적 실천이며, 네 가지 맥락적 긴장이 이를 좌우한다는 점을 밝혔다.</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>How does context influence the practice of public values assessment (PVA)? This study examines how PVA is shaped in practice within a Dutch government organization. It constitutes a qualitative case study at the Dutch Central Government Real Estate Agency, based on interviews with policymakers and public managers, complemented by literature review and validation sessions within the agency. The study identifies four contextual tensions that shape how PVA is performed: (1) single-actor, single-level activity versus multi-actor, multi-level activity; (2) role clarity versus role ambiguity; (3) individual discretion versus organizational steering; and (4) emergent activity versus deliberate activity. The findings show that PVA is not a standalone analytical exercise, but a situated and ongoing practice shaped by organizational roles, governance arrangements, and interactions between actors. By grounding these tensions empirically, this study advances public value theory by showing how context conditions the practice of PVA in real-world settings.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -1412,12 +2228,36 @@
           <t>International Public Management Journal</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr"/>
-      <c r="F36" s="2" t="inlineStr"/>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr"/>
-      <c r="I36" s="2" t="inlineStr"/>
-      <c r="J36" s="2" t="inlineStr"/>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>혼합방법론</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>시차 다원자료</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Prosocial Impact</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>High-Performance Work Systems</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>공공의료 종사자의 부정적 수혜자 접촉이 서비스 지향 조직시민행동과 어떤 관계를 맺는지, 그리고 서비스 지향 고성과작업시스템(HPWS)이 이를 어떻게 조절하는지 검토했다. 루마니아와 이집트 병원의 간호사·직속 상사를 대상으로 한 시차·다원 자료 분석 결과, 친사회적 영향이 두 변수의 관계를 매개했지만 HPWS 인식이 높을 때 이 간접효과는 유의하지 않았다.</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>Although public healthcare workers frequently encounter negative interactions with patients and care recipients, research on how such contact shapes staff behavior is limited. The purpose of the current study is to advance knowledge of _how_ and _under what conditions_ negative beneficiary contact is related to service-oriented organizational citizenship behaviors (OCBs) in public healthcare organizations. Drawing on the relational job design perspective, this study examines prosocial impact as a mediator of the link between negative beneficiary contact and service-oriented OCBs, and the buffering role of service-oriented high-performance work systems (HPWS) on this mediated relationship. Two time-lagged, multisource datasets from nurses and their direct supervisors in hospitals in Romania (Study 1) and Egypt (Study 2) were used to test the proposed model. The results showed that prosocial impact mediates the relationship between negative beneficiary contact and service OCBs, but this indirect link was insignificant when perceptions of HPWS were high. Implications for public management theory and practice are discussed.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -1438,12 +2278,36 @@
           <t>Political Behavior</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr"/>
-      <c r="F37" s="2" t="inlineStr"/>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr"/>
-      <c r="I37" s="2" t="inlineStr"/>
-      <c r="J37" s="2" t="inlineStr"/>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>실험</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>신문기사 실험</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>Affective Polarization</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>Ideological Extremity</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>독일의 두 실험에서 신문 기사에 양극화 단서를 포함하거나 제외해, 이러한 단서가 이념적 외집단에 대한 인식과 행동에 미치는 영향을 검증했다. 양극화 단서는 정서적 양극화와 이념적 극단성을 높였지만, 독재자 게임에서는 외집단에 대한 공유를 줄인 반면 신뢰 게임에서는 상호 이익이 가능한 협력을 늘리는 등 행동 효과는 맥락에 따라 달랐다.</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>Abstract Do media depictions of a ‘polarized society’ merely describe division or actually deepen it? We report two laboratory experiments in Germany (Study1 $$N=302$$ ; Study2 $$N=295$$ ). After reading authentic newspaper articles in which brief polarization cues were experimentally included versus omitted, participants (i) completed standard affective- and ideological-polarization measures and (ii) played incentivized Dictator, Ultimatum, and Trust Games with ideological out-group partners. Polarization cues increased both affective polarization and ideological extremity. Behavioral responses, however, were mixed. In the Dictator Game, where the recipient cannot respond, treated participants shared less with the out-group. In the Trust Game, characterized by mutual dependence and potential efficiency gains, treated participants sent more to out-group partners. Ultimatum behavior, where interdependence is partial, showed weaker and less consistent shifts. Taken together, polarization cues reliably heighten perceived division but do not uniformly translate into behavioral antagonism: even after cues that increase self-reported polarization, participants can still cooperate with ideological opponents when cooperation is perceived as mutually beneficial.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -1464,12 +2328,36 @@
           <t>International Public Management Journal</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr"/>
-      <c r="F38" s="2" t="inlineStr"/>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr"/>
-      <c r="I38" s="2" t="inlineStr"/>
-      <c r="J38" s="2" t="inlineStr"/>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>질적연구</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>문서 분석·인터뷰</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>Collaborative Platforms</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>Coordination</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>노르웨이의 ‘생애사건’ 디지털 서비스 նախաձեռն উদ্যোগ을 대상으로, 문서 분석과 정부 관계자·플랫폼 조정자 22명에 대한 반구조화 인터뷰를 통해 협업 플랫폼의 조정 과제를 분석했다. 협업 플랫폼은 부문 간 상호작용과 공동창출을 지원하도록 설계되지만, 제한된 자원·불명확한 역할·비지원적 규제라는 구조적 장벽과 규범·기대·책임 해석을 둘러싼 문화적 긴장으로 그 효과와 지속·확장 가능성이 제약되는 것으로 나타났다.</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>Collaborative platforms are increasingly used to coordinate digital public services across organizational boundaries, yet how they function in practice remains poorly understood. This study examines the coordination challenges such platforms face, drawing on Norway’s “life event” initiatives—programs designed to deliver integrated, user-centered digital services across government sectors. Based on document analysis and semi-structured interviews with 22 government actors and platform coordinators, the study finds that while collaborative platforms are designed to enable cross-sectoral interaction and co-creation, their effectiveness is constrained by structural barriers—including limited resources, unclear roles, and unsupportive regulatory frameworks—and by cultural tensions over norms, expectations, and interpretations of responsibility. These findings clarify the concept of collaborative platforms in public management research, showing how coordination challenges shape their operation and outcomes. The study contributes to digital governance scholarship by identifying the difficulties public managers face in steering and sustaining scalable collaborative arrangements for digital transformation and public service delivery.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -1490,12 +2378,36 @@
           <t>Public Administration</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr"/>
-      <c r="F39" s="2" t="inlineStr"/>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr"/>
-      <c r="I39" s="2" t="inlineStr"/>
-      <c r="J39" s="2" t="inlineStr"/>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>질적연구</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>정책문서 내용분석</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>Public Values</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>AI Governance</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>미국 연방 AI 정책이 핵심 공공가치를 어떻게 반영하거나 간과하는지 분석하기 위해 2020~2023년 정책 문서의 120개 조항을 체계적으로 검토하고, AI 위험·피해와 공공가치의 연계를 구축했다. 개인 권리·공익·책임성은 자주 다뤄졌지만 시민 참여·직장 기준·대응성에 대한 추가 지침이 필요했으며, 규제 수단이 서비스 기반·정보 제공 수단보다 공공가치를 더 많이 반영했다.</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>ABSTRACT Governments at all levels are grappling with AI's implications for public administration. Because federal actions often establish the principles guiding wider governance efforts, this study asks how US federal AI policies reflect—or fail to reflect—core public values. Drawing on a dataset of US federal AI policies from 2020 to 2023, we systematically analyze the risks, harms, and governance strategies employed across government‐issued and enacted policy documents. Specifically, we analyze 120 discrete policy sections or subsections of federal laws and regulations, utilizing the parsing approach of the AI Governance and Regulatory Archive (AGORA), all of which regulate the operation of the government itself rather than private sector behavior. We develop a theoretical and empirical crosswalk linking AI‐related risks and harms to prominent public values. Results indicate that while values such as individual rights, the common good, and accountability are regularly invoked, additional guidance around public values like citizen engagement, workplace standards, and responsiveness may be necessary to prevent public value failure. The study further categorizes governance strategies in AI policy documents into regulatory, service‐based, and informational instruments, and finds that regulatory policies are most likely to engage with public values.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -1516,12 +2428,36 @@
           <t>Political Psychology</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr"/>
-      <c r="F40" s="2" t="inlineStr"/>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr"/>
-      <c r="I40" s="2" t="inlineStr"/>
-      <c r="J40" s="2" t="inlineStr"/>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>서베이</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>횡단면 설문분석</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>System Justification Theory</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>Meritocratic Ideology</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>라틴계·아시아계 미국인의 능력주의 이데올로기 수용이 추방 정책 태도 및 추방에 대한 정서적 우려와 어떤 관련이 있는지 2024년·2020년 다인종 선거 후 공동조사 자료로 분석했다. 능력주의 이데올로기가 강할수록 추방 정책 지지는 높고 추방에 대한 정서적 우려는 낮았다.</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>Abstract Why do some Latino and Asian Americans support conservative policies that may discriminate against them? Elaborating on system justification theory, we argue that ideologies such as meritocracy perpetuate the status quo by placating marginalized groups and assuaging their emotional concerns regarding their unfair treatment. This research examined the extent to which endorsing meritocratic ideology is associated with deportation policy attitudes and the degree of emotional concern about deportation among Latino and Asian Americans. Using data from the 2024 and 2020 Collaborative Multiracial Post‐Election Surveys, we find that higher meritocratic ideology predicted greater support for deportation policies and lower emotional concern about deportation for Latino and Asian Americans. This research demonstrates that Latino and Asian Americans who have ingrained the ethos of meritocracy are more likely to support conservative policies and develop sentiments that work against the interests of their communities.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -1542,12 +2478,36 @@
           <t>International Journal of Public Administration</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr"/>
-      <c r="F41" s="2" t="inlineStr"/>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr"/>
-      <c r="I41" s="2" t="inlineStr"/>
-      <c r="J41" s="2" t="inlineStr"/>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>실험</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>피험자 내 비네트</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>Representative Bureaucracy</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>Social Stereotypes</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>중국 관료 679명을 대상으로 한 피험자 내 비네트 실험을 통해, 사회적으로 낙인찍힌 여성 마사지 종사자 관련 재량적 판단에서 성별 일치와 사회적 고정관념의 상호작용을 분석했다. 여성 관료의 판단에서는 사회적 고정관념보다 성별 일치가 더 큰 영향을 미쳐, 낙인과 차별의 가능성에도 불구하고 공유된 성별 특성이 지지적 결정을 촉진하는 것으로 나타났다.</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>How female street-level bureaucrats navigate decisions involving socially stigmatized female clients lies at the intersection of a theoretical debate between representative bureaucracy and street-level stereotyping research. It also reflects a practical dilemma stemming from regulatory gaps in China’s online-to-offline (O2O) massage apps that compel frontline workers to adjudicate ambiguous disputes involving suspected sexual assault or sex work. Using a within-subject vignette experiment with 679 Chinese bureaucrats, this study examines how gender congruence and social stereotypes interact to shape discretionary decisions in high-discretion contexts. Findings reveal that gender congruence outweighs social stereotypes in shaping female bureaucrats’ decisions regarding stigmatized female massage therapists, suggesting that shared demographic traits foster supportive interactions (representation) even as they are counteracted by stigmatizing stereotypes (discrimination). These results highlight the role of individual-level discretion in protecting vulnerable groups and promoting social equity within regulatory gray areas, underscoring the need for more representative, socioculturally aware street-level bureaucracies.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -1568,12 +2528,36 @@
           <t>Public Administration Review</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr"/>
-      <c r="F42" s="2" t="inlineStr"/>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr"/>
-      <c r="I42" s="2" t="inlineStr"/>
-      <c r="J42" s="2" t="inlineStr"/>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>이론/개념</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>비교 사례 적용</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>Bureaucratic Repair</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>Democratic Backsliding</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>이 논문은 비자유주의 통치 이후 관료국가를 어떻게 복구할 수 있는지, 그리고 복구 전략의 선택과 한계가 비자유주의적 제도 고착 정도 및 후임 정부의 법·정치적 역량과 어떻게 연관되는지를 탐색적 틀로 분석한다. 폴란드·브라질·헝가리를 적용 사례로 검토한 결과, 공식·제도적 복구가 전문 규범·전문성·신뢰의 재구축보다 앞섰고, 비자유주의 시기의 수단이 일부 존속하는 층위적 행정질서가 형성되어 복구는 구조적으로 비대칭적이며 현상태 이전으로의 완전한 복귀는 어렵다고 본다.</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>ABSTRACT While scholarship has documented how populist and authoritarian‐leaning executives deform bureaucratic institutions, post‐illiberal reconstruction has only begun to receive attention. This paper develops an exploratory framework distinguishing four repair strategies (neutralizing, rectifying, balancing, and democratic hardening) and two repair modes (formal‐institutional and normative‐capacity repair). Applying the heuristic to Poland, Brazil, and Hungary, we posit that the selection and limits of repair strategies follow the gap between the depth of illiberal entrenchment and the legal‐political capacity of successor governments to overcome veto players and enact rectifying reforms. Within the periods observed, formal‐institutional repair has outpaced the reconstruction of professional norms, expertise, and trust, and repair has produced layered administrative orders in which illiberal‐era instruments partly persist and thus remain available to future governments. Administrative repair is thus structurally asymmetric. Democratic successors can rebuild the administrative state, but they are unlikely to restore it to the status quo ante.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -1594,12 +2578,36 @@
           <t>Public Administration Review</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr"/>
-      <c r="F43" s="2" t="inlineStr"/>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr"/>
-      <c r="I43" s="2" t="inlineStr"/>
-      <c r="J43" s="2" t="inlineStr"/>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>혼합방법론</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>회귀분석·인터뷰</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>Investor Orientation</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>Investor Commitment</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>성과기반 공공서비스 계약에서 투자자 지향성(사회적·재무적·이중 목적)이 투자 약정 규모와 어떻게 관련되는지, 전 세계 338개 계약의 기술통계·회귀분석과 질적 인터뷰를 통해 분석했다. 사회적 지향 투자자는 재무적·이중 목적 투자자보다 일관되게 더 큰 금액을 약정했으며, 인터뷰에서는 평판 위험, 현지 여건에 대한 제한적 이해, 성과 측정의 복잡성이 억제 요인으로 나타났다.</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>ABSTRACT Outcomes‐based contracts (OBCs) organize public service delivery around measurable results, yet little is known about how different investors engage with these instruments. This article examines how investor orientation (social, financial, or dual‐purpose) shapes investor commitment in OBCs worldwide. Drawing on a global dataset of 338 contracts, we combine descriptive analyses, regression models, and qualitative interviews to investigate how investor orientation relates to investment scale. We hypothesize that OBCs involving socially oriented investors are associated with higher levels of investment than those involving financially or dual‐purpose investors. Consistent with this prediction, socially oriented investors consistently commit larger amounts, whereas financially oriented and dual‐purpose investors typically participate with smaller contributions. These patterns challenge a central premise of OBCs: that such instruments would mobilize significant mainstream private capital for public services. Interview evidence points to reputational risks, limited familiarity with local conditions, and outcome measurement complexity as key deterrents.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -1620,12 +2628,36 @@
           <t>Review of Public Personnel Administration</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr"/>
-      <c r="F44" s="2" t="inlineStr"/>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr"/>
-      <c r="I44" s="2" t="inlineStr"/>
-      <c r="J44" s="2" t="inlineStr"/>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>준실험</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>패널 자료 분석</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>Job Satisfaction</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>Stress</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>덴마크 경찰 조직개발 변화 전후의 패널 자료를 활용해 스트레스와 직무만족도가 질병 결근 및 질병 출근에 미치는 경로와 변화 유형별 출근 양상을 분석했다. 질병 결근은 직무만족도나 스트레스보다 변화 유형의 영향을 주로 받았고, 장기 비전 지원형 변화에서는 결근이 감소했으며, 질병 출근은 변화 유형과 무관하게 직무만족도가 높을수록 감소했다.</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>This study investigates sickness absenteeism and sickness presenteeism in the context of organizational development (OD) changes in the police force, focusing on health-related and motivational pathways. Using panel data from 407 employees from 36 Danish police units (1,021 observations), we analyze attendance patterns before the change, immediately after, and 1 year later. Findings reveal that sickness absenteeism is primarily influenced by the type of OD change rather than by job satisfaction or stress, while sickness presenteeism decreases with higher job satisfaction independent of the change type. Notably, employees experiencing an OD change aimed at supporting a long-term vision exhibit reduced sickness absence in the change period. OD changes focused on distributed leadership and enhancing employee motivation did not have the same effect on sickness absenteeism. These results underscore the importance of considering both motivational and health-related dynamics, as well as the type of change, in understanding attendance during OD change.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -1646,12 +2678,36 @@
           <t>Public Management Review</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr"/>
-      <c r="F45" s="2" t="inlineStr"/>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr"/>
-      <c r="I45" s="2" t="inlineStr"/>
-      <c r="J45" s="2" t="inlineStr"/>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>질적연구</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>사례 비교 분석</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>transformative governance</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>small wins</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>이 연구는 사회 변혁을 위한 디자인의 잠재력이 실현되지 못하는 장벽과 이를 극복하는 전략을 어떻게 설명할 수 있는지 묻고, 디자인 실천에서의 세 사례를 ‘맥락 안의 디자인·맥락 설계·맥락 디자인’의 세 수준으로 분석했다. 장벽은 세 수준에 걸쳐 상호 연관되며, 디자인의 변혁적 특성을 활용하면 이를 헤쳐 나갈 수 있고, 디자인은 ‘작은 승리’의 논리로 작동하는 변혁적 거버넌스 방식이 될 수 있음을 제시한다.</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>Design is increasingly recognized as a promising approach to foster societal transformation, yet its transformative potential is rarely realized. Empirical guidance on how to unlock this potential remains limited. To address this gap, we first conceptualize design for societal transformation as operating across three levels of design activity – i.e. design within context, designing context, and design of context – in mutually reinforcing ways to enable broad, deep, and lasting change. Using this lens, we then examine three cases from our own design practice to identify (1) key barriers constraining design’s transformative potential, and (2) main strategies that can be employed to navigate them. Our analysis reveals that barriers interrelate across the three levels of design activity, and that design’s inherent transformative qualities can be leveraged to navigate them. Together, these insights suggest that design can function as a mode of transformative governance that operates through a small wins logic.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -1672,12 +2728,36 @@
           <t>Journal of Public Administration Research and Theory</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr"/>
-      <c r="F46" s="2" t="inlineStr"/>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr"/>
-      <c r="I46" s="2" t="inlineStr"/>
-      <c r="J46" s="2" t="inlineStr"/>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>준실험</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>종단 패널분석</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>Institutional Conversion</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>Information Governance</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>브라질 지방정부가 유사한 제도적 조건에서도 서로 다른 디지털 전환 경로를 보이는 이유를 규명하기 위해, 2004~2024년 7개 시점의 5,569개 지방정부 패널에 고정효과 모형과 궤적 기반 군집분석을 적용했다. 기술 역량 증가는 디지털 서비스 확대와 관련되지만 그 효과는 점진적·조건부였으며, 정보 거버넌스가 기술 자원의 지속적 활용을 형성하고 비선형적·체감적인 네 가지 전환 궤적이 나타났다.</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>Abstract This article asks a central question in digital government research: why do local governments operating under similar institutional conditions follow sharply different digital transformation trajectories over time? Drawing on theories of gradual institutional change, the study conceptualizes digital transformation not as a discrete adoption outcome, but as a process of institutional conversion through which technological capacity is translated into sustained digital service provision. Information governance is theorized as the key conditioning mechanism linking technological resources to durable organizational outcomes. The analysis combines longitudinal panel models, fixed-effects estimators, and trajectory-based clustering using a panel of all Brazilian municipalities (MUNIC/IBGE; N = 5,569) across seven waves between 2004 and 2024. Results show that increases in technological capacity are associated with subsequent gains in digital services, but these effects are gradual and conditional. Information governance significantly shapes how municipalities mobilize and stabilize technological resources over time, while interaction models reveal non-linear and diminishing returns consistent with institutional coordination limits. Trajectory analyses identify four distinct patterns of digital transformation, ranging from ‘institutionalized pioneers’ to ‘persistent stagnation’, demonstrating that digital development unfolds through path-dependent and institutionally anchored trajectories rather than through simple convergence. The article contributes to public administration research in three ways: provides rare longitudinal evidence on local digital transformation over two decades; integrates institutional change theory into digital government research by conceptualizing governance as a mechanism of institutional conversion; and advances a trajectory-based explanation of digital transformation that shifts attention from episodic technological adoption to cumulative institutional processes shaping long-run administrative performance.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -1698,12 +2778,36 @@
           <t>Public Administration</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr"/>
-      <c r="F47" s="2" t="inlineStr"/>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr"/>
-      <c r="I47" s="2" t="inlineStr"/>
-      <c r="J47" s="2" t="inlineStr"/>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>질적연구</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>구성적 유형화</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>co-production</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>governance pathways</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>이 연구는 공공서비스 공동생산의 구체적 거버넌스 경로가 어떻게 형성되는지를 탐구하기 위해 상하이 지역재생사업 76개를 분석했다. 분석 결과, 제공자의 역량·시민의 권한부여·정치적 리더십·공공서비스 특성의 조합에 따라 국가 주도형과 시민 주도형 공동생산 및 그 하위 유형이 나타나는 것으로 확인됐다.</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>ABSTRACT This study addresses the under‐theorized formation of specific co‐production arrangements by exploring governance pathway formation. Using 76 community regeneration projects in Shanghai, we identify a parsimonious two‐level typology: State‐led co‐production (comprising sub‐type A: state as operator and sub‐type B: non‐state as operator ) and Citizen‐led co‐production (comprising sub‐type C: volunteers as operator and sub‐type D: users as operator ). Findings reveal pathway emergence is contingent upon configurations of providers' capabilities, citizen empowerment, political leadership, and public service characteristics, reflecting logics associated with Neo‐Weberian State, New Public Management, and New Public Governance paradigms. The study shifts focus from static lists to dynamic governance pathways by proposing a configurational contingency framework that explains how governance logics are activated by specific contextual conditions.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -1724,12 +2828,36 @@
           <t>Political Analysis</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr"/>
-      <c r="F48" s="2" t="inlineStr"/>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr"/>
-      <c r="I48" s="2" t="inlineStr"/>
-      <c r="J48" s="2" t="inlineStr"/>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>실험</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>현장 무작위실험</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>Political Participation</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>Voice</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>네덜란드 정당의 회원 3만 5천 명 이상을 대상으로 선거 전 두 차례 현장실험을 실시해, 개인 전화·이메일·두 방식 병행이 자원봉사 참여를 늘리고 활동가 기반을 다양화할 수 있는지 검증했다. 의견을 말할 기회를 제공한 전화는 특히 젊은 회원의 자원봉사 신청을 크게 늘렸지만, 이메일은 효과가 없었다.</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>Abstract Political parties in advanced democracies face a dual challenge: fewer citizens are willing to volunteer, and those who remain active are disproportionately older and male. This is troubling given the central role that volunteers play in campaigns and party processes. Whether party leaders can recruit a larger and more diverse activist base remains an open question. We partnered with a major party in the Netherlands and conducted two field experiments before the 2021 general and 2022 municipal elections, targeting over 35,000 party members. The party randomized whether members received a personal call, an email or both. Results show that calls—where members could voice their opinions—increased volunteer sign-up rates (83% in Study 1 and 361% in Study 2), especially among younger members. By contrast, emails had no effect. These findings clarify mixed evidence in the literature, suggesting that voice opportunities are key to expanding and diversifying the activist base.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -1750,12 +2878,36 @@
           <t>Political Communication</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr"/>
-      <c r="F49" s="2" t="inlineStr"/>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr"/>
-      <c r="I49" s="2" t="inlineStr"/>
-      <c r="J49" s="2" t="inlineStr"/>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>실험</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>무작위 광고 실험</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>Emotional Appeals</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>Persuasion</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>2016년 미국 대선 기간 29주 동안 약 2만8천 명을 대상으로 48개의 실제 선거광고와 위약을 무작위 배정한 실시간 실험을 실시해, 광고의 정서 반응과 설득 효과의 관계를 검토했다. 광고는 주로 당파적으로 정서를 변화시켰지만, 정서 반응의 크기는 후보 호감도·투표 의향·정책 선호·투표 참여 의향에 대한 광고 효과의 크기를 예측하지 못했다.</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>We evaluate whether campaign advertisements that generate larger emotional reactions also generate larger persuasive effects in contemporary elections. We analyze 29 weeks of experiments conducted during the 2016 U.S. presidential campaign, in which 48 authentic campaign ads were tested in real time, often within days of their debut. The ads and a placebo were randomly assigned to approximately 28,000 subjects. We find that campaign ads reliably move emotions, albeit in largely partisan ways, with comparatively muted reactions among independents. Critically, however, these emotional reactions do not predict the magnitude of an ad’s effect on candidate favorability, vote intention, policy preferences, or turnout intention. Our results cast doubt on emotion-based accounts of advertising persuasion in polarized elections and caution practitioners against using self-reported emotional reactions as a measure of message effectiveness.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -1776,12 +2928,36 @@
           <t>Policy Studies Journal</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr"/>
-      <c r="F50" s="2" t="inlineStr"/>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr"/>
-      <c r="I50" s="2" t="inlineStr"/>
-      <c r="J50" s="2" t="inlineStr"/>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>준실험</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>이중차분·불연속</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>Particularism</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>Universalism</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>복지정책의 범위·급여·포괄 기준에서 특수주의와 보편주의의 결합 변화가 취약한 저지위 집단에 대한 대중의 태도에 어떤 영향을 미치는지 분석했다. 중국 호구제도 개혁 기간의 웨이보 게시물을 대상으로 이중차분과 회귀불연속 분석을 실시한 결과, 특수주의적 구성으로의 변화는 저숙련 이주노동자에 대한 부정적 태도와, 보편주의적 구성으로의 변화는 긍정적 태도와 연관되었다.</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>ABSTRACT Welfare policies often combine particularistic and universalistic elements, yet we know less about how shifts in this balance shape public attitudes toward vulnerable low‐status groups. This article develops a three‐dimensional framework for analyzing welfare policy, distinguishing among welfare scope, welfare benefits, and inclusion criteria. We argue that public attitudes toward lower‐status groups are shaped by the combined signal about the welfare deservingness hierarchy generated by the configuration of particularistic and universalistic elements across these dimensions. Because policy design packages convey a broader normative stance about who belongs and who deserves, they can influence perceptions of groups that are not directly targeted by a policy change, lowering or raising their perceived deservingness. Using difference‐in‐differences and regression discontinuity methods, we analyze Weibo posts during China's two‐round hukou reform. We find that shifts toward more particularistic policy configurations lead to more negative attitudes toward low‐skilled migrant workers, whereas shifts toward more universalistic configurations yield more positive attitudes. Subgroup analyses yield suggestive patterns across local economic contexts and individual characteristics. These findings have broader implications for research on welfare policy systems and for reform efforts regarding social integration.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -1802,12 +2978,36 @@
           <t>Political Psychology</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr"/>
-      <c r="F51" s="2" t="inlineStr"/>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr"/>
-      <c r="I51" s="2" t="inlineStr"/>
-      <c r="J51" s="2" t="inlineStr"/>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>서베이</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>다집단 측정검증</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>Science-Related Populism</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>Measurement Invariance</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>이 연구는 SciPop 척도의 요인구조·신뢰도·측정불변성과 국가·집단 간 비교 가능성을 검토하고, Bollen식과 Goertz식 점수 산정 및 다차원 문항반응이론을 비교했다. 68개국 자료와 스위스 자료에서 4요인 모형이 가장 넓게 적합했으며, 국가 간 비교는 제한적이지만 측정 정렬로 개선되고 Bollen 기반 정렬 점수가 기준타당도에서 일관되게 우수했다.</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>Abstract Science‐related populism—populist attitudes toward scientific authority—has attracted growing scholarly attention. Although the SciPop Scale measures this construct, its cross‐national psychometric properties remain underexamined. Using data from the Trust in Science and Science‐Related Populism project ( N = 69,341; 68 countries/regions) and the Swiss Science Barometer ( N = 1124), we evaluate factor structure and reliability, test multigroup invariance, apply alignment for approximate invariance, and compare scoring philosophies (Bollen vs. Goertz approach) on criterion validity. We further employ multidimensional item response theory models to provide complementary item‐level diagnostics, including discrimination, threshold, item information, and differential item functioning. Results show that reliability is high and a four‐factor model fits most broadly. Full measurement invariance holds across sex, age, education, residence, political orientation, and religiosity; partial invariance appears across regions, economic development, cultural values, and regime types. Cross‐national comparability is limited but improves via measurement alignment. Different scoring methods identify different weakest dimensions. For criterion validity, Bollen‐based aligned scores consistently outperform the Goertz approach, yielding higher explanatory power in cross‐national and cross‐group analyses. Finally, we provide guidelines for researchers using the SciPop Scale and future directions for measuring science‐related populism.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -1828,12 +3028,36 @@
           <t>International Journal of Public Administration</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr"/>
-      <c r="F52" s="2" t="inlineStr"/>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr"/>
-      <c r="I52" s="2" t="inlineStr"/>
-      <c r="J52" s="2" t="inlineStr"/>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>실험</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>설문 실험</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>Algorithmic Discretion</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>Accountability</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>독일 시민을 대상으로 신분증 갱신 과정의 벌금 부과 상황에서 인간 공무원과 스마트 무인단말기(SSST)의 의사결정을 비교하는 비네트 실험을 실시했다. 부정적 결정은 인간보다 SSST가 내릴 때 더 긍정적으로 평가되어, 알고리즘 재량이 불리한 결과에 대한 시민의 반응을 다르게 만들 수 있음을 보였다.</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>This study investigates how citizens perceive human versus algorithmic decision-making in routine public service interactions involving administrative discretion. We conducted a vignette experiment on a sample of 2,345 German citizens, focusing on the renewal of an ID card, a low-complexity task involving potential fines for late submission. The experiment varied service agent type (human vs. Smart-Self-Service Terminal (SSST)), decision outcome (fine vs. no fine), and agents’ human-likeness. Results show that citizens respond differently to negative outcomes depending on whether they are delivered by a human or a SSST. Unfavorable decisions were evaluated more positively when made by a SSST than by human officials. These findings point to a potential dark side of algorithmic discretion. Even in routine interactions, negative outcomes imposed by an allegedly cold machine may be perceived more positively than those delivered by human bureaucrats, which could incentivize governments to digitize enforcement and weaken public accountability.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -1854,12 +3078,36 @@
           <t>Public Management Review</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr"/>
-      <c r="F53" s="2" t="inlineStr"/>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr"/>
-      <c r="I53" s="2" t="inlineStr"/>
-      <c r="J53" s="2" t="inlineStr"/>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>서베이</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>3시점 설문</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>Uncertainty Management Theory</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>PSM</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>중국 공공부문에서 리더의 비윤리적 친조직 행동(UPB)이 부하직원의 UPB와 어떤 조건에서 연계되는지 231명의 공무원을 대상으로 한 3시점 설문으로 분석했다. 조직의 비윤리적 행동에 대한 책무성과 부하직원의 공공봉사동기(PSM)가 함께 낮을 때 이 효과가 가장 강했으며, 부하직원의 도덕적 정당화가 이를 매개했다.</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>Drawing upon uncertainty management theory, this study examines whether, how, and when leader unethical pro-organizational behaviour (UPB) is associated with subordinate UPB in the Chinese public sector. Using three-wave survey data from 231 civil servants, our study indicates that organizational accountability for unethical behaviour and subordinates’ public service motivation (PSM) jointly moderate this trickle-down effect. Specifically, the effect peaks when both factors are low, with subordinates’ moral justification mediating this process. These findings highlight the UPB trickle-down mechanism, suggesting managers enhance accountability and cultivate employees’ PSM to reduce moral justification and attenuate the spread of UPB.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -1880,12 +3128,36 @@
           <t>Journal of Public Administration Research and Theory</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr"/>
-      <c r="F54" s="2" t="inlineStr"/>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr"/>
-      <c r="I54" s="2" t="inlineStr"/>
-      <c r="J54" s="2" t="inlineStr"/>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>준실험</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>다층 로지스틱 회귀</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>Resource Dependence</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>Participatory Budgeting</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>이 연구는 자원 의존 관점에서 정부기관이 정치적 상급기관의 예산 승인 불확실성에 대응해 시민참여예산 제안을 채택하는 이유를 설명하고, 한국 국가참여예산제도에 제출된 제안 3,609건(2020~2023년)을 다층 혼합효과 로지스틱 회귀로 분석했다. 의회의 재정 지원이 적거나 기관 예산이 작을수록 제안 채택 가능성이 높았으며, 제안 채택을 통해 이전에 더 많은 재원을 확보한 기관에서도 채택 가능성이 높았지만 기관 예산 규모와 의회 지원이 클수록 이 효과는 약해졌다.</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>Abstract Based on resource dependence theory, this article theorizes why government agencies adopt citizen proposals in participatory budgeting. Agencies depend on the executive budget office and the legislature for budget approval, which makes them face uncertainty in securing budgets from these political principals. In this context, agencies can adopt citizen proposals to present their requests as reflecting citizen demands, thereby increasing the probability of approval. Building on this logic, this study argues that the greater the uncertainty agencies face in their dependencies on principals, the more likely they are to depend on proposals. This argument is tested using multilevel mixed-effects logistic regression based on citizen proposals (N = 3,609) submitted through Korea’s national participatory budgeting initiative from 2020 through 2023. The results show that agencies with less financial support from the legislature or those with smaller budgets are more likely to adopt proposals, as they face greater uncertainty due to unstable budgetary flows or fewer response options to manage resource instability. Agencies are also more likely to adopt proposals when they previously secured greater funding through proposal adoption, but this effect weakens for larger-budget agencies or those receiving greater legislative support. These findings emphasize the strategic nature of proposal adoption and the role of resource dependence in agency responses to proposals.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -1906,12 +3178,36 @@
           <t>Public Management Review</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr"/>
-      <c r="F55" s="2" t="inlineStr"/>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr"/>
-      <c r="I55" s="2" t="inlineStr"/>
-      <c r="J55" s="2" t="inlineStr"/>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>서베이</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>시간차 설문</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>Illegitimate Tasks</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>Work Cynicism</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>베트남 공무원을 대상으로 시간차 설문을 실시해, 정당화되기 어렵다고 인식되는 과업이 업무 냉소를 높여 시민지향적 경계확장 행동을 간접적으로 감소시키는지 분석했다. 공공봉사동기와 윤리적 리더십은 이러한 부정적 영향을 완화하기보다 오히려 강화하는 것으로 나타났다.</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>The bureaucratic, resource-constrained, and politically contested nature of the public sector often exposes public servants to illegitimate tasks – assignments perceived as unreasonable or unnecessary. Such tasks frustrate public servants and can undermine behaviours critical to high-quality public service. Despite their prevalence, their consequences in public sector contexts remain underexplored. This study investigates how illegitimate tasks affect citizen-oriented boundary-spanning behaviours (COBSBs), a set of positive work behaviours connecting agencies with stakeholders through service delivery, knowledge sharing, and external representation. Using a time-lagged survey of Vietnamese public servants, we find that illegitimate tasks indirectly reduce COBSBs by increasing work cynicism. Surprisingly, public service motivation and ethical leadership – typically considered resources – intensify rather than buffer the negative effects of illegitimate tasks. By uncovering the costs of illegitimate tasks and these counterintuitive moderating mechanisms, the study offers new insights for public management theory and practice concerning task assignment, leadership, and motivation.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -1932,12 +3228,36 @@
           <t>Administration &amp; Society</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr"/>
-      <c r="F56" s="2" t="inlineStr"/>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr"/>
-      <c r="I56" s="2" t="inlineStr"/>
-      <c r="J56" s="2" t="inlineStr"/>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>이론/개념</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>개념적 논의</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>Meritocracy</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>Bureaucracy</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>본 논문은 메리토크라시가 능력에 따른 공정한 배분이라는 이상에서 출발했지만, 관료제에 뿌리를 둔 합리화된 신화로 인해 승자와 패자를 만들어내는 허브리스로 변질되는 과정을 개념적으로 논의한다.</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>MIchael Young satirizes a global society envisaged for the 21st century, in which all job appointments and rewards are determined solely by merit. Notable advancements in intelligence and ability testing were assumed to enable accurate performance projections and effective educational monitoring. Consequently, the influence of social obstacles such as socioeconomic class, family, race, and religion would be significantly mitigated. The system, however, has shifted to produce winners and losers, a phenomenon Sandel characterizes as hubris . We argue that this hubris stems from meritocracy’s roots in bureaucracy, grounded in a rationalized myth.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -1958,12 +3278,36 @@
           <t>Public Administration</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr"/>
-      <c r="F57" s="2" t="inlineStr"/>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr"/>
-      <c r="I57" s="2" t="inlineStr"/>
-      <c r="J57" s="2" t="inlineStr"/>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>이론/개념</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>연구 실천 분석</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>Interdisciplinarity</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>Temporal Framing</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>이 논문은 Christopher Hood의 연구 실천에서 지배적 서사에 대한 회의적 검토, 장기적 시간 프레임의 선택, 진정한 학제성을 어떻게 결합했는지 분석하고, 이러한 접근이 지속적 가치가 있는 연구를 산출하는 데 어떤 지침을 제공하는지 고찰한다. 분석 결과, 세 요소의 결합은 행정·정책 개혁의 숨은 복잡성과 장기적 패턴을 드러내며, 오늘날 학문 환경에서 연구 전략으로 활용될 수 있음을 제시한다.</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>ABSTRACT In an era of time constraints and publication pressures, scholars risk becoming entrenched in familiar approaches. Christopher Hood's public administration scholarship reminds us that excellence often arises from a broad exploration of ideas. This paper identifies three core elements of Hood's research practice. First, a deep skepticism toward dominant narratives, which often revealed hidden complexities. Second, careful selection of temporal frames: this often meant adopting remarkably long time‐horizons to reveal patterns in administrative and policy reform. Third, genuine interdisciplinarity. While firmly rooted in public administration, Hood drew on concepts, evidence, and methods from a wide range of disciplines. Analyzing how these three elements interacted in Hood's work, the paper reflects on how adopting aspects of his approach can help scholars produce work of lasting value. Hood's legacy is therefore not only a record of past achievement but also a practical guide to navigating the contemporary academic environment.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -1984,12 +3328,36 @@
           <t>Public Management Review</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr"/>
-      <c r="F58" s="2" t="inlineStr"/>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr"/>
-      <c r="I58" s="2" t="inlineStr"/>
-      <c r="J58" s="2" t="inlineStr"/>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>질적연구</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>문서분석·인터뷰</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>Performance Measurement Systems</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>Boundary Objects</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>영국 교도소 서비스 제공에서 성과측정시스템(PMS)이 조직 간 관계와 인간·비인간 행위자를 연결하는 경계 객체로 어떻게 작동하는지 문서분석과 인터뷰로 탐색했다. PMS는 능동적 비인간 행위자이자 경계 객체로 기능하며, 행위자들의 위치 설정은 2차 경계 객체로 나타나고, 이러한 연결은 당초 의도된 목적을 넘어서는 가능성을 생성했다.</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>The paper explores the performance-measurement systems (PMSs) used in the provision of prison services (and their non-human agent role) to reflect on: the role PMSs play in inter-organisational relationships; the boundary objects that connect human and non-human actors across inter-organisational levels; and what affordances such connections generate. The study focuses on the English prison sector, drawing on document analysis and interviews. The findings show that PMSs represent both active non-human agents and boundary objects. The positioning of the actors involved can be seen as a second-order boundary object. Moreover, PMSs can generate affordances that go beyond the initially-intended purposes.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -2010,12 +3378,36 @@
           <t>International Journal of Public Administration</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr"/>
-      <c r="F59" s="2" t="inlineStr"/>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr"/>
-      <c r="I59" s="2" t="inlineStr"/>
-      <c r="J59" s="2" t="inlineStr"/>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>실험</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>로지스틱 회귀</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>Information Asymmetry</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>Organizational Mission</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>이 연구는 시장화된 대외원조 체계에서 USAID가 어떤 조건에서 NGO를 계약자로 선정하는지 분석하기 위해 2008~2023년 USAID 계약·세계은행 자료에 로지스틱 회귀분석을 적용했다. 경쟁이 클수록 NGO 선정 가능성은 낮아지고, NGO는 측정·검증이 어려운 인적 서비스 사업에서 상대적으로 더 많이 선정되는 반면, 인프라·경제개발 계약은 영리기업을 선호하는 것으로 나타났다.</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>This article examines the conditions under which USAID awards contracts to NGOs within an increasingly marketized foreign aid system. Using procurement data on USAID contracts awarded between 2008 and 2023, as well as World Bank data, I employ logistic regression to identify the macro-level factors associated with NGO selection as contractors. Results suggest that NGO selection is primarily shaped by competitive pressures, information asymmetries, and task characteristics. Greater competition reduces the likelihood of NGO selection, while prior contracting experience is associated with for-profit rather than NGO selection. Moreover, NGOs are more likely to be selected for human service projects, where outcomes are difficult to measure and verify. In contrast, infrastructure and economic development contracts predominantly favor for-profit firms. Overall, these findings suggest that although U.S. foreign assistance is oriented toward market principles, NGOs persist in sectors where their organizational characteristics and mission orientation align with USAID’s priorities.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -2036,12 +3428,36 @@
           <t>Public Administration</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr"/>
-      <c r="F60" s="2" t="inlineStr"/>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr"/>
-      <c r="I60" s="2" t="inlineStr"/>
-      <c r="J60" s="2" t="inlineStr"/>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>혼합방법론</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>수학적 모형·계량분석</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>Polycentric Governance</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>Multilayer Network</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>이 연구는 다중심 거버넌스 이론과 다층 네트워크 이론에 기반해 AI가 협력적 거버넌스를 촉진하는 메커니즘과 다차원적 효과를 중국 도시 자료로 분석했다. 기준회귀와 내생성·강건성 검증, 이중차분·임계값·공간계량 분석 결과, AI는 디지털 정부 발전, 기업 투명성 제고, 시민 지식 향상을 통해 협력적 거버넌스를 촉진하는 것으로 나타났다.</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>ABSTRACT Collaborative governance is becoming a practical imperative. At the same time, resolving complex public affairs could offer opportunities to overcome bottlenecks, while Artificial Intelligence (AI) could help. This study draws on polycentric governance theory and multilayer network theory to explain why collaborative governance could occur and how it could be influenced by AI, respectively. Mathematical deductions from both micro and macro perspectives are employed to reinforce this theoretical viewpoint. Using Chinese cities as a case study, the impact of AI on collaborative governance has been tested in practice, supported by benchmark regression and subsequent tests for endogeneity and robustness. Mechanism tests demonstrate AI's functions by advancing digital government, lifting corporate transparency, and improving public knowledge. Moreover, econometric evidence from difference‐in‐differences, threshold regressions, and spatial econometric models robustly addresses concerns about AI. This study offers a quantifiable multi‐stakeholder governance framework and actionable policy insights for China and the Global South.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -2062,12 +3478,36 @@
           <t>International Journal of Public Administration</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr"/>
-      <c r="F61" s="2" t="inlineStr"/>
-      <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr"/>
-      <c r="I61" s="2" t="inlineStr"/>
-      <c r="J61" s="2" t="inlineStr"/>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>질적연구</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>비교 사례연구</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>Instrumental Incompleteness</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>Sensemaking</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>이 연구는 구조적 변화가 운영적 인사관리 인프라의 발전을 앞서는 ‘도구적 불완전성’ 상황에서 지방 관료들이 기능화를 어떻게 실행하는지, 인도네시아 4개 지방정부의 비교 질적 사례연구로 분석한다. 인사 도구의 공백은 운영상 모호성을 낳고 집단적 의미형성과 적응적 조정을 촉발하며, 재정역량만이 아니라 행정지원과 개혁 촉진을 포함한 조직지원 조건의 결합에 따라 일부 지역은 기능직 역할을 부분적으로 공식화하는 반면 다른 지역은 위계적 조정에 계속 의존하는 것으로 나타났다.</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>This study examines how bureaucrats enact functionalization reform under conditions of unfinished reform, conceptualized as instrumental incompleteness in which structural change outpaces the development of operational HR infrastructures. Drawing on a comparative qualitative case study across four Indonesian local government jurisdictions, the study identifies a common mechanism through which an HR-instrument void generates operational ambiguity, prompting collective sensemaking and adaptive coordination. Cross-case comparison shows that these mechanisms follow different reform trajectories according to organizational support conditions, comprising fiscal capacity, administrative support, and reform facilitation. Rather than fiscal capacity alone, the combined configuration of these conditions explains why some jurisdictions move toward partial formalization of functional roles while others continue to rely on hierarchical coordination. The study contributes by conceptualizing unfinished reform as instrumental incompleteness and by integrating structural reform, operational HR infrastructures, and bureaucratic sensemaking into a comparative mechanism-based explanation of reform enactment in decentralized public administration.</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -2088,12 +3528,36 @@
           <t>International Journal of Public Administration</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr"/>
-      <c r="F62" s="2" t="inlineStr"/>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr"/>
-      <c r="I62" s="2" t="inlineStr"/>
-      <c r="J62" s="2" t="inlineStr"/>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>서베이</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>횡단면 설문</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>Performance Information Use</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>Goal Clarity</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>본 연구는 비영리조직에서 성과정보 활용이 실제 조직성과와 어떤 관련을 맺는지, 그리고 그 메커니즘이 무엇인지 검토했다. 캘리포니아 비영리조직 134곳의 설문자료를 분석한 결과, 성과정보 활용은 조직성과와 긍정적으로 관련되었으며, 이 관계는 목표 명확성, 발전적 조직문화, 조직역량을 통해 주로 간접적으로 나타났다.</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>The ultimate objective of performance measurement is to enhance organizational performance, with the use of performance information often regarded as a proxy for its effectiveness. However, there remains a limited understanding of the mechanisms through which performance information use is associated with actual performance improvements within the nonprofit sector. Drawing on survey data from 134 California-based nonprofits, this study finds that the use of performance information is positively associated with organizational performance, with these associations operating through goal clarity, developmental culture, and organizational capacity. The study advances theoretical understanding by developing and testing an integrated model showing that the relationship between performance information use and performance improvement is primarily indirect and operates through internal organizational processes. By revealing these underlying mechanisms, the findings also provide practical insights for nonprofit leaders seeking to optimize performance measurement practices.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -2114,12 +3578,36 @@
           <t>Policy Studies Journal</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr"/>
-      <c r="F63" s="2" t="inlineStr"/>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr"/>
-      <c r="I63" s="2" t="inlineStr"/>
-      <c r="J63" s="2" t="inlineStr"/>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>준실험</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>패널자료 분석</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>Federalism</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>Policy Exclusion</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>미국 각 주의 이민자 복지정책을 결정하는 요인을 2000~2020년 Urban Institute 복지 규칙 데이터베이스와 정책 포용성 지수, 패널자료 분석으로 검토했다. 보수적 주의회는 빈곤 증가에 대응해 더 제한적인 정책을, 진보적 주의회는 반이민 정서 감소에 대응해 더 포용적인 정책을 채택하는 경향이 나타났다.</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>ABSTRACT The intersection of immigration and welfare has taken a central stage in the politics of social policy and garnered increasing scholarly attention in welfare politics research. While prior research has examined how immigration affects welfare support and welfare generosity in the US, less is known about the determinants of immigrant‐related welfare policies. This paper investigates how state‐level policymakers shape immigrant welfare policies in response to changing social and economic state contexts across the U.S. states from 2000 to 2020. Using data from the Urban Institute's Welfare Rules Database, we create a policy index of welfare inclusion of immigrants to track policy variations across the American states from 2000 to 2020. We then employ panel data analyses to explore the determinants of state immigrant TANF policies. Our findings reveal diverging strategies of state legislatures: conservative state legislatures tend to be associated with more restrictive immigrant welfare policies than their liberal counterparts; moreover, conservative and liberal state legislatures respond to different types of state contexts in adjusting their immigrant welfare policies. Conservative state legislatures respond to rising poverty by enacting restrictive policies, whereas liberal state legislatures respond to declining levels of anti‐immigration sentiment by adopting more inclusive policies.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -2140,12 +3628,36 @@
           <t>Policy Studies Journal</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr"/>
-      <c r="F64" s="2" t="inlineStr"/>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr"/>
-      <c r="I64" s="2" t="inlineStr"/>
-      <c r="J64" s="2" t="inlineStr"/>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>서베이</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>로지스틱 회귀</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>Street-Level Bureaucracy</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>Discrimination</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>멕시코 형사사법체계에서 민족·인종적 특성과 경찰 학대 신고 경험의 연관성을 2021년 수감자 전국조사 자료와 로지스틱 회귀모형으로 분석했다. 아프리카계·아프리카계 후손 및 원주민은 학대 신고 오즈가 높았지만, 원주민 언어 사용과 어두운 피부색은 낮은 신고와 연관되어 복합적인 양상이 나타났다.</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>ABSTRACT This study examines the association between ethnoracial characteristics (ethnoracial self‐identification, speaking an Indigenous language, and skin tone) and police abuse within Mexico's criminal justice system, drawing on street‐level bureaucracy frameworks. Using data from the 2021 National Survey of Persons Deprived of Liberty (ENPOL in Spanish), we analyze whether ethnoracial traits are conditionally associated with reported experiences of police abuse. Logistic regression models suggest that Afro‐Mexican or Afro‐descendant and Indigenous persons have higher odds of reporting abuse, supporting existing literature on discrimination and policing. Unexpectedly, speaking an Indigenous language and having darker skin tones were associated with lower reported abuse, suggesting a complex relationship that merits further examination. These results underscore the need to incorporate ethnoracial variables into the study of police behavior and public administration in Mexico, while informing public policies aimed at preventing and addressing police abuse to strengthen accountability within the criminal justice system.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -2166,12 +3678,36 @@
           <t>American Journal of Political Science</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr"/>
-      <c r="F65" s="2" t="inlineStr"/>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr"/>
-      <c r="I65" s="2" t="inlineStr"/>
-      <c r="J65" s="2" t="inlineStr"/>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>방법 미상</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>합성통제 표집</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>External Validity</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>Synthetic Control</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>다기관 연구에서 외적 타당성을 확보하기 위한 사이트 선택 방법을 어떻게 설계할 것인지 묻고, 합성통제 방법과 목적표집을 결합한 합성 목적표집(SPS)을 제안한다. SPS는 선택되지 않은 사이트를 선택된 사이트의 가중평균으로 잘 근사하도록 다양성이 높은 사이트를 최적으로 선정하며, 실험·관찰 연구를 통해 일반적 적용 가능성을 보인다.</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>Abstract Multi‐site/context studies have become popular strategies to address the most common and challenging external validity concerns about contexts. Under such studies, scholars conduct causal studies in each site and evaluate whether findings generalize across sites. Despite the potential, there has been little guidance on the fundamental research design question—how should we select sites for external validity? Existing approaches have challenges: random sampling of sites is often infeasible, while the current practice of purposive sampling is suboptimal without statistical guarantees. We propose synthetic purposive sampling (SPS), which optimally selects diverse sites for external validity. SPS combines ideas of purposive sampling and the synthetic control method—it selects diverse sites such that nonselected sites are well approximated by the weighted average of the selected sites. We illustrate its general applicability using both experimental and observational studies. Overall, this paper offers a new statistical foundation to design multisite studies for external validity.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -2192,12 +3728,36 @@
           <t>International Journal of Public Administration</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr"/>
-      <c r="F66" s="2" t="inlineStr"/>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr"/>
-      <c r="I66" s="2" t="inlineStr"/>
-      <c r="J66" s="2" t="inlineStr"/>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>이론/개념</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>문헌·공인용 분석</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>Accountability</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>Institutional Norms</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>공공행정의 책무성 문헌이 어떻게 형성되고 통합되어 왔는지를 규명하기 위해 PRISMA에 따라 동 분야의 동료심사 논문 81편을 검토하고 인용·공인용 분석을 실시했다. 분석 결과, 현재의 책무성 개념과 이론은 관리개혁, 제도적 규범, 민주적 가치의 상호 영향 속에서 형성된 것으로 나타났다.</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>The idea of accountability has shaped public institutions across multiple countries, impacting how institutions are designed and governance is executed. In the public administration domain, it has been studied from a variety of disciplinary perspectives; however, the development of the field remains fragmented across many domains. The fragmentation is not just attributed to the domain of conception and its subsequent development but also the origins and adoption of accountability in practice. To understand this, we explore the intellectual structure of accountability literature. Using the PRISMA framework, we reviewed the literature in public administration and identified 81 peer-reviewed articles influencing the scholarship of the domain. Further, building on this literature, we conducted the citation and co-citation analysis for understanding the intellectual structure of the domain. The findings reveal the way in which managerial reforms, institutional norms, and democratic values have collectively influenced present-day accountability conception and theory.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -2218,12 +3778,36 @@
           <t>Public Administration Review</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr"/>
-      <c r="F67" s="2" t="inlineStr"/>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr"/>
-      <c r="I67" s="2" t="inlineStr"/>
-      <c r="J67" s="2" t="inlineStr"/>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>이론/개념</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>체계적 문헌검토</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>Moral Decision-Making</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>Political Office</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>정치적 직위의 어떤 속성이 정치인의 도덕적 의사결정과 행동에 영향을 미치는지 파악하기 위해 행정학·정치학 등 관련 분야의 80편을 체계적으로 검토했다. 정치체계 설계, 정치적 역할, 사회 행위자와의 관계, 법·규제 조치, 정치 주기, 정치기관 규모 등 여섯 범주의 속성이 관련되지만, 기존 연구는 비윤리적 행동에 치우쳐 전반적인 도덕적 의사결정 과정에 대한 이해에는 공백이 있는 것으로 나타났다.</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>ABSTRACT The moral decision‐making and behavior of politicians is influenced by the distinctive and characteristic attributes of political office. This literature review analyzes 80 articles from public administration, political science and related disciplines to systematically map these attributes and their underlying mechanisms. This study identifies six categories of attributes of political office that relate to moral decision‐making and behavior: political system design, political role, relations to societal actors, legal and regulatory measures, political cycle, and some general attributes such as the size of the political institution. Interestingly, existing research focuses mostly on unethical behavior, creating white spots in our understanding of how the attributes of political office shape individual and collective processes of moral decision‐making and behavior more generally. We conclude with an agenda for future research that advocates for more targeted research of the sociopsychological aspects that shape the moral decision‐making and behavior of politicians across their different roles.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -2244,12 +3828,36 @@
           <t>Public Administration</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr"/>
-      <c r="F68" s="2" t="inlineStr"/>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr"/>
-      <c r="I68" s="2" t="inlineStr"/>
-      <c r="J68" s="2" t="inlineStr"/>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>질적연구</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>텍스트 분석·심층 인터뷰</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>Policy Entrepreneurs</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>Collaborative Networks</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>정치인이 정책 과정에 직접 관여하지 않을 때 정책기업가가 어떻게 정책 변화를 추진하는지 탐구하기 위해, 이스라엘군 내 자폐 스펙트럼 개인의 포용을 지원하는 ‘로임 라촉’ 프로그램을 사례로 텍스트 분석과 30건의 심층 인터뷰를 실시했다. 정책기업가들은 제도화된 협력 네트워크, 안보 위기를 활용한 정책 틀, 조직 인프라 구축, 안보 조직과의 신뢰 형성을 통해 독자적으로 정책 변화를 진전시켰다.</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>ABSTRACT How do policy entrepreneurs change policy when politicians are not directly involved in the process? While public policy scholars have examined the conditions under which politicians refrain from direct engagement in policy design, they have paid less attention to the strategies policy entrepreneurs employ in the absence of political actors. Drawing on textual analysis and 30 in‐depth interviews with members of the “Roim Rachok” (“Looking Ahead”) program, which facilitates the inclusion of individuals on the autism spectrum in the Israel Defense Forces as a case study, we addressed this lacuna by exploring how policy entrepreneurs independently advance policy change. The findings suggest that the policy entrepreneurs operated through institutionalized collaborative networks. They also leveraged Israel's security challenges as a structured framework for promoting their new policy. In addition, they created an organizational infrastructure. Finally, they focused on establishing trust with the security organizations with whom they collaborated.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -2270,12 +3878,36 @@
           <t>International Journal of Public Administration</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr"/>
-      <c r="F69" s="2" t="inlineStr"/>
-      <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr"/>
-      <c r="I69" s="2" t="inlineStr"/>
-      <c r="J69" s="2" t="inlineStr"/>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>이론/개념</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>문헌 검토</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>Philosophy</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>Public Administration</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>이 서평은 Edoardo Ongaro의 저서가 공공행정의 철학적 가정과 철학·공공행정 간 탐구 방향을 어떻게 제시하는지 검토한다. 초록에 제시된 범위에서는 구체적 연구질문이나 분석 결과는 확인되지 않는다.</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>Edoardo Ongaro’s Connecting Philosophy and Public Administration: Directions of Inquiry (Ongaro, 2026) opens with a provocation that is easy to underestimate: philosophical assumptions, it argues, ...</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -2296,12 +3928,36 @@
           <t>International Journal of Public Administration</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr"/>
-      <c r="F70" s="2" t="inlineStr"/>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr"/>
-      <c r="I70" s="2" t="inlineStr"/>
-      <c r="J70" s="2" t="inlineStr"/>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>이론/개념</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>개념적 모형</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>Bounded Rationality</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>Target Groups</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>이 논문은 복잡한 정책 맥락을 포괄적으로 이해하고 정확한 정보를 수집하는 데 제약을 받는 정책결정자의 제한된 합리성을 검토하며, 이를 정책 대상 집단의 행동과 연결해 공공정책을 설명한다. 초록에 제시된 범위에서는 이러한 제약이 정책과정과 정책결정에 어떤 함의를 갖는지를 이론적으로 논의한다.</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>Bounded rationality represents a relevant issue in public policy, not only because policymakers face constraints in comprehensively understanding complex contexts and collecting accurate informatio...</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -2322,12 +3978,36 @@
           <t>Administration &amp; Society</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr"/>
-      <c r="F71" s="2" t="inlineStr"/>
-      <c r="G71" s="2" t="inlineStr"/>
-      <c r="H71" s="2" t="inlineStr"/>
-      <c r="I71" s="2" t="inlineStr"/>
-      <c r="J71" s="2" t="inlineStr"/>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>질적연구</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>사례 분석</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>Political Trust</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>Legitimacy</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>이 연구는 정치적 신뢰와 정당성에 기반한 체계적 정치역량이 미국 멸종위기종보호법에 따른 선제적 보전에서 어떻게 작용하는지 콜로라도 세이지그라우스 사례로 분석한다. 강제적 연방 개입의 정당성을 둘러싼 갈등이 규제 권위에 대한 정치적 신뢰를 약화시켜, 연방 요건을 충족하는 집행 가능한 보전 합의의 형성을 제약한 것으로 나타났다.</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>Contemporary governance faces mounting environmental challenges, straining governmental capacity to achieve policy objectives. We extend Wu et al.'s policy capacity framework, arguing that systemic political capacity is grounded in political trust, itself conditioned by legitimacy. Applying this framework to proactive conservation under the U.S. Endangered Species Act, we analyze the failure of Colorado’s sage-grouse initiative. Findings suggest contested legitimacy surrounding coercive federal intervention diminished political trust in regulatory authority, constraining systemic political capacity and limiting development of enforceable conservation arrangements satisfying federal requirements. The analysis has broader implications for collaborative governance dependent on credible regulatory authority.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -2348,12 +4028,36 @@
           <t>Public Performance &amp; Management Review</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr"/>
-      <c r="F72" s="2" t="inlineStr"/>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr"/>
-      <c r="I72" s="2" t="inlineStr"/>
-      <c r="J72" s="2" t="inlineStr"/>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>질적연구</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>문서 과정추적</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>Accountability</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>Recentralization</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>본 연구는 인도네시아 지방선거에서 중앙 운영 디지털 플랫폼이 행정성과와 책임성을 어떻게 형성·재분배하는지 문서·플랫폼 산출물 분석과 과정추적을 통해 분석했다. Sidalih·Silon·Sirekap은 업무를 가시적 성과 신호로 전환하면서 데이터 구조와 검증·수정 절차를 중앙집중화해, 통제권이 제한된 지방 집행기관에 책임과 위험을 집중시키는 ‘책임성 압박’을 সৃষ্টি했다.</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>Digital election platforms increasingly mediate administrative performance, transparency, and accountability in electoral governance. Examining Indonesia’s regional elections, this study analyzes how such platforms shape administrative performance and redistribute accountability. A qualitative design combining documentary analysis, platform-artifact analysis, and documentary process tracing compares three centrally governed platforms operated by Indonesia’s General Elections Commission: Sidalih for voter registration, Silon for candidate nomination, and Sirekap for results reporting. Findings show that these platforms operate as performance regimes, translating electoral work into visible signals such as synchronization status, validation outcomes, upload completion, dashboard display, correction records, and verification pathways. Platform architecture simultaneously centralizes operational control over data structures, validation rules, user permissions, publication logic, and correction procedures, while subnational offices retain implementation responsibility. Such arrangements create an accountability squeeze: implementing units become increasingly visible as responsible actors without commensurate control over technical conditions shaping performance outcomes. By linking platform-mediated visibility to asymmetries in control, this study shows how digital transparency can strengthen administrative legibility while redistributing responsibility, risk, and authority across organizational levels.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -2374,12 +4078,36 @@
           <t>Governance</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr"/>
-      <c r="F73" s="2" t="inlineStr"/>
-      <c r="G73" s="2" t="inlineStr"/>
-      <c r="H73" s="2" t="inlineStr"/>
-      <c r="I73" s="2" t="inlineStr"/>
-      <c r="J73" s="2" t="inlineStr"/>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>혼합방법론</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>대규모 사례분석</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>Policy Change</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>Adaptive Governance</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>중국의 정책 실험이 확장되지 않는 경로와 그 이후의 정책 변화를 어떻게 설명할 수 있는지 분석하기 위해, 2013~2018년에 발표된 정책 실험 27,103건의 대규모 분석과 질적 사례연구를 결합했다. 분석 결과 최대 90%의 실험이 ‘막다른 길’에 도달했으며, 이는 지도자 교체, 정책 복잡성, 관료적 유인 및 사회경제적 조건과의 불일치와 관련되어 롤백·전환·종료 같은 후속 변화를 구조화했다.</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>ABSTRACT Not all policy change is expansive, yet non‐expansive trajectories remain underexamined. This article introduces the concept of dead ends: a stage of the policy process in which initiatives cease to develop or be implemented in their existing form, structuring subsequent policy change such as rollback, redirection, or termination. To examine such trajectories, the article combines large‐scale analysis of 27,103 policy experiments announced in the People's Republic of China between 2013 and 2018 with qualitative case studies. The findings suggest that a substantial majority—up to 90%—of experiments reach dead ends. These dead ends are associated with leadership turnover, policy complexity, and misalignment with bureaucratic incentives and socio‐economic conditions. Altogether, the article provides new frameworks for understanding alternative directions of policy change. In doing so, it also sheds new light on the adaptive capacity and structural constraints of China's governance system.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -2400,12 +4128,36 @@
           <t>Political Analysis</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr"/>
-      <c r="F74" s="2" t="inlineStr"/>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr"/>
-      <c r="I74" s="2" t="inlineStr"/>
-      <c r="J74" s="2" t="inlineStr"/>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>서베이</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>최대우도 추정</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>Nonignorable Nonresponse</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>Post-Stratification</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>비순응답자가 응답자와 결과변수에서 다를 수 있는 상황에서, 응답자에게 관측된 응답성향 대리변수와 공변량 및 사후층화 정보를 통합해 순서형 조사자료의 비무작위 응답편향을 보정하는 방법을 제시한다. 2024년 미국선거연구 자료에 적용한 결과, 삶의 만족도에서는 추정치가 실질적으로 변했지만 회고적 경제평가에서는 변화가 비교적 작았다.</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>Abstract Many political surveys rely on post-stratification, raking or related weighting adjustments to align respondents with the target population. But when respondents differ from nonrespondents on the outcome itself (nonignorable nonresponse), these adjustments can fail, introducing bias even into basic descriptives. We provide a practical method that corrects for nonignorable nonresponse by leveraging response-propensity proxies (e.g., a respondent’s rating of the interview or interviewer-coded cooperativeness) observed among respondents to extrapolate toward nonrespondents, while directly integrating observable covariates and retaining the benefits of post-stratification with known population shares. The method generalizes the variable-response-propensity framework of Peress (2010) from binary to ordinal outcomes, which are widely used to measure trust, satisfaction and policy attitudes. The resulting estimator is computed by maximum likelihood and implemented in a compact R routine that handles both ordinal and binary outcomes. Using the 2024 American National Election Study, we show that accounting for nonignorable nonresponse produces substantively meaningful shifts for life satisfaction (estimated latent correlation ρ ≈ 0.47 $\rho \approx 0.47$ rho almost equals 0.47 ), while yielding only modest changes for retrospective economic evaluations ( ρ ≈ 0.14 $\rho \approx 0.14$ rho almost equals 0.14 ), highlighting when nonignorable nonresponse substantively affects survey estimates.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -2426,12 +4178,36 @@
           <t>Political Behavior</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr"/>
-      <c r="F75" s="2" t="inlineStr"/>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr"/>
-      <c r="I75" s="2" t="inlineStr"/>
-      <c r="J75" s="2" t="inlineStr"/>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>혼합방법론</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>순차 혼합</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>Role Models</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>Political Engagement</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>여성 정치인의 성별 외 추가 공유 정체성이 여성의 정치 참여에 미치는 역할모델 효과를 검토하기 위해 컨조인트 실험, 동영상 설문 실험, 관찰분석을 실시했다. 추가 공유 정체성은 정치인을 더 친근하고 영감을 주는 인물로 인식하게 했지만, 정치적 관심·내적 정치효능감·초기 정치적 야망을 높이는 효과는 확인되지 않았으며 백인 여성과 흑인 여성 간 처치 효과도 달랐다.</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>Abstract Women consistently report lower levels of political interest and political ambition than men. Studies have examined how women politicians as role models can make women more politically engaged, but studies have not typically examined additional shared identities beyond gender. I propose that women politicians with whom women share additional identities will be perceived as more relatable and inspiring and, consequently, have stronger role model effects on women’s political engagement. Through a conjoint experiment (Study 1), I find that having additional shared identities with a woman politician increases perceptions of her as relatable and inspiring. However, a survey experiment with novel video treatments depicting a woman politician’s story (Study 2) did not produce positive role model effects on women’s political interest, internal political efficacy, or nascent political ambition – regardless of additional shared racial and partisan identity with the woman politician. Moreover, the video treatment had remarkably different effects across White and Black women, regardless of additional shared racial and partisan identity. An observational analysis (Study 3) replicates the finding that additional shared racial and partisan identity with women political representatives is not systematically correlated with higher levels of political interest. These findings carry important implications for understanding women politicians’ role model effects and the potential of role models to increase women’s political engagement.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -2452,12 +4228,36 @@
           <t>Public Administration Review</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr"/>
-      <c r="F76" s="2" t="inlineStr"/>
-      <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr"/>
-      <c r="I76" s="2" t="inlineStr"/>
-      <c r="J76" s="2" t="inlineStr"/>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>혼합방법론</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>디지털 기록분석·인터뷰</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>Performance Measurement</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>Accountability</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>써니베일의 성과측정 체계가 의사결정의 모범으로 기능했는지, 그리고 장기간 어떻게 변화했는지를 1984~2023년 3만 5,000쪽의 문서와 152개 지표에 대한 디지털 기록 분석 및 핵심 관계자 인터뷰로 추적했다. 초기에는 성과기반 의사결정을 지원했지만, 헌신 약화와 지속적인 실행비용으로 체계의 편익이 감소했으며, 연구는 중요사항 측정의 양-질, 연속성-유연성, 책무성-생산성 간 상충을 제시한다.</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>ABSTRACT Few regulatory reforms are as celebrated or emulated as the performance measurement system of Sunnyvale, California, which inspired the Government Performance and Results Act of 1993 and countless other national and local efforts. This study presents the first longitudinal, cross‐programmatic analysis of a performance measurement system, introducing a digital archival approach to analyze 152 performance indicators across 35,000 pages of documents from 1984 to 2023, supplemented with interviews of key stakeholders. Even if Sunnyvale's system initially functioned as an exemplar of performance‐based decision‐making, it deteriorated with weakened commitment and, more importantly, sustained significant implementation costs while its benefits reduced over time. The findings illustrate three core trade‐offs for performance measurement systems: measuring what matters (the “quantity‐quality” tradeoff); ensuring continuity while allowing for adaptation (the “continuity‐flexibility” tradeoff); and ensuring accountability without having implementation detract from productivity (the “accountability‐productivity” tradeoff).</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -2478,12 +4278,36 @@
           <t>Policy Studies Journal</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr"/>
-      <c r="F77" s="2" t="inlineStr"/>
-      <c r="G77" s="2" t="inlineStr"/>
-      <c r="H77" s="2" t="inlineStr"/>
-      <c r="I77" s="2" t="inlineStr"/>
-      <c r="J77" s="2" t="inlineStr"/>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>혼합방법론</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>순차 혼합</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>Policy Legitimacy</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>Blame Avoidance</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>덴마크의 코로나19 밍크 전량 살처분 위기에서 정부가 정당화·정당성 훼손·책임회피의 담론 전략을 어떻게 전환했는지를 순차 혼합방법으로 분석했다. 신문 기사 947건과 질적 분석 결과, 초기에는 과학적 권위와 법적 호소로 정책을 정당화했지만 법적·과학적 도전 이후 절차적 정당성에 대한 비판이 커지자 책임회피로 전환했으며, 정책은 이러한 전략 속에서 지속되었다.</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>ABSTRACT This paper examines how governments navigate policy legitimacy during crises through three distinct discursive processes: legitimization, delegitimization, and blame avoidance. Using a sequential mixed‐methods design, the study analyzes Denmark's decision to cull all mink during the COVID‐19 pandemic. The quantitative analysis of 947 newspaper articles indicates that while both periods were characterized by negative coverage, the force and target of delegitimization discourses shifted dramatically from questioning policy outcomes to scrutinizing procedural legitimacy. The qualitative analysis illustrates how, initially, the government successfully legitimized the mink culling through appeals to scientific authority, with broad political and public support. However, following legal and scientific challenges, policy legitimacy collapsed, coinciding with a strategic pivot from policy justification to blame avoidance. The analysis illustrates that legitimization and blame avoidance can be treated as analytically distinct discursive strategies: legitimization proactively affirms policy necessity through evidence and legal appeals, while blame avoidance reactively deflects responsibility through reframing, buck‐passing, and scapegoating. The policy persisted despite sustained delegitimization, initially aided by legitimization efforts and later by blame avoidance strategies. The findings advance policy theory by clarifying how discursive strategies evolve across a policy's lifecycle and offer a framework applicable to other high‐salience domains such as climate emergencies and migration policies.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -2504,12 +4328,36 @@
           <t>Journal of Policy Analysis and Management</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr"/>
-      <c r="F78" s="2" t="inlineStr"/>
-      <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" s="2" t="inlineStr"/>
-      <c r="I78" s="2" t="inlineStr"/>
-      <c r="J78" s="2" t="inlineStr"/>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>실험</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>설문 실험</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>Administrative Burden</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>Construal Level Theory</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>이 연구는 선별적 사회복지 프로그램에서 행정적 부담으로 인한 자격 있는 수급자의 배제와 부적격 수급자의 부정수급 사이의 상충관계를 어떻게 평가하는지 묻고, 2,250명을 대상으로 한 조건부 가치평가 설문실험으로 이를 측정했다. 응답자들은 적격자 1,000명의 배제를 막기 위해 약 192명의 부적격 수급자가 급여를 받는 것을 수용했으며, 전체 표본에서는 심리적 거리의 직접 효과가 나타나지 않았지만 정당 소속과 복지 경험에 따라 부정수급 허용도가 달라졌다.</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>ABSTRACT Administrative burden represents political choices embedded in policy design that affect how people perceive and experience government. While policymakers frequently invoke fraud prevention to justify imposing burdens in welfare programs, this rhetoric embodies an unacknowledged normative judgment about the relative costs of fraud and abuse versus program exclusion for eligible beneficiaries. This study quantifies this access–fraud trade‐off in means‐tested social welfare programs through a contingent valuation experiment ( N = 2250). We find that respondents were willing to accept approximately 192 ineligible recipients receiving benefits in exchange for 1000 eligible beneficiaries not being excluded due to administrative burdens. While we find no direct evidence that psychological distance (i.e., randomized exposure to “welfare” vs. specific programs) affects this trade‐off across the full sample, political affiliation is a significant moderator in our exploratory analysis. Unlike Democrats/Independents, Republicans demonstrate substantially lower tolerance for potential fraud when evaluating abstract “welfare” compared to specific programs like unemployment insurance. Experience with means‐tested welfare programs, which reduces psychological distance, has a similar moderating effect. These findings extend construal level theory to administrative burden preferences and contribute to the policy implementation literature by quantifying the access–fraud trade‐off—a metric largely absent from academic and policy discussions despite its importance for program legitimacy.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -2530,12 +4378,36 @@
           <t>The American Review of Public Administration</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr"/>
-      <c r="F79" s="2" t="inlineStr"/>
-      <c r="G79" s="2" t="inlineStr"/>
-      <c r="H79" s="2" t="inlineStr"/>
-      <c r="I79" s="2" t="inlineStr"/>
-      <c r="J79" s="2" t="inlineStr"/>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>서베이</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>횡단면 설문</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>Moral Judgment Theory</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>AI Acceptance</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>독일과 네덜란드 시민 2,072명을 대상으로 설문조사를 실시해, 정부의 AI 도입을 이끄는 동기에 대한 인식이 시민의 AI 활용 수용과 어떻게 관련되는지 네 가지 AI 활용 유형별로 분석했다. 시민이 정부 AI 도입의 동기를 효율성·효과성·생산성 같은 성과 관련 가치로 인식할 때 수용성이 높아졌지만, 공정성·동등대우·투명성 같은 절차 관련 가치에 대한 인식은 유의한 관련이 없었다.</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>What do citizens believe to be guiding motives behind the increasing adoption of artificial intelligence (AI) in government, and how are these beliefs related to AI acceptance? Drawing on moral judgment theory, the present article argues that the presumed intentions behind AI use matter for citizens’ evaluations of this use. It studies how citizens’ beliefs about public values motives are associated with AI acceptance across four types of AI use that involve different citizen-state relationships. The analysis uses survey data from 2072 respondents in Germany and the Netherlands and finds that that acceptance of AI use hinges on whether citizens believe that government AI adoption is guided by performance-related values – efficiency, effectiveness, productivity. Beliefs about procedure-related public values motives – impartiality, equal treatment, transparency – do not matter. The findings have implications for how to engender public support for government AI use and for understanding imbalances in public values driving AI adoption.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -2556,12 +4428,36 @@
           <t>Public Performance &amp; Management Review</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr"/>
-      <c r="F80" s="2" t="inlineStr"/>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr"/>
-      <c r="I80" s="2" t="inlineStr"/>
-      <c r="J80" s="2" t="inlineStr"/>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>준실험</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>주정부 패널</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>Multiple Streams Framework</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>Personnel Stability</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>2008년 경기침체 이후 미국 주정부의 인력 안정성이 어떻게 형성되는지, 재정·조직 조건과 정책과정 요인이 고용 규모 및 부처 간 인력 재배치에 어떤 영향을 미치는지를 주정부 부처별 패널의 이원 고정효과 모형으로 분석했다. 정책형성 역량은 경기침체기의 인력 감소를 막지는 못했지만, 부처 간 인력 이동의 변동성을 낮춰 보다 조정된 인력 조정을 보이는 것과 관련됐다.</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>The 2008 recession forced U.S. state governments to make rapid personnel and fiscal decisions under austerity. Classic cutback management work catalogues managerial options and personnel stability research links stability to performance, but there is little work to date connecting these fields. This study begins to do so by examining changes in state employment in the wake of the 2008 recession. We conceptualize the components of Kingdon’s Multiple Streams Framework as competing policy influences to assess how state fiscal and organizational conditions shape personnel stability in the following years. Using a state-level panel of by-department employment and a battery of factors that influence the policy process, we estimate two-way fixed-effects models relating Political Competition, Institutional Influence, Policymaking Capacity, and Intragovernmental Conflict indices to two outcomes: year-to-year change in total employment and year-to-year variance in the distribution of jobs across departments. We find significant effects of policymaking capacity on both outcomes. Substantively, the relative strength of policymaking does not prevent recession-era workforce contraction, but it is associated with lower variance in cross-department personnel shifts, suggesting more coordinated adjustments that reduce disruption to routines, coordination, and the distribution of expertise.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -2582,12 +4478,36 @@
           <t>Public Performance &amp; Management Review</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr"/>
-      <c r="F81" s="2" t="inlineStr"/>
-      <c r="G81" s="2" t="inlineStr"/>
-      <c r="H81" s="2" t="inlineStr"/>
-      <c r="I81" s="2" t="inlineStr"/>
-      <c r="J81" s="2" t="inlineStr"/>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>준실험</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>패널 2SLS</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>Fiscal Competition</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>Intergovernmental Transfers</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>중국 지방정부 채권시장에서 조세 경쟁과 지출 경쟁이 지방정부 부채 관리에 미치는 영향을 2010~2018년 272개 지급시 패널자료와 2단계 최소제곱법(2SLS)으로 분석하고, 정부 간 이전의 조절 역할을 검토했다. 조세·지출 경쟁은 지방정부 부채를 유의하게 늘렸으며, 정부 간 이전은 대체효과로 직접 차입 수요를 줄이지만 재정 경쟁 상황에서는 재정 규율을 약화해 부채 누적을 심화시켰다.</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>This study examines how tax and expenditure competition, two distinct yet complementary mechanisms of horizontal fiscal governance, affect local debt management in China’s local government bond market, using a two-stage least squares (2SLS) approach. It further investigates the moderating role of intergovernmental transfers intended to promote fiscal stabilization and equalization. Drawing on panel data from 272 prefecture-level cities between 2010 and 2018, the results indicate that intensified tax and expenditure competition significantly increases local government debt, while intergovernmental transfers reduce direct borrowing needs through a substitution effect but exacerbate debt accumulation under fiscal competitive pressure by weakening local fiscal discipline. The study contributes to the public management and performance literature by highlighting how fiscal governance can distort local managerial incentives and undermine local debt management.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -2608,12 +4528,36 @@
           <t>The American Review of Public Administration</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr"/>
-      <c r="F82" s="2" t="inlineStr"/>
-      <c r="G82" s="2" t="inlineStr"/>
-      <c r="H82" s="2" t="inlineStr"/>
-      <c r="I82" s="2" t="inlineStr"/>
-      <c r="J82" s="2" t="inlineStr"/>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>질적연구</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>심층 인터뷰</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>Administrative Capacity</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>Legitimacy</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>이 연구는 마우이 산불 이후 문화가 재난 대응과 회복의 행정 인프라로 어떻게 작동했는지를 질적 인터뷰와 12개월 이내의 공청회 자료로 분석했다. 토지·물·공동체·역사에 대한 문화적으로 뿌리내린 관계가 공식 회복 노력의 정당성 해석, 외부 정부체계 동원, 재건 권위의 주장, 회복의 의미 정의를 형성했으며, 행정 역량이 기관·자원·절차·네트워크뿐 아니라 문화적으로 내재된 정당성·지식·권위·집합적 돌봄에도 기반함을 보였다.</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>Despite growing attention to culture in public administration responses to crisis events, culture is often treated as background context rather than as part of the administrative infrastructure through which governance occurs. This article extends the theory of administrative capacity by arguing that culture can function as administrative infrastructure in post-disaster public management. Using qualitative interviews with community members, grassroots organizers, and nonprofit leaders in Maui, as well as public forum data collected within 12 months of the 2023 Maui wildfires, we examine how culture shaped legitimacy, coordination, authority, and recovery capacity in the aftermath of disaster. Findings show that culturally grounded relationships to land, water, community, and history shaped how residents interpreted formal recovery efforts, mobilized outside government systems, asserted authority over rebuilding, and defined what recovery should mean. We develop a culture as administrative infrastructure framework that shows how culturally grounded forms of authority, resistance, and place-based knowledge reveal the limits of culturally neutral administrative systems. The article contributes to public administration theory by showing that administrative capacity is not only built through agencies, resources, procedures, and networks, but also through culturally embedded systems of legitimacy, knowledge, authority, and collective care.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -2634,12 +4578,36 @@
           <t>International Journal of Public Administration</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr"/>
-      <c r="F83" s="2" t="inlineStr"/>
-      <c r="G83" s="2" t="inlineStr"/>
-      <c r="H83" s="2" t="inlineStr"/>
-      <c r="I83" s="2" t="inlineStr"/>
-      <c r="J83" s="2" t="inlineStr"/>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>질적연구</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>심층 인터뷰</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>Policy Alienation</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>Street-Level Bureaucracy</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>스웨덴 교도소 간호사 인터뷰를 통해, 돌봄과 처벌이 충돌하는 조직 맥락에서 정책 소외가 어떻게 형성되고 완화되는지 분석했다. 간호사들은 전술적 무력감과 공간적 제약을 경험했지만, 높은 업무 자율성·신뢰에 기반한 관리적 거리·전문직 네트워크를 통해 본래의 정책 영역과 다시 연결되었다.</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>Policy alienation research highlights how public professionals experience powerlessness and meaninglessness when policies misalign with their professional values and work context. While previous research conceptualizes policy alienation as a largely static condition, this article advances a processual understanding by examining how organizational context shapes its development. Drawing on interviews with nurses working in Swedish prisons—a paradigmatic case of misalignment between care and punishment—the study reveals that both expected (tactical powerlessness) and novel (spatial limitation) patterns of alienation coexist with processes that counteract it. Nurses describe how they re-connect with their primary policy domain through considerable work autonomy, trust-based managerial distance, and supportive professional networks. These findings extend policy alienation theory by demonstrating how misaligned organizational environments can generate both alienating and re-connecting processes. The study thus advances understanding of policy alienation as a dynamic, context-mediated phenomenon with important implications for public administration practice.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -2660,12 +4628,36 @@
           <t>Government Information Quarterly</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr"/>
-      <c r="F84" s="2" t="inlineStr"/>
-      <c r="G84" s="2" t="inlineStr"/>
-      <c r="H84" s="2" t="inlineStr"/>
-      <c r="I84" s="2" t="inlineStr"/>
-      <c r="J84" s="2" t="inlineStr"/>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>질적연구</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>질적 사례연구</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>Semantic Reconciliation</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>Data Governance</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>분권화된 지방정부에서 채용 AI 평가 결과가 공급업체·인사 전문가·채용 담당자·관리자 사이에서 어떻게 의미적으로 조정되는지를 질적 사례연구로 분석했다. 스웨덴 대규모 지방자치단체 사례는 위임 범위 설정, 범주 매핑, 맥락 보완, 해석의 조직 내 정착, 인간 판단과의 결합이라는 반복적 조정 작업을 통해 AI 정보의 이동성을 확보하면서도 직무 맥락과 인간의 결정 권한을 유지한다고 보여준다.</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>Local governments are beginning to use artificial intelligence (AI) in internal administrative work, including recruitment. In a decentralized municipality, however, a standardized AI assessment must travel between a technology vendor, central HR specialists, recruiters, and hiring managers responsible for different services. This creates a tension between representational portability and contextual adequacy. Based on a qualitative case study of a large Swedish municipality, we examine an AI interviewing system that translated candidates' open-ended responses into competency indicators and narrative summaries used in early-stage recruitment. We develop a process model of semantic reconciliation comprising five recurrent forms of work: scoping what could be delegated to the system, mapping vendor categories to municipal and occupational vocabularies, refining interpretations when role context was lost, embedding shared interpretations across a distributed organization, and composing AI reports with locally accountable human judgment. The study contributes to research on local-government AI and data governance by showing how semantic machines make evaluative information portable while requiring continuous organizational work to restore context. It also specifies practical arrangements through which municipalities can use common AI tools without allowing standardized outputs to displace role-specific knowledge or human decision authority.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -2686,12 +4678,36 @@
           <t>Government Information Quarterly</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr"/>
-      <c r="F85" s="2" t="inlineStr"/>
-      <c r="G85" s="2" t="inlineStr"/>
-      <c r="H85" s="2" t="inlineStr"/>
-      <c r="I85" s="2" t="inlineStr"/>
-      <c r="J85" s="2" t="inlineStr"/>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>이론/개념</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>체계적 문헌고찰</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>Trustworthy AI</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>Explainability</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>본 연구는 공공조달 부정탐지에 AI를 적용할 때 자율성 존중, 위해 방지, 공정성, 설명가능성 등의 윤리적 우려를 어떻게 다룰 것인지 탐구한다. 윤리 원칙 선정, 체계적 문헌고찰, 선임 감사관과의 교차분석·전문가 검증을 거쳐, 불투명성·사용자 투명성 부족·설명 도구의 한계·운영 감독 부족·전략적 통제 부족에 대응하는 윤리 지향적 AI 구축 파이프라인인 PRO-Trust를 제시한다.</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>Applying Artificial Intelligence (AI) to fraud detection in Public Procurement (PP) has become increasingly relevant due to its ability to process large volumes of data and identify suspicious patterns more efficiently than traditional methods. However, its implementation raises critical ethical concerns regarding respect for human autonomy, prevention of harm, fairness, and explainability. This study investigates these concerns through a four-phase methodology: (i) selection of ethical principles for AI in PP fraud detection, (ii) a Systematic Literature Review (SLR) on current approaches, (iii) cross-analysis and expert validation with senior auditors, and (iv) the construction of PRO-Trust, an ethics-oriented pipeline for constructing trustworthy AI-based fraud detection systems for PPs, based on the findings of the three former stages. PRO-Trust addresses five recurrent ethical challenges — system opacity, lack of user transparency, limitations in explainability tools, lack of operational oversight, and lack of strategic control — connected between tasks we specified for the construction process of AI-based technologies to fraud detection in PP, the responsible actors, and technological strategies to operationalize ethical principles. By doing so, this study contributes to the development of more trustworthy, transparent, and accountable AI-based fraud detection systems in public administration.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -2712,12 +4728,36 @@
           <t>Public Administration Review</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr"/>
-      <c r="F86" s="2" t="inlineStr"/>
-      <c r="G86" s="2" t="inlineStr"/>
-      <c r="H86" s="2" t="inlineStr"/>
-      <c r="I86" s="2" t="inlineStr"/>
-      <c r="J86" s="2" t="inlineStr"/>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>이론/개념</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>개념적 모형</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>Liberal Democracy</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>Autocratic Populism</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>이 논문은 권위주의적 포퓰리즘의 부상에 대응해 공공관리자가 선출 정치인과 다양한·양극화된 시민집단을 연결하고, 집단 간 합의와 타협을 촉진하며, 대표민주주의와 협력적 거버넌스를 연계하는 역할을 할 수 있는지 개념화한다. 공공관리자를 민주주의의 수호자이자 행위자로 확장하는 것이 정당한지에 관한 문제도 제기한다.</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>ABSTRACT After decades of expansion, liberal democracy is threatened by autocratic populists. These actors exploit widening gaps between leaders and citizens, as well as growing political polarization in the population, to consolidate executive power by undermining courts, sidelining elected assemblies, discrediting public administrators, and intimidating both opposition and the press. This alarming predicament begs the question of what enterprising role public administrators can play in curbing the rise of autocratic populism by reconnecting elected politicians with diverse and polarized population groups while fostering alignment among them. To this end, public administrators are conceptualized as bridgebuilders promoting interactive political leadership along the vertical axis of the political system; as mediators fostering agreement, accommodation, or compromise between polarized groups along the horizontal axis; and as institutional architects linking representative democracy and collaborative governance arenas. This expanded role of public administrators as democratic guardians and protagonists raises important questions regarding its legitimacy.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -2738,12 +4778,36 @@
           <t>Government Information Quarterly</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr"/>
-      <c r="F87" s="2" t="inlineStr"/>
-      <c r="G87" s="2" t="inlineStr"/>
-      <c r="H87" s="2" t="inlineStr"/>
-      <c r="I87" s="2" t="inlineStr"/>
-      <c r="J87" s="2" t="inlineStr"/>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>질적연구</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>서사 텍스트분석</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>Normative Entrainment</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>Affective Narratives</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>유럽 22개국의 국가 인공지능 전략을 분석해, 이 문서들이 책임 있는 AI 논의에서 감정이 결합된 서사를 통해 규범적 지향을 설정·고착하고 실행을 촉진하는 방식을 규명한다. 전략들은 AI에 사회적 가치를 부여하고 문화적 정체성과 일상에 연결하며, 두려움과 희망 같은 도덕적 감정을 활용해 긴급성·리더십·책임을 동원하는 것으로 나타났다.</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>Policy documents guide technological transformations. Prior research on national artificial intelligence (AI) strategies has examined how these texts articulate governance values and principles, but how they promote identification, urgency, and action is less well understood. This gap is especially striking given arguments that national AI strategies are typically written for policy professionals. We show that these documents are also widely used as publicly accessible reference points in debates on responsible AI. Building on the narrative turn in public policy scholarship, we analyse 22 European national AI strategies. We find that AI strategies create normative entrainment through affect, constituted by three narratives: (1) establishing normative orientations by ascribing societal values to AI; (2) anchoring these orientations by invoking social emotions that embed AI in cultural identity and everyday life; and (3) promoting implementation by juxtaposing moral emotions such as fear and hope while mobilising urgency, leadership, and responsibility. By specifying how emotional narratives are woven into policy texts, this framework contributes to research on the communicative construction of AI policy and offers implications for responsible digital transformation.</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -2764,12 +4828,36 @@
           <t>Government Information Quarterly</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr"/>
-      <c r="F88" s="2" t="inlineStr"/>
-      <c r="G88" s="2" t="inlineStr"/>
-      <c r="H88" s="2" t="inlineStr"/>
-      <c r="I88" s="2" t="inlineStr"/>
-      <c r="J88" s="2" t="inlineStr"/>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>질적연구</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>NPF 서사 코딩</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>Narrative Policy Framework</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>Risk-Based Regulation</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>본 연구는 유럽의회 의원들이 2024년 EU 인공지능법으로 이어진 입법 과정에서 AI 정책 서사를 어떻게 구성하고 변화시켰는지 분석했다. 2020~2024년 의회 문서 18건의 서사 500개를 서사정책체계(NPF) 범주로 수기 코딩한 결과, ChatGPT 3.5 출시 같은 외부 충격에도 서사는 대체로 안정적이었으며, 통제와 부상 플롯 및 영웅·수혜자 구도가 AI를 관리 가능하고 유익한 대상으로 제시하고 위험기반 규제·윤리 기준·공동 접근을 강조했다.</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>This article investigates how Members of the European Parliament (MEPs) constructed policy narratives on artificial intelligence (AI) in the legislative process leading up to the EU Artificial Intelligence Act (AI Act) adopted in 2024. While previous research has primarily focused on executive-driven strategy documents, the Parliament's discursive role remains underexplored. To address this gap, the study applies the Narrative Policy Framework (NPF) to a corpus of 18 parliamentary documents from 2020 to 2024, in which 500 narratives were manually coded according to the NPF categories of plot, character, setting, and moral. The findings reveal remarkable stability in the Parliament's AI narratives over time, despite significant external shocks such as the release of ChatGPT 3.5 in 2022. Plots were dominated by stories of control and rising, supported by heroes and beneficiaries, framing AI as both manageable and beneficial. Settings spanned security, global competition, and European legal norms, while morals centered on risk-based regulation, ethical standards, and calls for a joint approach. By illuminating how the European Parliament narrates AI policy, this study contributes to understanding the discursive dynamics shaping EU AI governance and their implications for digital government research, particularly regarding the normative conditions under which AI systems are adopted in public administration.</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -2790,12 +4878,36 @@
           <t>American Political Science Review</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr"/>
-      <c r="F89" s="2" t="inlineStr"/>
-      <c r="G89" s="2" t="inlineStr"/>
-      <c r="H89" s="2" t="inlineStr"/>
-      <c r="I89" s="2" t="inlineStr"/>
-      <c r="J89" s="2" t="inlineStr"/>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>혼합방법론</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>컴퓨터 언어처리</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>Partisanship</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>Political Representation</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>의원들이 소셜미디어와 인터넷을 통해 의정 커뮤니케이션을 어떻게 수행하며, 그 과정에서 당파성과 대표성이 어떻게 나타나는지를 분석한다. 2009~2022년 약 470만 건의 트윗, 240만 건의 페이스북 게시물, 18만4천 건의 이메일 뉴스레터를 언어처리로 분류·측정한 결과, 소셜미디어 이용 증가와 함께 의회 수사가 더 당파적이고 부정적으로 변했으며, 소셜미디어에서는 당파적·부정적 메시지가 다른 메시지보다 긍정적 참여를 더 많이 얻는 것으로 나타났다.</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>Social media and the internet have created new ways for representatives to communicate. How have members of Congress responded to these opportunities? We introduce a multi-platform dataset of congressional communications extending back to the onset of the social media era. Using computational language processing, we classify approximately 4.7 million tweets, 2.4 million Facebook posts, and 184,000 email newsletters authored by members of Congress between 2009 and 2022 based on intended purpose, and scale the partisanship of each message along a continuous left–right dimension. After validation, we demonstrate how our data can be used to study partisanship and representation in the contemporary Congress. Importantly, our data show congressional rhetoric has become more partisan and negative as social media usage has increased. We identify one potential mechanism contributing to this trend: partisanship and negativity receive inflated levels of positive engagement on social media relative to other forms of messaging like credit claiming or constituency service.</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -2816,12 +4928,36 @@
           <t>Government Information Quarterly</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr"/>
-      <c r="F90" s="2" t="inlineStr"/>
-      <c r="G90" s="2" t="inlineStr"/>
-      <c r="H90" s="2" t="inlineStr"/>
-      <c r="I90" s="2" t="inlineStr"/>
-      <c r="J90" s="2" t="inlineStr"/>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>질적연구</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>근거이론 연구</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>Sociotechnical Systems Theory</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>Public Service Ethics</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>영국 지방정부 기관을 대상으로 근거이론 연구를 수행해, 관리자가 디지털 감시를 어떻게 저항하는지와 그 동기를 분석했다. 관리자는 직원 보호, 데이터 은폐, 감시 정당성에 대한 담론적 이의 제기를 통해 저항했으며, 이러한 전략은 자기보호와 가치 지향적 동기에 의해 함께 형성되었다.</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>Workplace surveillance is an increasingly pervasive feature of contemporary organisations, yet research overwhelmingly positions employees as its primary subjects and agents of resistance. Managers, by contrast, are implicitly framed as a homogeneous group who design, implement, and sustain surveillance. We argue that such framing ignores the complex positions managers simultaneously occupy as implementers, mediators, and potential subjects of surveillance, and further obscures situations in which they themselves are monitored, oppose surveillance, or actively engage in resisting it. Drawing on a grounded theory study of a UK local government authority, we examine how and why managers resist digitally augmented surveillance systems, revealing three interrelated resistance strategies: shielding employees from surveillance, obfuscating data to undermine system integrity, and deploying discursive practices to contest surveillance legitimacy. These strategies are simultaneously shaped by self-protective and value-driven motivations. By integrating sociotechnical systems theory with public service ethics, we develop a conceptual framework that repositions managers as agentive, morally reasoning actors navigating the contested terrain of digital control. The findings advance interdisciplinary understanding of resistance and ethics in digitally mediated public sector organisations, and respond to calls for research that recognises managerial diversity and conceptualises resistance as a situated sociotechnical process.</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -2842,12 +4978,36 @@
           <t>Public Administration Review</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr"/>
-      <c r="F91" s="2" t="inlineStr"/>
-      <c r="G91" s="2" t="inlineStr"/>
-      <c r="H91" s="2" t="inlineStr"/>
-      <c r="I91" s="2" t="inlineStr"/>
-      <c r="J91" s="2" t="inlineStr"/>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>서베이</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>횡단면 설문</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>Social Equity</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>본 연구는 2024년 5개 대학 MPA 졸업생 설문을 통해 공공서비스 자료 접근성 제작에 대한 친숙도와 소속 기관의 관련 정책·절차·교육 인식 간의 관계를 기술적으로 분석했다. 기관의 실천에 대한 인식이 높은 응답자는 접근 가능한 자료 제작에 더 익숙했지만, 많은 응답자가 기관의 관련 실천을 알지 못해 조직 내 논의 확대의 필요성이 제기되었다.</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>ABSTRACT As the digital footprint of public service expands, the need for accessible materials for individuals with disabilities grows. Public servants must consider accessibility in the creation of all materials, from websites to PDFs to audio and visual media. However, research around accessible material creation in public service has been limited. This study uses data from a 2024 survey of MPA alumni from five universities to identify their familiarity with accessible material creation, including their awareness of their own organization's policies, processes, and training. The findings reveal that respondent awareness of their own organization's practices was correlated with higher familiarity in generating accessible materials. However, many respondents did not know about their organization's practices, identifying the need for increased dialogue about this essential element of social equity and inclusion. As such, suggestions for organizations to improve their practices around accessible material creation along with ideas for continued research are shared.</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -2868,12 +5028,36 @@
           <t>Government Information Quarterly</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr"/>
-      <c r="F92" s="2" t="inlineStr"/>
-      <c r="G92" s="2" t="inlineStr"/>
-      <c r="H92" s="2" t="inlineStr"/>
-      <c r="I92" s="2" t="inlineStr"/>
-      <c r="J92" s="2" t="inlineStr"/>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>질적연구</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>문서분석·인터뷰</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>bureaucracy</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>hybridity</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>디지털 기술과 제도적 배열의 관계를 규명하기 위해 세 개의 대규모 스칸디나비아 공공복지기관을 대상으로 문서분석과 고위 관리자·정보기술 및 업무개발 담당자 인터뷰를 실시했다. 분석 결과, 하나의 기관 안에서 가로·스크린·시스템 수준 관료제가 동시에 결합되는 다기능적 ‘혼합 관료제’가 나타나며, 자동화 수준과 조직 경로가 서비스별로 달라질 수 있음을 제시했다.</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>Public agencies are strategically adapting and applying digital technologies to improve their business processes and deliver greater value to society. This development has a profound impact on the agencies' institutional arrangements. While some services that the agencies offer are almost fully automated, others still require a high level of caseworker involvement. The variance in levels of automation and the coexistence of different institutional arrangements within the same agency are interesting and challenging because they contradict predictions made by both scholars and policymakers. Therefore, we present a study of three large Scandinavian public welfare agencies, utilizing document analysis supplemented by interviews with top managers and senior IT and business developers. We apply Bovens and Zouridis' (2002) typology of street-, screen-, and system-level bureaucracies as our main analytical lens, combined with Christensen and Lægreid's (2011) concepts of hybridity and sedimentation, with a socio-technical perspective in the background. We contribute to digital government and public administration research by enhancing theoretical understanding of the relationship between digital technologies, institutional arrangements and organizational trajectories. Specifically, we identify the hybrid bureaucracy as a composite, multifunctional organizational entity that encompasses several institutional arrangements simultaneously and combines aspects of street-, screen-, and system-level bureaucracies while also exhibiting its own distinct characteristics.</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -2894,12 +5078,36 @@
           <t>Government Information Quarterly</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr"/>
-      <c r="F93" s="2" t="inlineStr"/>
-      <c r="G93" s="2" t="inlineStr"/>
-      <c r="H93" s="2" t="inlineStr"/>
-      <c r="I93" s="2" t="inlineStr"/>
-      <c r="J93" s="2" t="inlineStr"/>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>서베이</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>설문 실험</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>Data Custodianship</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>Institutional Trust</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>홍콩과 한국 시민을 대상으로 안면인식용 생체정보의 관리 주체에 대한 신뢰를 설문 실험으로 비교한 결과, 제도적 신뢰는 책임성 장치뿐 아니라 공공기관 경험, 정치적 성향, 사회적 신뢰, 개인정보보호 선호에 의해 형성되며 수집·저장·관리 등 데이터 관리 기능별로 서로 다를 수 있었다. 따라서 데이터 수탁이 이용자 통제의 대안이 되려면 사회·개인·거버넌스 기능별 신뢰의 차이를 반영해야 한다.</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>Public administration researchers traditionally approach the use of personal information in public service through the lens of direct user control, but a combination of cognitive constraints and rapid digitization has made privacy-preserving choices exceedingly difficult for citizens to manage independently. Recent research has shifted toward the notion of “data custodianship”, where public institutions serve as custodians of personal information. In a survey experiment conducted in Hong Kong ( n = 1031) and South Korea ( n = 1040), citizens evaluated their trust in various institutions serving as custodians tasked with managing biometric information for facial recognition. The findings suggest that while institutional trust can be influenced by accountability mechanisms, it is also shaped by individuals' experiences with public institutions, as well as their political orientation, social trust, and privacy preferences. Trust in one functional domain of data custodianship—such as data collection—may not carry over to others, like storage or management. Custodianship is only viable as a policy alternative to user control in data-intensive solutions if its design accounts for variation in public trust across societies, individuals, and aspects of data governance.</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -2920,12 +5128,36 @@
           <t>Government Information Quarterly</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr"/>
-      <c r="F94" s="2" t="inlineStr"/>
-      <c r="G94" s="2" t="inlineStr"/>
-      <c r="H94" s="2" t="inlineStr"/>
-      <c r="I94" s="2" t="inlineStr"/>
-      <c r="J94" s="2" t="inlineStr"/>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>혼합방법론</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>탐색·확인 요인분석</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>Digital Maturity</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>Scale Development</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>스웨덴 공공부문 118개 조직의 자료에 탐색적·확인적 요인분석을 적용해 기존 디지털 성숙도 프레임워크의 잠재 구조를 검증한 결과, 디지털 운영·디지털 유산·편익 관리·디지털 개발의 4요인 모형이 2차 요인인 평가된 디지털 성숙도 아래에서 지지되었다.</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>Digital maturity frameworks have become central instruments of digital government practice, used by public sector organizations, national agencies, and international bodies to assess and steer digital transformation. Despite their widespread use, few frameworks have been subjected to rigorous psychometric testing. The scores they produce therefore rest on unverified assumptions about dimensionality, reliability, and validity. We address this gap by applying scale development methodology to a digital maturity framework deployed across more than 160 Swedish public sector organizations since 2018. Through exploratory and confirmatory factor analysis on a cleaned and multiply imputed sample from 118 organizations, we evaluate the framework's latent factor structure. The analysis yields a four-factor model that is empirically supported within the studied sample, comprising Digital Operations, Digital Legacy, Benefit Management, and Digital Development, subsumed under a second-order factor of Evaluated Digital Maturity. The results also reveal specific weaknesses that are predictable consequences of deploying an instrument developed without scale development methodology. We make two contributions. First, we provide a large-scale empirical test of a widely used digital maturity framework in the public sector, identifying its strengths and the implications of developing an instrument without psychometric grounding. Second, we adapt scale development methodology from prospective scale construction to retrospective framework evaluation, strengthening measurement in digital government research.</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -2946,12 +5178,36 @@
           <t>Government Information Quarterly</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr"/>
-      <c r="F95" s="2" t="inlineStr"/>
-      <c r="G95" s="2" t="inlineStr"/>
-      <c r="H95" s="2" t="inlineStr"/>
-      <c r="I95" s="2" t="inlineStr"/>
-      <c r="J95" s="2" t="inlineStr"/>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>질적연구</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>탐색적 사례분석</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>Assemblage Thinking</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>Public Value</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>이 연구는 분권화된 공공부문 데이터 플랫폼이 어떤 조건에서 공공가치를 창출하는지 탐색하기 위해 조립체 관점과 공공가치 프레임워크를 적용해 함부르크 도시 데이터 플랫폼을 사례 분석했다. 분석 결과, 공공가치는 기술적 분권화만으로 결정되지 않으며, 분권적·중앙집중적 실천의 결합과 이를 조정하는 핵심 오케스트레이터를 포함한 아키텍처-거버넌스 구성에 달려 있는 것으로 나타났다.</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>Technology decentralisation is increasingly proposed as a key feature to build more trustworthy, accessible, and innovative digital public infrastructure, yet there is limited empirical knowledge of the actual benefits that such decentralised approaches would create from a public sector perspective. Furthermore, existing literature often relies on a linear dichotomy between data supply and demand that fails to capture the complexity of decentralised data ecosystems. This paper addresses these gaps by adopting an assemblage thinking perspective to conceptualise data platforms as complex socio-technical arrangements, and by developing a public values framework to broaden the understanding of the various outcome that data platforms can create. We apply this approach to an exploratory case study of Hamburg's Urban Data Platform (UDP). Our findings demonstrate that public value creation is not determined by technical decentralisation alone but by specific architecture-governance configurations. We illustrate that both decentral and central practices can co-occur within the same system, where the role of a leading orchestrator is crucial to drive public value creation.</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -2998,12 +5254,36 @@
           <t>American Political Science Review</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr"/>
-      <c r="F97" s="2" t="inlineStr"/>
-      <c r="G97" s="2" t="inlineStr"/>
-      <c r="H97" s="2" t="inlineStr"/>
-      <c r="I97" s="2" t="inlineStr"/>
-      <c r="J97" s="2" t="inlineStr"/>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>서베이</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>반복 설문조사</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>Myopic Voter</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>Retrospective Voting</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>유권자가 과거와 미래의 조건을 평가할 때 시간적으로 가까운 정보만 중시하는지, 아니면 개선되는 조건 자체를 선호하는지를 네 표본을 대상으로 한 네 차례 설문으로 검토했다. 유권자는 과거와 미래 모두에서 초기 정보도 무시하지 않으며 개선되는 조건을 선호했고, 이는 단순한 상승 추세 휴리스틱이나 보편적 근시안성으로 설명되지 않았다.</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>Abstract Timing of valence outcomes plays an important role in key theories of electoral choice, and different models place different emphases on past and future outcomes. Whereas sanctioning models consider only retrospective evaluations as an accountability mechanism, selection models hold that voters use past and proposed future conditions to infer the incumbent’s ability to deliver benefits. Drawing on four surveys run on six different samples, we demonstrate that voters prefer improving conditions in both retrospection and prospection. In retrospection, this pattern is difficult to distinguish from overweighting of temporally proximate conditions, which gave rise to the notion of “the myopic voter.” Distinguishing the two processes, we find that people do not ignore early datapoints and reward improving conditions (in both retrospection and prospection). This preference for improvement does not simply reflect an uncritical heuristic for upward trends. People are not universally myopic and many genuinely value improving aggregate conditions retrospectively and prospectively.</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -3024,12 +5304,36 @@
           <t>Government Information Quarterly</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr"/>
-      <c r="F98" s="2" t="inlineStr"/>
-      <c r="G98" s="2" t="inlineStr"/>
-      <c r="H98" s="2" t="inlineStr"/>
-      <c r="I98" s="2" t="inlineStr"/>
-      <c r="J98" s="2" t="inlineStr"/>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>서베이</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>국제 설문자료 비교</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>Corruption Susceptibility</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>Democratic Values</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>90개국 공무원 18,277명의 자료를 활용해 공직자의 부패행위 취약성을 예측할 때 기존 회귀모형과 5개 지도학습 모형의 성과를 비교했다. 머신러닝이 더 높은 예측 정확도를 보였으며, 소득·교육·성별보다 민주적 가치, 경쟁에 대한 신념, 리더십 태도가 일관되게 중요한 예측변수로 나타났다.</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>Public corruption undermines government performance, erodes trust, and fuels illiberal populism. While macro-level drivers of corruption are well documented, little is known about the individual-level attitudes and beliefs associated with public servants' susceptibility to engaging in corrupt behaviour. Using a large-scale, globally stratified dataset of 18,277 public servants across 90 countries, we systematically compare a conventional regression baseline with five contemporary supervised machine learning models to predict susceptibility to corruption. Machine learning improves predictive accuracy and shows that democratic values, beliefs about competition, and attitudes towards leadership are more consistently predictive than socio-economic characteristics such as income, education, or gender. These patterns are robust across modelling approaches and analytical settings. The findings illustrate the value of transparent model comparison and machine learning for studying integrity risks, provide exploratory insights for corruption prevention strategies, and open new avenues for research on predictive modelling for public sector integrity.</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -3076,12 +5380,36 @@
           <t>Governance</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr"/>
-      <c r="F100" s="2" t="inlineStr"/>
-      <c r="G100" s="2" t="inlineStr"/>
-      <c r="H100" s="2" t="inlineStr"/>
-      <c r="I100" s="2" t="inlineStr"/>
-      <c r="J100" s="2" t="inlineStr"/>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>질적연구</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>비교 사례연구</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>Critical Junctures</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>Policy Paths</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>본 연구는 왜 일부 중대 국면(critical junctures)이 정책의 실질적 변화를 이끌지 못하는지를 정책 경로의 동태성과 정태성 관점에서 두 사례를 비교해 분석한다. 덴마크에서는 기후정책 합의가 농업정책의 새로운 방향과 변화를 만들었지만, 노르웨이에서는 부문별 정책의 경로가 유지되었으며, 동태적 경로에는 프레이밍·대상뿐 아니라 정책수단과 행위자·제도의 유의미한 변화도 필요하다고 주장한다.</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>ABSTRACT Some critical junctures fail to cause significant change in practice. Inspired by historical institutionalism, this article develops the concept of dynamic and static policy paths to explain why some critical junctures do not lead to change, while others do. Combining insights from policy process literature and policy implementation, it conceptualizes critical junctures through four elements: framing, targets, instruments, and actors/institutions. Based on two case studies, the article argues that the importance of framing and targets has been overexaggerated, and that a dynamic path will not occur unless there is also a significant change in instruments and actors/institutions. In Denmark, a climate policy agreement created a new policy direction for agriculture in which climate policy is a key component. In Norway, a climate policy agreement did not change the trajectory of sectoral policy and climate policy development has remained stagnant. Thus, differences in the critical junctures led to different policy paths.</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -3102,12 +5430,36 @@
           <t>American Journal of Political Science</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr"/>
-      <c r="F101" s="2" t="inlineStr"/>
-      <c r="G101" s="2" t="inlineStr"/>
-      <c r="H101" s="2" t="inlineStr"/>
-      <c r="I101" s="2" t="inlineStr"/>
-      <c r="J101" s="2" t="inlineStr"/>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>이론/개념</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>사례 기반 분석</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>Territorial Rights</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>Political Standing</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>본 논문은 인간의 영토권을 정당화하는 이론적 논리가 야생동물에게도 적용되는지, 특히 야생 당나귀사슴이 점유·거주·자원 이용·통제에 충분히 중대한 이해관계를 갖는지를 검토한다. 나인과 무어의 영토권 논리를 사례에 적용한 결과, 야생동물을 단순한 천연자원으로 취급하지 말고 인간에게 의무와 정치적 고려의 근거가 될 수 있는지 재검토해야 한다고 주장한다.</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>Abstract Territorial rights (TR) have become foundational in normative political theory, addressing pressing questions about boundary drawing, governance, and resource use. Influential TR theorists Cara Nine and Margaret Moore justify humans’ TR based on the functional, social, and identity‐anchored normative significance of non‐substitutable places. However, these arguments treat animals as resources, excluding them from normative consideration and political standing. This article analyzes Nine and Moore's arguments to assess whether their justificatory logic applies to wild animals. Using mule deers as a case study, I test whether they have sufficiently weighty interests in occupancy, residency, resource use, and control to ground duties on humans and whether TR theories should continue to treat animals as mere natural resources.</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -3128,12 +5480,36 @@
           <t>Review of Public Personnel Administration</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr"/>
-      <c r="F102" s="2" t="inlineStr"/>
-      <c r="G102" s="2" t="inlineStr"/>
-      <c r="H102" s="2" t="inlineStr"/>
-      <c r="I102" s="2" t="inlineStr"/>
-      <c r="J102" s="2" t="inlineStr"/>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>서베이</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>단면 전국설문</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>Public Service Motivation</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>Job Satisfaction</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>미국 지방정부 관리자 대상 전국 대표 단면 설문을 활용해, 공공참여 노출과 직무만족도가 자원봉사 참여 및 강도와 어떻게 관련되는지 개인의 기존 자원봉사 여부에 따라 분석했다. 비자원봉사자는 공공참여 노출과 직무만족도가 높을수록 자원봉사를 시작할 가능성이 높았고, 현재 자원봉사자는 이 수준이 낮을수록 더 많은 시간을 봉사했지만 높은 수준에서는 더 다양한 영역에서 봉사했으며, 직무만족도는 공공참여 노출과 봉사 강도의 관계를 부적으로 조절했다.</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>Public employees serve the public interest through their work and extend this commitment through volunteerism. However, it remains unclear what motivates them to volunteer when professional roles already fulfill intrinsic prosocial motivations. Drawing on theories from multiple life domains and public service motivation, this study examines how public sector workplace experiences, specifically exposure to public participation and job satisfaction, are associated with volunteering behavior. Using cross-sectional, nationally representative survey data from U.S. local government managers, this study finds that the relationships vary by individuals’ prior volunteering status. Among non-volunteers, higher levels of public participation exposure and job satisfaction are both associated with a greater probability of initiating volunteering. Among current volunteers, lower levels are associated with greater time devoted to volunteering, whereas higher levels are linked to volunteering across a wider range of domains. Job satisfaction negatively moderates the relationship between public participation exposure and volunteering intensity. This study extends conventional understanding of public employee volunteering beyond public service motivation and sector differences by demonstrating a contingent work–volunteerism association, offering practical insights into managing workplace experiences to sustain public service both within and beyond organizational boundaries.</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -3154,12 +5530,36 @@
           <t>Political Communication</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr"/>
-      <c r="F103" s="2" t="inlineStr"/>
-      <c r="G103" s="2" t="inlineStr"/>
-      <c r="H103" s="2" t="inlineStr"/>
-      <c r="I103" s="2" t="inlineStr"/>
-      <c r="J103" s="2" t="inlineStr"/>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>혼합방법론</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>계산적 콘텐츠분석</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>Identity Politics</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>Political Polarization</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>이 연구는 인종적으로 주변화된 공동체의 사회정의 담론이 트위터와 유튜브에서 문화전쟁 서사를 통해 어떻게 정치화되는지 2012~2022년 자료에 대한 이용자·콘텐츠 수준의 계산분석으로 검토했다. ‘woke’는 양 플랫폼에서 문화전쟁 담론 속에서 점점 증폭되었고, 트위터에서는 문화전쟁 주제가, 유튜브에서는 보수적 뉴스·논평 채널이 두드러졌으며, 특히 보수 이용자들의 플랫폼 간 콘텐츠 공유가 이러한 정치화를 연계·증폭했다.</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>This paper explores how the discourse surrounding a racially marginalized community becomes politicized via culture war narratives across platforms. Drawing from identity politics and political polarization research, we discuss how racial justice discourse can be hijacked by partisan opinion leaders and their followers over time and explain how this process plays out through both differentiated and coordinated social media platform use. Situating our discussion in the “woke” discourse as originated within the Black Twitter community, we collect data from 2012 through 2022 on Twitter and YouTube and apply user- and content-level computational analyses. Results show that the term “woke” has been increasingly amplified in culture war conversations on both platforms over time. However, the two platforms exhibited differences: culture war topics dominated on Twitter, while conservative news and commentary channels were most prevalent on YouTube. These two platforms were also interrelated in the politicization process. YouTube was a top domain within external links embedded in tweets, and Twitter was also a top destination within the external links embedded in YouTube video descriptions. Conservatives were especially keen on sharing right-wing content across platforms, from YouTube to Twitter, suggesting the success of cross-platform coordination in amplifying culture wars. Both theoretical and political implications for polarization on social media are discussed.</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -3180,12 +5580,36 @@
           <t>Political Communication</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr"/>
-      <c r="F104" s="2" t="inlineStr"/>
-      <c r="G104" s="2" t="inlineStr"/>
-      <c r="H104" s="2" t="inlineStr"/>
-      <c r="I104" s="2" t="inlineStr"/>
-      <c r="J104" s="2" t="inlineStr"/>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>실험</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>설문 실험</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>Democratic Accountability</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>Democratic Norms</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>일본·한국·대만·미국 유권자 10,194명을 대상으로 한 비네트 실험을 통해 선거 부정, 시위 억압, 사법부 공격 등 민주적 규범 위반 정치인에 대한 제재와 정파적 이중 기준을 비교했다. 동아시아 민주국가 유권자들이 미국 유권자보다 더 강하게 제재했으며, 선거 부정에 대한 제재가 가장 일관되게 강했고 국가별·위반 유형별 차이도 나타났다.</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>Existing research shows that voters in established democracies often fail to penalize politicians who violate democratic norms, as many are willing to trade democratic principles for partisan interests in polarized environments. Yet such partisan double standards remain underexplored in East Asia, where countries share authoritarian legacies, face ongoing risks of democratic backsliding, and operate under the geopolitical shadow of powerful authoritarian neighbors. Using a large-scale vignette experiment conducted in Japan, South Korea, Taiwan, and the United States (N = 10,194), this study examines whether voters sanction politicians who engage in democratic norm violations. We focus on reactions to three types of undemocratic statements: election denial, protest suppression, and attacks on the judiciary. The results show that voters in East Asian democracies impose stronger penalties than their American counterparts, though the degree and pattern of accountability differ across cases. Election denial consistently generates the strongest sanctions, while Japan and Taiwan show robust reactions across all scenarios. South Korea displays comparatively modest responses to protest suppression, and the United States shows the weakest effects overall. These findings highlight both the resilience and the heterogeneity of democratic accountability in East Asia and underscore the need to understand regional variation when assessing the prospects for democratic stability.</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -3206,12 +5630,36 @@
           <t>Review of Public Personnel Administration</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr"/>
-      <c r="F105" s="2" t="inlineStr"/>
-      <c r="G105" s="2" t="inlineStr"/>
-      <c r="H105" s="2" t="inlineStr"/>
-      <c r="I105" s="2" t="inlineStr"/>
-      <c r="J105" s="2" t="inlineStr"/>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>질적연구</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>문서 기반 사례</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>Institutional Theory</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>Strategic PHRM</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>이 연구는 레바논 공공조달법 제244호(2021) 아래 공공조달 인력의 전문화가 어떻게 구축·제도화되고 있는지를 문서 기반 질적 사례연구로 분석했다. 역량 프레임워크, 자격인증, 전문교육 체계를 통해 전문화가 진전됐지만, 공무원 체계 전반에 고르게 정착되지는 않은 것으로 나타났다.</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
+          <t>A capable public sector workforce is essential for sustainable development. In public procurement, the ability of procurement reform to support Sustainable Development Goals depends on a workforce with the competencies and professional standing needed to translate reform into administrative practice. Drawing on Institutional Theory and strategic PHRM, this study examines how workforce professionalization in public procurement is being constructed and institutionalized in Lebanon under Public Procurement Law No. 244 of 2021. Using a document-based qualitative case study, the study analyzes legal documents, technical reports, competency frameworks, and training materials produced between 2020 and 2025. The findings show that workforce professionalization in public procurement advanced through competency frameworks, certification initiatives, and professional training systems. However, workforce professionalization remains unevenly embedded across the civil service system. The study contributes to strategic public HRM and procurement governance scholarship and offers insight into workforce professionalization in governance-constrained settings in the Global South.</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -3232,12 +5680,36 @@
           <t>Governance</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr"/>
-      <c r="F106" s="2" t="inlineStr"/>
-      <c r="G106" s="2" t="inlineStr"/>
-      <c r="H106" s="2" t="inlineStr"/>
-      <c r="I106" s="2" t="inlineStr"/>
-      <c r="J106" s="2" t="inlineStr"/>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>실험</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>설문 실험</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>Social Norms</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>Motivation Crowding</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>중국에서 부패에 대한 사회적 관용 수준을 실제보다 높게 인식하는 오해를 바로잡는 정보가 반부패 태도와 의도를 강화하는지, 그리고 처벌 단서가 이 효과에 미치는 영향을 대규모 설문실험으로 검증했다. 실제 관용 수준이 낮다는 정보는 특히 다수가 부패를 용인한다고 잘못 믿은 사람들에게 효과적이었지만, 처벌 정보와 결합하면 규범 기반 메시지의 동기 효과가 약화됐다.</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>ABSTRACT A growing body of scholarship views corruption not merely as a failure of monitoring and enforcement but as a resilient informal institution sustained by social perceptions—and misperceptions. When citizens believe others tolerate or engage in corruption, resisting it becomes a collective action problem, allowing corruption to perpetuate itself. Using a large‐scale survey experiment in China, this study tests whether correcting exaggerated perceptions of social tolerance for corruption can help break this cycle. We find that providing information about the actual (low) level of tolerance significantly strengthens anti‐corruption attitudes and intentions, especially among those who mistakenly believed a majority tolerated corruption. However, this effect is weakened when paired with punishment cues, suggesting that enforcement information can crowd out the motivational force of norm‐based messages. Our findings demonstrate both the potential and the limits of norm‐based informational interventions and offer implications for anti‐corruption messaging in comparable contexts.</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -3258,12 +5730,36 @@
           <t>The American Review of Public Administration</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr"/>
-      <c r="F107" s="2" t="inlineStr"/>
-      <c r="G107" s="2" t="inlineStr"/>
-      <c r="H107" s="2" t="inlineStr"/>
-      <c r="I107" s="2" t="inlineStr"/>
-      <c r="J107" s="2" t="inlineStr"/>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>실험</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>비네트 설문 실험</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>Credit Attribution</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>Contracting Out</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>이 연구는 정부가 직접 서비스를 제공하는 경우와 외부 위탁하는 경우에 공공서비스 제공기관과 개별 직원에게 공로가 어떻게 귀속되는지를 연방·주·지방정부 수준별 비네트 설문실험으로 분석했다. 뛰어난 성과에 대한 공로는 정부보다 제3자 제공기관에 더 많이 돌아갔지만, 개별 직원 차원에서는 특히 연방정부에서 공무원에게 공로를 주려는 경향이 더 강했다.</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>Both government and government employees alike face negativity bias, but could conveying the exemplary work of public service help address declining public trust and engagement? While scholarly research has examined how the public assigns blame when the government or a contractor falls short, far less attention has been paid to the positive side. How is credit assigned to employees and agencies when they go above and beyond what is required in their jobs? This research addresses this gap through a vignette survey experiment, which is used to determine how contracting influences credit given to the service provider and the individual employee across levels of government –federal, state, and local. The results reveal that credit is more likely to be given to third-party providers than the government directly providing the service. However, at the individual employee level, the public prefers to give credit to public employees, especially at the federal government level, when outstanding work occurs. Findings have implications for contracting, performance, and accountability, where perhaps sharing more positive stories of public service can foster more positive public views.</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -3284,12 +5780,36 @@
           <t>Policy Studies Journal</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr"/>
-      <c r="F108" s="2" t="inlineStr"/>
-      <c r="G108" s="2" t="inlineStr"/>
-      <c r="H108" s="2" t="inlineStr"/>
-      <c r="I108" s="2" t="inlineStr"/>
-      <c r="J108" s="2" t="inlineStr"/>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>실험</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>종단 네트워크 모형</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>SAOM</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>Preferential Attachment</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>이 연구는 라틴아메리카 한 도시의 지방정부 간 네트워크가 2009~2021년 세 차례 시장 임기 동안 어떻게 변화했으며, 그 과정에서 권력 비대칭이 완화되거나 심화되는지를 분석한다. 종단 네트워크 자료에 확률적 행위자 지향 모형(SAOM)을 적용한 결과, 자원 격차와 선호적 연결이 일부 지방정부의 중심적 지위를 강화해 광역 거버넌스의 권력 불균형을 심화시킬 가능성이 나타났다.</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr">
+        <is>
+          <t>ABSTRACT This study investigates power dynamics in metropolitan governance by analyzing the evolution of an inter‐municipal network in a Latin American city. It argues that actors build partnering strategies in a bid to improve their position in the network while minimizing the costs of collaborative action. These network micro‐mechanisms aggregate to produce macro‐level structures that may or may not mitigate the starting power asymmetries. By applying stochastic actor‐oriented models (SAOMs) to longitudinal data for 2009–2021, corresponding to three mayoral terms, the research reveals how collaborative dynamics are driven by resource disparities and preferential attachment that, in turn, reinforce the central positions of certain municipalities and potentially exacerbate power imbalances in metropolitan governance. The findings underscore the critical importance of considering these power dynamics when studying the operation and performance of polycentric governance systems, particularly in contexts marked by existing inequalities.</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -3310,12 +5830,36 @@
           <t>Political Behavior</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr"/>
-      <c r="F109" s="2" t="inlineStr"/>
-      <c r="G109" s="2" t="inlineStr"/>
-      <c r="H109" s="2" t="inlineStr"/>
-      <c r="I109" s="2" t="inlineStr"/>
-      <c r="J109" s="2" t="inlineStr"/>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>서베이</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>군집·회귀분석</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>Affective Polarization</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>Democratic Participation</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>이 연구는 정서적 양극화가 민주주의에 대한 시민의 인식과 참여에 미치는 영향을 이해하기 위해, 정당에 대한 절대적 호감도의 차이를 반영하여 미국 전국대표 설문 3건을 군집분석과 회귀분석으로 분석했다. 정서적으로 비양극화된 시민은 양당에 미지근한 집단과 모두에게 냉담한 집단으로 나뉘며, 두 집단은 민주주의 태도와 참여 양상에서 서로 다른 것으로 나타났다.</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="inlineStr">
+        <is>
+          <t>Abstract Does affective polarization change how citizens view and participate in democracy? We posit that the answer to this crucial question depends on how affectively un polarized citizens view and participate in democracy. Yet, the most common operationalization of affective polarization––measuring sympathy ratings for one party relative to another––does not differentiate between people’s absolute sympathy ratings for the parties, which may mask essential heterogeneity among unpolarized citizens. This paper theorizes the methodological origin of this heterogeneity, describes it, and highlights its implications. Cluster analyses and regressions from three nationally representative surveys in the US provide three conclusions. First, substantial shares of the US population are affectively un polarized. Second, unpolarized citizens cluster into two groups: one feeling lukewarm and one feeling cold toward both parties. Third, these unpolarized groups report diverging democratic attitudes and participation patterns. We discuss the methodological implications and the need for future research on affectively unpolarized citizens.</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -3336,12 +5880,36 @@
           <t>Political Behavior</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr"/>
-      <c r="F110" s="2" t="inlineStr"/>
-      <c r="G110" s="2" t="inlineStr"/>
-      <c r="H110" s="2" t="inlineStr"/>
-      <c r="I110" s="2" t="inlineStr"/>
-      <c r="J110" s="2" t="inlineStr"/>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>실험</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>설문 실험</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>Opinion-Policy Congruence</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>Political Equality</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>정책 선호와 실제 정책의 일치 여부가 정부 만족도에 미치는 영향과, 정책 결과가 선호와 일치하더라도 정치적 영향력의 불평등이 불만을 초래하는지를 사전등록 설문실험으로 검토했다. 정책-의견 일치는 만족도의 중요한 예측요인이었지만, 응답자들은 정책 결과와 무관하게 정치적 평등도 중시했으며, 우연한 대표성이 영향력 불평등을 완전히 보상하지 못하는 것으로 나타났다.</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="inlineStr">
+        <is>
+          <t>A much-cited finding in recent political science is that average citizens in established democracies appear to have little influence on public policy, while the affluent have strong influence. Yet, as critics have pointed out, average and affluent often want the same from government, meaning that even without influence, average citizens often get the policies they want ‘by coincidence’. This raises an important question: Do citizens care about ‘who governs’ if government regularly adopts their preferred policies anyway? Using a preregistered survey experiment, I show that political inequality causes just as much popular dissatisfaction with government when policy outcomes are highly consistent with a respondent’s policy preferences, as it does when policy outcomes are inconsistent with those preferences. While opinion-policy congruence remains an important predictor of satisfaction, citizens also appear to value political equality independently of policy outcomes. These findings suggest that coincidental representation may not fully compensate for perceived inequalities in political influence.</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -3362,12 +5930,36 @@
           <t>Public Administration Review</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr"/>
-      <c r="F111" s="2" t="inlineStr"/>
-      <c r="G111" s="2" t="inlineStr"/>
-      <c r="H111" s="2" t="inlineStr"/>
-      <c r="I111" s="2" t="inlineStr"/>
-      <c r="J111" s="2" t="inlineStr"/>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>질적연구</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>다지역 사례연구</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>Co-production</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>이 연구는 인도네시아 아동 발육부진 감축 프로그램에서 성별이 공동생산의 공동기획·공동설계·공동집행·공동평가를 어떻게 형성하는지 탐색한다. 세 지방정부 지역에 대한 질적 연구와 ‘Four Co(s)’ 틀을 적용한 결과, 조혼·빈곤·농촌 및 기술적 불리함이 지속적인 문제로 나타났으며 특히 여성이 공동생산을 촉진하는 핵심 행위자로 기능하는 것으로 분석되었다.</t>
+        </is>
+      </c>
+      <c r="J111" s="2" t="inlineStr">
+        <is>
+          <t>ABSTRACT Co‐production is a complex and nuanced field of social action that operates at multiple levels of the policy cycle, closely interconnecting the roles, motivations, and outcomes of different social actors. But how co‐production practices are shaped by gender is often overlooked. This article highlights the complexity of co‐production practices within Indonesia's ambitious national strategy to reduce child stunting. Based on qualitative research of three local government areas implementing stunting intervention programs, we draw on the ‘Four Co(s)’ framework to explore variations across co‐commissioning, co‐design, co‐delivery, and co‐assessment. Ongoing challenges to the eradication of stunting in some areas highlight the tense intersections between early marriage, poverty and rural and technological disadvantage. But as we argue, it is also dependent on social actors, especially women, who serve as catalysts. Future research that pays closer attention to the inherently gendered expressions of co‐production is both theoretically and practically necessary.</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -3388,12 +5980,36 @@
           <t>Public Administration Review</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr"/>
-      <c r="F112" s="2" t="inlineStr"/>
-      <c r="G112" s="2" t="inlineStr"/>
-      <c r="H112" s="2" t="inlineStr"/>
-      <c r="I112" s="2" t="inlineStr"/>
-      <c r="J112" s="2" t="inlineStr"/>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>준실험</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>다중 회귀모형</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>Institutional Collective Action</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>Coordination Costs</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>이 연구는 제도적 집합행동(ICA) 관점에서 캘리포니아 Homekey 프로그램의 지방 집행자들이 호텔 전환, 다가구주택 매입, 모듈러·신축 중 주거 형태를 선택하는 데 조정 수요가 어떤 영향을 미치는지 분석했다. 이항 로지스틱, GEE, 다항 로지스틱 모형을 사용한 결과, 대규모·영구주택 사업은 호텔 전환을, 주택당국은 다가구주택 매입을 더 선택했으며, 지역 공실 제약은 모듈러·신축보다 호텔 전환을 유도했다.</t>
+        </is>
+      </c>
+      <c r="J112" s="2" t="inlineStr">
+        <is>
+          <t>ABSTRACT Local implementers have discretion in selecting forms of housing for the homeless, yet the determinants of these choices remain poorly understood. Using the institutional collective action (ICA) framework, this study examines California's Homekey program to assess how coordination demands shape decisions among hotel conversions, multifamily acquisitions, and modular or new construction. Drawing on binary logistic, generalized estimating equation (GEE), and multinomial logistic models, we find that larger projects and those designated as permanent housing are significantly more likely to pursue hotel conversions. Housing authorities—owing to their specialized missions and lower form‐specific coordination costs—are over six times more likely than cities to select multifamily acquisition. Local vacancy constraints further steer implementers away from modular or new construction and toward hotel conversions. These results demonstrate that implementation form is not a neutral technical decision but an institutional response to coordination challenges embedded in intergovernmental and interorganizational contexts.</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -3414,12 +6030,36 @@
           <t>Public Management Review</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr"/>
-      <c r="F113" s="2" t="inlineStr"/>
-      <c r="G113" s="2" t="inlineStr"/>
-      <c r="H113" s="2" t="inlineStr"/>
-      <c r="I113" s="2" t="inlineStr"/>
-      <c r="J113" s="2" t="inlineStr"/>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>질적연구</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>단일국가 사례</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>Robust Governance</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>Intergovernmental Cooperation</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>이 글은 체코의 코로나19 팬데믹과 우크라이나 전쟁에 따른 난민 위기 대응을 단일국가 사례연구로 분석해, 도시와 지역 간 협력이 강건한 거버넌스 해법을 제공할 수 있는지 탐색한다. 협력은 지역사회의 삶을 개선하고 강건한 해법에 기여했지만, 중앙정부의 실패, 리더십과 전략적 초점 부족, 공식화된 학습의 부재로 그 잠재력이 충분히 실현되지 않았다.</t>
+        </is>
+      </c>
+      <c r="J113" s="2" t="inlineStr">
+        <is>
+          <t>The goal of this article is to explore whether municipal and regional cooperation can provide robust governance solutions during a polycrisis. The methodology of the article is based on a single-country case study from Czechia. The case study focuses on coping with the COVID-19 pandemic and the refugee crisis resulting from the war in Ukraine. We demonstrate how cooperation between a city and a region contributed to robust solutions and improved the lives of local communities. Although municipal and regional cooperation can potentially create significant positive effects that align with the definition of robust governance, this potential is not fully realized in Czechia. The main reasons for this untapped potential are failures of the central government, a lack of leadership and strategic focus, and the absence of formalized learning.</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr"/>
@@ -3436,12 +6076,28 @@
           <t>Public Administration Review</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr"/>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>방법 미상</t>
+        </is>
+      </c>
       <c r="F114" s="2" t="inlineStr"/>
-      <c r="G114" s="2" t="inlineStr"/>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>Professional Association</t>
+        </is>
+      </c>
       <c r="H114" s="2" t="inlineStr"/>
-      <c r="I114" s="2" t="inlineStr"/>
-      <c r="J114" s="2" t="inlineStr"/>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>미국행정학회(ASPA)의 조직과 사명을 소개하는 호 정보로, 연구 질문·연구 방법·주요 발견은 제시되지 않는다.</t>
+        </is>
+      </c>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t>The American Society for Public Administration (ASPA) is a nonpartisan organization of more than 9,000 scholars, administrators, public managers, and students in the United States, and abroad.ASPA is committed to the advancement of excellence in</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -3462,12 +6118,36 @@
           <t>International Journal of Public Administration</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr"/>
-      <c r="F115" s="2" t="inlineStr"/>
-      <c r="G115" s="2" t="inlineStr"/>
-      <c r="H115" s="2" t="inlineStr"/>
-      <c r="I115" s="2" t="inlineStr"/>
-      <c r="J115" s="2" t="inlineStr"/>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>이론/개념</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>체계적 문헌고찰</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>governance</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>cross-sectoral collaboration</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t>취약 구직자의 고용 증진을 위한 자발적 부문 간 협력에 관한 71편의 연구를 체계적으로 종합해, 협력의 조직·지속 방식과 성과 근거를 검토했다. 문헌은 협력 과정에 집중하며 기존 행정 접근을 대체하기보다 그 위에 추가되는 경향을 보였고, 구직자 역량 강화와 고용 개선이 보고되었지만 협력이 기존 방식보다 성과를 향상한다는 거버넌스의 가정은 충분히 입증되지 않았다.</t>
+        </is>
+      </c>
+      <c r="J115" s="2" t="inlineStr">
+        <is>
+          <t>The governance turn in public administration suggests that collaboration with private and third-sector actors can improve services and results. However, evidence remains fragmented at the practice-field level, where such benefits are expected to materialize. To assess the evidence base, we synthesized 71 studies of voluntary cross-sectoral collaborations for work inclusion, that is, initiatives aimed at enhancing employment for vulnerable jobseekers. The literature is predominantly process oriented, emphasizing how these tension-prone collaborations can be organized and sustained. It further suggests that collaboration is often layered onto, rather than challenging, established administrative approaches. While studies report jobseeker empowerment and employment gains, the governance assumption that collaboration improves results remains weakly substantiated. Governance scholarship would benefit from stronger field-based evidence on when, how, and at what cost cross-sectoral collaboration improves results relative to what can be achieved through established approaches.</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -3488,12 +6168,36 @@
           <t>Journal of Public Administration Research and Theory</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr"/>
-      <c r="F116" s="2" t="inlineStr"/>
-      <c r="G116" s="2" t="inlineStr"/>
-      <c r="H116" s="2" t="inlineStr"/>
-      <c r="I116" s="2" t="inlineStr"/>
-      <c r="J116" s="2" t="inlineStr"/>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>실험</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>설문 실험</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>Democratic Backsliding</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>Managerial Signals</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>민주적 후퇴 상황에서 관료의 대응이 직속 상관의 정부 의사에 대한 반응성 신호에 따라 어떻게 달라지는지를 노르웨이 국가공무원 대상 무작위 설문실험과 미국 공무원 대상 개념적 반복·확장 설문으로 분석했다. 민주적 후퇴는 정부 요구에 대한 반대, 내부·외부 발언, 조직 이탈 고려를 높였으며, 상관이 정부 요구에 반응적이라고 신호할수록 우려 표명과 이탈 고려가 증가했지만 미국 표본에서는 상관에게 우려를 표명하려는 경향이 감소했다.</t>
+        </is>
+      </c>
+      <c r="J116" s="2" t="inlineStr">
+        <is>
+          <t>Abstract Political efforts to weaken democratic institutions place civil servants in a dilemma between political responsiveness and protecting democratic values. As civil servants are embedded in the political-administrative hierarchy, we argue that signals from their direct hierarchical superiors are critical to understand how civil servants address this dilemma. Using a randomized survey experiment among Norwegian national-level civil servants (N = 1,446) and ordered logistic regression models, we find that democratic backsliding increases opposition to government wishes, internal and external voice, and consideration of exit from the organization. Managerial signals moderate these effects: civil servants are more inclined to voice concerns or consider exit when managers signal responsiveness to government wishes. In a conceptual replication and extension among US federal, state and local civil servants (N = 504) using ordered logistic regression models, we likewise find a greater inclination to exit if the manager signals responsiveness to government wishes, but also that respondents are less inclined to voice concerns to the manager. Overall, our findings imply that managerial signals within the political-administrative hierarchy are shaping civil servants’ immediate reactions to democratic backsliding.</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -3514,12 +6218,36 @@
           <t>Administration &amp; Society</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr"/>
-      <c r="F117" s="2" t="inlineStr"/>
-      <c r="G117" s="2" t="inlineStr"/>
-      <c r="H117" s="2" t="inlineStr"/>
-      <c r="I117" s="2" t="inlineStr"/>
-      <c r="J117" s="2" t="inlineStr"/>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>질적연구</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>과정 분석</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>Complex Policy Change Analysis</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>Policy Coalition</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="inlineStr">
+        <is>
+          <t>이 연구는 복합 정책변화 분석(CPCA) 모형을 활용해 한국의 유치원 3법 개정 과정에서 주요 전환점을 분석하고, 해당 모형의 유용성을 평가했다. 분석 결과, 공공 및 대통령 지지를 확보한 개정 찬성 연합이 승리했으며, 의회 밖 투쟁에 의존한 반대 연합은 실패했고, 정책 중개자의 기능적 역할은 제한적이었다.</t>
+        </is>
+      </c>
+      <c r="J117" s="2" t="inlineStr">
+        <is>
+          <t>This study was conducted to assess the usefulness of the complex policy change analysis (CPCA) model and to identify key turning points in the process of revising South Korea’s three kindergarten laws (3KL). Using the CPCA model and its associated analytical methods, the analysis confirmed three main findings: the victory of the pro-revision coalition, which secured both public and presidential support; the failure of the anti-revision coalition due to its reliance on extra-parliamentary struggle; and the limited functional role played by the policy mediators. These findings offer empirical support for the explanatory power of the CPCA model in accounting for policy change.</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -3540,12 +6268,36 @@
           <t>Political Communication</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr"/>
-      <c r="F118" s="2" t="inlineStr"/>
-      <c r="G118" s="2" t="inlineStr"/>
-      <c r="H118" s="2" t="inlineStr"/>
-      <c r="I118" s="2" t="inlineStr"/>
-      <c r="J118" s="2" t="inlineStr"/>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>혼합방법론</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>내용분석·설문</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>Issue Ownership</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>Issue Yield</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="inlineStr">
+        <is>
+          <t>2025년 독일 연방선거에서 정당들이 페이스북·인스타그램·틱톡의 이용자층에 맞춰 이슈 전략을 조정하는지, 그리고 이러한 전략이 이용자 참여를 얼마나 이끌어내는지를 분석했다. 정당·후보자 게시물의 수동 정량 내용분석과 독일종단선거연구(GLES) 대규모 설문자료를 결합한 결과, 정당들은 소유 이슈와 일반 대중 의제의 현저성이 높은 이슈를 우선했지만 플랫폼별 선호와는 부분적으로만 일치했으며, 플랫폼 이용자 선호에 부합하는 게시물, 특히 지지자와 전체 이용자 모두에게 중요한 이슈를 다룬 게시물의 참여도가 가장 높았다.</t>
+        </is>
+      </c>
+      <c r="J118" s="2" t="inlineStr">
+        <is>
+          <t>How does the ever-growing relevance of social media shape political campaigning? A vibrant public and academic debate addresses the role of social media in elections and democratic processes. Yet, despite a surge in research, we still know little about the extent to which political parties adjust established issue strategies to the priorities of different social media platforms’ audiences and how effective these are in generating user engagement. Drawing on theories of issue competition – issue ownership, riding-the-wave, and issue yield – we analyze parties’ social media communication during the 2025 German federal election campaign on Facebook, Instagram, and TikTok. Combining manual quantitative content analysis of party and candidate posts with large-scale survey data from the German Longitudinal Election Study (GLES), we assess both strategic use and effectiveness of issue strategies. Our results show that parties strategically prioritize owned issues and those salient on the general public agenda, often combining both dimensions in issue yield strategies. However, these strategies only partly align with what the specific platform audiences value and reward. User engagement is highest for posts that match platform-specific issue preferences, especially when the issues are salient both to a party’s supporters on that platform and to its wider user base. The findings offer new insights into the dynamics of contemporary digital campaigning and cross-platform party competition.</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -3566,12 +6318,36 @@
           <t>American Journal of Political Science</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr"/>
-      <c r="F119" s="2" t="inlineStr"/>
-      <c r="G119" s="2" t="inlineStr"/>
-      <c r="H119" s="2" t="inlineStr"/>
-      <c r="I119" s="2" t="inlineStr"/>
-      <c r="J119" s="2" t="inlineStr"/>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>이론/개념</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>개념적 모형</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>Epistemic Inequality</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>Testimonial Injustice</t>
+        </is>
+      </c>
+      <c r="I119" s="2" t="inlineStr">
+        <is>
+          <t>정당 갈등의 사회적 동조화가 정당 불신을 개인의 인지 편향을 넘어 어떻게 인식론적 불평등으로 심화시키는지 이론적으로 분석한다. 정당과 특정 사회집단의 결합은 해당 집단 구성원에게 증언적 부정의와 신뢰성 결핍의 위험을 높이며, 특히 주변화된 집단에서 기존 편견과 결합해 피해를 키운다는 점을 보인다.</t>
+        </is>
+      </c>
+      <c r="J119" s="2" t="inlineStr">
+        <is>
+          <t>Abstract Normative and empirical scholars typically treat partisans’ distrust of their political rivals as a product of individual cognitive biases. But even if bias is inevitable, it is parties’ coalition‐building and messaging strategies that determine who bias is directed toward. This paper argues that the social sorting of party conflict exacerbates the epistemic and democratic harm of partisan distrust by generating distinctive patterns of epistemic inequality. I show that when voters associate parties with particular social groups, members of those groups suffer greater risk of testimonial injustice and related credibility deficits owing to their perceived partisanship. These dynamics are most damaging for members of marginalized groups, as party–group overlap can reinforce the prejudices they already face. Addressing these harms, I argue, requires looking beyond individual partisans to the background features of party systems that shape how elites mobilize group identities and animus in the struggle for office.</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -3592,12 +6368,36 @@
           <t>Political Behavior</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr"/>
-      <c r="F120" s="2" t="inlineStr"/>
-      <c r="G120" s="2" t="inlineStr"/>
-      <c r="H120" s="2" t="inlineStr"/>
-      <c r="I120" s="2" t="inlineStr"/>
-      <c r="J120" s="2" t="inlineStr"/>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>서베이</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>반복 전국 설문</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>Outgroup Empathy</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>Political Sophistication</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="inlineStr">
+        <is>
+          <t>2013년 이후 확산된 투표 접근 제한 법안에 대한 반대가 소수집단에 대한 공감과 어떤 관련이 있는지, 그리고 정치적 숙련도에 따라 이 관계가 달라지는지를 2018~2024년 여러 전국 설문으로 분석했다. 분석 결과, 외집단 공감이 높을수록 제한적 투표법에 반대했으며, 소수집단을 겨냥한 법안임을 인식할 가능성이 높은 정치적 숙련자에게서 이 관계가 특히 강하게 나타났다.</t>
+        </is>
+      </c>
+      <c r="J120" s="2" t="inlineStr">
+        <is>
+          <t>A suite of state-level laws that increase the burden placed on eligible voters has proliferated in the years following the 2013 Shelby County v. Holder decision. Critics have argued that these laws are thinly veiled attempts by Republicans to disenfranchise minority groups who lean toward the Democratic Party. If this is the case, attitudes about these restrictive policies should be powerfully driven by empathy for the groups negatively impacted, so long as individuals recognize the racialized intent behind the laws. This study examines the links between outgroup empathy and opposition to a variety of voting restrictions. Evidence from multiple national surveys conducted from 2018 to 2024 indicates that higher outgroup empathy indeed corresponds to greater opposition to restrictive voting laws. As predicted, however, this relationship is highly conditional on political sophistication: those most likely to be aware that these laws target minorities are also those who bring outgroup empathy to bear on their opposition to voting regulations intended to restrict access to the ballot.</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -3618,12 +6418,36 @@
           <t>The American Review of Public Administration</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr"/>
-      <c r="F121" s="2" t="inlineStr"/>
-      <c r="G121" s="2" t="inlineStr"/>
-      <c r="H121" s="2" t="inlineStr"/>
-      <c r="I121" s="2" t="inlineStr"/>
-      <c r="J121" s="2" t="inlineStr"/>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>준실험</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>행정자료 분석</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>Organizational Outgroups</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>Employee Discipline</t>
+        </is>
+      </c>
+      <c r="I121" s="2" t="inlineStr">
+        <is>
+          <t>시카고 민원처리기관의 1971~2018년 24만9천 건 이상 신고 자료를 분석해, 경찰 조직 내 흑인·히스패닉·여성 경찰관의 징계 결과가 백인 남성보다 불리한지, 그리고 민원 처분이 이를 매개하는지 검증했다. 여성 및 흑인 경찰관은 견책·정직 가능성이 더 높았지만, 그 차이는 이들에 대한 민원이 징계 조치를 정당화할 만큼 증거가 충분하다고 판단될 가능성이 더 높기 때문에 전적으로 설명되었다.</t>
+        </is>
+      </c>
+      <c r="J121" s="2" t="inlineStr">
+        <is>
+          <t>In response to demands for greater police accountability, many departments have adopted policies designed to better regulate the use of force and to make it easier to investigate and punish officers accused of wrongdoing. While not widespread, there is some evidence that these changes have increased disciplinary actions. However, it remains uncertain whether police discipline has been applied equitably across racial and gender groups within departments. Drawing on multiple bodies of scholarship, we develop the expectation that, because of their status as members of organizational outgroups, Black, Hispanic and female officers are likely to be disciplined at higher rates. Importantly, we also argue that racial, ethnic and gender differences in disciplinary outcomes are at least partially mediated by the way in which police departments treat complaints against these officers. We test these hypotheses in data from Chicago's Civilian Office of Police Accountability (COPA) from 1971 through 2018. Analyses of over 249,000 allegations indicate that female and Black officers and officers face a higher likelihood of reprimand and suspension compared to White male officers. Differences across these groups are entirely explained, however, by the greater likelihood that complaints against these officers are deemed sufficiently supported by evidence to warrant disciplinary action. We conclude by discussing the broader implications for understanding employee discipline and the potential impact of recent efforts to enhance police accountability.</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
@@ -3644,12 +6468,36 @@
           <t>International Journal of Public Administration</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr"/>
-      <c r="F122" s="2" t="inlineStr"/>
-      <c r="G122" s="2" t="inlineStr"/>
-      <c r="H122" s="2" t="inlineStr"/>
-      <c r="I122" s="2" t="inlineStr"/>
-      <c r="J122" s="2" t="inlineStr"/>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>서베이</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>전후 설문 비교</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>Organizational Resilience</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>Revenue Diversification</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t>이 연구는 코로나19 전후 인적서비스·예술문화 비영리단체 설문을 바탕으로 정부와의 네트워크 연결 및 수입구조가 조직 회복력과 어떤 관련이 있는지 분석했다. 정부와 더 많이 연결된 단체는 비영리 부문 내부에 관계가 집중된 단체보다 프로그램 제공, 계약 지속성, 자원봉사 역량에서 운영 중단을 덜 경험했으며, 수입 다변화의 효과는 예상보다 복합적이었다.</t>
+        </is>
+      </c>
+      <c r="J122" s="2" t="inlineStr">
+        <is>
+          <t>Drawing on pre- and post-COVID-19 surveys of human service and arts-and-culture nonprofits, this study examined how preexisting social connectedness and revenue structure were associated with organizational resilience. Nonprofits with more connections to government reported fewer operational disruptions, particularly in program delivery, contract continuity, and volunteer capacity, than peers whose ties were concentrated within the nonprofit sector. Financial profiles also mattered, although the relationship between revenue diversification and resilience was more complex than expected. Together, the findings identify social connectedness and revenue structure as important correlates of resilience. The study’s central contribution is to specify the conditions under which collaboration and resource diversification translate into organizational capacity during crises and to offer guidance for nonprofit leaders seeking to build more resilient organizations.</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
@@ -3670,12 +6518,36 @@
           <t>Public Management Review</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr"/>
-      <c r="F123" s="2" t="inlineStr"/>
-      <c r="G123" s="2" t="inlineStr"/>
-      <c r="H123" s="2" t="inlineStr"/>
-      <c r="I123" s="2" t="inlineStr"/>
-      <c r="J123" s="2" t="inlineStr"/>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>실험</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>설문 실험</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>Institutional Logics</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>Accountability</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t>이 연구는 제도적 논리 관점에서 위기 상황의 ‘고강도 맥락 논리’와 일상 행정의 ‘정례 거버넌스 논리’가 하향식 책무성 요구와 정책 집행에 미치는 영향을 설문 실험으로 분석했다. 800명 이상의 공공서비스 종사자를 대상으로 한 결과, 고강도 맥락에서는 책무성 강화가 순응을 점진적으로 높였지만 정례 거버넌스에서는 중간 수준의 책무성이 최적이었고 고강도 책무성은 한계효과를 보였다.</t>
+        </is>
+      </c>
+      <c r="J123" s="2" t="inlineStr">
+        <is>
+          <t>How does top-down accountability shape policy implementation? Drawing on institutional logics, this paper distinguishes two state sub-logics: ‘high-stakes context logic’ emphasizing centralized control during crises, and ‘routine governance logic’ allowing discretion during day-to-day administration. These sub-logics condition the perceived legitimacy of accountability demands, felt accountability, and behavioural responses. A survey experiment with over 800 public service respondents shows that, under high-stakes logic, intensified accountability progressively improve compliance, whereas under routine logic, moderate accountability produces optimal compliance, with high-intensity accountability yielding diminishing returns. These findings challenge binary views of accountability and reveal how within-logic variations may alter governance mechanisms.</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr"/>
@@ -3718,12 +6590,36 @@
           <t>Public Administration</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr"/>
-      <c r="F125" s="2" t="inlineStr"/>
-      <c r="G125" s="2" t="inlineStr"/>
-      <c r="H125" s="2" t="inlineStr"/>
-      <c r="I125" s="2" t="inlineStr"/>
-      <c r="J125" s="2" t="inlineStr"/>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>질적연구</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>심층 인터뷰</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>Passive Representation</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>Representative Bureaucracy</t>
+        </is>
+      </c>
+      <c r="I125" s="2" t="inlineStr">
+        <is>
+          <t>이스라엘 공공조직의 중·고위직 초정통파 여성 14명을 대상으로 한 15건의 심층 인터뷰와 포커스그룹을 통해, 남성 중심 환경에서 수동적 대표성이 어떻게 실행·협상되고 점차 제도화되는지 분석했다. 여성들은 높은 전문성, 성별분리 상황에 맞춘 창의적 네트워킹, 지원적 지도자와의 전략적 협력을 통해 정당성을 구축했으며, 멘토링과 기회 개방으로 다른 여성들의 접근과 참여를 확대했다.</t>
+        </is>
+      </c>
+      <c r="J125" s="2" t="inlineStr">
+        <is>
+          <t>ABSTRACT Studies in representative bureaucracy have focused on whether passive representation translates into active representation. We shift this analytical lens by conceptualizing passive representation not as a static demographic condition or a preliminary stage, but as a dynamic organizational process. Drawing on 15 in‐depth interviews and a focus group with 14 ultra‐Orthodox women serving in mid‐ and senior‐level public positions in Israel, we examine how passive representation is enacted, negotiated, and gradually institutionalized in male‐dominated settings. Findings show how women's underrepresentation structures their entry and advancement through informal expectations and gendered networks, and how women “negotiate presence” by building legitimacy through heightened professionalism, creative networking in the face of gender segregation, and strategic engagement with supportive leaders. Through mentoring and gate‐opening practices, our participants created ripple effects that increased access for others over time. We argue that passive representation is a relational and evolving mechanism shaped by role interpretations and organizational constraints, reshaping access and participation even without formal policy changes.</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -3744,12 +6640,36 @@
           <t>International Journal of Public Administration</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr"/>
-      <c r="F126" s="2" t="inlineStr"/>
-      <c r="G126" s="2" t="inlineStr"/>
-      <c r="H126" s="2" t="inlineStr"/>
-      <c r="I126" s="2" t="inlineStr"/>
-      <c r="J126" s="2" t="inlineStr"/>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>준실험</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>암묵연합 측정</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>Public Value Preferences</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>Dual-Attitudes Model</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="inlineStr">
+        <is>
+          <t>공무원의 공공가치 선호가 명시적·암묵적 태도의 이중 구조를 갖는지 준실험적으로 검증했다. 공무원은 비공무원보다 명시적 선호는 더 긍정적이지만 암묵적 선호는 상대적으로 부정적이어서 두 차원 간 불일치가 나타났다.</t>
+        </is>
+      </c>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
+          <t>Research on public value preferences (PVPs) among civil servants is a key area in public value studies. However, existing research on PVPs has not considered their implicit dimensions, which largely limits the understanding of the concept’s structure and measurement. Drawing on the dual-attitudes model from social psychology, this article proposes an explicit–implicit dual structure of PVPs and empirically tests this structure using a quasi-experimental design. The sample comprised a civil servant group (n = 109) and a non‑civil servant group (n = 116). Findings show that civil servants’ PVPs have a two-dimensional structure of explicit and implicit: Compared with non-civil servants, civil servants have more positive explicit PVPs but relatively negative implicit PVPs. This study systematically examines the existence, direction, and magnitude of the incongruence between civil servants’ implicit and explicit PVPs, offering a more cognitively complex theoretical framework for PVPs.</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
@@ -3770,12 +6690,36 @@
           <t>Public Management Review</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr"/>
-      <c r="F127" s="2" t="inlineStr"/>
-      <c r="G127" s="2" t="inlineStr"/>
-      <c r="H127" s="2" t="inlineStr"/>
-      <c r="I127" s="2" t="inlineStr"/>
-      <c r="J127" s="2" t="inlineStr"/>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>질적연구</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>심층 인터뷰</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>Street-Level Bureaucracy</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>Gender Inequality</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>이스라엘 사회복지사 59명을 대상으로 한 심층 인터뷰를 통해, 일선 관료가 재량으로 제공하는 비공식적 개인 자원이 성별에 따라 어떻게 다르게 나타나는지 분석했다. 여성과 남성 모두 이러한 관행을 광범위하게 활용하지만, 자원의 가시성 및 개인적·전문적 영역의 경계 설정 차이가 불평등을 재생산하고 성별 불평등을 심화시키는 것으로 나타났다.</t>
+        </is>
+      </c>
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t>This study examines whether gendered differences in discretion shape inequality among street-level bureaucrats (SLBs). Focusing on the provision of informal personal resources (IFRs) to clients, we analyzed 59 in-depth interviews with social workers in Israel. While both women and men engage in extensive informal practices, their scope and form differ. Two mechanisms drive the reproduction of inequality: invisibility versus visibility of IFRs, and boundary setting between personal and professional spheres. These findings reveal that discretion in implementation not only is gendered but also reproduces conventional hierarchies, intensifying gender inequality at the street level of public administration.</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -3796,12 +6740,36 @@
           <t>Public Management Review</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr"/>
-      <c r="F128" s="2" t="inlineStr"/>
-      <c r="G128" s="2" t="inlineStr"/>
-      <c r="H128" s="2" t="inlineStr"/>
-      <c r="I128" s="2" t="inlineStr"/>
-      <c r="J128" s="2" t="inlineStr"/>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>질적연구</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>심층 인터뷰</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>Resource Dependence Theory</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>knowledge integration</t>
+        </is>
+      </c>
+      <c r="I128" s="2" t="inlineStr">
+        <is>
+          <t>네덜란드 지방자치단체가 에너지 전환 의무를 이행할 때 외부 인력 의존과 내부 역량 개발이 어떻게 상호작용하는지를 6개 지방자치단체 대상 15건의 인터뷰로 분석했다. 인력 부족과 한시적 보조금이 외부 인력 채용을 촉진하고, 짧은 계약과 제한적인 지식 이전이 의존성을 높였지만, 지식 통합·거버넌스 방식·관계적 역학에 따라 의존의 경로는 달라졌으며 의존성을 고정된 결과가 아닌 과정으로 개념화했다.</t>
+        </is>
+      </c>
+      <c r="J128" s="2" t="inlineStr">
+        <is>
+          <t>Municipalities implementing energy transition mandates rely on contingent workers to fill capacity and expertise gaps, raising concerns about dependency and knowledge loss. Drawing on Resource Dependence Theory and client–consultant literature, this study develops a framework capturing the feedback loop between external reliance and internal capacity development. Fifteen interviews across six Dutch municipalities show that labour shortages and temporary subsidies drive contingent hiring, while short contracts and limited knowledge transfer heighten dependency. Municipalities facing similar constraints diverge through knowledge integration, governance arrangements, and relational dynamics. It advances public administration scholarship by conceptualising dependency as a process rather than structural outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
@@ -3822,12 +6790,36 @@
           <t>The American Review of Public Administration</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr"/>
-      <c r="F129" s="2" t="inlineStr"/>
-      <c r="G129" s="2" t="inlineStr"/>
-      <c r="H129" s="2" t="inlineStr"/>
-      <c r="I129" s="2" t="inlineStr"/>
-      <c r="J129" s="2" t="inlineStr"/>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>서베이</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>횡단면 설문</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>Cultural Theory</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>Administrative Burden</t>
+        </is>
+      </c>
+      <c r="I129" s="2" t="inlineStr">
+        <is>
+          <t>미국 응답자 설문자료를 활용해 행정 부담 수용도 측정의 타당성을 양극화 수준이 다른 정책들에서 확인하고, 문화이론의 세계관 변수와 행정 부담 관용도의 관계를 분석했다. 평등주의자와 개인주의자는 부담에 덜 관용적이고 위계주의자는 더 수용적일 것으로 가설화했으며, 그 효과는 부담의 성격과 각 세계관이 인식하는 위협에 따라 달라질 수 있음을 검토했다.</t>
+        </is>
+      </c>
+      <c r="J129" s="2" t="inlineStr">
+        <is>
+          <t>Administrative burdens embedded within many public policies are often politically contentious, such that core values and belief systems can drive either support or opposition. In this paper, we use survey data from US respondents to replicate and extend previous research on the public acceptance of administrative burdens in general. First, we confirm the measure's validity by examining its effects on beliefs across policies that range from highly polarized to less politically contentious. Second, we test the relationship between tolerance of administrative burden and cultural theory (CT) variables that tap into worldview orientations related to hierarchy, egalitarianism, individualism, and fatalism, which previous research has found predictive of policy preferences across a wide range of domains, even after accounting for political ideology and partisanship. We hypothesize that egalitarians and individualists will generally be less tolerant of burdens, while hierarchs will be more accepting of burdensome requirements. However, this effect varies depending on the nature of the burdens and how they relate to perceived threats for each worldview.</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -3848,12 +6840,36 @@
           <t>Public Administration</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr"/>
-      <c r="F130" s="2" t="inlineStr"/>
-      <c r="G130" s="2" t="inlineStr"/>
-      <c r="H130" s="2" t="inlineStr"/>
-      <c r="I130" s="2" t="inlineStr"/>
-      <c r="J130" s="2" t="inlineStr"/>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>질적연구</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>반구조화 인터뷰</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>Relational Dynamics</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>Systems Approach</t>
+        </is>
+      </c>
+      <c r="I130" s="2" t="inlineStr">
+        <is>
+          <t>칠레의 장기 재직 우수 고위 공공관리자 7명을 대상으로 27건의 반구조화 인터뷰를 분석해, 효과적인 최고위 관리가 개인 속성의 단순한 발현이 아니라 기관 내부 및 외부 사회정치적 환경과의 관계적 상호작용 속에서 형성되는 과정을 규명했다. 특히 전략 수립, 동기 부여, 기술적 전문성은 이러한 상호작용을 통해 주로 출현하며, 이에 맞는 인사정책과 거버넌스 환경이 필요하다고 제시한다.</t>
+        </is>
+      </c>
+      <c r="J130" s="2" t="inlineStr">
+        <is>
+          <t>ABSTRACT The complex nature of top public managerial work is widely acknowledged in theory but rarely examined empirically. Existing research has mostly analyzed bivariate relationships among core components of top managerial work in government, including managers' attributes, practices, outcomes, and contexts. Drawing on a systems‐based framework, we investigate how effective top managerial work unfolds as a complex relational practice. We analyze seven cases of long‐serving, distinguished Chilean senior executives through a comprehensive and process‐oriented lens, based on 27 semi‐structured interviews with the managers and members of their personal and professional networks. Our findings indicate how the relational dynamics in which senior public executives engage shape their managerial attributes and practices. Specifically, strategizing, motivation building, and technical expertise are best understood as emerging primarily through interactions within agencies and with external sociopolitical environments. These results qualify perspectives that explain senior public management effectiveness by overemphasizing executives' individual attributes and views, and underscore the need for personnel policies and governance environments that equip managers with the capacities called for by a systems approach to top public management.</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
@@ -3874,12 +6890,36 @@
           <t>Public Administration</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr"/>
-      <c r="F131" s="2" t="inlineStr"/>
-      <c r="G131" s="2" t="inlineStr"/>
-      <c r="H131" s="2" t="inlineStr"/>
-      <c r="I131" s="2" t="inlineStr"/>
-      <c r="J131" s="2" t="inlineStr"/>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>준실험</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>시차 도입 사건연구</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>Gender Budgeting</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>Women’s Empowerment</t>
+        </is>
+      </c>
+      <c r="I131" s="2" t="inlineStr">
+        <is>
+          <t>성인지 예산이 여성의 웰빙·평등·역량 강화에 실질적 개선을 가져왔는지를 검토하기 위해 2000~2023년 47개국 자료에 시차를 둔 도입을 활용한 사건연구를 실시했다. 성인지 예산은 단기·장기적으로 모성 사망률과 청소년 출산율을 유의하게 낮추고 여성의 정치적 역량 강화를 개선한 것으로 나타났다.</t>
+        </is>
+      </c>
+      <c r="J131" s="2" t="inlineStr">
+        <is>
+          <t>ABSTRACT The United Nations' fifth Sustainable Development Goal calls for gender equality and empowerment. Gender budgeting (GB) has been proposed as a potential mechanism to reduce gender disparities. This is a novel approach to budgeting that considers the impact of public spending on women and other underrepresented groups. Despite its growing popularity, spreading to over 80 countries since its launch in the 1980s, the effectiveness of GB remains less understood. This study tests whether GB has led to tangible improvements in women's well‐being, equality, and empowerment. We use an event study research design with staggered adoption to analyze data across 47 countries from 2000 to 2023. Our analyses of average and heterogeneous treatment effects reveal short‐ and long‐term impacts; notably, we find significant reductions in maternal mortality ratios and adolescent birth rates, as well as improvements in women's political empowerment.</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -3900,12 +6940,36 @@
           <t>Perspectives on Public Management and Governance</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr"/>
-      <c r="F132" s="2" t="inlineStr"/>
-      <c r="G132" s="2" t="inlineStr"/>
-      <c r="H132" s="2" t="inlineStr"/>
-      <c r="I132" s="2" t="inlineStr"/>
-      <c r="J132" s="2" t="inlineStr"/>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>이론/개념</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>개념적 모형</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>Circuits of Power</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>Power Circuit Alignment</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="inlineStr">
+        <is>
+          <t>공공관리 개혁에서 서로 분리되어 연구된 권력의 양상을 어떻게 통합적으로 설명할 수 있는지를 탐구한다. Clegg의 권력 회로 이론에 기반한 다층적 개념 모형을 제시하며, 개혁 성과와 경로는 일화적·성향적·촉진적 권력 회로의 완전한 정렬, 부분적 정렬 또는 불일치에 따라 달라진다고 주장한다.</t>
+        </is>
+      </c>
+      <c r="J132" s="2" t="inlineStr">
+        <is>
+          <t>Abstract Public management research has long recognized that power shapes reform outcomes. However, it has often examined different manifestations of power through separate research streams, including street-level discretion, professional power, and network governance, without integrating them into a unified theoretical framework. Drawing on Clegg’s circuits of power framework, this article develops an integrative approach that examines how episodic, dispositional, and facilitative power interact during public management reform. We argue that reform outcomes depend largely on whether these circuits exhibit full alignment, partial alignment, or misalignment. We develop this argument into a Power Circuit Alignment framework, which connects micro-level practices, meso-level structures, and macro-level systems and identifies circuit alignment as the key process explaining divergent reform trajectories. In doing so, the framework advances public management research by integrating previously separate power literatures within a single multi-level account. It also specifies how the circuits operate in public management: democratic accountability shapes the distribution of episodic authority, professional norms shape dispositional support and resistance, and interorganizational and intergovernmental complexity shapes facilitative capacity.</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
@@ -3926,12 +6990,36 @@
           <t>Public Performance &amp; Management Review</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr"/>
-      <c r="F133" s="2" t="inlineStr"/>
-      <c r="G133" s="2" t="inlineStr"/>
-      <c r="H133" s="2" t="inlineStr"/>
-      <c r="I133" s="2" t="inlineStr"/>
-      <c r="J133" s="2" t="inlineStr"/>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>준실험</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>고정효과 패널</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>Gender-Responsive Budgeting</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>Title IX</t>
+        </is>
+      </c>
+      <c r="I133" s="2" t="inlineStr">
+        <is>
+          <t>이 연구는 성인지 예산(GRB) 관점에서 Title IX 적용 연방 지원 고등교육기관의 운동부 장학금 배분이 성별 참여 및 등록 구성과 어떻게 연관되는지, 2010~2022년 NCAA 디비전 I EADA 패널자료로 분석했다. 고정효과 회귀 결과, 총 운동부 학자금 지원은 특히 공립기관에서 남학생 선수 참여 규모와 양의 관계를 보였으며, 참여·등록 구성 조정 후에는 공·사립기관 모두 여성 선수 지원이 Title IX 비례성 기준과 대체로 부합했고 사립기관의 여성 1인당 조정 효과가 더 강했다.</t>
+        </is>
+      </c>
+      <c r="J133" s="2" t="inlineStr">
+        <is>
+          <t>Literature in public administration and public budgeting examines how budgetary processes affect the allocation of public resources across different populations. Using a gender-responsive budgeting (GRB) framework, this study examines patterns of athletic scholarship funding in the context of Title IX mandates in federally funded higher education institutions. Drawing on Equity in Athletics Disclosure Act (EADA) data from 2010 to 2022, the analysis focuses on scholarship allocations across National Collegiate Athletic Association (NCAA) Division I institutions. Distinct from much of the existing GRB literature, the study incorporates legal guidelines, panel data methods, and explicit distinctions by biological sex. Fixed-effects regressions indicate that total athletic student aid is positively associated with the scale of male student athletic participation, particularly in public institutions. Participation-adjusted analyses further show that both public and private institutions allocate athletic student aid to female student-athletes at levels broadly consistent with Title IX’s proportionality standards after accounting for enrollment composition. Specifically, private institutions exhibit stronger per capita adjustments favoring female student-athletes, pointing to meaningful heterogeneity in how funding allocations are implemented across institutional contexts. Overall, the findings demonstrate how a GRB-informed approach aids in interpreting aggregate funding patterns and highlight variation in institutional responses to mandates and policies pertinent to gender issues in collegiate athletics.</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
@@ -3952,12 +7040,36 @@
           <t>The American Review of Public Administration</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr"/>
-      <c r="F134" s="2" t="inlineStr"/>
-      <c r="G134" s="2" t="inlineStr"/>
-      <c r="H134" s="2" t="inlineStr"/>
-      <c r="I134" s="2" t="inlineStr"/>
-      <c r="J134" s="2" t="inlineStr"/>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>서베이</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>다층자료 분석</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>Street-Level Bureaucracy</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>Job Demands–Resources</t>
+        </is>
+      </c>
+      <c r="I134" s="2" t="inlineStr">
+        <is>
+          <t>중국 비영리기관 사회복지사를 대상으로 다층 자료를 분석해 조직 투명성과 역할 갈등이 이직 의도에 미치는 영향을 검토했다. 조직 투명성은 이직 의도를 낮추고 역할 갈등은 높였으며, 가치 적합성이 두 관계를 매개하고 직무 자율성이 투명성의 효과를 강화하고 역할 갈등의 부정적 영향을 완화했다.</t>
+        </is>
+      </c>
+      <c r="J134" s="2" t="inlineStr">
+        <is>
+          <t>Street-level bureaucrats often lack workplace clarity, which contributes to higher turnover. Drawing on street-level bureaucracy theory and the Job Demands–Resources model, this study examines how organizational transparency and role conflict, two dimensions of workplace clarity, shape turnover intentions among social workers in Chinese nonprofit organizations. Using multilevel data from the China Social Work Longitudinal Study, we find that organizational transparency reduces and role conflict increases turnover intentions. Value fit mediates both relationships, and job autonomy moderates them by enhancing the benefits of organizational transparency and buffering the harms of role conflict. Findings validate the extension of street-level bureaucracy theory to the nonprofit context and offer actionable insights for improving workforce stability in a complex governance environment.</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
@@ -3978,12 +7090,36 @@
           <t>Public Management Review</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr"/>
-      <c r="F135" s="2" t="inlineStr"/>
-      <c r="G135" s="2" t="inlineStr"/>
-      <c r="H135" s="2" t="inlineStr"/>
-      <c r="I135" s="2" t="inlineStr"/>
-      <c r="J135" s="2" t="inlineStr"/>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>질적연구</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>체계적 국가비교</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>Social Procurement</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t>Indigenous Economic Sovereignty</t>
+        </is>
+      </c>
+      <c r="I135" s="2" t="inlineStr">
+        <is>
+          <t>캐나다·호주·아오테아로아 뉴질랜드의 정체성 기반 원주민 조달 정책 구조를 McCrudden의 사회적 조달 프레임워크로 체계적으로 비교해, 계약 가치가 대도시와 일부 산업에 집중되고 원격·초기 단계 공동체 기업이 주변화되며 데이터 공백과 집계 보고가 이러한 불평등과 전면기업(fronting)을 가린다는 점을 밝혔다. 지역별 기준과 독립 감사 등 구조 개혁이 실질적 원주민 경제 주권에 맞게 조달을 조정해야 한다고 제안한다.</t>
+        </is>
+      </c>
+      <c r="J135" s="2" t="inlineStr">
+        <is>
+          <t>Indigenous procurement is widely promoted as an instrument of economic reconciliation, yet headline gains often mask limited transformational impact. Applying McCrudden’s social procurement framework, we conduct a systematic cross-national comparison of identity-specific procurement architectures across Canada, Australia, and Aotearoa New Zealand. We show that contract values cluster heavily within major metropolitan hubs and narrow industry sectors, leaving remote and early-stage community enterprises marginalized. Furthermore, persistent cross-national data gaps and aggregated reporting conceal these structural inequities while enabling policy distortions like fronting. We recommend structural reforms including regional benchmarks and independent auditing to align procurement with genuine Indigenous economic sovereignty.</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -4004,12 +7140,36 @@
           <t>Public Administration Review</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr"/>
-      <c r="F136" s="2" t="inlineStr"/>
-      <c r="G136" s="2" t="inlineStr"/>
-      <c r="H136" s="2" t="inlineStr"/>
-      <c r="I136" s="2" t="inlineStr"/>
-      <c r="J136" s="2" t="inlineStr"/>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>준실험</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>동적 패널 GMM</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>Women’s Political Empowerment</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>Tax Mobilization</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="inlineStr">
+        <is>
+          <t>아프리카 41개국의 2000~2022년 패널자료에 시스템 일반화적률법(GMM)을 적용해 여성의 정치적 권한이 조세수입 동원에 미치는 영향을 분석한 결과, 여성의 정치적 권한 확대는 조세 동원을 유의하게 높였지만 일정 전환점을 넘으면 그 효과가 약화되었다. 이 관계는 부패 통제, 비공식경제 규모, 여성 노동력 참여를 통해 작동했으며, 정책적으로는 여성 대표성의 양보다 질과 성별 할당제의 강화가 중요하다고 제시한다.</t>
+        </is>
+      </c>
+      <c r="J136" s="2" t="inlineStr">
+        <is>
+          <t>ABSTRACT This article examines the effects of women's political empowerment (WPE) on tax revenue mobilization using a panel sample of 41 African countries over the 2000–2022 period. Utilizing the system Generalized Method of Moments, the empirical results demonstrate that WPE significantly enhances tax revenue mobilization in Africa. This finding remains robust to alternative measures of both WPE and tax revenue. Furthermore, beyond a specific turning point, increased WPE tends to diminish tax revenue mobilization. Finally, the study highlights that WPE operates through several transmission channels, including corruption control, the size of the informal economy, and female labor force participation. In terms of public policy, strengthening gender quotas within the African political sphere is crucial to enhancing tax mobilization. Nonetheless, given the threshold effects identified in this relationship, policymakers must prioritize the quality of women's political representation rather than focusing solely on increasing their numerical representation within political decision‐making circles.</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
@@ -4030,12 +7190,36 @@
           <t>Public Administration Review</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr"/>
-      <c r="F137" s="2" t="inlineStr"/>
-      <c r="G137" s="2" t="inlineStr"/>
-      <c r="H137" s="2" t="inlineStr"/>
-      <c r="I137" s="2" t="inlineStr"/>
-      <c r="J137" s="2" t="inlineStr"/>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>질적연구</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>연방 인력자료 분석</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>Organizational Knowledge</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>State Capacity</t>
+        </is>
+      </c>
+      <c r="I137" s="2" t="inlineStr">
+        <is>
+          <t>본 연구는 2025년 연방공무원 이직이 어디에서 발생했으며 조직의 지식과 역량에 어떤 영향을 미쳤는지를 파악하기 위해 2015년 1월부터 2025년 12월까지의 연방 인력 자료를 분석했다. 분석 결과, 자발적·비자발적 퇴직을 통해 상당한 전문성과 경험이 유실된 것으로 나타났다.</t>
+        </is>
+      </c>
+      <c r="J137" s="2" t="inlineStr">
+        <is>
+          <t>ABSTRACT The federal service experienced unprecedented turnover in the first year of the second Trump administration. Early reports have documented the substantial losses of personnel and the politicization and antagonism underlying those changes. This research breaks down separations over the past year, with a focus on the Deferred Resignation Program (DRP), to understand where turnover occurred and how it affected organizational knowledge and capacity. The analysis examines federal workforce data from January 2015 to December 2025 and reveals that the federal service lost substantial expertise and experience through both voluntary and involuntary means of separation. These results shed light on the fallout from 2025 executive actions, clarify the implications for government capacity, and point out prospective pathways for mitigating damages to the federal service moving forward.</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
@@ -4056,12 +7240,36 @@
           <t>Political Communication</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr"/>
-      <c r="F138" s="2" t="inlineStr"/>
-      <c r="G138" s="2" t="inlineStr"/>
-      <c r="H138" s="2" t="inlineStr"/>
-      <c r="I138" s="2" t="inlineStr"/>
-      <c r="J138" s="2" t="inlineStr"/>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>실험</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>선택 실험</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>Moral-Emotional Content</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>Content Selection</t>
+        </is>
+      </c>
+      <c r="I138" s="2" t="inlineStr">
+        <is>
+          <t>도덕적·감정적 정치 콘텐츠를 사람들이 정보환경에서 적극적으로 선택하는지, 미국에서 2022~2023년에 사전등록된 세 연구로 검증했다. 참가자들은 중립적 콘텐츠나 감정적 콘텐츠보다 도덕적·감정적 콘텐츠를 더 선택하지 않았으며, 이는 해당 콘텐츠의 확산과 실제 선호가 다를 수 있음을 시사한다.</t>
+        </is>
+      </c>
+      <c r="J138" s="2" t="inlineStr">
+        <is>
+          <t>Recent work has shown that moral-emotional content spreads rapidly on social media platforms such as X (Twitter). These patterns have led to concerns that social media facilitates the spread of moral outrage – potentially exacerbating political conflict and animosity. While most past work has focused on the supply side of this phenomenon, i.e. the transmission of morally charged political content, we consider the demand side: do people actually want to see this type of content in their information environment? In this paper, we first theoretically contextualize the motivations to engage with or avoid moral-emotional content. Then, through three pre-registered studies conducted in the U.S. in 2022 and 2023, we test whether people actively choose information that includes moral-emotional elements. Contrary to our initial expectations, we find that participants do not actively select moral-emotional content compared to neutral or emotional content. Despite previous findings on transmission, our results suggest that people may not want to see this type of content in their information environment. By focusing on selection rather than transmission, the findings presented in this paper add another nuance to an ongoing debate on the prevalence and consequences of online political outrage.</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
@@ -4082,12 +7290,36 @@
           <t>Political Psychology</t>
         </is>
       </c>
-      <c r="E139" s="2" t="inlineStr"/>
-      <c r="F139" s="2" t="inlineStr"/>
-      <c r="G139" s="2" t="inlineStr"/>
-      <c r="H139" s="2" t="inlineStr"/>
-      <c r="I139" s="2" t="inlineStr"/>
-      <c r="J139" s="2" t="inlineStr"/>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>혼합방법론</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>실험·상관·질적</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>Interdependence</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>Expectancy Violation</t>
+        </is>
+      </c>
+      <c r="I139" s="2" t="inlineStr">
+        <is>
+          <t>부정적 상호의존으로 인식되는 갈등에서 외집단의 무관심이 외집단의 분노나 증오보다 부정적 정서를 줄이고 협력 기대를 높여 협력 지지를 촉진하는지 네 차례 연구(N=2,521)로 검토했다. 연구 결과, 외집단 무관심은 부정적 상호의존 맥락에서 긍정적 기대 위반으로 작용해 협력 기대와 협력 지지를 높였으며, 이러한 효과는 주로 부정적 정서 감소와 협력 기대 증가를 통해 나타났다.</t>
+        </is>
+      </c>
+      <c r="J139" s="2" t="inlineStr">
+        <is>
+          <t>Abstract We examined how responses to outgroup indifference in conflict are shaped by the perceived nature of interdependence, which changes expectations of outgroup emotions toward the ingroup. Unlike conflicts perceived as positively interdependent, we hypothesized that in conflicts perceived as negatively interdependent, outgroup indifference would constitute a positive expectancy violation, thereby inviting favorable responses. Moreover, we examined affective and inferential processes as mediators across four studies ( N = 2521). In Study 1, outgroup indifference (vs. anger and hatred but not hope) reduced negative emotions (but did not affect expected collaboration), subsequently increasing support for cooperation. Study 2 added qualitative measures and showed that outgroup indifference (vs. anger) increased support for cooperation through decreased negative emotions and increased expected collaboration. Study 3 provided correlational evidence that perceptions of interdependence predict participants' expectations of outgroup emotions. Lastly, in Study 4, outgroup indifference increased expected collaboration and emotions when interdependence was perceived as negative.</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
@@ -4108,12 +7340,36 @@
           <t>Public Administration Review</t>
         </is>
       </c>
-      <c r="E140" s="2" t="inlineStr"/>
-      <c r="F140" s="2" t="inlineStr"/>
-      <c r="G140" s="2" t="inlineStr"/>
-      <c r="H140" s="2" t="inlineStr"/>
-      <c r="I140" s="2" t="inlineStr"/>
-      <c r="J140" s="2" t="inlineStr"/>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>이론/개념</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>사례 기반 이론화</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>Advisory Capture</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>Legitimacy Regime</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="inlineStr">
+        <is>
+          <t>이 글은 비공식 행위자가 공식 권한 없이 어떻게 관료제를 신속히 해체할 수 있는지를 DOGE 구상 분석을 통해 이론화한다. 성과 기반 정당성이 절차적 정당성을 대체하는 정당성 체제 전환 속에서 자문 포획과 제한된 강제가 제도적 안전장치를 우회·재편하며, 그 과정이 정치적 취약성에 따른 기관 표적화와 공식 규칙화를 수반하고 사법심사는 지속적 경합으로 작동한다고 주장한다.</t>
+        </is>
+      </c>
+      <c r="J140" s="2" t="inlineStr">
+        <is>
+          <t>ABSTRACT How do informal actors achieve rapid bureaucratic dismantlement without formal authority? Analyzing the Department of Government Efficiency (DOGE) initiative, this article argues that when performance‐based legitimacy displaces procedural legitimacy as the dominant evaluative framework, informal actors can bypass established safeguards and reshape government institutions. Three concepts capture this process: advisory capture , legitimacy regime transition , and constrained coercion . The analysis reveals that dismantlement targets agencies based on political vulnerability rather than functional logic, that informal authority becomes institutionalized through formal rulemaking such as the Schedule Policy/Career rule, and that judicial review operates as ongoing contestation rather than definitive constraint. Protecting democratic governance requires defending not only formal rules but the legitimacy regimes within which those rules derive meaning.</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
@@ -4134,12 +7390,36 @@
           <t>Political Communication</t>
         </is>
       </c>
-      <c r="E141" s="2" t="inlineStr"/>
-      <c r="F141" s="2" t="inlineStr"/>
-      <c r="G141" s="2" t="inlineStr"/>
-      <c r="H141" s="2" t="inlineStr"/>
-      <c r="I141" s="2" t="inlineStr"/>
-      <c r="J141" s="2" t="inlineStr"/>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>실험</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>패널 실험</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>Fact-checking</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>Accuracy Reminders</t>
+        </is>
+      </c>
+      <c r="I141" s="2" t="inlineStr">
+        <is>
+          <t>사실확인 효과가 빠르게 약화되는 문제를 해결하기 위해, 사실확인 후 동일한 주장에 대한 재평가를 유도하는 저비용 ‘정확성 알림’이 효과의 지속성을 높이는지 대규모 사전등록 패널 종단실험(N=7,188)으로 검증했다. 정확성 알림은 주제와 당파적 정체성에 관계없이 최대 4주간 신념 교정 효과를 지속시켰으며, 알림이 없을 때보다 효과의 지속성이 두 배 이상 높았다.</t>
+        </is>
+      </c>
+      <c r="J141" s="2" t="inlineStr">
+        <is>
+          <t>Prior evidence suggests that fact-checking can update beliefs regarding factually incorrect information in the short term but its effects often decay rapidly. Such decay raises normative concerns about its sustainability and real-world impact. Here, we examine whether a cognitively efficient, low-cost intervention – called an “accuracy reminder” – can enhance the durability of fact-checking effects. In a large-scale pre-registered panel longitudinal experiment (N = 7,188), participants were randomly assigned to receive fact-checks and, under some conditions, follow-up prompts to reevaluate the same claim at interval-optimized time points. Across topical domains and partisan identities, reminder conditions produced durable belief correction effects lasting up to four weeks, more than doubling the persistence observed without reminders. Effects were robust across reminder frequency and timing, as well as against individual differences, suggesting implementation flexibility and theoretical generalizability. These findings identify retrieval-based reinforcement as a scalable means of sustaining factual belief correction and reinforcing shared factual baselines in spite of cognitive decay and partisan resistance.</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
@@ -4160,12 +7440,36 @@
           <t>Political Psychology</t>
         </is>
       </c>
-      <c r="E142" s="2" t="inlineStr"/>
-      <c r="F142" s="2" t="inlineStr"/>
-      <c r="G142" s="2" t="inlineStr"/>
-      <c r="H142" s="2" t="inlineStr"/>
-      <c r="I142" s="2" t="inlineStr"/>
-      <c r="J142" s="2" t="inlineStr"/>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>준실험</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>행정자료 분석</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>Electoral Participation</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>Family Background</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="inlineStr">
+        <is>
+          <t>이 연구는 지적장애가 있는 청년의 선거 참여를 결정하는 요인을 스웨덴 지적장애 학생 대상 행정자료와 부모 자료(5개 코호트, N=8,438)로 분석했다. 장애의 중증도와 부모의 투표 경험이 가장 강한 예측요인이었으며, 부모의 교육·소득·직업과 같은 가족의 사회경제적 지위는 상대적으로 덜 중요했다.</t>
+        </is>
+      </c>
+      <c r="J142" s="2" t="inlineStr">
+        <is>
+          <t>Abstract Systematic differences of electoral participation between various social groups indicate crucial constraints of comprehensive democratic inclusion. Yet, there is a dearth of research on electoral participation among individuals with intellectual disability (ID), whose participation rates are considerably lower than among non‐ID citizens. This study examines determinants of electoral participation among individuals with ID based on administrative records covering five cohorts of individuals from the Swedish upper‐secondary school for pupils with ID ( N = 8438), and their parents. Our main results indicate that the severity of the disability and parents who have voted are the strongest predictors of voting among individuals with ID. The latter suggests that family background is vital. However, the socioeconomic status of the families, such as parents' level of education, income, and occupation, are less pivotal factors.</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
@@ -4186,12 +7490,36 @@
           <t>Governance</t>
         </is>
       </c>
-      <c r="E143" s="2" t="inlineStr"/>
-      <c r="F143" s="2" t="inlineStr"/>
-      <c r="G143" s="2" t="inlineStr"/>
-      <c r="H143" s="2" t="inlineStr"/>
-      <c r="I143" s="2" t="inlineStr"/>
-      <c r="J143" s="2" t="inlineStr"/>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>질적연구</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>문서 비교</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>Public Value</t>
+        </is>
+      </c>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>Organizational Viability</t>
+        </is>
+      </c>
+      <c r="I143" s="2" t="inlineStr">
+        <is>
+          <t>이 글은 정부 내부 컨설팅 조직이 추구하는 공공가치와 조직 생존가능성에 따라 어떻게 설계되어야 하는지를 묻고, 5개국 8개 조직의 문서 비교를 통해 세 가지 구성(전략적 전환, 확장 가능한 해결책, 전문성 플랫폼)을 제시한다. 분석 결과, 업무·인력·지식·권한·고객관계·재원·평가가 해당 구성과 발전 단계에 맞게 정렬되고 후속 업무의 조건을 재생산할 때 조직이 지속가능하며, 내부화는 조달 결정을 되돌리는 것이 아니라 조직을 구축하는 과정으로 나타났다.</t>
+        </is>
+      </c>
+      <c r="J143" s="2" t="inlineStr">
+        <is>
+          <t>ABSTRACT Governments have created in‐house consulting organizations to reduce dependence on external firms and retain public capability and control. Yet organizations grouped under this label pursue different forms of public value that require different designs. This article distinguishes three reasons for a dedicated unit: retaining control over consequential work, capturing returns from problems that recur across government, and mobilizing expertise dispersed across public and adjacent institutions. It develops three corresponding configurations—Strategic Transformation, Scalable Solutions, and Expertise Platform—and shows how choices about work, staffing, knowledge, authority, client relationships, financing, and evaluation must fit together. Documentary comparison of eight units in five countries grounds the analysis. The cases show that viability depends on whether work renews the conditions needed for subsequent work and that evaluation must reflect configuration and stage. Internalization is therefore organization‐building, not the reversal of a procurement decision: a unit creates public value only when work reproduces the conditions on which that value depends.</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
@@ -4212,12 +7540,36 @@
           <t>The American Review of Public Administration</t>
         </is>
       </c>
-      <c r="E144" s="2" t="inlineStr"/>
-      <c r="F144" s="2" t="inlineStr"/>
-      <c r="G144" s="2" t="inlineStr"/>
-      <c r="H144" s="2" t="inlineStr"/>
-      <c r="I144" s="2" t="inlineStr"/>
-      <c r="J144" s="2" t="inlineStr"/>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>질적연구</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>내용 분석</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>Public Service Values</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>Employee Recognition</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="inlineStr">
+        <is>
+          <t>이 연구는 2025년 미국 주지사들의 공공서비스 인식 주간 포고문에서 공공서비스 가치가 어떻게 강조되는지, 그리고 주지사의 정당과 포고문 발행 간 관계가 있는지를 분석했다. 포고문에는 헌신·청렴·전문성이 공통적으로 나타났고 정당별 강조 가치에는 일부 차이가 있었지만, 주지사 정당과 발행 여부 사이에는 통계적으로 식별 가능한 관계가 없었으며 약 3분의 1의 주지사만 포고문을 발행했다.</t>
+        </is>
+      </c>
+      <c r="J144" s="2" t="inlineStr">
+        <is>
+          <t>Since 1985, Public Service Recognition Week acknowledges the role of government employees in American democracy. Building upon the study of public service values, this research investigates gubernatorial proclamations issued in 2025, treating that years as a crucial case for the study of government employee recognition. Despite instability in the U.S. federal government, state-level proclamations illustrate a consistent emphasis on common public service values, including commitment, integrity, and professionalism. The analysis of proclamation content shows some variation in the values emphasized by the two major political parties, but no statistically discernable relationship between gubernatorial party and proclamation issuance. Still, only about one third of U.S. governors issued proclamations for Public Service Recognition Week in 2025, pointing to the need for ongoing scrutiny of employee recognition practices at the state and national level. This research closes by comparing state-level action to presidential proclamations from 1987 to 2024 and discusses implications for the application of public service value theory to the study of state government employment and employee recognition.</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
@@ -4238,12 +7590,36 @@
           <t>Public Administration</t>
         </is>
       </c>
-      <c r="E145" s="2" t="inlineStr"/>
-      <c r="F145" s="2" t="inlineStr"/>
-      <c r="G145" s="2" t="inlineStr"/>
-      <c r="H145" s="2" t="inlineStr"/>
-      <c r="I145" s="2" t="inlineStr"/>
-      <c r="J145" s="2" t="inlineStr"/>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>실험</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>통제 실험</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>Administrative Burden</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>Affective Events Theory</t>
+        </is>
+      </c>
+      <c r="I145" s="2" t="inlineStr">
+        <is>
+          <t>디지털 복지 신청에서 행정적 만남 중 부정적 감정의 심리적 비용이 어떻게 나타나는지, 그리고 사전 입력 양식에 따른 절차 단순화가 이를 완화하는지 통제 실험과 얼굴 표정 코딩으로 분석했다. 부정적 감정, 특히 좌절은 신청자의 오류를 늘렸고 사전 입력은 감정적 각성을 줄이지 않았지만 절차 만족도를 높였으며, 저학력자와 외국 국적자에게 효과가 더 컸다.</t>
+        </is>
+      </c>
+      <c r="J145" s="2" t="inlineStr">
+        <is>
+          <t>ABSTRACT Recent scholarship on administrative burden has increasingly focused on psychological costs, design interventions, and digital burdens. This study combines these interests and examines the psychological costs of negative emotions during administrative encounters at varying levels of digital maturity. Building on affective events theory and employing facial coding in a controlled experiment, the study demonstrates that negative emotions rise during bureaucratic encounters, with frustration resulting in more errors made by applicants. Simplifying the procedure through pre‐filled forms does not reduce negative emotional arousal; however, it enhances satisfaction with the procedure. Vulnerable citizens, as indicated by low education and foreign citizenship, benefit more from this informational integration than other groups, suggesting that procedural redesign can enhance the inclusiveness of public service delivery. Overall, the research advances both scholarly and practical understanding of the emotional dimension of administrative burdens from a process‐oriented perspective, highlighting the persistent challenge of reducing emotional costs to enhance citizen experiences.</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
@@ -4264,12 +7640,36 @@
           <t>Public Administration Review</t>
         </is>
       </c>
-      <c r="E146" s="2" t="inlineStr"/>
-      <c r="F146" s="2" t="inlineStr"/>
-      <c r="G146" s="2" t="inlineStr"/>
-      <c r="H146" s="2" t="inlineStr"/>
-      <c r="I146" s="2" t="inlineStr"/>
-      <c r="J146" s="2" t="inlineStr"/>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>질적연구</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>심층 인터뷰</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>Public Value Governance</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>Public Service Delivery</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="inlineStr">
+        <is>
+          <t>이 연구는 공공도서관을 사례로, 모두를 위한 서비스 제공·전문성·윤리적 책임·지역사회 요구에 대한 성찰적 의사결정이 확장적 공공서비스 제공을 어떻게 구성하는지 탐색한다. 사서 25명과의 심층 질적 인터뷰를 통해, 이러한 책임들이 공공조직의 활력과 지속가능성을 높일 수 있음을 제시한다.</t>
+        </is>
+      </c>
+      <c r="J146" s="2" t="inlineStr">
+        <is>
+          <t>ABSTRACT Public administration has traditionally emphasized the normative ideal that public agencies have a responsibility to improve the lives of communities through public service delivery. We turn to public libraries to explore possibilities for what we call Expansive Public Service Delivery. Expansive Public Service Delivery is defined by a mission to serve all, professional and ethical responsibilities, and proactive responsiveness through outreach and (re)assessment. Public libraries have long aimed to improve communities and advance democracy by providing open, free information access to all. Today, they also proactively seek to expand their services to underserved groups ensuring their relevance and mission achievement. This research draws from 25 in‐depth qualitative interviews to explore librarian narratives to identify four core responsibilities that constitute Expansive Public Service Delivery. We conclude with a discussion of how service for all, professionalism, ethical responsibility, and reflexive decision‐making around community needs can result in more vibrant, sustainable public organizations.</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
@@ -4290,12 +7690,36 @@
           <t>American Journal of Political Science</t>
         </is>
       </c>
-      <c r="E147" s="2" t="inlineStr"/>
-      <c r="F147" s="2" t="inlineStr"/>
-      <c r="G147" s="2" t="inlineStr"/>
-      <c r="H147" s="2" t="inlineStr"/>
-      <c r="I147" s="2" t="inlineStr"/>
-      <c r="J147" s="2" t="inlineStr"/>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>이론/개념</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>정치 동학 모형</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>Political Divergence</t>
+        </is>
+      </c>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>Institutional Change</t>
+        </is>
+      </c>
+      <c r="I147" s="2" t="inlineStr">
+        <is>
+          <t>왜 일부 사회는 역사적 전통에서 벗어나고 다른 사회는 그 경로에 머무는지를 설명하기 위해, 통치자·엘리트·평민 간 단기 전략과 연합이 정치체제·재분배를 형성하고 이것이 장기적으로 부와 권력의 축적을 바꾸는 형식이론을 제시한다. 초기의 작은 차이가 제도와 사회구조의 공진화를 통해 상이한 발전 경로로 이어질 수 있음을 보이며, 중세 유럽·제국 중국·중세 이슬람 세계의 사례로 가능한 경로를 예시한다.</t>
+        </is>
+      </c>
+      <c r="J147" s="2" t="inlineStr">
+        <is>
+          <t>Abstract Why do some societies succeed in breaking away from historical traditions while others remain trapped? This paper proposes a formal theory to investigate the interaction between short‐run and long‐run political dynamics, highlighting a co‐evolution of political institutions and social structures. A society consists of various social groups, such as the rulers, the elites, and the commoners. Short‐run strategic considerations give rise to different coalitions among these groups, which determine not only political regimes but also redistribution policies. In the long run, these policies shape the accumulation of wealth and power, where small initial differences can lead to divergent paths of development. Finally, the paper examines three historical case studies on medieval Europe, imperial China, and the medieval Muslim world to illustrate potential pathways of long‐run political development.</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
@@ -4316,12 +7740,36 @@
           <t>Public Administration Review</t>
         </is>
       </c>
-      <c r="E148" s="2" t="inlineStr"/>
-      <c r="F148" s="2" t="inlineStr"/>
-      <c r="G148" s="2" t="inlineStr"/>
-      <c r="H148" s="2" t="inlineStr"/>
-      <c r="I148" s="2" t="inlineStr"/>
-      <c r="J148" s="2" t="inlineStr"/>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>혼합방법론</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>패널 행정자료 분석</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>Administrative Burden</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>Policy Inequity</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="inlineStr">
+        <is>
+          <t>중국 공공부조 프로그램의 2015~2017년 자료를 활용해 정책 불공평성이 행정 부담에 미치는 영향을 분석했다. 정책 불공평성은 심리적 비용과 순응 비용을 높이고 복지 프로그램 참여를 줄였으며, 개인 수준의 사회적 자본과 맥락 수준의 정보 투명성은 예상과 달리 이 영향을 완화하지 않고 증폭했다.</t>
+        </is>
+      </c>
+      <c r="J148" s="2" t="inlineStr">
+        <is>
+          <t>ABSTRACT The relationship between inequity and administrative burden constitutes a pivotal concern in the realm of public administration and policy, but how policy inequity (i.e., inequity in policy implementation) influences administrative burden has garnered scant attention. The present study employs data about public assistance programs in China spanning from 2015 to 2017 to examine the consequences of policy inequity on administrative burden. The empirical findings underscore that policy inequity augments psychological and compliance costs while concurrently diminishing citizens' participation in welfare programs, thereby indicating that policy inequity intensifies administrative burden. Notably, individual‐level social capital and contextual‐level information transparency in terms of public exposure related to welfare approval and receipt significantly moderate this relationship. Contrary to our theoretical expectations, social capital and public exposure amplify, rather than dampen, the impact of policy inequity on administrative burden. This study highlights the policy inequity lens and offers important implications for burden reduction.</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
@@ -4342,12 +7790,36 @@
           <t>Public Management Review</t>
         </is>
       </c>
-      <c r="E149" s="2" t="inlineStr"/>
-      <c r="F149" s="2" t="inlineStr"/>
-      <c r="G149" s="2" t="inlineStr"/>
-      <c r="H149" s="2" t="inlineStr"/>
-      <c r="I149" s="2" t="inlineStr"/>
-      <c r="J149" s="2" t="inlineStr"/>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>질적연구</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>다중 사례분석</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>innovation management</t>
+        </is>
+      </c>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t>innovation capacity</t>
+        </is>
+      </c>
+      <c r="I149" s="2" t="inlineStr">
+        <is>
+          <t>본 연구는 불확실성, 기술·사회 변화, 관료적 제약 속에서 공공조직의 혁신 역량을 유지하기 위한 의도적 조직 व्यवस्था인 혁신관리의 구성과 지속 조건을 탐구한다. 5개 국가 경찰기관의 다중 사례를 비교한 결과, 혁신 부서의 책임은 유사했지만 혁신관리 체계의 구성과 지속 방식은 달랐으며, 이를 Strong Heavyweight, Light Heavyweight, Lightweight의 세 유형으로 구분하고 촉진·제약 메커니즘이 혁신 역량의 차이를 설명함을 제시한다.</t>
+        </is>
+      </c>
+      <c r="J149" s="2" t="inlineStr">
+        <is>
+          <t>This paper examines innovation management as a deliberate organizational arrangement through which public organizations seek to remain relevant in contexts of uncertainty, technological and societal changes, and bureaucratic constraints. Drawing on a multiple-case study of five national police agencies, the study analyzes what works well and less well in systematic innovation management arrangements. While all agencies established innovation units with similar responsibilities, they differed in how innovation management systems were configured and sustained. Three configurations are identified – Strong Heavyweight, Light Heavyweight, and Lightweight – showing how enabling and constraining mechanisms help explain variation in innovation capacity across highly institutionalized public-sector contexts.</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
@@ -4368,12 +7840,36 @@
           <t>International Public Management Journal</t>
         </is>
       </c>
-      <c r="E150" s="2" t="inlineStr"/>
-      <c r="F150" s="2" t="inlineStr"/>
-      <c r="G150" s="2" t="inlineStr"/>
-      <c r="H150" s="2" t="inlineStr"/>
-      <c r="I150" s="2" t="inlineStr"/>
-      <c r="J150" s="2" t="inlineStr"/>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>실험</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>설문 결합실험</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>Information Framing</t>
+        </is>
+      </c>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>Citizen Support</t>
+        </is>
+      </c>
+      <c r="I150" s="2" t="inlineStr">
+        <is>
+          <t>미국 지방 판매세 주민투표에서 정보 제시 방식과 선택적 정보가 시민의 지지에 어떤 영향을 미치는지 분석하기 위해, 실제 주민투표 형식을 모방한 문단형 결합실험을 실시했다. 시민들은 대체로 소수의 핵심 정보에 집중했지만, 일부 하위집단은 제안된 판매세의 더 많고 다른 특성에도 관심을 보여, 관리자들이 특정 인구집단에 더 큰 영향력을 행사할 가능성을 시사했다.</t>
+        </is>
+      </c>
+      <c r="J150" s="2" t="inlineStr">
+        <is>
+          <t>Local option sales taxes in the United States are an interesting form of direct democracy that is influenced directly by public managers. The referenda, or ballot measures, in which people vote on sales taxes have multiple features that can be presented in a variety of ways. As such, they represent a unique opportunity to study the behavioral impact of options and information on citizen choice. With this research, we develop a novel experiment that uses the logic of a conjoint design by varying all of the key features in the referenda, but presents that information in a paragraph form that mimics the format of actual referenda. Results of this sales tax ballot conjoint experiment show that, in general, people only focus on a few key pieces of information, but specific sub-groups are interested in more and different features of the proposed sales tax. This suggests that managers may have more influence among key demographics, and knowing the attributes that matter to those demographics may help shape how sales tax ballot referenda are presented.</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
@@ -4394,12 +7890,36 @@
           <t>Public Administration Review</t>
         </is>
       </c>
-      <c r="E151" s="2" t="inlineStr"/>
-      <c r="F151" s="2" t="inlineStr"/>
-      <c r="G151" s="2" t="inlineStr"/>
-      <c r="H151" s="2" t="inlineStr"/>
-      <c r="I151" s="2" t="inlineStr"/>
-      <c r="J151" s="2" t="inlineStr"/>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>혼합방법론</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>구조방정식 패널</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>Democratic Backsliding</t>
+        </is>
+      </c>
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t>Bureaucratic Impartiality</t>
+        </is>
+      </c>
+      <c r="I151" s="2" t="inlineStr">
+        <is>
+          <t>민주적 후퇴가 정치적 책무성과 행정적 경로를 통해 정부효과성·규제의 질·부패통제에 미치는 영향을 1996~2024년 86개국 국가-연도 패널과 일반화 구조방정식 모형으로 분석한다. 거버넌스 악화는 단계·경로·성과지표별로 다르며, 권위주의적 회귀보다 민주주의의 완전한 침식에서 가장 크게 나타나는 비선형 U자형 패턴을 보인다.</t>
+        </is>
+      </c>
+      <c r="J151" s="2" t="inlineStr">
+        <is>
+          <t>ABSTRACT Democratic backsliding has emerged as a defining political challenge of the contemporary era, yet systematic cross‐national evidence linking it to governance outcomes remains scarce. This article argues that backsliding affects governance through two analytically distinct channels: a political accountability channel, whereby weakened contestation and oversight reduce the external costs of poor performance; and an administrative channel, through which executive politicization erodes meritocratic recruitment and bureaucratic impartiality. Using a country‐year panel of 86 countries from 1996 to 2024 and generalized structural equation models, we decompose the direct, indirect, and total effects of backsliding on government effectiveness, regulatory quality, and control of corruption across stages of democratic decline. The findings show that governance deterioration is stage‐specific, channel‐specific, and outcome‐specific, following a nonlinear, U‐shaped pattern in which complete erosion—rather than autocratic reversion—produces the largest governance losses.</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
@@ -4412,7 +7932,7 @@
       </c>
       <c r="C152" s="3" t="inlineStr">
         <is>
-          <t>Conditional Compliance: The Role of Sector and Policy Design in State Sexual Misconduct Policy</t>
+          <t>Conditional compliance: the role of sector and policy design in state sexual misconduct policy</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
@@ -4420,12 +7940,36 @@
           <t>Journal of Public Administration Research and Theory</t>
         </is>
       </c>
-      <c r="E152" s="2" t="inlineStr"/>
-      <c r="F152" s="2" t="inlineStr"/>
-      <c r="G152" s="2" t="inlineStr"/>
-      <c r="H152" s="2" t="inlineStr"/>
-      <c r="I152" s="2" t="inlineStr"/>
-      <c r="J152" s="2" t="inlineStr"/>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>준실험</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>시차적 이중차분</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>Principal-Agent Theory</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>Policy Design</t>
+        </is>
+      </c>
+      <c r="I152" s="2" t="inlineStr">
+        <is>
+          <t>미국 주의 대학 성적 misconduct 관리 법정책에서 부문과 정책 설계가 조직의 축소 보고·관리 실패를 줄이는 데 어떤 영향을 미치는지, 2007~2018년 전수 정책 코딩과 포아송 의사최대우도·시차적 이중차분으로 분석했다. 교육·인식 제고형 예방정책은 공립기관의 보고를 늘렸지만 사립기관에는 효과가 없었고, 집행·인프라 규제정책은 두 부문 모두에서 유의한 효과가 없었다.</t>
+        </is>
+      </c>
+      <c r="J152" s="2" t="inlineStr">
+        <is>
+          <t>Abstract The role of principal-agent dynamics in performance and accountability reforms has been a recurring theme in public administration research. Yet, less attention has been dedicated to how the intersection of sector and policy design shapes principal-agent dynamics and subsequent policy outcomes. This study theoretically explores and empirically tests how sector and policy design shape the effects of state legislation that seeks to prevent shirking (mismanagement and underreporting) in the context of sexual misconduct outcomes in US colleges and universities. We code every state policy designed to regulate higher education institutions’ management of sexual misconduct from 2007 to 2018 in the US and leverage a Poisson pseudo-maximum likelihood with a staggered difference-in-differences design to identify the effects. Our findings suggest that both sector and policy design matter: public institutions increase reporting in response to prevention policies that promote education and awareness, but prevention policies have no effect on private institutions. Other policies regulating enforcement and infrastructure produce null effects across both sectors. These findings have important implications for principal-agent theory and policy design research on effective methods for reducing shirking in social equity, accountability, and performance reporting.</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
@@ -4446,12 +7990,36 @@
           <t>Public Administration Review</t>
         </is>
       </c>
-      <c r="E153" s="2" t="inlineStr"/>
-      <c r="F153" s="2" t="inlineStr"/>
-      <c r="G153" s="2" t="inlineStr"/>
-      <c r="H153" s="2" t="inlineStr"/>
-      <c r="I153" s="2" t="inlineStr"/>
-      <c r="J153" s="2" t="inlineStr"/>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>질적연구</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>질적 내용 분석</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>bureaucracy</t>
+        </is>
+      </c>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t>governance</t>
+        </is>
+      </c>
+      <c r="I153" s="2" t="inlineStr">
+        <is>
+          <t>이 연구는 비서구 역사 기록이 베버 관료제와 다른 거버넌스 이론을 제시할 수 있는지 탐구하기 위해 14세기 자바 궁정 문헌 『나가라크레타가마』 98편 전체를 질적 내용 분석했다. 분석 결과 관료제적 위계, 만달라 기반 영토 행정, 조건부 재정 면제, 성문법과 관습을 결합한 법질서, 행정과 통합된 의례라는 다섯 영역을 통해 자바 제국의 통치가 권위·영토·수입·법·정당성을 조직한 대안적 행정 개념을 보여준다고 제시한다.</t>
+        </is>
+      </c>
+      <c r="J153" s="2" t="inlineStr">
+        <is>
+          <t>ABSTRACT Public administration scholarship often treats the Weberian ideal type as a universal model of bureaucracy, making governance arrangements that differ from it appear deficient rather than different. A decolonizing approach instead asks whether non‐Western historical records can offer alternative ways of theorizing governance. This study explores that possibility through the Nagarakretagama, a 14th‐century Javanese court eulogy composed by Mpu Prapanca in 1365, which predates Machiavelli's The Prince by 148 years. Qualitative content analysis of all 98 cantos identifies five governance domains: bureaucratic hierarchy, mandala‐based territorial administration, conditional fiscal exemptions, a legal order combining written law and custom, and ceremonial practices integrated with administration. These dimensions show how the Javanese empire organized authority, territory, revenue, law, and legitimacy through institutional arrangements that differ from the Weberian model. Reading this governance system as theory reveals an alternative conceptualization of administration and advances a decolonizing, pluriversal approach to public administration.</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
@@ -4472,17 +8040,41 @@
           <t>American Journal of Political Science</t>
         </is>
       </c>
-      <c r="E154" s="2" t="inlineStr"/>
-      <c r="F154" s="2" t="inlineStr"/>
-      <c r="G154" s="2" t="inlineStr"/>
-      <c r="H154" s="2" t="inlineStr"/>
-      <c r="I154" s="2" t="inlineStr"/>
-      <c r="J154" s="2" t="inlineStr"/>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>혼합방법론</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>이중차분·설문·인터뷰</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>Participatory Institutions</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>Regime Consolidation</t>
+        </is>
+      </c>
+      <c r="I154" s="2" t="inlineStr">
+        <is>
+          <t>정부에 포획된 참여제도가 개발을 촉진할 수 있는 조건과 정권 우선순위 변화가 그 효과에 미치는 영향을 이론적으로 제시하고, 베네수엘라 공동체평의회를 대상으로 이중차분 분석, 참여자 설문, 51건의 인터뷰를 실시했다. 정치적 안정과 정권 공고화 시기에는 평의회가 경제적·정치적 성과를 냈지만, 경제 붕괴로 정부가 권위주의적 생존 모드에 들어서자 정치 활동에 특화되었다.</t>
+        </is>
+      </c>
+      <c r="J154" s="2" t="inlineStr">
+        <is>
+          <t>Abstract Can participatory institutions (PIs) facilitate development when captured by the government? We propose an original theoretical framework to investigate how changing incumbent priorities can shape the developmental and political effects of captured PIs. While patrons concerned with survival can force PIs to specialize in political activities, those pursuing regime consolidation may incentivize PIs to multitask, delivering developmental gains and political rewards. We deploy our framework to study Venezuela's Communal Councils. Leveraging difference‐in‐differences analyses, an original survey of Council participants, and 51 interviews with government officials and grassroots Communal Council members, we find that Councils yielded both economic and political returns during an early period marked by political stability and regime consolidation. However, as Venezuela's economic collapse pushed the government into an authoritarian survival mode, Councils became politically specialized. While showing that captured PIs can foster development under certain circumstances, our findings cast doubt on PIs’ development‐enhancing potential under autocracy.</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>Joshua P. Darr; Susan Robinson</t>
+          <t>Joshua P. Darr; Sue Robinson</t>
         </is>
       </c>
       <c r="B155" s="2" t="n">
@@ -4498,12 +8090,36 @@
           <t>Political Communication</t>
         </is>
       </c>
-      <c r="E155" s="2" t="inlineStr"/>
-      <c r="F155" s="2" t="inlineStr"/>
-      <c r="G155" s="2" t="inlineStr"/>
-      <c r="H155" s="2" t="inlineStr"/>
-      <c r="I155" s="2" t="inlineStr"/>
-      <c r="J155" s="2" t="inlineStr"/>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>혼합방법론</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>컨조인트 실험</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>Civic Journalism</t>
+        </is>
+      </c>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t>News Trust</t>
+        </is>
+      </c>
+      <c r="I155" s="2" t="inlineStr">
+        <is>
+          <t>미국 언론인의 재훈련으로 참여·해결책·‘건설적 갈등’ 방식으로 재구성된 뉴스가 전통적인 엘리트 중심·문제 중심·갈등 중심 뉴스보다 선택되는지, 그리고 그 이유가 무엇인지 검토했다. 세 개의 뉴스룸 훈련기관과 협력해 컨조인트 실험을 실시하고 7개 포커스그룹(n=49) 및 설문으로 보완한 결과, 응답자들은 재구성된 콘텐츠를 압도적으로 선택·긍정적으로 평가했으며 뉴스 브랜드에 대한 신뢰와 구독·후원 의향이 높아졌다고 보고했다.</t>
+        </is>
+      </c>
+      <c r="J155" s="2" t="inlineStr">
+        <is>
+          <t>This mixed‑method applied research study examines how audiences are responding to news stories that are shaped by retraining efforts to help American journalists rebuild audiences. We wanted to know: were these trainings working? Do audiences choose stories that were influenced by these trainings over more traditional elite-focused, problem-oriented, conflict-driven stories? Working with three newsroom-training organizations, we report the results of a series of conjoint experiments that test how well stories abiding by new journalistic techniques of engagement, solutions and “good-conflict” framing play with audiences. We then use the findings from seven focus groups (n = 49) with surveys to explain why people may have responded the way they did in the tests. We found that audiences overwhelmingly selected and appreciated the re-framed content and reported that it makes them trust the news brands more. The focus group participants claimed such content would entice them to become members, subscribe, or even donate to the mainstream brand – if they came across it. However, only a few of the participants said they had heard about the news outlet. Though the principles behind these trainings may seem counterintuitive to some journalists, they offer a potential path forward in uncertain times for local news.</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
@@ -4524,12 +8140,36 @@
           <t>Administration &amp; Society</t>
         </is>
       </c>
-      <c r="E156" s="2" t="inlineStr"/>
-      <c r="F156" s="2" t="inlineStr"/>
-      <c r="G156" s="2" t="inlineStr"/>
-      <c r="H156" s="2" t="inlineStr"/>
-      <c r="I156" s="2" t="inlineStr"/>
-      <c r="J156" s="2" t="inlineStr"/>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>혼합방법론</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>지표·설문·인터뷰</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>Nonprofit Capacity</t>
+        </is>
+      </c>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>Network Embeddedness</t>
+        </is>
+      </c>
+      <c r="I156" s="2" t="inlineStr">
+        <is>
+          <t>이 연구는 경제학의 공급·수요 관점과 실무자 관점을 통합해 지역 비영리 부문의 역량이 무엇에 의해 형성되는지 조사했다. 미국 중간 규모 도시의 보건·인간서비스 비영리단체를 대상으로 지역 지표, 설문, 인터뷰를 결합한 결과, 역량은 자원 가용성이나 조직 밀도뿐 아니라 지역 네트워크의 강도와 공동체 맥락에도 좌우되며, 네트워크에 깊이 embedded된 기존 단체와 연결성이 낮은 단체는 역량 인식과 지역 수요 충족 능력에서 차이를 보였다.</t>
+        </is>
+      </c>
+      <c r="J156" s="2" t="inlineStr">
+        <is>
+          <t>This study examines nonprofit sector capacity by integrating economic concepts of supply and demand with practitioner perspectives. Focusing on health and human services nonprofits in a midsize southeastern U.S. city, it combines community indicators with survey and interview data. Findings suggest that sector capacity depends not only on resource availability and organizational density but also on the strength of local networks and community context. Well-established nonprofits embedded in local networks differ from more loosely connected organizations, demonstrating how network position shapes perceptions of capacity and the ability to meet community needs. These findings advance research on nonprofit carrying capacity.</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
@@ -4550,12 +8190,36 @@
           <t>Public Opinion Quarterly</t>
         </is>
       </c>
-      <c r="E157" s="2" t="inlineStr"/>
-      <c r="F157" s="2" t="inlineStr"/>
-      <c r="G157" s="2" t="inlineStr"/>
-      <c r="H157" s="2" t="inlineStr"/>
-      <c r="I157" s="2" t="inlineStr"/>
-      <c r="J157" s="2" t="inlineStr"/>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>실험</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>설문 실험</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>Attitude Polarization</t>
+        </is>
+      </c>
+      <c r="H157" s="2" t="inlineStr">
+        <is>
+          <t>Response Satisficing</t>
+        </is>
+      </c>
+      <c r="I157" s="2" t="inlineStr">
+        <is>
+          <t>AI 매개 반구조화 면접이 고정형 설문과 비교해 응답자의 만족도·이탈, 응답의 양과 구체성, 후속 태도 응답에 미치는 영향을 대규모 완전 무작위 실험으로 비교했다. AI 면접은 응답자가 제시한 근거의 양과 구체성을 높였고 만족도 저하나 이탈 증가는 거의 없었지만, 후속 문항에서 응답 양극화를 증가시켰다.</t>
+        </is>
+      </c>
+      <c r="J157" s="2" t="inlineStr">
+        <is>
+          <t>Abstract Artificial intelligence (AI) interviewing offers the potential to enhance the depth and quality of survey research, yet it may also introduce respondent fatigue and unintended consequences for the measurement of political attitudes. From the standpoint of respondents, more extensive interviews impose greater cognitive and temporal burdens, which may reduce engagement or increase satisficing. From the perspective of political behavior researchers, deeper probing may shift the subset of beliefs or arguments that respondents access when forming opinions, thereby altering the distribution and apparent stability of measured attitudes. To investigate these dynamics, we conduct a large-scale, fully randomized experiment. We find that AI-mediated interviewing significantly increases both the volume and specificity of respondents’ articulated rationales, but any decline in participant satisfaction is minuscule and we detect no increase in participant rolloff. However, AI interviews appear to shape subsequent responses: After offering justifications through AI interaction, respondents exhibit greater polarization in follow-up items. This result suggests that AI interviewing may alter the cognitive architecture of opinion formation. These findings both highlight the potential for AI interviewing and underscore the need for studies of how AI interviewing may become a source of attitudinal change.</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
@@ -4576,12 +8240,36 @@
           <t>Public Administration</t>
         </is>
       </c>
-      <c r="E158" s="2" t="inlineStr"/>
-      <c r="F158" s="2" t="inlineStr"/>
-      <c r="G158" s="2" t="inlineStr"/>
-      <c r="H158" s="2" t="inlineStr"/>
-      <c r="I158" s="2" t="inlineStr"/>
-      <c r="J158" s="2" t="inlineStr"/>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>질적연구</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>전문가 인터뷰</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>Agile Methods</t>
+        </is>
+      </c>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>Rule of Law</t>
+        </is>
+      </c>
+      <c r="I158" s="2" t="inlineStr">
+        <is>
+          <t>이 논문은 네덜란드 지방정부와 벨기에 플랑드르 지역정부의 사례를 전문가 인터뷰로 분석해, 유연성을 중시하는 애자일 디지털 전환이 기존 행정 루틴 및 법치주의와 어떻게 상호작용하는지 살펴본다. 애자일 방식은 분권적 리더십과 협업을 중시하는 루틴과 부합하며, 법치주의를 위협하기보다 촉진할 수 있고, 법적 불확실성의 주요 원인은 애자일 자체보다 복잡한 법·정책에 있음을 보인다.</t>
+        </is>
+      </c>
+      <c r="J158" s="2" t="inlineStr">
+        <is>
+          <t>ABSTRACT This paper examines the interplay between agile digital transformation and the rule of law within the public sector, focusing on case studies from a semi‐large municipal government in the Netherlands and a department of the Flemish regional government in Belgium. Drawing on expert interviews, the paper explores how agile methods, championed for flexibility, interact with existing administrative routines and affect rule of law principles that prioritize consistency. Theoretically, the paper builds on public administration scholarship concerning administrative routines and the rule of law. Empirically, the paper shows that agile methods align well with administrative routines that prioritize decentralized leadership and collaboration. Moreover, it shows that agile approaches can foster, rather than threaten, the rule of law: many legal uncertainties arise not from agile practices themselves but from existing complexities in laws and policies, highlighting a need for stronger technical precision in lawmaking and administrative awareness in digital implementation.</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
@@ -4602,12 +8290,36 @@
           <t>Public Administration Review</t>
         </is>
       </c>
-      <c r="E159" s="2" t="inlineStr"/>
-      <c r="F159" s="2" t="inlineStr"/>
-      <c r="G159" s="2" t="inlineStr"/>
-      <c r="H159" s="2" t="inlineStr"/>
-      <c r="I159" s="2" t="inlineStr"/>
-      <c r="J159" s="2" t="inlineStr"/>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>혼합방법론</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>종단 공간분석</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>Institutional Trust</t>
+        </is>
+      </c>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t>Political Polarization</t>
+        </is>
+      </c>
+      <c r="I159" s="2" t="inlineStr">
+        <is>
+          <t>2016·2020·2024년 미국의 경쟁적 ‘스윙’·‘피벗’ 카운티에서 지방선거관리관(LEO)의 이직을 유발하는 요인을 분석하고, 경쟁 카운티 74곳과 초대형 압승 카운티 25곳의 자료를 포함한 종단·공간 혼합방법을 활용했다. 경쟁이 치열한 관할에서는 제도적 신뢰의 약화가 LEO 이탈의 주요 촉진 요인으로 나타났다.</t>
+        </is>
+      </c>
+      <c r="J159" s="2" t="inlineStr">
+        <is>
+          <t>ABSTRACT Post‐2024, the United States faces an acute labor crisis marked by accelerating Local Election Official (LEO) attrition. This study examines causal drivers of this exodus, focusing specifically on disproportionate turnover within volatile “swing” and “pivot” counties. Utilizing a mixed‐methods design, using longitudinal data from the Bipartisan Policy Center, US Census Bureau, Elections Voter Survey, MIT Election Data and Science Lab (MEDSL), and the Reed LEO survey, alongside an original dataset compiled from 74 competitive counties and 25 “super landslide” counties. Using Geographic Information Systems, we connect a detailed county profile to spatial mapping of the legal and political environment across the 2016, 2020, and 2024 elections. LEOs in highly competitive jurisdictions face an erosion of institutional trust, serving as a primary catalyst for departure. These volatile jurisdictions highlight where democratic machinery is vulnerable, offering evidence‐based insights for state‐level policy interventions designed to stabilize the public administrative workforce amidst unprecedented hyperpolarization.</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
@@ -4628,12 +8340,36 @@
           <t>Political Communication</t>
         </is>
       </c>
-      <c r="E160" s="2" t="inlineStr"/>
-      <c r="F160" s="2" t="inlineStr"/>
-      <c r="G160" s="2" t="inlineStr"/>
-      <c r="H160" s="2" t="inlineStr"/>
-      <c r="I160" s="2" t="inlineStr"/>
-      <c r="J160" s="2" t="inlineStr"/>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>질적연구</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>시각 내용분석</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>Digital Placemaking</t>
+        </is>
+      </c>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>Symbolic Geographies</t>
+        </is>
+      </c>
+      <c r="I160" s="2" t="inlineStr">
+        <is>
+          <t>팔레스타인 인스타그램 이용자들이 장소의 일상, 기쁨·가족·신앙, 장소·전통·환경 표지를 시각적으로 기록해 이주와 지리적 삭제에 저항하고 문화적 존재감을 주장하는 방식을 분석했다. 2023년 10월부터 2024년 3월까지 834명의 이용자가 게시한 9,126개 게시물과 국제 뉴스 헤드라인 7,448개를 비교한 결과, 이용자 게시물은 주류 서사에 없는 대안적 프레임을 제시하며 위협받는 공간과 문화 기억을 보존하는 네트워크형 기록보관소를 형성했다.</t>
+        </is>
+      </c>
+      <c r="J160" s="2" t="inlineStr">
+        <is>
+          <t>Palestinians use Instagram to construct symbolic geographies that resist displacement and assert cultural presence. Analyzing 9,126 posts from 834 users posted between October 2023-March 2024, we identify three recurring visual themes that serve as anchors of digital placemaking. The sharing of images depicting everyday routines and familiar spaces functions as an act of asserting belonging in the face of cartographic erasure. Resilience is conveyed through motifs of joy, family, and faith, symbolizing continuity under siege. Knowledge cultivation emerges through practices of naming places, traditions, and environmental markers, reinforcing cultural memory. Comparing Instagram content with 7,448 international news headlines, we find that user-generated posts often offer alternative framings that are absent in mainstream narratives. We close with a discussion of how Palestinian Instagram users created a networked archive that resists material destruction and algorithmic suppression, mapping threatened spaces and producing narrative coherence through everyday digital acts of documentation and resistance.</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
@@ -4654,12 +8390,36 @@
           <t>Public Administration</t>
         </is>
       </c>
-      <c r="E161" s="2" t="inlineStr"/>
-      <c r="F161" s="2" t="inlineStr"/>
-      <c r="G161" s="2" t="inlineStr"/>
-      <c r="H161" s="2" t="inlineStr"/>
-      <c r="I161" s="2" t="inlineStr"/>
-      <c r="J161" s="2" t="inlineStr"/>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>서베이</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>패널 설문</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t>Capacity Building Framework</t>
+        </is>
+      </c>
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t>Adaptive Capacity</t>
+        </is>
+      </c>
+      <c r="I161" s="2" t="inlineStr">
+        <is>
+          <t>미국 지방정부 비상관리 조직이 사회적 형평성 중심 실천을 추진할 조직 역량을 갖추었는지를 역량 구축 프레임워크와 전국 패널 설문 자료를 통해 탐색적으로 분석했다. 정치적·기술적·재정적·관리적 역량이 모두 중요했지만, 재정 역량이 가장 큰 제약으로 나타났으며 응답자들은 인력, 지역사회 홍보·교육, 접근 가능한 공공자원 개발을 위한 추가 재원을 우선시했다.</t>
+        </is>
+      </c>
+      <c r="J161" s="2" t="inlineStr">
+        <is>
+          <t>ABSTRACT The emergency management profession and discipline is increasingly embracing social equity as a core value, yet limited attention has been paid to whether local emergency management organizations possess the capacity to implement equity‐focused practices. Drawing on the Capacity Building Framework, this exploratory study analyzes data from a national panel survey of US emergency managers to examine the organizational capacity to advance social equity through the lens of adaptive capacity. The findings reveal that while political, technical, financial, and managerial capacities matter, financial capacity is the most critical constraint. Respondents prioritized additional funding for personnel, community outreach and education, and the development of accessible public resources. The results highlight how resource scarcity shapes the pursuit of equity at the local level and underscores the need to align equity goals with investments in organizational capacity. This study contributes insight into the practical challenges emergency managers face in translating equity commitments into action.</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
@@ -4680,12 +8440,36 @@
           <t>Public Administration</t>
         </is>
       </c>
-      <c r="E162" s="2" t="inlineStr"/>
-      <c r="F162" s="2" t="inlineStr"/>
-      <c r="G162" s="2" t="inlineStr"/>
-      <c r="H162" s="2" t="inlineStr"/>
-      <c r="I162" s="2" t="inlineStr"/>
-      <c r="J162" s="2" t="inlineStr"/>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>혼합방법론</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>카운티 패널 분석</t>
+        </is>
+      </c>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>Racial Threat</t>
+        </is>
+      </c>
+      <c r="H162" s="2" t="inlineStr">
+        <is>
+          <t>Political Representation</t>
+        </is>
+      </c>
+      <c r="I162" s="2" t="inlineStr">
+        <is>
+          <t>이 연구는 소수인구 규모와 지방정부의 착취적 세입 의존 간 관계를 분석하고, 소수자 정치적 대표성이 이를 조절하는지 검토했다. 2011~2019년 플로리다 66개 카운티 자료를 분석한 결과, 소수인구가 많은 카운티일수록 착취적 세입에 더 의존했지만 소수자 대표성이 높아지면 이 관계가 약화됐다.</t>
+        </is>
+      </c>
+      <c r="J162" s="2" t="inlineStr">
+        <is>
+          <t>ABSTRACT Social equity budgeting has gained increasing attention, yet research has largely focused on expenditures while neglecting revenue equity. This study contributes to the literature by examining the relationships between minority population size and local governments' reliance on exploitative revenues, and whether minority political representation moderates this relationship. Drawing on racial threat and political representation theories, we analyze data from 66 Florida counties between 2011 and 2019. Results show that counties with larger minority populations rely more heavily on exploitative revenues, but this relationship diminishes when minority political representation increases. These findings highlight how minority leadership could moderate fiscal practices that disproportionately burden minority communities. More broadly, this study advances the framework of social equity budgeting by shifting the focus from expenditure allocation to revenue generation.</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
@@ -4706,12 +8490,36 @@
           <t>Political Communication</t>
         </is>
       </c>
-      <c r="E163" s="2" t="inlineStr"/>
-      <c r="F163" s="2" t="inlineStr"/>
-      <c r="G163" s="2" t="inlineStr"/>
-      <c r="H163" s="2" t="inlineStr"/>
-      <c r="I163" s="2" t="inlineStr"/>
-      <c r="J163" s="2" t="inlineStr"/>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>혼합방법론</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>내용분석·설문실험</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>Threat Perception</t>
+        </is>
+      </c>
+      <c r="H163" s="2" t="inlineStr">
+        <is>
+          <t>Racial Attitudes</t>
+        </is>
+      </c>
+      <c r="I163" s="2" t="inlineStr">
+        <is>
+          <t>중국을 위협으로 묘사하는 언론 보도가 미국인의 대중국 강경 외교정책 지지와 아시아계 미국인에 대한 반감을 어떻게 형성하는지 분석했다. 2010~2020년 CNN·Fox News 내용분석, 전국 설문, 사전등록 설문실험을 통해 위협 대상이 미국인지 다른 국가인지와 무관하게 이러한 서사가 강경정책 지지와 반아시아 정서를 높이며, 특히 공화당원에게서 효과가 크게 나타남을 밝혔다.</t>
+        </is>
+      </c>
+      <c r="J163" s="2" t="inlineStr">
+        <is>
+          <t>How do portrayals of foreign nations as threats shape public opinion on foreign policy and domestic racial attitudes? This study examines how portrayals of China as a threat influence Americans’ support for U.S. policy toward China and attitudes toward Asian Americans. A content analysis of CNN and Fox News transcripts from 2010 to 2020 shows that both outlets increasingly portrayed China as a threat, although Fox News more often emphasized threats to the United States, whereas CNN focused more on threats affecting other countries, international institutions, and populations. A national survey and a preregistered survey experiment further demonstrate that exposure to China threat narratives, regardless of whether the threat targets the United States or another country, increases support for hawkish U.S. foreign policy and heightens anti-Asian resentment, especially among Republicans. These findings show how portrayals of foreign threats shape public opinion and spill over into racial attitudes at home.</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
@@ -4732,12 +8540,36 @@
           <t>Public Opinion Quarterly</t>
         </is>
       </c>
-      <c r="E164" s="2" t="inlineStr"/>
-      <c r="F164" s="2" t="inlineStr"/>
-      <c r="G164" s="2" t="inlineStr"/>
-      <c r="H164" s="2" t="inlineStr"/>
-      <c r="I164" s="2" t="inlineStr"/>
-      <c r="J164" s="2" t="inlineStr"/>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>서베이</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>반복 횡단 설문</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>Issue Salience</t>
+        </is>
+      </c>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t>Energy Security</t>
+        </is>
+      </c>
+      <c r="I164" s="2" t="inlineStr">
+        <is>
+          <t>본 연구는 2006~2024년 46개 유로바로미터 파동을 조화한 자료로 EU 회원국의 에너지 이슈 현저성, 정책 우선순위, 재생에너지에 대한 태도의 국가별·시기별 변화를 추적한다. 에너지에 대한 관심은 위기, 특히 2022년 러시아의 우크라이나 침공기에 크게 높아졌으며, 일부 중·동부 및 남부 유럽에서는 재생에너지 지지가 비용 부담과 에너지 안보 우려와 공존했다.</t>
+        </is>
+      </c>
+      <c r="J164" s="2" t="inlineStr">
+        <is>
+          <t>Abstract Our study describes European attitudes toward energy using a harmonized dataset comprising 46 waves of the Eurobarometer (2006–2024). This tracking survey covers all European Union member states; hence, our data accumulates 1,286 individual country surveys. We focus on attitudes relevant to energy transition through three complementary lenses: energy issue salience, policy priorities, and opinions on renewable energy sources. This study documents cross-national and temporal variation in attitudes without estimating the causal effects of specific energy-related European policies or contextual events. We record a marked increase in the salience of energy during crisis periods, especially Russia’s 2022 invasion of Ukraine, which rapidly elevated energy’s importance in the hierarchy of public concerns. We also show that support for renewables, in the context of energy transition, coexists with affordability and security concerns in some regions of the EU, particularly in Central-Eastern and Southern Europe. To our knowledge, this is the first study to systematically harmonize such a large collection of Eurobarometer waves into a single comparable dataset, enabling long-term tracking of energy attitudes across all EU member states. In addition to the substantive results, our study also points to several difficulties the Eurobarometer project faces in providing long-term monitoring of public opinion across the highly diverse member states of the European Union.</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
@@ -4758,12 +8590,36 @@
           <t>Public Administration Review</t>
         </is>
       </c>
-      <c r="E165" s="2" t="inlineStr"/>
-      <c r="F165" s="2" t="inlineStr"/>
-      <c r="G165" s="2" t="inlineStr"/>
-      <c r="H165" s="2" t="inlineStr"/>
-      <c r="I165" s="2" t="inlineStr"/>
-      <c r="J165" s="2" t="inlineStr"/>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>준실험</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>지속기간 분석</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="H165" s="2" t="inlineStr">
+        <is>
+          <t>Employee Turnover</t>
+        </is>
+      </c>
+      <c r="I165" s="2" t="inlineStr">
+        <is>
+          <t>청년 코호트의 공공·비영리 부문 최초 진입과 이탈을 성별에 따라 어떻게 설명할 수 있는지, NLSY97 코호트에 대한 지속기간 분석으로 검토했다. 여성은 남성보다 최초 공공·비영리 일자리에 더 빠르게 진입했지만 최초 재직기간에는 성별 차이가 없었으며, 이러한 패턴은 여성 지배 직종에 대한 여성의 높은 유입과 남성 지배 직종에서의 여성 이직률 증가가 함께 작용한 결과로 나타났다.</t>
+        </is>
+      </c>
+      <c r="J165" s="2" t="inlineStr">
+        <is>
+          <t>ABSTRACT Public and nonprofit organizations exhibit high rates of female employment often attributed to sector structures and social roles. To better understand how individual behaviors dynamically contribute to these distinctive ratios, we deconstruct public and nonprofit employment into gendered patterns of attraction and attachment. Using duration analysis and following a cohort from the National Longitudinal Survey of Youth 1997, this research finds that women demonstrate a higher attraction to their first public and nonprofit job compared to men, evidenced through a faster rate of entry into this employment. There are no significant gender differences when considering the duration of an individual's first stint in these sectors. Additional investigation finds that these sector‐level patterns, when decomposed to account for gender‐dominant professions, are driven by stronger female attraction to female‐dominated professions while masking higher female turnover from male‐dominated professions. Results inform recruitment and retention strategies for public and nonprofit organizations.</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
@@ -4784,12 +8640,36 @@
           <t>Public Performance &amp; Management Review</t>
         </is>
       </c>
-      <c r="E166" s="2" t="inlineStr"/>
-      <c r="F166" s="2" t="inlineStr"/>
-      <c r="G166" s="2" t="inlineStr"/>
-      <c r="H166" s="2" t="inlineStr"/>
-      <c r="I166" s="2" t="inlineStr"/>
-      <c r="J166" s="2" t="inlineStr"/>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>이론/개념</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>메타분석·메타회귀</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>Inter-organizational Cooperation</t>
+        </is>
+      </c>
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t>Cost Efficiency</t>
+        </is>
+      </c>
+      <c r="I166" s="2" t="inlineStr">
+        <is>
+          <t>공공조직 간 협력이 서비스 제공 비용을 낮추는지, 그리고 비용 절감 효과의 차이를 설명하는 조건이 무엇인지 26개 연구(152개 효과크기)의 메타분석과 메타회귀로 검토했다. 협력은 작지만 통계적으로 유의한 비용 절감 효과(r=-.05)를 보였으며, 여러 서비스 영역을 포괄할수록 절감이 어려워지고, 측정 방식과 연구 설계에 따라 추정치가 달라졌다.</t>
+        </is>
+      </c>
+      <c r="J166" s="2" t="inlineStr">
+        <is>
+          <t>Inter-organizational cooperation is widely promoted as a strategy to improve cost efficiency in public service delivery. However, empirical findings on the efficiency gains remain mixed, and the conditions under which cost savings are realized are not well understood. To further the research field, this meta-analysis synthesizes evidence from 26 studies comprising 152 effect sizes to examine whether cooperation involving public organizations reduces service provision costs and to examine why estimated cost effects vary across studies. Through the analysis, we find a small but statistically significant cost-reducing effect (r = −.05), indicating that cooperation is associated with modestly lower service costs. The meta-regression results further show that the difficulty of achieving cost savings is significantly increased when cooperation spans multiple service areas. The estimated cost effects also vary with the study design and measurement choices: intensity-based operationalizations are associated with larger cost reductions than propensity-based measures, and quasi-experimental designs yield more conservative estimates than simple regressions. In contrast, the type of cooperation, asset specificity, and measurement difficulty do not affect cost outcomes significantly. Based on these findings, we offer cautious implications for policymakers and public managers seeking to design cost-effective cooperative service arrangements and identify priorities for future research.</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
@@ -4810,12 +8690,36 @@
           <t>American Journal of Political Science</t>
         </is>
       </c>
-      <c r="E167" s="2" t="inlineStr"/>
-      <c r="F167" s="2" t="inlineStr"/>
-      <c r="G167" s="2" t="inlineStr"/>
-      <c r="H167" s="2" t="inlineStr"/>
-      <c r="I167" s="2" t="inlineStr"/>
-      <c r="J167" s="2" t="inlineStr"/>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>혼합방법론</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>자료 결합 분석</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>Distributive Concerns</t>
+        </is>
+      </c>
+      <c r="H167" s="2" t="inlineStr">
+        <is>
+          <t>Green Coalitions</t>
+        </is>
+      </c>
+      <c r="I167" s="2" t="inlineStr">
+        <is>
+          <t>브라질에서 대규모 산불이 녹색 후보 지지에 미치는 영향이 산불로 조성된 토지에서 경제적 이익을 얻을 가능성에 따라 달라지는지 분석했다. 위성·행정·선거 자료와 설문 자료를 활용한 결과, 산불의 경제적 이익을 얻기 어려운 지방자치단체에서만 녹색 후보 지지가 증가했으며, 유권자도 새로 개간된 토지에서 얻을 이익이 제한적일 때에만 경제성장보다 환경보호를 우선했다.</t>
+        </is>
+      </c>
+      <c r="J167" s="2" t="inlineStr">
+        <is>
+          <t>Abstract Large‐scale fires are becoming increasingly common due to climate change. While conventional wisdom suggests that firsthand experiences with natural disasters foster green coalitions by raising awareness of environmental degradation, we propose an alternative view: Natural disasters can heighten the perceived trade‐off between economic development and environmental policies. This study examines the case of Brazil, where large‐scale fires, by clearing natural vegetation, create new opportunities for land grabbing and the expansion of agriculture and livestock production. Using satellite, administrative, and electoral data, we provide evidence that large‐scale fires increase support for green candidates only in municipalities that are unlikely to reap economic benefits from fires. Survey data further indicate that voters prioritize environmental protection over economic growth only when they stand to receive limited or no benefit from the newly cleared land. Our findings suggest that the potential for natural disasters to foster green coalitions is contingent upon distributive concerns.</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
@@ -4836,12 +8740,36 @@
           <t>Political Communication</t>
         </is>
       </c>
-      <c r="E168" s="2" t="inlineStr"/>
-      <c r="F168" s="2" t="inlineStr"/>
-      <c r="G168" s="2" t="inlineStr"/>
-      <c r="H168" s="2" t="inlineStr"/>
-      <c r="I168" s="2" t="inlineStr"/>
-      <c r="J168" s="2" t="inlineStr"/>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>혼합방법론</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>관찰자료·설문 실험</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>Propaganda</t>
+        </is>
+      </c>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t>Entertainment</t>
+        </is>
+      </c>
+      <c r="I168" s="2" t="inlineStr">
+        <is>
+          <t>중국의 새로운 선전 영화에서 오락 요소가 대중의 자발적 시청과 정치적 주입에 대한 수용성을 높이는지 관찰자료와 사전등록 설문실험으로 분석했다. 인물 중심·서사 중심 오락 요소는 특히 원래 선전에 노출되려 하지 않는 집단의 시청을 늘렸고, 시청자가 선전성을 인식하더라도 오락과 결합된 정치적 메시지를 더 수용하게 했다.</t>
+        </is>
+      </c>
+      <c r="J168" s="2" t="inlineStr">
+        <is>
+          <t>For authoritarian propaganda to change hearts and minds, it must first reach the masses and capture their attention. In an era of media proliferation, what can an authoritarian regime do to make ordinary citizens consume pro-regime propaganda voluntarily? How can it lower citizens’ resistance to being indoctrinated? In this article, we answer these questions by studying a new generation of propaganda movies in contemporary China. Leveraging observational data and a pre-registered survey experiment, we find that entertainment elements in propaganda movies – both personality-based and narrative-based – play a key role in appealing to viewers and increasing consumption; this effect is especially pronounced among groups that are the least inclined to expose themselves to propaganda in the first place. Also, viewers are more receptive to political indoctrination when it is interwoven with entertainment, even when they recognize such content. Combined, these findings highlight the importance of entertainment in authoritarian propaganda: not only does it serve as a vehicle to disseminate political indoctrination, but it also functions as a source of appeal that renders such indoctrination more palatable to the masses.</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
@@ -4862,12 +8790,36 @@
           <t>Political Communication</t>
         </is>
       </c>
-      <c r="E169" s="2" t="inlineStr"/>
-      <c r="F169" s="2" t="inlineStr"/>
-      <c r="G169" s="2" t="inlineStr"/>
-      <c r="H169" s="2" t="inlineStr"/>
-      <c r="I169" s="2" t="inlineStr"/>
-      <c r="J169" s="2" t="inlineStr"/>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>혼합방법론</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>설문·헤드라인 분석</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>Affective Legitimacy</t>
+        </is>
+      </c>
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>Digital Populism</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="inlineStr">
+        <is>
+          <t>루마니아 헌법재판소의 대선 1차 투표 무효화 결정을 시민들이 정당하지 않다고 인식하게 만드는 사회·정치적·미디어 요인을 전국 대표 설문(N=964), 이항 로지스틱 회귀와 매개분석으로 분석하고, 헤드라인 분석(N=3,923)으로 미디어 맥락을 보완했다. 틱톡 이용, 분노·실망·원망, 정치적 불신, 반기성 정당 지지는 정당성 인식을 낮추는 가능성을 높인 반면 기자 신뢰는 이를 낮췄으며, 주류 언론의 절차적 언어 정상화와 개인의 정서적 반응이 분리되는 양상이 나타났다.</t>
+        </is>
+      </c>
+      <c r="J169" s="2" t="inlineStr">
+        <is>
+          <t>On 6 December 2024, Romania’s Constitutional Court annulled the first round of presidential elections, triggering an exceptional crisis of democratic legitimacy in post-communist Europe. While procedurally justified, the decision sparked intense public reactions, both emotional and political. The findings confirm that populist interpretations of institutional actions proliferate in fragmented and emotionalized digital media environments, where distrust is personalized and intensified. Drawing on a nationally representative survey (N = 964), conducted by IRES shortly after the annulment, the study examines how Romanian citizens perceived the legitimacy of the Court’s decision and identifies the key socio-political and media-related factors shaping these perceptions. Binary logistic regression and mediation models were used to assess the drivers of perceived illegitimacy. TikTok use, negative emotions (anger, disappointment, resentment), political distrust, and anti-establishment party support significantly increase the likelihood of viewing the decision as illegitimate, whereas trust in journalists reduces it. The study contributes to the literature on populism as a communicative style and emotional register, showing how legitimacy itself becomes a contested symbol in digital environments marked by personalization, fragmentation, and affective intensification. We argue that institutional legitimacy is no longer grounded solely in procedural legality but is increasingly shaped by emotionally resonant narratives circulating through digital platforms. We complement the survey with a headline-level media analysis (N = 3,923; Dec 2024 - Aug 2025), to serve as a contextual counterfactual: instead of escalating antagonism, mainstream media gradually stabilize institutional language. A keyness comparison shows that the Early window (first 14 days) is driven by institutional/legal terms (CCR, decision, annulment), while the Late window becomes actor-centric (Simion, Antonescu, Ponta, Bolojan). Over time, lexical entropy declines markedly, signaling a standardization of vocabulary around procedural frames rather than escalating antagonism. Taken together, the results point to a decoupling between media normalization and individual affect, suggesting that democratic legitimacy in platformized communication environments is increasingly produced through affective legitimacy rather than procedural authority.</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
@@ -4888,12 +8840,36 @@
           <t>American Journal of Political Science</t>
         </is>
       </c>
-      <c r="E170" s="2" t="inlineStr"/>
-      <c r="F170" s="2" t="inlineStr"/>
-      <c r="G170" s="2" t="inlineStr"/>
-      <c r="H170" s="2" t="inlineStr"/>
-      <c r="I170" s="2" t="inlineStr"/>
-      <c r="J170" s="2" t="inlineStr"/>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>이론/개념</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>개념적 논의</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>Belonging</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>Political Freedom</t>
+        </is>
+      </c>
+      <c r="I170" s="2" t="inlineStr">
+        <is>
+          <t>이 글은 시민의 불완전한 소속감이 형식적 권리 보장 아래에서도 개인의 자유와 집단적·정치적 자유를 어떻게 약화시키는지 개념적으로 논의한다. 소속되지 않은 것으로 인식되는 시민들은 이방인으로 보일 위험을 피하려고 표현과 행동을 제한하며, 그 결과 공적 공간의 다원성·숙의·정치적 행동의 기회가 축소된다고 주장한다.</t>
+        </is>
+      </c>
+      <c r="J170" s="2" t="inlineStr">
+        <is>
+          <t>Abstract This article centers on the concept of “belonging” to argue that belonging and freedom are fundamentally related, and that this relationship cannot be easily captured in formal terms alone. I contend that experiences of incomplete belonging among citizens deserve attention from political science because, in addition to their more obvious challenge to equality, they also erode freedom, even in the context of robust formal guarantees. Citizens perceived as not fully belonging are more likely to eschew behaviors or opinions they know can exacerbate the likelihood of being perceived as interlopers. But although this challenge to individual freedom may be by itself worrisome, I focus on the ways in which some citizens’ unequal belonging undermines collective freedom—what Hannah Arendt calls political freedom—by confining some people's sincere expressions to narrow public spaces, limiting pluralism, and depleting the public space of opportunities for deliberation and political action.</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
@@ -4914,12 +8890,36 @@
           <t>Administration &amp; Society</t>
         </is>
       </c>
-      <c r="E171" s="2" t="inlineStr"/>
-      <c r="F171" s="2" t="inlineStr"/>
-      <c r="G171" s="2" t="inlineStr"/>
-      <c r="H171" s="2" t="inlineStr"/>
-      <c r="I171" s="2" t="inlineStr"/>
-      <c r="J171" s="2" t="inlineStr"/>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>실험</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>기관 패널 자료</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>Political Patronage</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>Managerial Human Capital</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="inlineStr">
+        <is>
+          <t>이 연구는 2017~2021년 이탈리아 공공병원 79곳의 CEO 138명 자료를 이용해 공식적 정치화가 고위 공공경영자의 퇴임에 미치는 영향을 분석했다. 정당 충성도가 관리 역량보다 퇴임을 더 크게 좌우했으며, 정치적 안정성은 조직 성과나 관리 인적자본이 약해도 해임 위험을 낮췄다.</t>
+        </is>
+      </c>
+      <c r="J171" s="2" t="inlineStr">
+        <is>
+          <t>This study investigates how formal politicization shapes the turnover of senior public executives. Using a dataset of 138 CEOs across 79 Italian public hospitals between 2017 and 2021, it examines the relative influence of managerial competence and partisan loyalty on the likelihood of CEO exit. Although both factors affect turnover, partisan loyalty emerges as the primary driver. Political stability significantly lowers CEO dismissal risk, even with weak organizational performance or limited managerial human capital, which plays a secondary role. These findings suggest that NPM reforms have been only partially effective, with patronage practices persisting within a formally meritocratic institutional framework.</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
@@ -4940,12 +8940,36 @@
           <t>Public Management Review</t>
         </is>
       </c>
-      <c r="E172" s="2" t="inlineStr"/>
-      <c r="F172" s="2" t="inlineStr"/>
-      <c r="G172" s="2" t="inlineStr"/>
-      <c r="H172" s="2" t="inlineStr"/>
-      <c r="I172" s="2" t="inlineStr"/>
-      <c r="J172" s="2" t="inlineStr"/>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>서베이</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>횡단면 설문</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>Political Trust</t>
+        </is>
+      </c>
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t>Local Identification</t>
+        </is>
+      </c>
+      <c r="I172" s="2" t="inlineStr">
+        <is>
+          <t>네덜란드 지방자치단체의 2세 이민자를 대상으로 지방정부에 대한 행동 의향(이탈·발언·충성·방임)이 신뢰, 지역 정체성, 차별에 따라 어떻게 달라지는지 설문조사로 분석했다. 충성이 가장 우세했으며, 신뢰·지역 정체성·차별이 지방정부에 대한 이러한 행동 지향을 형성하는 것으로 나타났다.</t>
+        </is>
+      </c>
+      <c r="J172" s="2" t="inlineStr">
+        <is>
+          <t>Public and political debate increasingly problematizes the relationship between second-generation migrants and public authorities, yet little is known about how they evaluate local government. This study examines behavioural intentions towards municipalities – exit, voice, loyalty and neglect – and assesses how trust, local identification and discrimination shape these responses. Using survey data from second-generation migrants in Dutch municipalities, we find loyalty predominates, while trust, local identification and discrimination shape these orientations towards local government. These findings highlight the central role of trust and inclusion in shaping citizen–state relations and demonstrate the value of integrating migrant-centred perspectives into public administration research.</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
@@ -4966,12 +8990,36 @@
           <t>Political Communication</t>
         </is>
       </c>
-      <c r="E173" s="2" t="inlineStr"/>
-      <c r="F173" s="2" t="inlineStr"/>
-      <c r="G173" s="2" t="inlineStr"/>
-      <c r="H173" s="2" t="inlineStr"/>
-      <c r="I173" s="2" t="inlineStr"/>
-      <c r="J173" s="2" t="inlineStr"/>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>질적연구</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>비판적 담론분석</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>Anti-political Space</t>
+        </is>
+      </c>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>Boundary Work</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="inlineStr">
+        <is>
+          <t>정치화된 대중문화 공간의 이용자들이 제도정치와 대중문화를 어떻게 구분하고 정치적 비판에 대응하는지, 2019~2025년 r/BarstoolSports의 비판적 보도 관련 16개 게시물에 대한 비판적 담론분석으로 검토했다. 이용자들은 비판을 근거 없거나 ‘정치에 집착하는 진보적 문화’의 산물로 묘사하며 피해의식과 소외감을 드러냈고, 이러한 경계 설정이 대중문화의 정치적 침투를 막는 동시에 반동적 정치 담론을 비제도적 공간에 재현한다고 주장한다.</t>
+        </is>
+      </c>
+      <c r="J173" s="2" t="inlineStr">
+        <is>
+          <t>Recent scholarship attends to politicized popular cultural spaces. Scarcely understood is how audiences of these spaces contend with this scrutiny. In response, I introduce the concept of anti-political space to describe how fans of politicized media spatially distinguish popular cultural spaces from institutional politics. This is conceptualized through a critical discourse analysis of the official Barstool Sports (Barstool) subreddit from 2019 to 2025, where fans share critical news coverage of Barstool. Across 16 analyzed threads, criticism is rendered unfounded or demonstrative of politically obsessed liberal culture. I argue fans’ varied expressions of victimhood and estrangement, while nominally defending against politicization, showcase how reactionary political discourse appears beyond institutional political spaces. Theoretically, this analysis recognizes how symbolic contests over what constitutes politics occur through boundary work. As the political relevance of popular cultural spaces increases in the contemporary media landscape, this analysis underscores how boundary work defends against the felt intrusion of politics into popular culture. Amid broader sociotechnical changes, I suggest anti-political spaces are poised to be a continued feature of the contemporary media environment.</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
@@ -4992,12 +9040,36 @@
           <t>Political Communication</t>
         </is>
       </c>
-      <c r="E174" s="2" t="inlineStr"/>
-      <c r="F174" s="2" t="inlineStr"/>
-      <c r="G174" s="2" t="inlineStr"/>
-      <c r="H174" s="2" t="inlineStr"/>
-      <c r="I174" s="2" t="inlineStr"/>
-      <c r="J174" s="2" t="inlineStr"/>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>질적연구</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>다중양식 분석</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>Meme Culture</t>
+        </is>
+      </c>
+      <c r="H174" s="2" t="inlineStr">
+        <is>
+          <t>Electoral Mediation</t>
+        </is>
+      </c>
+      <c r="I174" s="2" t="inlineStr">
+        <is>
+          <t>이 연구는 2024년 미국 대선을 앞두고 ‘Kamala is Brat’ 트렌드의 틱톡 밈이 카멀라 해리스의 이미지를 어떻게 해석·재구성했는지를 다중양식 분석으로 탐구했다. 분석 결과, 틱톡의 플랫폼 고유 밈 형식과 대중문화적 상호텍스트성이 정체성 신호와 미학적 대비를 통해 후보자 이미지와 정치 서사를 재구성하는 참여적 선거 매개의 수단으로 작동했다.</t>
+        </is>
+      </c>
+      <c r="J174" s="2" t="inlineStr">
+        <is>
+          <t>In this article, we examine TikTok memes about former Vice president Kamala Harris that circulated through the digital registers of the Charli XCX-inspired “Kamala is Brat” trend. By analyzing the form, function, and affective resonance of these memes, we explore how creators interpreted and reframed Harris’s image leading up to the 2024 U.S. presidential election. Using a multimodal analysis, we introduce a three-layer analytic that distinguishes memetic form, communicative function, and affective character. Our findings show how creators mobilized recognizable meme templates, narrative positioning, and affective cues to recast Harris through identity-signaling and aesthetic contrast to her opponent. We also find that TikTok’s features enabled a pop culture intertextuality in which other viral trends – including the appeal of “it girl” Julia Fox, and the symbolic ambiguity of signifiers ranging from Pulp Fiction, The Matrix, and coconuts – become linked to the candidate. We argue that platform-native meme cultures on TikTok operate as mechanisms of vernacular electoral mediation, enabling creators to reinterpret candidate imagery and political narratives through the aesthetic conventions of platform culture. In doing so, this work demonstrates how participatory meme practices contribute to the symbolic construction of electoral candidates in contemporary digital media environments.</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
@@ -5018,12 +9090,36 @@
           <t>Perspectives on Public Management and Governance</t>
         </is>
       </c>
-      <c r="E175" s="2" t="inlineStr"/>
-      <c r="F175" s="2" t="inlineStr"/>
-      <c r="G175" s="2" t="inlineStr"/>
-      <c r="H175" s="2" t="inlineStr"/>
-      <c r="I175" s="2" t="inlineStr"/>
-      <c r="J175" s="2" t="inlineStr"/>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>이론/개념</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>개념적 모형</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>QuantCrit</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>Critical Race Theory</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="inlineStr">
+        <is>
+          <t>이 글은 인종적 불평등을 간과하거나 재생산할 수 있는 공공행정의 전통적 양적 연구 관행을 어떻게 교정할 수 있는지 검토한다. QuantCrit의 네 가지 원칙을 바탕으로 대표관료제와 공공예산 등 분야에 적용할 수 있는 성찰성·자산 중심 질문·교차성 측정의 설계 방향을 제시하며, 단순한 격차 기록을 넘어 인종화된 통계 논리와 제도적 구조를 분석해야 한다고 주장한다.</t>
+        </is>
+      </c>
+      <c r="J175" s="2" t="inlineStr">
+        <is>
+          <t>Abstract Quantitative methods remain central in public administration research, but without a corrective lens, they can obscure the underlying dynamics they purport to measure. Building on Critical Race Theory’s critique of color-blind objectivity and the emerging QuantCrit literature, this article frames how conventional statistical practices, including feedback-driven policies, fixed classification schemes, and unexamined research standpoints, perpetuate racialized inequities. We position Quantitative Critical Race Theory (QuantCrit) as a methodological corrective, anchored by four tenets: the centrality of racism, the non-neutrality of numbers, the contingency of categories, and the necessity to incorporate marginalized voices. Applying these principles, we trace QuantCrit’s evolution, illustrate its relevance across public administration subfields (notably representative bureaucracy and public budgeting), and provide a practical roadmap for embedding reflexivity, asset-focused questions, and intersectional measures into quantitative designs. By shifting from mere demographic tabulation to interrogating the statistical logics that entrench racial inequities, QuantCrit empowers public administration scholars to move beyond documenting disparities and toward dismantling the institutional structures of systemic racism.</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
@@ -5044,17 +9140,41 @@
           <t>Public Opinion Quarterly</t>
         </is>
       </c>
-      <c r="E176" s="2" t="inlineStr"/>
-      <c r="F176" s="2" t="inlineStr"/>
-      <c r="G176" s="2" t="inlineStr"/>
-      <c r="H176" s="2" t="inlineStr"/>
-      <c r="I176" s="2" t="inlineStr"/>
-      <c r="J176" s="2" t="inlineStr"/>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>혼합방법론</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>민감도 분석</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>Nonignorable Response</t>
+        </is>
+      </c>
+      <c r="H176" s="2" t="inlineStr">
+        <is>
+          <t>Survey Weighting</t>
+        </is>
+      </c>
+      <c r="I176" s="2" t="inlineStr">
+        <is>
+          <t>대표성이 낮은 표본에서 발생하는 비무시적 응답 편향에 대한 불확실성을 어떻게 평가할지 분석하기 위해, 연구진은 설문 가중치에 대한 민감도 분석 틀을 제시하고 코로나19 백신 접종률 설문에 적용했다. 그 결과, 표준오차는 더 작더라도 대표성이 낮은 표본을 사용한 대규모 조사가 대표성이 높은 소규모 조사보다 잠재적 편향에 더 취약할 수 있음을 보였다.</t>
+        </is>
+      </c>
+      <c r="J176" s="2" t="inlineStr">
+        <is>
+          <t>Abstract Standard statistical uncertainty measures, like standard errors, are unable to quantify the uncertainty from an unrepresentative sampling process. Existing work has highlighted the potential risk in large datasets, in which larger surveys resulting in more precise estimates can misleadingly overstate the degree of confidence in biased survey results. In this research note, we introduce a sensitivity framework for researchers to transparently summarize their uncertainty to a biased sampling process. We illustrate the framework on a set of COVID-19 vaccine surveys, and show that had researchers conducted a sensitivity analysis, they would have found that despite substantially smaller standard errors, the larger surveys conducted on less representative samples were more susceptible to potential bias than smaller surveys conducted on more representative samples. We argue that these summary measures should be routinely reported to accurately quantify uncertainty to potential bias, allowing researchers to assess their confidence in results, in large and small datasets.</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>Alastair Stark; Hridesh Gajural; Jack Corbett; Dennis C Grube; Heather Lovell; Rodney Scott</t>
+          <t>Alastair Stark; Hridesh Gajural; Jack Corbett; Dennis C Grube; Heather Lovell; Rodney J Scott</t>
         </is>
       </c>
       <c r="B177" s="2" t="n">
@@ -5062,7 +9182,7 @@
       </c>
       <c r="C177" s="3" t="inlineStr">
         <is>
-          <t>Institutional Amnesia and Public Administration: Does History Repeat?</t>
+          <t>Institutional amnesia and public administration: does history repeat?</t>
         </is>
       </c>
       <c r="D177" s="2" t="inlineStr">
@@ -5070,12 +9190,36 @@
           <t>Journal of Public Administration Research and Theory</t>
         </is>
       </c>
-      <c r="E177" s="2" t="inlineStr"/>
-      <c r="F177" s="2" t="inlineStr"/>
-      <c r="G177" s="2" t="inlineStr"/>
-      <c r="H177" s="2" t="inlineStr"/>
-      <c r="I177" s="2" t="inlineStr"/>
-      <c r="J177" s="2" t="inlineStr"/>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>혼합방법론</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>순차 혼합</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>Institutional Amnesia</t>
+        </is>
+      </c>
+      <c r="H177" s="2" t="inlineStr">
+        <is>
+          <t>Institutional Memory</t>
+        </is>
+      </c>
+      <c r="I177" s="2" t="inlineStr">
+        <is>
+          <t>이 연구는 제도적 기억의 부재인 ‘제도적 망각’이 공공기관에서 행정의 역사를 어떻게 반복시키는지 설명하고자, 호주·뉴질랜드·영국 공공서비스의 설문조사(n=1,608)와 인터뷰(n=75)를 활용한 순차적 혼합방법을 적용했다. 제도적 망각은 아이디어와 관행의 재순환, 정보탐색 과정의 비효율적 재학습을 초래하지만, 역사적 문제 해결에 도움이 되는 의사결정 환경도 조성할 수 있어 역사 반복은 부정적·긍정적 방식 모두로 나타났다.</t>
+        </is>
+      </c>
+      <c r="J177" s="2" t="inlineStr">
+        <is>
+          <t>Abstract Existing research suggests that a lack of institutional memory causes history to repeat in problematic ways within public administration agencies. However, this claim has not been well supported by theory or data that illuminate the process and effects of history repeating. To remedy this, the nascent concept of institutional amnesia is presented here as a means of theorizing repetitions of public administrative history. A sequential explanatory mixed method research design uses quantitative survey data (n = 1608) and qualitative interview data (n = 75) generated in the public services of Australia, New Zealand, and the UK to show how institutional amnesia can lead to the recycling of ideas and practices, the inefficient relearning of information-seeking processes and the delivery of conducive decision-making environments that can help address historical problems. These findings draw attention to the fact that administrative history does indeed repeat in public agencies because of institutional amnesia, but that it does so in positive as well as negative ways.</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
@@ -5096,12 +9240,36 @@
           <t>The American Review of Public Administration</t>
         </is>
       </c>
-      <c r="E178" s="2" t="inlineStr"/>
-      <c r="F178" s="2" t="inlineStr"/>
-      <c r="G178" s="2" t="inlineStr"/>
-      <c r="H178" s="2" t="inlineStr"/>
-      <c r="I178" s="2" t="inlineStr"/>
-      <c r="J178" s="2" t="inlineStr"/>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>질적연구</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>종단 단일사례</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>Institutional Entrepreneurship</t>
+        </is>
+      </c>
+      <c r="H178" s="2" t="inlineStr">
+        <is>
+          <t>Co-creation</t>
+        </is>
+      </c>
+      <c r="I178" s="2" t="inlineStr">
+        <is>
+          <t>노르웨이 대규모 지방자치단체의 보건의료 서비스를 대상으로 한 종단적 단일사례연구는 일선 공공관리자가 어떻게 제도적 기업가가 되는지를 분석했다. 이들은 외부·내부 변화를 감지하고 정당화·협상한 뒤, 주민 및 부문 간 파트너십을 통한 공동창조와 일상 업무·팀 구조·역할의 제도화를 통해 제약된 자원 속에서도 혁신을 새로운 제도적 배열로 정착시켰다.</t>
+        </is>
+      </c>
+      <c r="J178" s="2" t="inlineStr">
+        <is>
+          <t>How do front-line public managers become institutional entrepreneurs? This article answers that question through a longitudinal single-case study of a large Norwegian municipality's healthcare services. Drawing on organizational institutionalism and public management scholarship, I first show how front-line public managers initiate divergent change by leveraging a sensing–legitimation nexus. They detect external and internal triggers, frame the need for change, and secure political, administrative, and professional support through direct negotiation and compelling operational narratives. They then act as co-creation catalysts, engaging residents and building cross-sector partnerships to adapt service designs and mobilize scarce resources. Finally, they institutionalize transformative public healthcare delivery by embedding routines in daily operations, formalizing interdisciplinary team structures, clarifying roles, and demonstrating performance gains. Evidence from two innovation projects shows that resource-constrained, non-heroic actors can disrupt entrenched practices and stabilize innovation as the new institutional arrangement. The study contributes to institutional entrepreneurship theory by positioning front-line public managers as credible entrepreneurial agents and by identifying co-creation as a core mechanism of public sector institutional change.</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
@@ -5122,12 +9290,36 @@
           <t>The American Review of Public Administration</t>
         </is>
       </c>
-      <c r="E179" s="2" t="inlineStr"/>
-      <c r="F179" s="2" t="inlineStr"/>
-      <c r="G179" s="2" t="inlineStr"/>
-      <c r="H179" s="2" t="inlineStr"/>
-      <c r="I179" s="2" t="inlineStr"/>
-      <c r="J179" s="2" t="inlineStr"/>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>서베이</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>가중 회귀·PSM</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t>Civic Engagement</t>
+        </is>
+      </c>
+      <c r="H179" s="2" t="inlineStr">
+        <is>
+          <t>PSM</t>
+        </is>
+      </c>
+      <c r="I179" s="2" t="inlineStr">
+        <is>
+          <t>이 연구는 2023년 CPS 자원봉사·시민생활 보충조사를 활용해 정부 수준별 공공부문 종사자와 다른 시민의 시민참여가 어떻게 다른지 분석했다. 가중 회귀와 성향점수매칭 결과, 특히 지방정부 종사자는 투표·자원봉사 같은 제도적 참여는 더 많지만 정치적 대화·사회적 교류 같은 비공식 참여는 더 적은 독특한 참여 양상을 보였다.</t>
+        </is>
+      </c>
+      <c r="J179" s="2" t="inlineStr">
+        <is>
+          <t>Research on public service motivation consistently finds that public employees volunteer and contribute more than their private sector counterparts, yet less is known about how engagement varies across behavioral domains and institutional contexts. This study examines how civic engagement is structured among public employees compared to other citizens, with particular attention to variation across levels of government. Using the 2023 CPS Volunteering and Civic Life Supplement, the analysis constructs multidimensional measures across four domains: political participation, civic involvement, political expression, and social connectedness. Weighted regressions and propensity score matching show that public employees, especially at the local level, exhibit a distinct civic profile characterized by greater involvement in institutional forms of participation such as voting and volunteering, but lower engagement in informal activities such as political discussion and social interaction. These patterns persist after accounting for observable characteristics and suggest that public employment channels participation into specific forms rather than uniformly increasing overall engagement, with implications for how civil service reforms may alter the civic composition of local communities.</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
@@ -5148,12 +9340,36 @@
           <t>Public Management Review</t>
         </is>
       </c>
-      <c r="E180" s="2" t="inlineStr"/>
-      <c r="F180" s="2" t="inlineStr"/>
-      <c r="G180" s="2" t="inlineStr"/>
-      <c r="H180" s="2" t="inlineStr"/>
-      <c r="I180" s="2" t="inlineStr"/>
-      <c r="J180" s="2" t="inlineStr"/>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>실험</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>설문 실험</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t>Nudge</t>
+        </is>
+      </c>
+      <c r="H180" s="2" t="inlineStr">
+        <is>
+          <t>Trust in Government</t>
+        </is>
+      </c>
+      <c r="I180" s="2" t="inlineStr">
+        <is>
+          <t>두 온라인 실험(미국 참가자 3,010명)을 통해 시민들이 선택구조로 제한된 합리성을 활용하는 ‘넛지’와 숙의를 통해 성찰을 촉진하는 ‘싱크’ 중 무엇을 더 지지하는지, 그리고 정부 신뢰가 이러한 선호에 미치는 영향을 검토했다. 시민들은 넛지보다 싱크를 더 지지했으며, 정부 신뢰를 높이는 것은 싱크보다 넛지 지지에 더 큰 영향을 미쳤지만, 넛지 채택 자체는 싱크와 비교해 정부 신뢰에 뚜렷한 영향을 주지 않았다.</t>
+        </is>
+      </c>
+      <c r="J180" s="2" t="inlineStr">
+        <is>
+          <t>We explore citizens’ support for behavioral interventions by distinguishing interventions that exploit citizens’ bounded rationality through choice architecture (Nudge) from those that challenge bounded rationality by promoting reflection through deliberative forums (Think). We also examine the role of trust in government in shaping these preferences. Findings from two experiments involving 3,010 US participants show that citizens are more willing to support Think rather than Nudge. Whereas the adoption of Nudge, as compared to Think, does not seem to influence trust in government, encouraging higher levels of trust in government has a stronger effect on support for Nudge than for Think.</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
@@ -5174,12 +9390,36 @@
           <t>Political Communication</t>
         </is>
       </c>
-      <c r="E181" s="2" t="inlineStr"/>
-      <c r="F181" s="2" t="inlineStr"/>
-      <c r="G181" s="2" t="inlineStr"/>
-      <c r="H181" s="2" t="inlineStr"/>
-      <c r="I181" s="2" t="inlineStr"/>
-      <c r="J181" s="2" t="inlineStr"/>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>서베이</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>3시점 패널</t>
+        </is>
+      </c>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t>Political Knowledge</t>
+        </is>
+      </c>
+      <c r="H181" s="2" t="inlineStr">
+        <is>
+          <t>Opinion Leadership Gratifications</t>
+        </is>
+      </c>
+      <c r="I181" s="2" t="inlineStr">
+        <is>
+          <t>16~30세 청년을 대상으로 3시점 패널조사를 실시해 정치인·동료·인플루언서 등 소셜미디어 정보 큐레이터에 대한 노출이 시사 지식 습득과 어떻게 관련되는지, 그리고 의견지도자 보상 인식이 매개하는지를 분석했다. 모든 큐레이터의 정치 콘텐츠 노출은 같은 시점의 의견지도자 보상 인식 증가와 관련됐지만, 시간에 따른 개인 내 간접 학습 효과는 대체로 미약했으며, 전국 선거 기간에만 동료 콘텐츠에서 얻은 의견지도자 보상 인식이 객관적 정치 지식의 평소보다 큰 증가와 연결됐다.</t>
+        </is>
+      </c>
+      <c r="J181" s="2" t="inlineStr">
+        <is>
+          <t>Whether youth can gain political knowledge through social media is long debated. Existing research has insufficiently accounted for different curating actors of political information, an indirect learning logic, and within-person changes. To fill these gaps, we conducted a large-scale three-wave panel study among 16- to 30-year-olds (NT3 = 2276) to examine how exposure to different social media actors such as politicians, peers, or influencers relates to the acquisition of current affairs knowledge over time. We investigated perceived opinion leadership gratifications as a novel underlying mechanism in this process. While increased exposure to all curating actors’ political content was related to higher opinion leadership gratifications in the same wave, we found little indirect learning effects over time on the within-person level through obtained gratifications. This association emerged only during the national election period, when perceived opinion leadership gratifications from peers’ political content were linked to above-usual gains in objective political knowledge over time.</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
@@ -5200,12 +9440,36 @@
           <t>Public Administration Review</t>
         </is>
       </c>
-      <c r="E182" s="2" t="inlineStr"/>
-      <c r="F182" s="2" t="inlineStr"/>
-      <c r="G182" s="2" t="inlineStr"/>
-      <c r="H182" s="2" t="inlineStr"/>
-      <c r="I182" s="2" t="inlineStr"/>
-      <c r="J182" s="2" t="inlineStr"/>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>이론/개념</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>개념적 모형</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t>Ethical Pluralism</t>
+        </is>
+      </c>
+      <c r="H182" s="2" t="inlineStr">
+        <is>
+          <t>Collaborative Governance</t>
+        </is>
+      </c>
+      <c r="I182" s="2" t="inlineStr">
+        <is>
+          <t>이 글은 참여·협력적 거버넌스에서 민주적 정당성이라는 호소가 특정한 정의관에 대한 암묵적 약속을 포함한다는 점을 문제로 제기하고, 민주주의 대신 정의를 핵심 규범적 기준으로 명확히 이론화할 것을 제안한다. 거버넌스 설계의 투입·과정·산출 차원을 각각 대표성·절차·분배 정의에 연결하는 분석 틀을 제시하며, 정의 원칙의 다원성과 충돌이 서로 다른 설계 딜레마와 상충을 낳는다고 주장한다.</t>
+        </is>
+      </c>
+      <c r="J182" s="2" t="inlineStr">
+        <is>
+          <t>ABSTRACT Participatory and collaborative governance (P&amp;CG) is widely celebrated as an institutional vehicle for democratizing public decision‐making by inviting affected stakeholders into inclusive and deliberative policy processes. This essay argues that underlying appeals to democratic legitimacy in P&amp;CG are tacit commitments to specific (and often ideologically bounded) conceptions of justice. Democracy, far from being normatively univocal, encompasses competing justice principles that yield divergent and sometimes incompatible design imperatives. In response, this essay calls for a shift from vague democratic invocations to a more precise theorization of justice as the operative normative currency in P&amp;CG. To this end, the essay outlines an analytical framework that maps three core dimensions of governance design (input, process, and output) onto corresponding domains of justice: representational, procedural, and distributive. Systematically unpacking the plural and conflicting ethical principles within each domain shows how different principles of justice produce distinct governance dilemmas and trade‐offs.</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
@@ -5226,12 +9490,36 @@
           <t>Public Administration Review</t>
         </is>
       </c>
-      <c r="E183" s="2" t="inlineStr"/>
-      <c r="F183" s="2" t="inlineStr"/>
-      <c r="G183" s="2" t="inlineStr"/>
-      <c r="H183" s="2" t="inlineStr"/>
-      <c r="I183" s="2" t="inlineStr"/>
-      <c r="J183" s="2" t="inlineStr"/>
+      <c r="E183" s="2" t="inlineStr">
+        <is>
+          <t>실험</t>
+        </is>
+      </c>
+      <c r="F183" s="2" t="inlineStr">
+        <is>
+          <t>설문 실험</t>
+        </is>
+      </c>
+      <c r="G183" s="2" t="inlineStr">
+        <is>
+          <t>Blame Attribution</t>
+        </is>
+      </c>
+      <c r="H183" s="2" t="inlineStr">
+        <is>
+          <t>Causal Responsibility</t>
+        </is>
+      </c>
+      <c r="I183" s="2" t="inlineStr">
+        <is>
+          <t>영국 지방 폐기물 수거 실패를 다룬 설문 실험과 인과적 매개분석을 통해, 공공서비스 위탁이 정치인의 서비스 제공 통제력에 대한 인식을 낮춰 비난을 주로 감소시키는지, 그리고 서비스 품질 확보 의무 인식이 이를 매개하는지를 검토했다. 위탁은 통제력 인식을 낮추는 경로를 통해 비난을 줄였지만, 기능적 책임 의무 인식을 통한 매개에 대한 강한 증거는 없었다.</t>
+        </is>
+      </c>
+      <c r="J183" s="2" t="inlineStr">
+        <is>
+          <t>ABSTRACT A growing body of experimental public administration research examines how structural arrangements in public services, such as delegating service delivery to public or private actors, shape citizens' blame attributions for service failures. However, the mechanisms underlying these attributions are less well understood. This article investigates two mechanisms, focusing on the mediating roles of citizens' perceptions of politicians' causal responsibility (perceived control over service delivery) and functional responsibility (perceived duty to ensure service quality). A UK‐based survey experiment on local waste collection failures tests these mechanisms using causal mediation analysis. The results show higher levels of delegation reduce blame primarily by lowering perceptions of politicians' control over service delivery. In contrast, there is no strong evidence of mediation through perceived duty, suggesting that role‐based expectations of functional responsibility are more resistant to change. These findings provide new insight into how different public service delivery methods influence blame attribution for service performance.</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
@@ -5252,12 +9540,36 @@
           <t>The American Review of Public Administration</t>
         </is>
       </c>
-      <c r="E184" s="2" t="inlineStr"/>
-      <c r="F184" s="2" t="inlineStr"/>
-      <c r="G184" s="2" t="inlineStr"/>
-      <c r="H184" s="2" t="inlineStr"/>
-      <c r="I184" s="2" t="inlineStr"/>
-      <c r="J184" s="2" t="inlineStr"/>
+      <c r="E184" s="2" t="inlineStr">
+        <is>
+          <t>혼합방법론</t>
+        </is>
+      </c>
+      <c r="F184" s="2" t="inlineStr">
+        <is>
+          <t>단일 사례 혼합</t>
+        </is>
+      </c>
+      <c r="G184" s="2" t="inlineStr">
+        <is>
+          <t>Street-Level Discretion</t>
+        </is>
+      </c>
+      <c r="H184" s="2" t="inlineStr">
+        <is>
+          <t>Policy Ambiguity</t>
+        </is>
+      </c>
+      <c r="I184" s="2" t="inlineStr">
+        <is>
+          <t>이스라엘 국립 초등학교 교장에 대한 단일 사례 혼합방법 연구를 통해, 종교 정책 집행에서 일선 관리자의 재량이 언제 사회적 만족과 결속을 높이는지 분석했다. 정책이 모호하고 유연하며 사회집단 간 논쟁의 대상이고, 관리자가 이용자 선호에 응답할 때 재량의 긍정적 효과가 커졌으며, 관리자의 개인 이념이 이용자 태도·기대와 일치할 때 서비스 만족도도 높아졌다.</t>
+        </is>
+      </c>
+      <c r="J184" s="2" t="inlineStr">
+        <is>
+          <t>This study explores the intersection of religion and state through a single-case, mixed-methods research design, focusing on Israeli state elementary school principals, who administer religious directives embedded in state legislation. We ask: Under what conditions street-level managers’ discretion in policy implementation increases social satisfaction and cohesion? We argue that such discretion increases social satisfaction and cohesion under the following conditions: (1) When state policies are explicitly or implicitly vague and flexible, (2) When official policy is contested among societal groups, and (3) When street-level managers opt to respond to client preferences. In addition, we suggest that public satisfaction with the resulted public services increases when a manager's personal ideology aligns with client attitudes and expectations. The study demonstrates how principals exercise significant discretion in implementing religious policy and thus contributes to broader public administration literature by highlighting the role of street-level managers in navigating policy ambiguity, while mediating societal tensions.</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
@@ -5278,12 +9590,32 @@
           <t>American Political Science Review</t>
         </is>
       </c>
-      <c r="E185" s="2" t="inlineStr"/>
-      <c r="F185" s="2" t="inlineStr"/>
-      <c r="G185" s="2" t="inlineStr"/>
+      <c r="E185" s="2" t="inlineStr">
+        <is>
+          <t>방법 미상</t>
+        </is>
+      </c>
+      <c r="F185" s="2" t="inlineStr">
+        <is>
+          <t>확인 불가</t>
+        </is>
+      </c>
+      <c r="G185" s="2" t="inlineStr">
+        <is>
+          <t>Homonationalism</t>
+        </is>
+      </c>
       <c r="H185" s="2" t="inlineStr"/>
-      <c r="I185" s="2" t="inlineStr"/>
-      <c r="J185" s="2" t="inlineStr"/>
+      <c r="I185" s="2" t="inlineStr">
+        <is>
+          <t>초록이 제공되지 않아 연구 질문, 접근법, 주요 결과를 확인할 수 없다. 따라서 해당 교정 논문의 내용에 근거한 요약을 제시할 수 없다.</t>
+        </is>
+      </c>
+      <c r="J185" s="2" t="inlineStr">
+        <is>
+          <t>//static.cambridge.org/content/id/urn%3Acambridge.org%3Aid%3Aarticle%3AS000305542610197X/resource/name/firstPage-pdf-S000305542610197Xa.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
@@ -5304,12 +9636,36 @@
           <t>Political Communication</t>
         </is>
       </c>
-      <c r="E186" s="2" t="inlineStr"/>
-      <c r="F186" s="2" t="inlineStr"/>
-      <c r="G186" s="2" t="inlineStr"/>
-      <c r="H186" s="2" t="inlineStr"/>
-      <c r="I186" s="2" t="inlineStr"/>
-      <c r="J186" s="2" t="inlineStr"/>
+      <c r="E186" s="2" t="inlineStr">
+        <is>
+          <t>혼합방법론</t>
+        </is>
+      </c>
+      <c r="F186" s="2" t="inlineStr">
+        <is>
+          <t>미디어·검색자료 분석</t>
+        </is>
+      </c>
+      <c r="G186" s="2" t="inlineStr">
+        <is>
+          <t>Media Coverage</t>
+        </is>
+      </c>
+      <c r="H186" s="2" t="inlineStr">
+        <is>
+          <t>Information Seeking</t>
+        </is>
+      </c>
+      <c r="I186" s="2" t="inlineStr">
+        <is>
+          <t>주(州) 고등법원 후보자에 대한 언론 보도가 시민의 구글 정보탐색을 촉진하는지 2004~2020년 AP 보도와 Google Trends 자료로 분석한 결과, 보도량이 많을수록 정보탐색이 증가했다. 특히 재판 외 행동에 관한 보도가 효과가 컸으며, 비정당 선출 방식에서는 보도 유형과 관계없이 정보탐색이 촉진된 반면, 현직자의 선거운동 보도는 이를 늘렸지만 직무수행 보도는 그렇지 않았다.</t>
+        </is>
+      </c>
+      <c r="J186" s="2" t="inlineStr">
+        <is>
+          <t>Does news coverage stimulate curiosity in state high court candidates? Data compiled from the Associated Press and Google Trends from 2004 to 2020 suggest that as media coverage increases on candidates, people are more likely to seek information about the candidates on Google. Furthermore, reports about the candidates’ off-bench behavior are more likely to promote information-seeking behavior. State judicial selection method also plays a crucial role in information-seeking behavior, as coverage of nonpartisan justices motivates information-seeking regardless of the type of coverage. This study suggests that information about the campaigns of incumbent officeholders increases information-seeking behavior, but information about their job performance does not.</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
@@ -5330,12 +9686,36 @@
           <t>American Journal of Political Science</t>
         </is>
       </c>
-      <c r="E187" s="2" t="inlineStr"/>
-      <c r="F187" s="2" t="inlineStr"/>
-      <c r="G187" s="2" t="inlineStr"/>
-      <c r="H187" s="2" t="inlineStr"/>
-      <c r="I187" s="2" t="inlineStr"/>
-      <c r="J187" s="2" t="inlineStr"/>
+      <c r="E187" s="2" t="inlineStr">
+        <is>
+          <t>혼합방법론</t>
+        </is>
+      </c>
+      <c r="F187" s="2" t="inlineStr">
+        <is>
+          <t>네트워크 모형 검증</t>
+        </is>
+      </c>
+      <c r="G187" s="2" t="inlineStr">
+        <is>
+          <t>Policy Learning</t>
+        </is>
+      </c>
+      <c r="H187" s="2" t="inlineStr">
+        <is>
+          <t>Coalition Formation</t>
+        </is>
+      </c>
+      <c r="I187" s="2" t="inlineStr">
+        <is>
+          <t>정책 논쟁에서 행위자들이 다른 행위자의 정책 신념을 채택하는 방식이 연합의 형성과 유지 및 정책학습에 어떻게 작용하는지를 이론화하고, 시간적 네트워크 의존성을 반영한 미시 수준 경험자료로 검증했다. 연합 내부의 단서 활용(bonding), 외부 신념 탐색(bridging), 연합 간 반발(repulsion)이 상호보완적으로 신념체계를 형성하고 양극화를 강화하는 것으로 제시된다.</t>
+        </is>
+      </c>
+      <c r="J187" s="2" t="inlineStr">
+        <is>
+          <t>Abstract Political actors form coalitions around their joint normative beliefs in order to influence the policy process on contentious issues such as climate change or population aging. Policy process theory maintains that learning within and across coalitions is a central predictor of policy change but has yet to explain how policy learning works. This article explains the formation and maintenance of coalitions by focusing on the ways actors adopt policy beliefs from other actors in policy debates. A policy debate is a complex social system in which temporal network dependence guides how actors contribute ideological statements. Belief adoption matters in three complementary ways: bonding , which exploits cues within coalitions; bridging , which explores new beliefs outside one's perimeter; and repulsion , which reinforces polarization between coalitions and cements their belief systems. We formalize this theory of endogenous coalition formation in policy debates and test it on a micro‐level empirical data set.</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
@@ -5356,12 +9736,36 @@
           <t>American Journal of Political Science</t>
         </is>
       </c>
-      <c r="E188" s="2" t="inlineStr"/>
-      <c r="F188" s="2" t="inlineStr"/>
-      <c r="G188" s="2" t="inlineStr"/>
-      <c r="H188" s="2" t="inlineStr"/>
-      <c r="I188" s="2" t="inlineStr"/>
-      <c r="J188" s="2" t="inlineStr"/>
+      <c r="E188" s="2" t="inlineStr">
+        <is>
+          <t>이론/개념</t>
+        </is>
+      </c>
+      <c r="F188" s="2" t="inlineStr">
+        <is>
+          <t>개념적 모형</t>
+        </is>
+      </c>
+      <c r="G188" s="2" t="inlineStr">
+        <is>
+          <t>Gerrymandering</t>
+        </is>
+      </c>
+      <c r="H188" s="2" t="inlineStr">
+        <is>
+          <t>Durable Majorities</t>
+        </is>
+      </c>
+      <c r="I188" s="2" t="inlineStr">
+        <is>
+          <t>이 연구는 야당의 주 의회 다수당 승리 가능성을 낮추는 ‘지속 가능한 다수 게리맨더링’을 개념화하고, 이를 추정하는 도구로 선거구 재획정이 다수당의 형성과 지속에 미치는 영향을 분석한다. 제약이 없으면 모든 주에서 한 정당이 예상 가능한 미래 선거 변동에도 견디는 의석 다수를 만들 수 있지만, 실제 확정된 지도는 지리, 유권자 당파성, 주 차원의 지침 때문에 덜 지속적인 것으로 나타난다.</t>
+        </is>
+      </c>
+      <c r="J188" s="2" t="inlineStr">
+        <is>
+          <t>Abstract We develop the concept of, and estimation tools for, durable majority gerrymanders : electoral district maps drawn to reduce an opposing political party's probability of winning a majority in a legislative chamber. Directly interpretable, forward‐looking, and motivated by the democratic principle that a party in power should have some chance of losing it, this measure provides new insights into the role of redistricting in state legislative elections. We show that, when map drawers are unconstrained, the ability to create durable majorities is so widespread that at least one party in every state can draw a map where a majority of legislative districts withstand almost any likely future electoral swing. Enacted maps are less durable due to a combination of underlying geography, voter partisanship, and state‐level guidelines. This paper provides the theoretical framework and empirical tools to understand which gerrymandered maps enable state‐level majorities to emerge and to endure.</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
@@ -5382,12 +9786,36 @@
           <t>Governance</t>
         </is>
       </c>
-      <c r="E189" s="2" t="inlineStr"/>
-      <c r="F189" s="2" t="inlineStr"/>
-      <c r="G189" s="2" t="inlineStr"/>
-      <c r="H189" s="2" t="inlineStr"/>
-      <c r="I189" s="2" t="inlineStr"/>
-      <c r="J189" s="2" t="inlineStr"/>
+      <c r="E189" s="2" t="inlineStr">
+        <is>
+          <t>혼합방법론</t>
+        </is>
+      </c>
+      <c r="F189" s="2" t="inlineStr">
+        <is>
+          <t>순차 혼합</t>
+        </is>
+      </c>
+      <c r="G189" s="2" t="inlineStr">
+        <is>
+          <t>Co-production</t>
+        </is>
+      </c>
+      <c r="H189" s="2" t="inlineStr">
+        <is>
+          <t>Citizen Agency</t>
+        </is>
+      </c>
+      <c r="I189" s="2" t="inlineStr">
+        <is>
+          <t>상하이의 정부 촉진 시민 중심 공동생산에서 시민의 신뢰, 공공서비스 지향 동기, 공동생산 효능감이 가치 창출과 어떤 관련이 있으며 제도적 환경이 이를 어떻게 조건화하는지, 246건의 인터뷰와 1,476명 주민 설문을 활용한 혼합방법으로 분석했다. 시민의 인지적 요인은 가치 창출과 긍정적으로 관련되지만, 경직된 공식 제도와 과도한 제도화는 시민 주체성을 제약하고 사회적 밀도는 신뢰가 실질적 성과로 이어지는 것을 약화시킬 수 있다고 밝혔다.</t>
+        </is>
+      </c>
+      <c r="J189" s="2" t="inlineStr">
+        <is>
+          <t>ABSTRACT Public service co‐production is often framed as a means of creating public value, yet its dynamics are complex when citizen‐led participation is catalyzed by strong public institutions. This mixed‐methods study examines government‐catalyzed, citizen‐centric co‐production in Shanghai, China, where the state provides institutional support, policy legitimacy, and infrastructure while citizens undertake much of the work of deliberation, coordination, and implementation. Drawing on 246 interviews and survey data from 1476 residents involved in community new infrastructure projects, we examine how citizen trust, public‐service‐oriented motivation, and perceived co‐production efficacy are associated with process and outcome value creation, and how perceived institutional settings condition these relationships. The findings show that citizen cognitive factors are positively associated with value creation, while stronger perceived institutional settings can negatively moderate these relationships. Recursive qualitative analysis suggests two mechanisms that help interpret this pattern: formal rigidity may crowd out citizen agency in the co‐production process, while informal social density may generate lock‐in effects that weaken the translation of trust into substantive outcomes. The study contributes to co‐production and institutional theory by specifying the boundary conditions under which institutional support becomes over‐institutionalization. Effective co‐production requires not less government, but strong enabling support at the initiation stage combined with greater local discretion, participatory rule revision, and flexible enforcement.</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
@@ -5408,12 +9836,36 @@
           <t>Public Administration</t>
         </is>
       </c>
-      <c r="E190" s="2" t="inlineStr"/>
-      <c r="F190" s="2" t="inlineStr"/>
-      <c r="G190" s="2" t="inlineStr"/>
-      <c r="H190" s="2" t="inlineStr"/>
-      <c r="I190" s="2" t="inlineStr"/>
-      <c r="J190" s="2" t="inlineStr"/>
+      <c r="E190" s="2" t="inlineStr">
+        <is>
+          <t>질적연구</t>
+        </is>
+      </c>
+      <c r="F190" s="2" t="inlineStr">
+        <is>
+          <t>민족지적 사례연구</t>
+        </is>
+      </c>
+      <c r="G190" s="2" t="inlineStr">
+        <is>
+          <t>Public Values</t>
+        </is>
+      </c>
+      <c r="H190" s="2" t="inlineStr">
+        <is>
+          <t>Public-Private Partnerships</t>
+        </is>
+      </c>
+      <c r="I190" s="2" t="inlineStr">
+        <is>
+          <t>네덜란드 대학병원 영상의학과에서 채택 결정 이후 구현 이전의 AI 도입 과정을 민족지적 현장연구, 인터뷰, 문서분석으로 분석해 공공가치가 도입 과정과 재귀적으로 상호작용하며, 도구적 가치와 내재적 가치가 조정된다는 점을 밝혔다. 또한 하향식 도입 결정과 민관협력에서 공공가치의 인식 및 보호가 중요함을 제시했다.</t>
+        </is>
+      </c>
+      <c r="J190" s="2" t="inlineStr">
+        <is>
+          <t>ABSTRACT Artificial Intelligence (AI) is adopted in public organizations as a transformative innovation, yet how value prioritizations unfold in AI adoption processes remains underexplored. Therefore, we ask: How do public values unfold in AI adoption processes in public organizations? We conducted a qualitative case study of an AI adoption process at the radiology department of a Dutch academic hospital after the decision to adopt is made and before implementation, using ethnographic fieldwork, interviews, and document analysis. Our findings highlight how public values and the AI adoption process are balanced in the transition from the initiation to the implementation stage. We find a recursive relationship between public values and the AI adoption process. We show an interplay of instrumental and intrinsic values. We highlight the importance of top‐down adoption decisions for how public values are perceived, and we show the importance of public organizations ensuring public values are safeguarded in public‐private partnerships.</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
@@ -5434,12 +9886,36 @@
           <t>Political Psychology</t>
         </is>
       </c>
-      <c r="E191" s="2" t="inlineStr"/>
-      <c r="F191" s="2" t="inlineStr"/>
-      <c r="G191" s="2" t="inlineStr"/>
-      <c r="H191" s="2" t="inlineStr"/>
-      <c r="I191" s="2" t="inlineStr"/>
-      <c r="J191" s="2" t="inlineStr"/>
+      <c r="E191" s="2" t="inlineStr">
+        <is>
+          <t>실험</t>
+        </is>
+      </c>
+      <c r="F191" s="2" t="inlineStr">
+        <is>
+          <t>사전등록 설문실험</t>
+        </is>
+      </c>
+      <c r="G191" s="2" t="inlineStr">
+        <is>
+          <t>Sunk-Cost Effect</t>
+        </is>
+      </c>
+      <c r="H191" s="2" t="inlineStr">
+        <is>
+          <t>Commitment</t>
+        </is>
+      </c>
+      <c r="I191" s="2" t="inlineStr">
+        <is>
+          <t>세 차례 사전등록 실험(N=1,462)에서 정치 지도자에 대한 유권자 평가가 매몰비용보다 사업 지속·중단 결정, 선거 공약, 과거 투표 단서에 어떻게 반응하는지 분석했다. 사업 지속은 헌신의 신호로 긍정적으로 평가된 반면 중단은 헌신 위반으로 평가를 낮췄으며, 매몰비용 효과와 공약·과거 투표의 독립적 영향은 지지되지 않았다.</t>
+        </is>
+      </c>
+      <c r="J191" s="2" t="inlineStr">
+        <is>
+          <t>Abstract Do sunk costs shape how voters judge political leaders, or do reputational signals carried by current choices dominate? Across three preregistered experiments (total N = 1462) using vignettes about a national rail project, we orthogonally manipulated sunk costs (high vs. absent), leaders' decisions (continue vs. abandon), campaign commitments (pro, anti, none), and reminders of prior voting behavior. In Experiment 1 ( N = 346), Bayesian ANOVA showed that evaluations (vote likelihood, perceived honesty, competence) were reliably higher when leaders continued rather than abandoned a project, with no main effect of sunk costs and no interaction. Experiment 2 ( N = 719) replicated the null sunk‐cost effect and further found no effect of campaign commitments once the leader's current decision was known. Experiment 3 ( N = 397) used a structural equation model to test mediation: perceived commitment—but not perceived sunk costs—robustly predicted evaluations, and abandonment sharply reduced perceived commitment; prior‐vote cues were weak and did not mediate effects. Together, the studies indicate that people take continuation to signal commitment and view it positively, whereas abandonment stopping signals a breach of commitment and is penalized. Apparent sunk‐cost sensitivity in politics may often reflect a premium on consistency rather than waste aversion. We discuss implications for designing “face‐saving” off‐ramps and reframing evidence‐based reversals as fidelity to higher order commitments.</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
@@ -5460,12 +9936,36 @@
           <t>Public Management Review</t>
         </is>
       </c>
-      <c r="E192" s="2" t="inlineStr"/>
-      <c r="F192" s="2" t="inlineStr"/>
-      <c r="G192" s="2" t="inlineStr"/>
-      <c r="H192" s="2" t="inlineStr"/>
-      <c r="I192" s="2" t="inlineStr"/>
-      <c r="J192" s="2" t="inlineStr"/>
+      <c r="E192" s="2" t="inlineStr">
+        <is>
+          <t>실험</t>
+        </is>
+      </c>
+      <c r="F192" s="2" t="inlineStr">
+        <is>
+          <t>설문 실험</t>
+        </is>
+      </c>
+      <c r="G192" s="2" t="inlineStr">
+        <is>
+          <t>Reference Points</t>
+        </is>
+      </c>
+      <c r="H192" s="2" t="inlineStr">
+        <is>
+          <t>Negativity Bias</t>
+        </is>
+      </c>
+      <c r="I192" s="2" t="inlineStr">
+        <is>
+          <t>홍콩에서 사회적·역사적 기준점과 부정성 편향이 시민의 정부 성과 평가에 미치는 영향을 설문 실험으로 복제·확장했다. 복제에서는 기준점과 부정성 편향의 영향에 대한 근거가 미미했지만, 확장에서는 부정적 정보가 제시될 때 두 기준점의 효과가 강해지고 정책 영역에 따라 기준점 조합의 효과가 달라졌다.</t>
+        </is>
+      </c>
+      <c r="J192" s="2" t="inlineStr">
+        <is>
+          <t>Experiments on how cognitive biases, such as social and historical reference points and negativity bias, shape citizens’ evaluations of government performance have produced mixed findings, which typically come from Western contexts and focus on single reference points. To address these gaps, we replicated (N = 3710) and extended (N = 2356) Olsen’s ‘Compared to what?’ to interactions between multiple social and historical reference points in Hong Kong. Very low baselines are found in the replication alongside trivial evidence for the importance of reference points in citizens’ performance evaluations and negativity bias. In the extension, we found that (1) when both social and historical reference points are presented to participants, they have stronger effects when negative information is provided and (2) the effects of combinations of historical and social reference points differ across policy domains. Though survey experiments can be noisy, the study demonstrates the value of replication to question the generalization of cognitive biases.</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
@@ -5486,12 +9986,36 @@
           <t>Public Management Review</t>
         </is>
       </c>
-      <c r="E193" s="2" t="inlineStr"/>
-      <c r="F193" s="2" t="inlineStr"/>
-      <c r="G193" s="2" t="inlineStr"/>
-      <c r="H193" s="2" t="inlineStr"/>
-      <c r="I193" s="2" t="inlineStr"/>
-      <c r="J193" s="2" t="inlineStr"/>
+      <c r="E193" s="2" t="inlineStr">
+        <is>
+          <t>준실험</t>
+        </is>
+      </c>
+      <c r="F193" s="2" t="inlineStr">
+        <is>
+          <t>확률적 네트워크 모형</t>
+        </is>
+      </c>
+      <c r="G193" s="2" t="inlineStr">
+        <is>
+          <t>Collaborative Governance</t>
+        </is>
+      </c>
+      <c r="H193" s="2" t="inlineStr">
+        <is>
+          <t>Smart City</t>
+        </is>
+      </c>
+      <c r="I193" s="2" t="inlineStr">
+        <is>
+          <t>이 연구는 중국의 스마트시티 프로젝트 3,482건을 대상으로 디지털 불확실성 속 협력적 거버넌스 네트워크와 참여자 속성이 어떻게 진화하는지 분석했다. 확률적 행위자 지향 모형과 협력적 거버넌스 이론을 적용한 결과, 정부 주도형·정부-공기업 혼합형·다중 이해관계자형의 세 패턴이 나타났으며, 전이적 삼각관계·연령 유사성·지리적 근접성·규모 이질성은 네트워크 진화를 촉진하고 외향 연결 정도는 이를 제약했다.</t>
+        </is>
+      </c>
+      <c r="J193" s="2" t="inlineStr">
+        <is>
+          <t>Smart city initiatives, as public service innovation, represent a major evolution within state-led meta-governance, requiring complex inter-participant collaboration. Yet scholarship often treats these networks as static, missing how governance structures adapt to digital uncertainties. To fill this gap, this study employs stochastic actor-oriented models and collaborative governance theory to examine the evolution of network structures and participant attributes across 3482 smart city projects in China. Results reveal three governance patterns: government-dominated, government-SOE hybrid, and multi-stakeholder. Transitive triads, age similarity, geographic proximity, and size heterogeneity promote evolution, while outdegree constrains it. Findings guide optimizing partner selection and strengthening adaptive governance.</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
@@ -5512,12 +10036,36 @@
           <t>Public Administration Review</t>
         </is>
       </c>
-      <c r="E194" s="2" t="inlineStr"/>
-      <c r="F194" s="2" t="inlineStr"/>
-      <c r="G194" s="2" t="inlineStr"/>
-      <c r="H194" s="2" t="inlineStr"/>
-      <c r="I194" s="2" t="inlineStr"/>
-      <c r="J194" s="2" t="inlineStr"/>
+      <c r="E194" s="2" t="inlineStr">
+        <is>
+          <t>실험</t>
+        </is>
+      </c>
+      <c r="F194" s="2" t="inlineStr">
+        <is>
+          <t>의사결정 시뮬레이션</t>
+        </is>
+      </c>
+      <c r="G194" s="2" t="inlineStr">
+        <is>
+          <t>Formal-Relational Contracting</t>
+        </is>
+      </c>
+      <c r="H194" s="2" t="inlineStr">
+        <is>
+          <t>Cooperation</t>
+        </is>
+      </c>
+      <c r="I194" s="2" t="inlineStr">
+        <is>
+          <t>불완전한 계약조건에서 정부 구매자와 판매자의 협력을 높일 수 있는지 검토하기 위해, 공공 계약관리자 320명이 순차적 선택을 수행하는 의사결정 시뮬레이션에서 공식-관계적 계약(FRC)과 전통적 공식 계약을 비교했다. FRC는 공식 계약보다 협력적 행동을 약 30%포인트 높였으며, 관리자들의 사고방식도 대립적 태도에서 협력적 태도로 전환한 것으로 나타났다.</t>
+        </is>
+      </c>
+      <c r="J194" s="2" t="inlineStr">
+        <is>
+          <t>ABSTRACT A central challenge in government contracting is fostering cooperation between buyers and sellers where contract terms are incomplete. This article introduces a framework for formal‐relational contracting (FRC) in public sector contexts, where rigid regulations, competing values, and market imperfections make cooperation both difficult and valuable. FRC promotes cooperation through contract terms defining shared goals, guiding principles, and governance mechanisms. We present the theoretical foundations of FRC and examine its potential through 320 government contract management decision simulations where public contract managers acted as government buyers and business sellers facing sequential choices under both FRC contracts and the more conventional formal contracting approach. The results show that FRC increased managers' cooperative behavior by around 30 percentage points compared to formal contracting. Qualitative evidence further suggests that FRC shifted managers' mindsets from adversarial to cooperative. We discuss theoretical and practical implications for how FRC can enhance cooperation and mutual value in government contracting.</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
@@ -5564,12 +10112,36 @@
           <t>Public Opinion Quarterly</t>
         </is>
       </c>
-      <c r="E196" s="2" t="inlineStr"/>
-      <c r="F196" s="2" t="inlineStr"/>
-      <c r="G196" s="2" t="inlineStr"/>
-      <c r="H196" s="2" t="inlineStr"/>
-      <c r="I196" s="2" t="inlineStr"/>
-      <c r="J196" s="2" t="inlineStr"/>
+      <c r="E196" s="2" t="inlineStr">
+        <is>
+          <t>질적연구</t>
+        </is>
+      </c>
+      <c r="F196" s="2" t="inlineStr">
+        <is>
+          <t>경험자 인터뷰</t>
+        </is>
+      </c>
+      <c r="G196" s="2" t="inlineStr">
+        <is>
+          <t>Evidence-Based Democracy</t>
+        </is>
+      </c>
+      <c r="H196" s="2" t="inlineStr">
+        <is>
+          <t>Professional Community</t>
+        </is>
+      </c>
+      <c r="I196" s="2" t="inlineStr">
+        <is>
+          <t>AAPOR 회장은 2025~2026년 연방 통계·과학 제도의 압박과 공공의견 연구 공동체가 겪은 고용·연구 환경의 불안정을 증언하고, 증거 기반 민주주의에서 조사 연구의 중요성을 강조한다. 연설은 AAPOR의 표준·교육·토론·상호지원 기능과 연구자들의 협력·참여를 통해 연구의 질과 공동체의 회복력·포용성을 지켜야 한다고 제안한다.</t>
+        </is>
+      </c>
+      <c r="J196" s="2" t="inlineStr">
+        <is>
+          <t>When I first became AAPOR’s vice president/president-elect in 2024, I thought I might focus my presidential address on something like “the business of research,” reflecting my perspective as chief business officer of a research company and considering how the association might think about its financial stability and growth. Then in 2025, a little something happened… A new administration arrived and took a chainsaw to the statistical and scientific institutions of this country. A national leader sued and threatened some of the most public faces of our industry. And the economic fallout of these and other actions shook our industry to the core. Once I got out of the fetal position, I had to grapple with new priorities for my AAPOR presidency. So today, what I want to do is bear witness to this time we are living through and provide hope for the future. There are four things I will reflect on: the moment we are in; the work we do; the community that makes that work possible; and how we respond to these times. I want to present not just my own voice, but those across our community. To do so, I have talked to members from a wide variety of fields, experiences, and circumstances. I share their views, along with my own, and I thank them for the honesty, vulnerability, and inspiration they gave me. We are living through a period of profound instability in the systems that produce and protect evidence. The federal statistical system—one of the pillars of how we understand this country—has faced extraordinary pressure. Programs have been halted. Funding has been threatened or withdrawn. Statistical leaders have been dismissed. Institutions designed to operate independently have faced increasing political pressure. Many of us have lost our jobs or found our work threatened. The American Statistical Association reported that all 13 federal statistical agencies lost staff in 2025, with some, like the National Center for Education Statistics (NCES)—at least temporarily—almost totally demolished (American Statistical Association 2025). The shuttering of USAID halted critical research projects and is projected to lead to a staggering number of avoidable deaths (Cavalcanti et al. 2025). These systems were built over decades. The people who have dedicated their lives to these objectives have created a body of knowledge that is essential to understanding the way we live and how that changes—the statisticians and survey methodologists, analysts and researchers, project managers and directors, contractors and subcontractors. There has been messaging through DOGE actions and other high-level communications that the work of these individuals is biased, wasteful, unneeded, or worse. Many of those people are members of this community. And this rhetoric and these actions are having a profound effect. One experienced federal researcher told me she was considering getting out of the field altogether. She couldn’t see a path forward for herself. We are losing some of our greatest assets and future leaders. For those that remain, we bear witness to their integrity, persistence, and quiet professionalism as they continue to produce evidence when the environment around them is uncertain and unsupportive. We see and empathize with the “survivors’ guilt” many experience. We also recognize the disruption in the lives of many who have lost their positions and now face remaking their careers. They must do so at a time when uncertainty and trepidation have affected the entire industry, making it a less-than-hospitable place for job seekers and career changers. A displaced federal worker I spoke to said she feels a sense of grief and loss. Grieving not only for her own personal losses, but for the bigger picture of what is happening to federal government data collection, to public health research, and to the scientific community. I spoke to a small business owner who saw critical work that she and her colleagues had done shelved, to possibly never see the light of day. A graduate student shared with me the challenges she has experienced—having her research funding terminated, seeing fewer placements for her fellow students at universities, and being forced to grapple with new worries about her international student status. She said, “When I was coming to the US, I didn’t think that I would have to worry that scientific research could be compromised in a country like this.” Others shared: “The last 18 months have felt like a ticking countdown clock”; “The institutional knowledge we have lost will take years to recover”; and “The foundation is shakier than I thought.” I want to acknowledge the extreme stress that has characterized our field and so many of our members in 2025 and 2026 and bear witness to the professional and personal toll this has taken. Next, I want to talk about the importance of our work. At its core, what we do is deceptively simple. We ask people about their lives—how they live, think, work, and experience the world. We do so carefully, systematically, and with the goal of understanding more than just the loudest voices. The importance of that work becomes clearer in moments like this, when increasingly, we are living in a world where the idea of shared evidence itself is contested. Where data can be dismissed because it is inconvenient. Where research can be labeled fraudulent if it challenges power. Some specific examples of this are the lawsuits against Ann Selzer (Doyle 2024); the litigation threats to the New York Times (Svirnovskiy 2026), CNN (Grynbaum and Haberman 2020), and their research partners; the demand for cancellation of programs deemed focused on DEI (Exec. Order No. 14151 2025; Hsu 2025); and the removal of nonbinary gender categories from federal research (Exec. Order No. 14168 2025), to name just a few. This runs counter to everything our field stands for. We may never measure perfectly. But through rigorous methods and transparency, we highlight the experiences, hopes, and fears of everyday Americans. In a democracy, that matters. Because governing without understanding the public is governing in the dark. What we produce is not just data. It is a record. A record of what people think, what they experience, and how society is changing. We must protect that, celebrate it, and feel pride in the importance of the work that we do. A researcher at the Census told me that she was most proud to be part of a system where, despite current narratives, the goal is to “measure truth, to the best of our ability, across time, across administrations, and across events.” Through all of this, the work continues. A statistician at a large research company spoke of his pride in what we do. He said, “Linking what people are thinking and saying to policy has never been more important.” I now want to reflect on the community, because this work does not happen in isolation. It depends on a diverse and interdependent community. The work we do is the product of government, academia, nonprofit organizations, and the private sector. Each plays a distinct role. Government statisticians establish benchmarks. Academics develop and test new ideas and train future researchers. Nonprofit and election researchers help us understand civic life. And commercial researchers innovate—finding ways to make data collection more scalable and accessible. We often approach problems differently. We use different methods. We operate under different constraints. We do not always agree (looking at you, AAPORnet). We debate probability and nonprobability sampling (boy, do we debate probability and nonprobability sampling!). We debate qualitative and quantitative approaches. We debate new tools, new data sources, and, more recently, artificial intelligence. These debates can be intense. They can feel divisive. But they exist because we are all trying to answer the same questions: How do we understand people accurately? How do we do this work responsibly? And how do we do it within real-world budgetary and time constraints? Our disagreements are a sign of a healthy scientific community—a community that makes our work possible, improves it, and, at times, helps us bear it. Multiple people I spoke to talked about the importance of having people to turn to that believe in the work that we do, to bounce ideas off of, to call when we need questions answered. A sympathetic human to talk to, not an obsequious chatbot. The government employees I spoke to remarked on how important this community has been in making it possible to keep going when they felt disparaged, and in helping make connections in the search for a new opportunity. A private-sector researcher reflected on how we share expertise to improve the work for us all, even when there could be commercial reasons for not doing so. A multicultural researcher noted that perhaps our recent struggles have brought us together. She said, “I have co-pollinated with so many others that I wouldn’t have before, because we’re working through the same struggles.” A methodologist at a start-up company noted that through all this craziness, he is seeing more acceptance and creativity in our community; more openness to the wide variety of practices and innovations. I can see frustration among our ranks as we debate how to respond to today’s challenges, how to move forward, how to value and publicize what we do. Some have called for the community to have a stronger voice. Some have expressed that doing so would put their membership at risk. Some have suggested our separating ourselves based on method. Some have felt marginalized, seeing the work that they do categorized as lesser. I urge our community to recognize that what unites us is more important than our differences. Remember that your fellow researchers are seeking to do just what you are doing—increase our understanding of a given population or issue. They may be doing it with different methods, budgets, and styles, but we are united in seeking clarity, and we are family in this enterprise. Be kind to each other. Seek to understand and empathize. Show respect for your fellow researcher, even if the work that they do seems only marginally connected in our big Venn diagram of the research industry (see figure 1). Humorous Venn diagram depicting our shared commitment to research. Now, what do we do with all of this? How will we respond to this moment—not just endure it, but build a more resilient, innovative, and inclusive future for our field? This is why AAPOR is so important. Through AAPOR we can support the work and strengthen the community that makes it possible. AAPOR facilitates the critical work of public opinion research by creating task forces, providing forums for debate and discussion, educating on best practices, and evolving standards for the industry. Our work on cell phone samples and text messaging has paved the way for the wide use of new methodological tools. Our pre-election polling task forces have changed the way we conduct and talk about election research. Our reports on opt-in and probability panels have given us frameworks for transparency and a shared language for these sample sources, to name just a few examples. Our response to these times should be to keep driving forward. We must continue what AAPOR has done for 81 years—help the industry understand itself, improve what we do, and identify new challenges and opportunities. In the past 18 months, through these challenging times, AAPOR has released major resources on pre-election polling (American Association for Public Opinion Research 2025a), establishment surveys (American Association for Public Opinion Research 2025b), texting for research (American Association for Public Opinion Research 2025c), linking survey and nonsurvey data (American Association for Public Opinion Research 2025d), and, most recently, on responsible AI integration (American Association for Public Opinion Research 2026). We have updated our code of professional ethics and practices, hosted webinars and short courses, organized new workshops, and put together two major conferences. Table 1 highlights a small selection of these achievements. Selected AAPOR resources and activities produced during 2025–2026. All of this is carried out by volunteers, supported by a small staff, who work collaboratively, from their different vantage points and experiences, to express the latest information about our field. Keeping this collaborative enterprise going is what will keep our industry vibrant and resilient through these times, and it is what AAPOR does best. AAPOR’s response is also to foster the community doing this important work. We are A Meeting Place (American Association for Public Opinion Research 2020). Every year, through our conference, we provide an opportunity to come together to share ideas and network. If lately the conference has felt like a therapy session (as in figure 2), it is needed for us to support each other during these times. Cartoon highlighting AAPOR’s annual conference as a place for mutual support around the emergence of AI. Created by author using ChatGPT. We also need to ensure that our industry is expanding and inclusive. AAPOR’s commitment to diversity has helped reshape the field and made this organization stronger and better able to respond to today’s challenges. We must continue to prioritize this. The AAPOR Affinity Groups give us more ways to connect and share our challenges. As shown in table 2, today we have 11 Affinity Groups, including ConsultPOR, formed in early 2026 in part as a reaction to the movement of practitioners out of traditional employee settings into business for themselves, and the Global Research Affinity Group, inaugurated at our May 2026 Conference. List of AAPOR Affinity Groups as of May 2026. We need to provide tangible, practical support to our community as well. Last year, when so many faced layoffs, travel restrictions, and financial hardships, we rallied as a community and raised a record amount of donations to support conference travel grants. We also provide upskilling sessions, professional development, job coaching, and networking opportunities, all led by volunteers in this room and beyond. In terms of our individual responses, the people I spoke with offered a clear message: steady on, stay curious, and do this together. One academic said, “We need to keep doing what we have always been doing—learning, innovating, and using evidence-based approaches.” A business owner urged us to “lean into the unknown.” And a student reminded me that when we multiply our efforts with others, “it’s way stronger than we can imagine.” My call to action today reflects these sentiments. Stay the course, seek help when you need it, and provide a hand up to another when you can. And don’t give up. Because what we do is important. The industry has faced challenges before: shifts in methodology, new technologies, declining response rates, new forms of data, and now a double whammy of a federal administration hostile to research and the rapid proliferation of artificial intelligence. What do we do? We engage with these challenges. We communicate our values. We set standards. We adapt our practices. And we continue the work. Get involved. AAPOR needs each of you. Join a committee. Say “yes” if I ask you to run for council! Ask me, or any of us on council, how to participate. Be a deeper part of this organization that provides a voice, a space, and a framework for what we do. Get involved outside of AAPOR, too. Write local op-eds, contact your representatives, reach out to colleagues in need, and support causes that support the industry, including AAPOR. Join us in this moment, in this community, and in being the way forward. As I close, I want to return to where I began. How do we bear witness to the moment we are living through? And how do we ensure that this work and this community can thrive in the years to come? AAPOR has existed for more than eight decades. Through profound change, the purpose of this work has remained remarkably consistent: to create valid and transparent data about behaviors, attitudes, and characteristics that enable informed societal decision-making. That work is not always easy. But it remains essential. Because no society can understand itself without evidence about the people who live within it. When we do this work well—carefully, ethically, and openly—we create something larger than a dataset, report, or publication. We create a record of the public’s voice. In that sense, this field helps our society bear witness to itself. One of the people I talked to said, “We are writing history right now.” How we respond to this moment is something future researchers will examine. They will seek to understand the foundations of our systems that produce evidence. They will ask how those systems were challenged. And they will ask what we did in response. Our responsibility is to strengthen what we do, improve our tools, defend our standards, and support one another. We continue by doing what this field has always done: help the public be heard, help society understand itself, and strengthen the democracy that depends on both.</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
@@ -5590,12 +10162,36 @@
           <t>Policy Studies Journal</t>
         </is>
       </c>
-      <c r="E197" s="2" t="inlineStr"/>
-      <c r="F197" s="2" t="inlineStr"/>
-      <c r="G197" s="2" t="inlineStr"/>
-      <c r="H197" s="2" t="inlineStr"/>
-      <c r="I197" s="2" t="inlineStr"/>
-      <c r="J197" s="2" t="inlineStr"/>
+      <c r="E197" s="2" t="inlineStr">
+        <is>
+          <t>실험</t>
+        </is>
+      </c>
+      <c r="F197" s="2" t="inlineStr">
+        <is>
+          <t>현장 무작위실험</t>
+        </is>
+      </c>
+      <c r="G197" s="2" t="inlineStr">
+        <is>
+          <t>Transparency</t>
+        </is>
+      </c>
+      <c r="H197" s="2" t="inlineStr">
+        <is>
+          <t>Accountability</t>
+        </is>
+      </c>
+      <c r="I197" s="2" t="inlineStr">
+        <is>
+          <t>우간다 서부 석유 부문에서 이해관계자 참여를 무작위 배정한 현장실험을 통해 투명성이 시민의 정책 책임 귀속을 바꾸는지 분석했다. 다자간 포럼 참여는 지역사회의 투명성을 높였지만 비난과 공로의 귀속은 변화시키지 않았으며, 그럼에도 집단행동 증가는 가능했다.</t>
+        </is>
+      </c>
+      <c r="J197" s="2" t="inlineStr">
+        <is>
+          <t>ABSTRACT The implementation of public policy is increasingly diffuse with responsibilities divided among several levels of government administration, the private sector, and nonprofits. In the face of such diffusion, many advocate for transparency initiatives to inform the public about policymaking. However, it remains unclear whether transparency initiatives clarify the blame and credit for policy, or what this means for collective action and accountability. Such concerns are especially pressing in complex settings like the non‐renewable extractives sector (oil, mining, and natural gas). We assess policy attributions of blame and credit using data from a field experiment that randomizes stakeholder engagement in Western Uganda's oil sector, building on our prior work showing that this intervention increased collective action. While participating in multistakeholder forums improved transparency for communities, we find that it did not change their attributions. In other words, improving transparency does not ensure that citizens will update their opinions about who is to blame for the problems they face. Yet, this did not preclude greater collective action. Evidence from this intervention highlights the need for more exploration of pathways linking transparency, collective action, and accountability.</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
@@ -5616,12 +10212,36 @@
           <t>Political Communication</t>
         </is>
       </c>
-      <c r="E198" s="2" t="inlineStr"/>
-      <c r="F198" s="2" t="inlineStr"/>
-      <c r="G198" s="2" t="inlineStr"/>
-      <c r="H198" s="2" t="inlineStr"/>
-      <c r="I198" s="2" t="inlineStr"/>
-      <c r="J198" s="2" t="inlineStr"/>
+      <c r="E198" s="2" t="inlineStr">
+        <is>
+          <t>실험</t>
+        </is>
+      </c>
+      <c r="F198" s="2" t="inlineStr">
+        <is>
+          <t>현장 무작위실험</t>
+        </is>
+      </c>
+      <c r="G198" s="2" t="inlineStr">
+        <is>
+          <t>Knowledge Gap</t>
+        </is>
+      </c>
+      <c r="H198" s="2" t="inlineStr">
+        <is>
+          <t>Civic Knowledge</t>
+        </is>
+      </c>
+      <c r="I198" s="2" t="inlineStr">
+        <is>
+          <t>온라인 검색을 통한 정책 정보 습득에서 교육수준에 따른 지식 격차가 줄어드는지를, 독일 참가자를 대상으로 한 무작위 현장실험과 브라우저 추적으로 분석했다. 정보탐색 행동은 개입으로 균등해졌지만, 지식 증가는 고학력자나 기초 시민지식이 높은 참여자에게 집중되어 지식 격차 가설을 일부 지지했다.</t>
+        </is>
+      </c>
+      <c r="J198" s="2" t="inlineStr">
+        <is>
+          <t>Persistent inequalities in political knowledge are a central concern in political communication. We organize the mechanisms underlying the knowledge-gap literature by distinguishing between individual preconditions, structural features of the information environment, and topic characteristics. Within this framework, we note that self-directed information seeking, a prototypical form of intentional exposure, has received little attention despite its importance in navigating today’s complex information environment. We conducted a field experiment in Germany, combining randomized encouragements and passive browser tracking, to examine how individuals with varying education levels acquire policy-specific knowledge through online search. Participants were randomly assigned to one of three conditions (verbal encouragement, financial encouragement, or control) to seek information on three salient policy topics differing in divisiveness and complexity (child support, energy transition, and cannabis legalization). We estimated both intention-to-treat (ITT) and local average treatment effects (LATE) of information seeking on post-search knowledge outcomes, with a focus on education and civic knowledge as moderators. While the interventions equalized information-seeking behavior, the results provide some support for the knowledge gap hypothesis: knowledge gains were concentrated among participants with higher education or baseline civic knowledge, who, according to our post-hoc exploratory analyses, appeared more effective at navigating search results. These findings indicate that a narrowing of knowledge inequalities goes beyond motivation: it calls for both individual-level interventions to strengthen citizens’ skills and structural-level adaptations to foster more equitable learning environments.</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
@@ -5642,12 +10262,36 @@
           <t>Public Administration</t>
         </is>
       </c>
-      <c r="E199" s="2" t="inlineStr"/>
-      <c r="F199" s="2" t="inlineStr"/>
-      <c r="G199" s="2" t="inlineStr"/>
-      <c r="H199" s="2" t="inlineStr"/>
-      <c r="I199" s="2" t="inlineStr"/>
-      <c r="J199" s="2" t="inlineStr"/>
+      <c r="E199" s="2" t="inlineStr">
+        <is>
+          <t>서베이</t>
+        </is>
+      </c>
+      <c r="F199" s="2" t="inlineStr">
+        <is>
+          <t>횡단면 설문</t>
+        </is>
+      </c>
+      <c r="G199" s="2" t="inlineStr">
+        <is>
+          <t>Digital Maturity</t>
+        </is>
+      </c>
+      <c r="H199" s="2" t="inlineStr">
+        <is>
+          <t>Administrative Capacity</t>
+        </is>
+      </c>
+      <c r="I199" s="2" t="inlineStr">
+        <is>
+          <t>본 연구는 플랑드르 지방정부의 디지털 성숙도 차이를 제도적 압력과 정치·행정 역량 중 어떤 요인이 더 잘 설명하는지 조사했다. 1차 설문자료에 다중회귀분석을 적용한 결과, 행정 역량이 디지털 성숙도의 발전에 핵심적이었으며 정치적 역량과 제도적 압력의 역할은 상대적으로 제한적이었다.</t>
+        </is>
+      </c>
+      <c r="J199" s="2" t="inlineStr">
+        <is>
+          <t>ABSTRACT Public administration research has identified institutional pressures and organizational capacity as digital maturity (DM) antecedents, yet these are typically considered in isolation. Taking the proverbial next step, this study draws on primary survey data to explain the variation of DM among local governments in Flanders (the northern region of Belgium) by juxtaposing the explanatory power of institutional pressures on the one hand, and political and administrative capacity on the other hand. Using multiple regression analyses, our findings highlight the critical role of administrative capacity in advancing DM among local governments. In contrast, and somewhat surprisingly, political capacity and institutional pressures appear to play a more limited role. These findings challenge conventional assumptions in existing literature, indicating that institutional pressures may catalyze the initial stages of DT, whereas organizational capacity seems to be more influential in sustaining and advancing DM.</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
@@ -5668,12 +10312,36 @@
           <t>Political Psychology</t>
         </is>
       </c>
-      <c r="E200" s="2" t="inlineStr"/>
-      <c r="F200" s="2" t="inlineStr"/>
-      <c r="G200" s="2" t="inlineStr"/>
-      <c r="H200" s="2" t="inlineStr"/>
-      <c r="I200" s="2" t="inlineStr"/>
-      <c r="J200" s="2" t="inlineStr"/>
+      <c r="E200" s="2" t="inlineStr">
+        <is>
+          <t>이론/개념</t>
+        </is>
+      </c>
+      <c r="F200" s="2" t="inlineStr">
+        <is>
+          <t>문헌 검토</t>
+        </is>
+      </c>
+      <c r="G200" s="2" t="inlineStr">
+        <is>
+          <t>Social Dominance Orientation</t>
+        </is>
+      </c>
+      <c r="H200" s="2" t="inlineStr">
+        <is>
+          <t>Social Dominance Theory</t>
+        </is>
+      </c>
+      <c r="I200" s="2" t="inlineStr">
+        <is>
+          <t>이 논문은 2010~2024년의 경험적 연구를 검토해 사회적 지배지향성(SDO)의 안정성과 측정 타당성, 집단 간 편견·고정관념 및 위계 강화 행동과의 관계, 그리고 SDO의 발달 경로를 종합한다. 검토 결과, SDO가 높은 사람일수록 지배집단을 선호하는 편견과 반사회적·위계 강화 성향이 강했으며, 이러한 성향은 범주화·서열화 학습과 부모의 높은 지위 강조를 통해 발달할 수 있는 것으로 나타났다.</t>
+        </is>
+      </c>
+      <c r="J200" s="2" t="inlineStr">
+        <is>
+          <t>Abstract Social dominance orientation (SDO) refers to how much a person generally opposes group‐based equality and supports group‐based dominance. SDO is measured as an individual difference and pertains very broadly to people's socio‐political attitudes and perceptions, to endorsement or rejection of political parties and candidates, and to behaviors that enforce organizational hierarchies. This paper reviews empirical evidence published from 2010 to 2024 concerning social dominance orientation, first presenting evidence of its stability over time and measurement integrity, next showing that, across numerous cultures and languages and ways of measuring group prejudice and stereotypes, SDO correlates with prejudice favoring people in dominant groups rather than people in subordinate groups, and that this effect is stronger within dominant groups than subordinate groups. Similarly, we review evidence that people higher on SDO are more anti‐social and tend to take hierarchy‐enhancing rather than hierarchy‐attenuating roles. We then delve into the psychology of SDO and summarize the evidence for the relation of SDO and closed cognitive styles, low scores on humility‐honesty, and low concern for other people rather than the self. Using existing adult and child development studies, we outline two processes by which higher SDO may develop: one based on learning to categorize and to rank categories as superior/inferior, and one based on parents' emphasis on obtaining high status to gain approval. We conclude by outlining the next questions that might be pursued.</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
@@ -5686,7 +10354,7 @@
       </c>
       <c r="C201" s="3" t="inlineStr">
         <is>
-          <t>Large Language Models and Conversational Counter-Arguments to Anti-Public Sector Bias</t>
+          <t>Large language models and conversational counter-arguments to antipublic sector bias</t>
         </is>
       </c>
       <c r="D201" s="2" t="inlineStr">
@@ -5694,12 +10362,36 @@
           <t>Journal of Public Administration Research and Theory</t>
         </is>
       </c>
-      <c r="E201" s="2" t="inlineStr"/>
-      <c r="F201" s="2" t="inlineStr"/>
-      <c r="G201" s="2" t="inlineStr"/>
-      <c r="H201" s="2" t="inlineStr"/>
-      <c r="I201" s="2" t="inlineStr"/>
-      <c r="J201" s="2" t="inlineStr"/>
+      <c r="E201" s="2" t="inlineStr">
+        <is>
+          <t>실험</t>
+        </is>
+      </c>
+      <c r="F201" s="2" t="inlineStr">
+        <is>
+          <t>사전등록 실험</t>
+        </is>
+      </c>
+      <c r="G201" s="2" t="inlineStr">
+        <is>
+          <t>Attitude Change</t>
+        </is>
+      </c>
+      <c r="H201" s="2" t="inlineStr">
+        <is>
+          <t>Sycophancy</t>
+        </is>
+      </c>
+      <c r="I201" s="2" t="inlineStr">
+        <is>
+          <t>생성형 인공지능과의 대화에서 정부기관에 대한 부정적 견해를 반박하는 논쟁적 스타일과 이를 수용하는 아첨형 스타일 중 어느 쪽이 태도 변화에 더 효과적인지 세 차례 사전등록 실험으로 분석했다. 반박적 스타일은 긍정적 태도 변화를 유도했지만, 이용자들이 더 즐겁고 덜 좌절하며 신뢰할 만하다고 평가한 아첨형 스타일은 그렇지 않아, 이용자 경험과 설득 효과가 일치하지 않았다.</t>
+        </is>
+      </c>
+      <c r="J201" s="2" t="inlineStr">
+        <is>
+          <t>Abstract Can a good argument change an individual’s mind? In three preregistered experiments, we explore this question in the domain of public sector organizational performance. We observe human subjects as they engage in conversations with a generative artificial intelligence programmed to argue in one of seven distinct “styles,” including a confrontational challenger style, a didactic style, and a sycophantic style. We develop a theory of effective argumentation predicting that conversational styles which are pleasant and engaging will be more persuasive than styles which are unpleasant or unstimulating. Contrary to this prediction, we find that conversational styles which challenge subjects’ negative views of government agencies produce significant positive attitude change, while sycophantic styles that indulge those views do not. Troublingly, subjects find the sycophantic styles more enjoyable, less frustrating, and more credible than the challenger styles. This dissociation between user experience and persuasive outcome—what we call “grudging persuasion”—suggests that attitude change does not require a pleasant conversational experience, and that the styles subjects enjoy most may be precisely the ones least likely to move them. Our findings point to a potentially dark side of large language model-based persuasion: sycophantic styles that users find most appealing are the least effective at correcting misinformed views.</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
@@ -5720,12 +10412,36 @@
           <t>Administration &amp; Society</t>
         </is>
       </c>
-      <c r="E202" s="2" t="inlineStr"/>
-      <c r="F202" s="2" t="inlineStr"/>
-      <c r="G202" s="2" t="inlineStr"/>
-      <c r="H202" s="2" t="inlineStr"/>
-      <c r="I202" s="2" t="inlineStr"/>
-      <c r="J202" s="2" t="inlineStr"/>
+      <c r="E202" s="2" t="inlineStr">
+        <is>
+          <t>이론/개념</t>
+        </is>
+      </c>
+      <c r="F202" s="2" t="inlineStr">
+        <is>
+          <t>개념적 모형</t>
+        </is>
+      </c>
+      <c r="G202" s="2" t="inlineStr">
+        <is>
+          <t>Epistemic Tension</t>
+        </is>
+      </c>
+      <c r="H202" s="2" t="inlineStr">
+        <is>
+          <t>Knowledge Logics</t>
+        </is>
+      </c>
+      <c r="I202" s="2" t="inlineStr">
+        <is>
+          <t>이 글은 하나의 의사결정 상황에서 타당하고 유용하며 권위 있는 지식의 기준들이 어떻게 동시에 작동하는지 분석한다. 다섯 가지 지식 논리(확실성·상호작용·정당성·네트워크·영향력)와 이들 간의 지배, 충돌, 분리, 생산적 결합을 제시하고, 행정 단계에 따라 상대적 비중이 달라진다고 주장한다.</t>
+        </is>
+      </c>
+      <c r="J202" s="2" t="inlineStr">
+        <is>
+          <t>In public and hybrid settings, substantial knowledge is often available, but its influence on decision making and implementation remains limited. Existing scholarship has shown that this problem involves more than a simple knowledge deficit. Greater analytical attention needs to be paid to how different standards for valid, useful, and authoritative knowledge operate simultaneously within the same decision situation. This essay develops a threefold claim. First, it distinguishes five knowledge logics: certainty, interaction, legitimacy, network, and influence. Second, it identifies four recurring dynamics among them: dominance, collision, decoupling, and productive combination. Third, it argues that their relative weight shifts across administrative phases.</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
@@ -5746,12 +10462,36 @@
           <t>Administration &amp; Society</t>
         </is>
       </c>
-      <c r="E203" s="2" t="inlineStr"/>
-      <c r="F203" s="2" t="inlineStr"/>
-      <c r="G203" s="2" t="inlineStr"/>
-      <c r="H203" s="2" t="inlineStr"/>
-      <c r="I203" s="2" t="inlineStr"/>
-      <c r="J203" s="2" t="inlineStr"/>
+      <c r="E203" s="2" t="inlineStr">
+        <is>
+          <t>서베이</t>
+        </is>
+      </c>
+      <c r="F203" s="2" t="inlineStr">
+        <is>
+          <t>횡단 설문·SEM</t>
+        </is>
+      </c>
+      <c r="G203" s="2" t="inlineStr">
+        <is>
+          <t>Social Cohesion</t>
+        </is>
+      </c>
+      <c r="H203" s="2" t="inlineStr">
+        <is>
+          <t>Municipal Legitimacy</t>
+        </is>
+      </c>
+      <c r="I203" s="2" t="inlineStr">
+        <is>
+          <t>이 연구는 코로나19 팬데믹과 2021년 5월 이스라엘 집단 간 폭력 상황에서 사회적 결속과 사회적 근접성이 지방정부 성과에 대한 만족도와 어떻게 관련되는지 23개 도시 주민 944명의 설문자료를 OLS와 구조방정식으로 분석했다. 사회적 결속은 일관되게 높은 만족도와 관련되었고, 사회적 근접성의 관련성은 주로 결속을 통해 나타났다.</t>
+        </is>
+      </c>
+      <c r="J203" s="2" t="inlineStr">
+        <is>
+          <t>As cities become more heterogeneous and polarized, local governments face crises that challenge both performance and legitimacy. This study examines how social cohesion and social proximity are associated with satisfaction with municipal performance during the COVID-19 pandemic and the May 2021 intergroup violence in Israel. Using survey data from 944 residents across 23 cities and employing OLS and SEM analyses, we find that social cohesion is consistently associated with higher satisfaction, whereas proximity is associated with satisfaction primarily through cohesion. These findings highlight the social foundations of municipal legitimacy and distinguish between contact and cohesion in crisis governance.</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
@@ -5772,12 +10512,36 @@
           <t>Policy Studies Journal</t>
         </is>
       </c>
-      <c r="E204" s="2" t="inlineStr"/>
-      <c r="F204" s="2" t="inlineStr"/>
-      <c r="G204" s="2" t="inlineStr"/>
-      <c r="H204" s="2" t="inlineStr"/>
-      <c r="I204" s="2" t="inlineStr"/>
-      <c r="J204" s="2" t="inlineStr"/>
+      <c r="E204" s="2" t="inlineStr">
+        <is>
+          <t>실험</t>
+        </is>
+      </c>
+      <c r="F204" s="2" t="inlineStr">
+        <is>
+          <t>사전등록 설문 실험</t>
+        </is>
+      </c>
+      <c r="G204" s="2" t="inlineStr">
+        <is>
+          <t>Government Trust</t>
+        </is>
+      </c>
+      <c r="H204" s="2" t="inlineStr">
+        <is>
+          <t>Collective Efficacy</t>
+        </is>
+      </c>
+      <c r="I204" s="2" t="inlineStr">
+        <is>
+          <t>정책의 성공 또는 실패 서사가 정부의 해당 문제 대응에 대한 신뢰, 문제의 중요성 인식, 집단적 효능감에 미치는 인과적 효과를 사전등록 실험으로 검증했다. 세 정책을 다룬 TikTok 형식의 짧은 뉴스 영상을 본 결과, 두 서사 모두 문제의 현저성을 높였지만 실패 서사는 정부의 대응 능력에 대한 냉소를 증가시켰다.</t>
+        </is>
+      </c>
+      <c r="J204" s="2" t="inlineStr">
+        <is>
+          <t>ABSTRACT While public policies usually have mixed effects, succeeding at some aspects and failing at others, this nuance is often lost in public discourse when political actors like advocacy groups and politicians strategically emphasize either the successes or failures of particular policies. For example, advocacy groups often emphasize the failures of existing policy with the goal of galvanizing public attention and concern. However, little empirical evidence exists assessing the actual causal impact of these different approaches on public attitudes. This paper presents the results of a pre‐registered experiment in which participants watch a TikTok‐style short news video about either the success or failure of one of three different public policies and then are asked about their trust in government to handle the issue, their perceptions of the issue's importance, and their feelings of collective efficacy. While success and failure narratives are both effective at raising an issue's salience, focusing on a policy's failure has the downstream effect of increasing cynicism about the government's ability to address the issue.</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
@@ -5798,12 +10562,36 @@
           <t>Political Psychology</t>
         </is>
       </c>
-      <c r="E205" s="2" t="inlineStr"/>
-      <c r="F205" s="2" t="inlineStr"/>
-      <c r="G205" s="2" t="inlineStr"/>
-      <c r="H205" s="2" t="inlineStr"/>
-      <c r="I205" s="2" t="inlineStr"/>
-      <c r="J205" s="2" t="inlineStr"/>
+      <c r="E205" s="2" t="inlineStr">
+        <is>
+          <t>질적연구</t>
+        </is>
+      </c>
+      <c r="F205" s="2" t="inlineStr">
+        <is>
+          <t>경험적 증언 분석</t>
+        </is>
+      </c>
+      <c r="G205" s="2" t="inlineStr">
+        <is>
+          <t>Ontological Security</t>
+        </is>
+      </c>
+      <c r="H205" s="2" t="inlineStr">
+        <is>
+          <t>Affective Regimes</t>
+        </is>
+      </c>
+      <c r="I205" s="2" t="inlineStr">
+        <is>
+          <t>공감의 정치가 국가의 존재론적 안보를 어떻게 강화하거나 위협하는지 분석하고, 국가는 공감의 정당한 대상을 관리하는 ‘감정 체제’를 구축하지만 시민들의 저항과 일탈로 이에 대한 대항적 안보·정체성 서사가 생성된다고 주장한다. 2011년 시리아 봉기의 경험적 증언과 아사드 정권의 폭력 전략을 바탕으로, 이러한 감정 역학과 국가 권력·정치적 폭력에 도전하는 공감의 가능성을 탐구한다.</t>
+        </is>
+      </c>
+      <c r="J205" s="2" t="inlineStr">
+        <is>
+          <t>Abstract The ontological security of states may be threatened by the politics of empathy. Empathy—as a contested affective‐political field—has a capacity to both consolidate and unravel dominant understandings of identity, security, political subjectivity, and self‐other relations. This article connects a politics of empathy to patterns of state violence and resistance in situations of conflict and authoritarian politics, arguing that the distribution of feeling that underpins a politics of empathy is structured by positionality, power, and social context. The article argues that states construct “affective regimes” through which they seek to manage the legitimate subjects of empathy in order to maintain their ontological security, and focuses on empirical testimony from the Syrian uprising in 2011 and the Assad regime's strategies of violence to explore these affective dynamics. It reveals ways in which the state's efforts are always resisted and transgressed by citizens, generating counter‐narratives of security‐identity and affective relations. A politics of empathy offers analytical tools for understanding the construction and effectiveness of states' affective regimes to maintain ontological security as well as being normatively essential to the task of challenging forms of state power, political violence, and generating alternative imaginings of ontological security and subjectivity.</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
@@ -5824,12 +10612,36 @@
           <t>International Journal of Public Administration</t>
         </is>
       </c>
-      <c r="E206" s="2" t="inlineStr"/>
-      <c r="F206" s="2" t="inlineStr"/>
-      <c r="G206" s="2" t="inlineStr"/>
-      <c r="H206" s="2" t="inlineStr"/>
-      <c r="I206" s="2" t="inlineStr"/>
-      <c r="J206" s="2" t="inlineStr"/>
+      <c r="E206" s="2" t="inlineStr">
+        <is>
+          <t>질적연구</t>
+        </is>
+      </c>
+      <c r="F206" s="2" t="inlineStr">
+        <is>
+          <t>주요정보제공자 인터뷰</t>
+        </is>
+      </c>
+      <c r="G206" s="2" t="inlineStr">
+        <is>
+          <t>Reasoned Action Approach</t>
+        </is>
+      </c>
+      <c r="H206" s="2" t="inlineStr">
+        <is>
+          <t>integrity</t>
+        </is>
+      </c>
+      <c r="I206" s="2" t="inlineStr">
+        <is>
+          <t>이 연구는 합리적 행위 접근법을 활용해 가나 대학 학생 지도자들의 부패·청렴 인식과 청렴 실천을 저해하거나 형성하는 요인을 주요 정보제공자 인터뷰로 분석했다. 약한 책임성 체계, 또래 압력, 정당의 영향, 국가 지도자들의 고무적이지 않은 리더십이 청렴 실천의 주요 장벽으로 나타났으며, 개인적 신념·사회적 기대·제도적 경험이 부패와 청렴에 대한 인식을 형성했다.</t>
+        </is>
+      </c>
+      <c r="J206" s="2" t="inlineStr">
+        <is>
+          <t>Ensuring that student leaders uphold integrity and ethical standards is a key concern for future governance and public administration, as many eventually assume leadership roles in both public and private sectors. Employing the Reasoned Action Approach, this study examined student leaders’ understanding of corruption and integrity, the factors that hinder them from upholding integrity, and the factors that shape their perceptions of corruption and integrity. Data were gathered through key informant interviews with student leaders. The findings revealed that weak accountability systems, pressure from peers, political party influence, and uninspiring leadership traits exhibited by national leaders were major barriers to upholding integrity, ultimately undermining ethical leadership. The study further found that student leaders’ perceptions of corruption are shaped by personal beliefs, social expectations, and institutional experiences. The findings highlight the need for improved governance structures, ethical mentorship, and training programmes to cultivate future leaders with strong moral foundations.</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
@@ -5850,12 +10662,36 @@
           <t>Administration &amp; Society</t>
         </is>
       </c>
-      <c r="E207" s="2" t="inlineStr"/>
-      <c r="F207" s="2" t="inlineStr"/>
-      <c r="G207" s="2" t="inlineStr"/>
-      <c r="H207" s="2" t="inlineStr"/>
-      <c r="I207" s="2" t="inlineStr"/>
-      <c r="J207" s="2" t="inlineStr"/>
+      <c r="E207" s="2" t="inlineStr">
+        <is>
+          <t>서베이</t>
+        </is>
+      </c>
+      <c r="F207" s="2" t="inlineStr">
+        <is>
+          <t>주 단위 비교분석</t>
+        </is>
+      </c>
+      <c r="G207" s="2" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="H207" s="2" t="inlineStr">
+        <is>
+          <t>Digital Divide</t>
+        </is>
+      </c>
+      <c r="I207" s="2" t="inlineStr">
+        <is>
+          <t>이 연구는 2021~2022년 미국에서 연방·주 정부의 상이한 원격의료 보상정책, 면허 규정, 비상 면제 조치가 개인 특성과 의료 필요를 통제한 뒤 디지털 의료서비스 이용 접근성의 차이와 어떤 관련이 있는지 분석한다. 미국 인구조사국 가구 동향조사와 주 단위 정책자료를 결합한 분석 결과, 원격의료 이용은 개인 자원뿐 아니라 정부 간 정책 구성과 강하게 연관되어 인구집단과 지역에 따라 불균등한 접근 기회를 보였다.</t>
+        </is>
+      </c>
+      <c r="J207" s="2" t="inlineStr">
+        <is>
+          <t>This article examines how fragmented governance shapes access to digital public services, focusing on telemedicine use in the United States during the 2021 to 2022 pandemic recovery. Using U.S. Census Bureau Household Pulse Survey data combined with state-level differences in reimbursement policies, licensure rules, and emergency waivers, the study analyzes whether telemedicine access varies across policy environments, controlling for individual characteristics and health needs. Findings show that telemedicine use is strongly associated with intergovernmental policy configurations, along with personal resources. The study highlights how federal and state institutions structure access, producing uneven opportunities for digitally mediated care across populations and territories. JEL codes: I18, H77, H75</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
@@ -5876,12 +10712,36 @@
           <t>Administration &amp; Society</t>
         </is>
       </c>
-      <c r="E208" s="2" t="inlineStr"/>
-      <c r="F208" s="2" t="inlineStr"/>
-      <c r="G208" s="2" t="inlineStr"/>
-      <c r="H208" s="2" t="inlineStr"/>
-      <c r="I208" s="2" t="inlineStr"/>
-      <c r="J208" s="2" t="inlineStr"/>
+      <c r="E208" s="2" t="inlineStr">
+        <is>
+          <t>이론/개념</t>
+        </is>
+      </c>
+      <c r="F208" s="2" t="inlineStr">
+        <is>
+          <t>개념적 모형</t>
+        </is>
+      </c>
+      <c r="G208" s="2" t="inlineStr">
+        <is>
+          <t>Lefebvre’s Spatial Triad</t>
+        </is>
+      </c>
+      <c r="H208" s="2" t="inlineStr">
+        <is>
+          <t>Assemblage Thinking</t>
+        </is>
+      </c>
+      <c r="I208" s="2" t="inlineStr">
+        <is>
+          <t>이 글은 장소만들기의 정서적 차원을 어떻게 이해할 것인지 탐구하며, 르페브르의 공간 삼분법과 어셈블리지 관점을 바탕으로 장소만들기를 정동적 실천으로 개념화한다. 장소감은 정동의 관계적 역학을 통해 형성되며, 장소만들기는 물질적·사회적·제도적 힘을 정동이 연결하는 분산적 과정이라는 점을 제시한다.</t>
+        </is>
+      </c>
+      <c r="J208" s="2" t="inlineStr">
+        <is>
+          <t>Placemaking is widely promoted as a tool for belonging and urban transformation, yet its affective dimensions remain undertheorized. This article develops a framework for placemaking as an affective practice, arguing that sense of place is best understood through the relational dynamics of affect. Drawing on Lefebvre’s spatial triad, I show how governance often privileges conceived space while overlooking lived dimensions. Distinguishing affect from emotion, I demonstrate how embodied and social interactions generate atmospheres that shape how places are governed. Building on assemblage thinking, I conceptualize placemaking as a distributed process where affect binds material, social, and institutional forces.</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
@@ -5902,12 +10762,36 @@
           <t>Public Performance &amp; Management Review</t>
         </is>
       </c>
-      <c r="E209" s="2" t="inlineStr"/>
-      <c r="F209" s="2" t="inlineStr"/>
-      <c r="G209" s="2" t="inlineStr"/>
-      <c r="H209" s="2" t="inlineStr"/>
-      <c r="I209" s="2" t="inlineStr"/>
-      <c r="J209" s="2" t="inlineStr"/>
+      <c r="E209" s="2" t="inlineStr">
+        <is>
+          <t>서베이</t>
+        </is>
+      </c>
+      <c r="F209" s="2" t="inlineStr">
+        <is>
+          <t>대표 표본 자료 분석</t>
+        </is>
+      </c>
+      <c r="G209" s="2" t="inlineStr">
+        <is>
+          <t>Personnel Stability</t>
+        </is>
+      </c>
+      <c r="H209" s="2" t="inlineStr">
+        <is>
+          <t>Buffering Function</t>
+        </is>
+      </c>
+      <c r="I209" s="2" t="inlineStr">
+        <is>
+          <t>코로나19로 인한 사회적 혼란 속에서 비영리 조직의 인력 안정성이 프로그램 서비스 제공량의 변화에 따른 성과 저하를 완화하는지 검토했다. 미국 지역사회의 서비스 제공 비영리 조직을 대표하는 표본 자료를 분석한 결과, 인력 구조의 안정성을 유지한 조직일수록 팬데믹 기간 서비스 제공의 부정적 영향이 작았다.</t>
+        </is>
+      </c>
+      <c r="J209" s="2" t="inlineStr">
+        <is>
+          <t>This study addresses how personnel stability in nonprofit organizations relates to an organization’s ability to maintain program performance during the societal disruptions caused by the COVID-19 pandemic. We specifically apply Meier and O’Toole’s buffering function to explain variation in disruptions to organizations’ program services, as indicated by changes in the number of people served from 2019 to 2020, using data from a nationally representative sample of service-providing nonprofit organizations across U.S. communities. We find that maintaining personnel structural stability is associated with reduced negative impacts on nonprofits’ service provision during the pandemic. This study is among the first to apply longstanding theoretical work in public management to the nonprofit sector, offering implications for nonprofit management theory and practice.</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
@@ -5928,12 +10812,36 @@
           <t>Policy Studies Journal</t>
         </is>
       </c>
-      <c r="E210" s="2" t="inlineStr"/>
-      <c r="F210" s="2" t="inlineStr"/>
-      <c r="G210" s="2" t="inlineStr"/>
-      <c r="H210" s="2" t="inlineStr"/>
-      <c r="I210" s="2" t="inlineStr"/>
-      <c r="J210" s="2" t="inlineStr"/>
+      <c r="E210" s="2" t="inlineStr">
+        <is>
+          <t>이론/개념</t>
+        </is>
+      </c>
+      <c r="F210" s="2" t="inlineStr">
+        <is>
+          <t>개념적 모형</t>
+        </is>
+      </c>
+      <c r="G210" s="2" t="inlineStr">
+        <is>
+          <t>Policy Evaluation Influence</t>
+        </is>
+      </c>
+      <c r="H210" s="2" t="inlineStr">
+        <is>
+          <t>Evidence-Informed Policymaking</t>
+        </is>
+      </c>
+      <c r="I210" s="2" t="inlineStr">
+        <is>
+          <t>정책평가가 정책·정체(polity)·정치의 변화를 어떻게 유발하고 이들 차원이 어떻게 상호작용하는지를 설명하고 분류하기 위해, 평가 문헌과 공공정책 연구를 바탕으로 새로운 개념적 틀을 제시한다. 이 틀은 정책평가 영향의 동적이고 포괄적인 분석을 가능하게 하며, 정책평가 영향과 전문가 지식·정책자문·증거기반 정책결정 연구의 이론화에 기여한다.</t>
+        </is>
+      </c>
+      <c r="J210" s="2" t="inlineStr">
+        <is>
+          <t>ABSTRACT Governments worldwide have invested heavily in policy evaluation, providing many policymakers with a steady stream of evidence into the effectiveness, efficiency, or relevance of policies. Yet, despite these investments, systematic knowledge about the actual influence of policy evaluations remains surprisingly limited. This is partly due to the insufficient conceptual differentiation of policy evaluation as a distinct type of policy advice. Building on interdisciplinary evaluation literature and public policy scholarship, the article introduces a new framework designed to enhance our understanding and categorization of the changes policy evaluations bring about in terms of policy, polity, and politics, and how these dimensions interrelate. As a parsimonious heuristic tool, the framework enables a dynamic and comprehensive assessment of the influence of policy evaluations. It contributes to the theorization of policy evaluation influence and offers insights that may inform related research on the influence of expert knowledge, policy advice, and evidence‐informed policymaking more broadly.</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
@@ -5954,12 +10862,36 @@
           <t>Public Performance &amp; Management Review</t>
         </is>
       </c>
-      <c r="E211" s="2" t="inlineStr"/>
-      <c r="F211" s="2" t="inlineStr"/>
-      <c r="G211" s="2" t="inlineStr"/>
-      <c r="H211" s="2" t="inlineStr"/>
-      <c r="I211" s="2" t="inlineStr"/>
-      <c r="J211" s="2" t="inlineStr"/>
+      <c r="E211" s="2" t="inlineStr">
+        <is>
+          <t>실험</t>
+        </is>
+      </c>
+      <c r="F211" s="2" t="inlineStr">
+        <is>
+          <t>설문 실험</t>
+        </is>
+      </c>
+      <c r="G211" s="2" t="inlineStr">
+        <is>
+          <t>Goal Clarity</t>
+        </is>
+      </c>
+      <c r="H211" s="2" t="inlineStr">
+        <is>
+          <t>Expectancy Disconfirmation</t>
+        </is>
+      </c>
+      <c r="I211" s="2" t="inlineStr">
+        <is>
+          <t>명확한 형평성 목표가 형평성 성과와 시민의 기관 성과 평가 간 관계를 어떻게 조절하는지, 가상의 경찰기관 목표·성과를 활용한 설문 비네트 실험(N=2,307)으로 분석했다. 명확한 형평성 목표가 제시되면 시민들은 높은 형평성 성과와 낮은 성과를 덜 구분했으며, 이는 형평성 목표가 성과 판단의 규범적 기준을 높이기 때문으로 해석된다.</t>
+        </is>
+      </c>
+      <c r="J211" s="2" t="inlineStr">
+        <is>
+          <t>While performance management systems increasingly require public agencies to set clear goals, equity, as a core democratic value, has been systematically underrepresented in performance goal setting, leaving its effects on citizen assessments largely understudied. Drawing on the frameworks of goal clarity, public values, and expectancy disconfirmation theories, this study examines how clear equity goals moderate the relationship between equity performance outcomes and citizen assessments. Using survey vignette experiments with a hypothetical police department’s performance goals and outcomes (_N_ = 2,307), the results show that there is a negative interaction effect of equity goals and equity performance outcomes, indicating that citizens distinguish less between high and low equity performance when clear equity goals are present. This study suggests that incorporating equity values into performance goals shapes how citizens evaluate government performance by raising the normative standard against which that performance is judged.</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
@@ -5980,12 +10912,36 @@
           <t>The Journal of Politics</t>
         </is>
       </c>
-      <c r="E212" s="2" t="inlineStr"/>
-      <c r="F212" s="2" t="inlineStr"/>
-      <c r="G212" s="2" t="inlineStr"/>
-      <c r="H212" s="2" t="inlineStr"/>
-      <c r="I212" s="2" t="inlineStr"/>
-      <c r="J212" s="2" t="inlineStr"/>
+      <c r="E212" s="2" t="inlineStr">
+        <is>
+          <t>준실험</t>
+        </is>
+      </c>
+      <c r="F212" s="2" t="inlineStr">
+        <is>
+          <t>근소당선 비교</t>
+        </is>
+      </c>
+      <c r="G212" s="2" t="inlineStr">
+        <is>
+          <t>Gender Discrimination</t>
+        </is>
+      </c>
+      <c r="H212" s="2" t="inlineStr">
+        <is>
+          <t>Political Violence</t>
+        </is>
+      </c>
+      <c r="I212" s="2" t="inlineStr">
+        <is>
+          <t>이탈리아 정치인에 대한 14년간의 공격 자료를 활용해, 유사한 지역에서 근소한 차이로 당선된 여성 시장이 남성 시장보다 공격을 받을 확률이 약 세 배 높은지 분석했다. 정책 성향·정책 결정·성과·부패에는 성별 차이가 없었으며, 공격 격차는 정치적 영향력보다 차별과 일치했고 공격받은 여성 시장은 재출마 가능성이 낮았다.</t>
+        </is>
+      </c>
+      <c r="J212" s="2" t="inlineStr">
+        <is>
+          <t>We present the first causal evidence that female politicians are more likely to face political violence. Using fourteen years of data on attacks against Italian politicians, we show that marginally elected female mayors—similar to men and elected in comparable towns—are three times as likely to be attacked. We find no gender differences in policy platforms, policymaking, performance, or corruption. Instead, violence emerges independently on women's choices, consistently with discrimination - rather than political influence - driving the gap in violence. Female mayors are less likely to seek re-election after attacks, highlighting violence’s role in perpetuating the gender gap.</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
@@ -6006,12 +10962,36 @@
           <t>Political Psychology</t>
         </is>
       </c>
-      <c r="E213" s="2" t="inlineStr"/>
-      <c r="F213" s="2" t="inlineStr"/>
-      <c r="G213" s="2" t="inlineStr"/>
-      <c r="H213" s="2" t="inlineStr"/>
-      <c r="I213" s="2" t="inlineStr"/>
-      <c r="J213" s="2" t="inlineStr"/>
+      <c r="E213" s="2" t="inlineStr">
+        <is>
+          <t>혼합방법론</t>
+        </is>
+      </c>
+      <c r="F213" s="2" t="inlineStr">
+        <is>
+          <t>순차 혼합</t>
+        </is>
+      </c>
+      <c r="G213" s="2" t="inlineStr">
+        <is>
+          <t>Propaganda</t>
+        </is>
+      </c>
+      <c r="H213" s="2" t="inlineStr">
+        <is>
+          <t>Psychological Needs</t>
+        </is>
+      </c>
+      <c r="I213" s="2" t="inlineStr">
+        <is>
+          <t>권위주의 체제의 선전이 어떤 심리적 욕구와의 부합을 통해 설득력을 얻는지 중국 사례로 분석했다. 다중 라운드 설문실험, 모바일 뉴스 앱을 활용한 현장 실험, 국가 매체 텍스트 분석, 현장 인터뷰를 종합한 결과, 소속감·자존감 유지·핵심 가치 표현 욕구에 호소하는 선전은 해당 욕구가 강한 사람에게 가장 효과적이지만, 심리적으로 매력적이더라도 일반화된 선전은 그렇지 않았다.</t>
+        </is>
+      </c>
+      <c r="J213" s="2" t="inlineStr">
+        <is>
+          <t>Abstract Existing scholarship on propaganda in authoritarian regimes centers on whether it persuades or coerces. Within the persuasion camp, researchers have examined how factors such as message source, content, credibility, and audience demographics shape propaganda effectiveness. This study shifts attention to psychological needs. Drawing on evidence from China, it integrates multi‐round survey experiments, a virtual lab‐in‐the‐field experiment using a mobile news app developed by the author, text analysis of state media, and field interviews. The results show that propaganda appealing to the need to belong, the need to maintain self‐esteem, or the need to express core values is most effective among individuals for whom the corresponding need is particularly strong—but generalized propaganda, even when psychologically engaging, is not. The findings suggest that propaganda is most persuasive when targeted to stable psychological orientations rather than designed for broad consumption. These findings have implications for understanding how authoritarian regimes sustain public support: propaganda effectiveness depends not only on content or reach, but also on how closely its psychological appeals correspond to the stable motivational orientations of its audience. The shift in authoritarian communication strategies toward psychologically targeted appeals makes the mechanisms identified here increasingly relevant to understanding contemporary propaganda.</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr"/>
@@ -6054,12 +11034,36 @@
           <t>Political Psychology</t>
         </is>
       </c>
-      <c r="E215" s="2" t="inlineStr"/>
-      <c r="F215" s="2" t="inlineStr"/>
-      <c r="G215" s="2" t="inlineStr"/>
-      <c r="H215" s="2" t="inlineStr"/>
-      <c r="I215" s="2" t="inlineStr"/>
-      <c r="J215" s="2" t="inlineStr"/>
+      <c r="E215" s="2" t="inlineStr">
+        <is>
+          <t>혼합방법론</t>
+        </is>
+      </c>
+      <c r="F215" s="2" t="inlineStr">
+        <is>
+          <t>순차 혼합</t>
+        </is>
+      </c>
+      <c r="G215" s="2" t="inlineStr">
+        <is>
+          <t>Moral Foundations</t>
+        </is>
+      </c>
+      <c r="H215" s="2" t="inlineStr">
+        <is>
+          <t>Discrimination Acceptance</t>
+        </is>
+      </c>
+      <c r="I215" s="2" t="inlineStr">
+        <is>
+          <t>이 연구는 차별 지지자와 반대자의 도덕적 가치와, 보수·진보적 가치 호소가 인종·민족 차별 수용에 미치는 영향을 두 개의 다방법 연구로 검토했다. 내집단 충성·돌봄, 권위, 신성성에 호소하면 정치 성향과 관계없이 차별 수용이 감소했으며, 진보적 가치 호소는 공화당 지지자의 수용을 오히려 높였다.</t>
+        </is>
+      </c>
+      <c r="J215" s="2" t="inlineStr">
+        <is>
+          <t>Abstract When political elites and activists promote anti‐discrimination policies, they often frame discrimination as violating liberal moral values such as fairness, care for vulnerable groups, and equality. However, this approach may fail to resonate with conservative voters and could even alienate them. Through two separate studies, this article uses a multi‐method approach to examine the moral values held by supporters and opponents of discrimination and test how conservative and liberal value appeals influence acceptance. The findings reveal that values like loyalty, care for the in‐group, authority, and sanctity appear in acceptors' justifications and that framing discrimination as a violation of these values, associated with conservatism, reduces acceptance across the political spectrum. Contrastingly, appealing to values associated with liberalism backfires and increases Republicans' acceptance. While liberal values were central in shifting social norms towards anti‐discrimination, appealing to conservative values may be more effective in reducing contemporary acceptance of discrimination.</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
@@ -6080,12 +11084,36 @@
           <t>Public Administration Review</t>
         </is>
       </c>
-      <c r="E216" s="2" t="inlineStr"/>
-      <c r="F216" s="2" t="inlineStr"/>
-      <c r="G216" s="2" t="inlineStr"/>
-      <c r="H216" s="2" t="inlineStr"/>
-      <c r="I216" s="2" t="inlineStr"/>
-      <c r="J216" s="2" t="inlineStr"/>
+      <c r="E216" s="2" t="inlineStr">
+        <is>
+          <t>준실험</t>
+        </is>
+      </c>
+      <c r="F216" s="2" t="inlineStr">
+        <is>
+          <t>이중차분</t>
+        </is>
+      </c>
+      <c r="G216" s="2" t="inlineStr">
+        <is>
+          <t>Political Decoupling</t>
+        </is>
+      </c>
+      <c r="H216" s="2" t="inlineStr">
+        <is>
+          <t>Privatization</t>
+        </is>
+      </c>
+      <c r="I216" s="2" t="inlineStr">
+        <is>
+          <t>공정시장가치(FMV) 민영화가 지방 상수도 관리와 현직 정치인의 선거 결과를 개선하는지 검토하기 위해, 일리노이주에서 FMV 법 제정 후 상수도를 매각한 15개 지방자치단체와 34개 통제집단을 대상으로 이중차분 분석을 실시했다. 민영화는 안전한 식수법 위반을 줄여 인력·기술 관리 성과를 개선했지만, 현직자의 득표율에는 유의한 영향을 미치지 않았다.</t>
+        </is>
+      </c>
+      <c r="J216" s="2" t="inlineStr">
+        <is>
+          <t>ABSTRACT Many U.S. municipalities face environmental service delivery challenges, including aging infrastructure and rising debt. In response, several states have adopted Fair Market Value (FMV) legislation, which aims to incentivize private firms to acquire and invest in municipal utilities—particularly in the water sector. However, the impacts of FMV privatization remain understudied. Guided by political decoupling theory, this study hypothesizes that FMV privatization improves drinking water utility management and local incumbent electoral outcomes. Using a difference‐in‐differences design, we analyze fifteen Illinois municipalities that sold their utilities after the state adopted FMV legislation relative to thirty‐four controls. Results suggest that FMV privatization improves personnel and technical management outcomes by reducing violations under the Safe Drinking Water Act but has no significant impact on incumbent vote share. These findings indicate that while FMV privatization may enhance utility management through political decoupling, its presumed political benefits warrant further investigation.</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
@@ -6106,12 +11134,36 @@
           <t>Public Administration Review</t>
         </is>
       </c>
-      <c r="E217" s="2" t="inlineStr"/>
-      <c r="F217" s="2" t="inlineStr"/>
-      <c r="G217" s="2" t="inlineStr"/>
-      <c r="H217" s="2" t="inlineStr"/>
-      <c r="I217" s="2" t="inlineStr"/>
-      <c r="J217" s="2" t="inlineStr"/>
+      <c r="E217" s="2" t="inlineStr">
+        <is>
+          <t>준실험</t>
+        </is>
+      </c>
+      <c r="F217" s="2" t="inlineStr">
+        <is>
+          <t>이산시간 사건사</t>
+        </is>
+      </c>
+      <c r="G217" s="2" t="inlineStr">
+        <is>
+          <t>Political Market Framework</t>
+        </is>
+      </c>
+      <c r="H217" s="2" t="inlineStr">
+        <is>
+          <t>policy diffusion</t>
+        </is>
+      </c>
+      <c r="I217" s="2" t="inlineStr">
+        <is>
+          <t>이 연구는 2016~2022년 미국 대도시 148곳의 패널 자료와 이산시간 사건사 분석을 통해 정책 수요·공급과 제도적 조건이 탄소중립 공약 채택에 미치는 영향, 그리고 그 영향이 연방 정책 환경에 따라 어떻게 달라지는지 분석했다. 전체 기간에는 시민 역량, 정치 이념, 수평적 확산이 관련되었으며, 연방 비개입기와 재관여기에 유의한 요인이 서로 달라져 연방 맥락이 공약 채택을 조건화하는 것으로 나타났다.</t>
+        </is>
+      </c>
+      <c r="J217" s="2" t="inlineStr">
+        <is>
+          <t>ABSTRACT Many cities have adopted net‐zero emission pledges, yet little is known about why these commitments emerge or how their determinants shift under changing policy environments. Using a panel of 148 large US cities from 2016 to 2022, this study applies the Political Market Framework and employs discrete‐time event‐history models to examine how policy demand, policy supply and institutional conditions shape adoption decisions. Results show that civic capacity, political ideology, and horizontal diffusion drive adoption in the full period, but their influence varies sharply across institutional contexts. During federal disengagement (2016–2018), cities with less population, strong vulnerability signals, supportive state policies, or fiscal cushioning through federal aid are more likely to adopt. When federal engagement returned (2019–2022), education, population size, and neighbor adoption emerged as significant correlates of net‐zero adoption. These findings extend the Political Market Framework by showing how federal contexts condition the adoption of ambitious climate commitments.</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
@@ -6132,12 +11184,36 @@
           <t>Governance</t>
         </is>
       </c>
-      <c r="E218" s="2" t="inlineStr"/>
-      <c r="F218" s="2" t="inlineStr"/>
-      <c r="G218" s="2" t="inlineStr"/>
-      <c r="H218" s="2" t="inlineStr"/>
-      <c r="I218" s="2" t="inlineStr"/>
-      <c r="J218" s="2" t="inlineStr"/>
+      <c r="E218" s="2" t="inlineStr">
+        <is>
+          <t>서베이</t>
+        </is>
+      </c>
+      <c r="F218" s="2" t="inlineStr">
+        <is>
+          <t>국가 간 설문 분석</t>
+        </is>
+      </c>
+      <c r="G218" s="2" t="inlineStr">
+        <is>
+          <t>Bureaucratic Politicization</t>
+        </is>
+      </c>
+      <c r="H218" s="2" t="inlineStr">
+        <is>
+          <t>Career Bureaucracy</t>
+        </is>
+      </c>
+      <c r="I218" s="2" t="inlineStr">
+        <is>
+          <t>당내·내각 분절이 정부 성과에 미치는 영향이 고위공무원 충원·승진 규칙에 따라 어떻게 달라지는지, 89개 민주국가의 정부의 질 전문가 설문 자료로 분석했다. 분절된 내각은 고위 관료 인사가 정치화된 경우 그 부정적 효과를 증폭했지만, 내부 충원과 장기 경력을 특징으로 하는 경력제 관료제가 있을 때는 더 효과적인 거버넌스와 연관되었다.</t>
+        </is>
+      </c>
+      <c r="J218" s="2" t="inlineStr">
+        <is>
+          <t>ABSTRACT Debates over the consequences of party and cabinet fragmentation for government performance remain unsettled. While some scholars argue that coalition governments foster instability and rent‐seeking, others contend that they enhance accountability and inclusion. This article argues that the effects of cabinet fragmentation depend on the rules of recruitment and promotion of the senior civil service. Using data from the Quality of Government Expert Survey covering 89 democracies, we examine how fragmentation interacts with both bureaucratic politicization and bureaucratic career systems. The results show that fragmentation amplifies the negative effects of politicized senior appointments, although we find limited evidence that fragmentation itself reduces the quality of government under high politicization. By contrast, fragmented cabinets are associated with more effective governance in the presence of career‐based structures characterized by internal recruitment of senior bureaucrats and long‐term careers. The findings highlight the importance of bureaucratic career structures for effective governance in multiparty systems.</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
@@ -6158,12 +11234,36 @@
           <t>Public Management Review</t>
         </is>
       </c>
-      <c r="E219" s="2" t="inlineStr"/>
-      <c r="F219" s="2" t="inlineStr"/>
-      <c r="G219" s="2" t="inlineStr"/>
-      <c r="H219" s="2" t="inlineStr"/>
-      <c r="I219" s="2" t="inlineStr"/>
-      <c r="J219" s="2" t="inlineStr"/>
+      <c r="E219" s="2" t="inlineStr">
+        <is>
+          <t>실험</t>
+        </is>
+      </c>
+      <c r="F219" s="2" t="inlineStr">
+        <is>
+          <t>컨조인트 실험</t>
+        </is>
+      </c>
+      <c r="G219" s="2" t="inlineStr">
+        <is>
+          <t>Accountability</t>
+        </is>
+      </c>
+      <c r="H219" s="2" t="inlineStr">
+        <is>
+          <t>Street-Level Bureaucracy</t>
+        </is>
+      </c>
+      <c r="I219" s="2" t="inlineStr">
+        <is>
+          <t>이 연구는 더 엄격한 정부 책임성 체계가 관료의 재량적 노력과 지원 대상 선택을 변화시키는지 뉴욕주 교사를 대상으로 컨조인트 실험으로 검토했다. 높은 책임성 환경의 교사는 성과가 낮은 학생을, 중간 수준 환경의 교사는 노력 수준이 높은 학생을 우선했으며, 전반적으로 교사들은 성실하지만 성과가 낮은 학생에게 추가 지원을 제공하는 약한 선호를 보였다.</t>
+        </is>
+      </c>
+      <c r="J219" s="2" t="inlineStr">
+        <is>
+          <t>Advocates for strengthening accountability in government assume stronger consequences will change bureaucratic behavior. This study considers whether more strict accountability regimes change bureaucrats’ discretionary efforts. We consider this puzzle using a conjoint experiment with teachers in New York State. Our results show street-level bureaucrats in high accountability settings prioritize low-performing clients, while street-level bureaucrats in moderate accountability settings prioritize clients exhibiting high levels of effort. Overall, teachers demonstrate a weak preference to provide extra assistance to students who are hardworking and low-performing.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:J1"/>
